--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3894,6 +3894,88 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>giangchismarthome</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@giangchismarthome/video/7652017265977609492</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vuột mất đơn hàng 30tr vì..... #robothutbui  #smarthome  #giangchismarthome  #roborockqrevo2pro </t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>174</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>giangchismarthome</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@giangchismarthome/video/7650891577631673621</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#robothutbui  #roborock  #qrevo2pro #giangchismarthome #smarthome </t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>179</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3976,6 +3976,211 @@
         <v>2</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7658305792403066133</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>TigerBot Smart Home 121F Nguyễn Huệ,  phường Long Châu, Vĩnh Long #robothutbui #roborock #qrevo2pro #Vinhlong#Dongthap</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>113</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>minhchautestthat</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@minhchautestthat/video/7658491250005265685</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Test 012: Khả năng tránh vật cản của Ecovacs T30C vs Roborock Qrevo 2 Pro  2 mã phân khúc 12-13tr ace cần test gì comment xuống dưới nhé  #minhchautestthat #ecovacs #T30C #Roborock #Qrevo2pro</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>28</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7658295947495017736</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>⚡ Không chỉ mạnh mẽ, Qrevo 2 Pro còn được tạo ra để chăm sóc ngôi nhà của bạn một cách toàn diện hơn. ✨ Lực hút HyperForce® 25.000Pa mạnh mẽ ✨ Chổi cạnh đảo chiều thế hệ mới quét sâu vào góc hơn ✨ FlexiArm™ vươn sát mép tường, giảm tối đa khu vực bỏ sót ✨ Hệ thống chống rối toàn thân đạt chứng nhận SGS ✨ Tự động tháo giẻ trước khi làm sạch thảm ✨ Dock đa năng tự giặt, tự sấy, tự làm sạch #Qrevo2Pro 👉 Inbox ngay để được tư vấn chi tiết &amp; giữ giá tốt ạ ✨ _______________________________ Hotline: 0365319688 Địa chỉ: 272-Phan Đình Phùng, tỉnh Thái Nguyên #3Tsmartthainguyen #Roborock #Robothutbui</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>208</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>tn.robot76</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tn.robot76/video/7658295776187141384</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>🌸🎉𝐂𝐡𝐚̀𝐨 𝐓𝐡𝐚́𝐧𝐠 𝟕, 𝐜𝐡𝐚̀𝐨 𝐦𝐨𝐝𝐞𝐥 𝐦𝐨̛́𝐢 𝐧𝐡𝐚̂́𝐭 𝐭𝐢𝐧𝐡 𝐜𝐮̉𝐚 𝐑𝐨𝐛𝐨𝐫𝐨𝐜𝐤 𝐠𝐨̣𝐢 𝐭𝐞̂𝐧 𝐐 𝐑𝐞𝐯𝐨 𝟐 𝐏𝐫𝐨. 💰Giá ưu đãi sản phẩm mới ra mắt từ 17,990,000 chỉ còn 13,490,000 đồng. Sẳn hàng giao ngay 🎁Và đếm quà mỏi tay khi mua ẻm nhé🎁 IB: biết quà👇🏽 📞Zalo.me/0943738613  Bảo Anh Robot Bình Dương 🏦Địa chỉ 1 Showroom: 690 đại lộ Bình Dương, P. phú Lợi, TPHCM (ĐC cũ: 690 đại lộ Bình Dương  P.Hiệp Thành, TP.TDM Tỉnh Bình Dương) #QRevo2Pro #nhachaymoingay #Robotbinhduon#Robotbinhduongtbinhduong #hottren</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>101</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7658513589283687701</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Các lí do nên chọn roborock qrevo 2 pro bạn đã biết chưa? #Qrevo2Pro #roborock #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4181,6 +4181,211 @@
         <v>0</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7658620169039662356</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Lên kệ  #Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>7</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7658597084202929429</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Các lý do mà qrevo 2 pro luôn được chọn làm robot hút bụi lau nhà #qrevo2pro #roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>25</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7658527650561953044</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#CapCut mời quý vị #Qrevo2pro #robothutbui #nghiennha #quyrobot </t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>88</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7658525176748920085</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siêu sạh cỡ này, không mua em nó hơi phí ạ. #Qrevo2pro #roborock #robothutbui #nghiennha #quyrobot </t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>94</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7658522932011994388</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mời quý vị đập hộp mã mới nhất với giá thành cực kì hợp lý nhà #roborock #Qrevo2pro #robothutbui #nghiennha #quyrobot </t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>98</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4386,6 +4386,334 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>minhchautestthat</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@minhchautestthat/video/7658646371309800725</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test 012: Robot hút bụi lau nhà có hút được tóc không ? Trên đây là mình test với Roborock 2 pro - bản có đổ rác tự động và chổi cuốn chống mắc tóc nhé anh em. #minhchautestthat #roborock #qrevo2pro #robothutbuibacgiang #minhchausmarthome </t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>420</v>
+      </c>
+      <c r="H87" t="n">
+        <v>7</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7658677422375701781</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roborock Qrevo 2 Pro xuất hiện như một lựa chọn dành cho những tổ ấm muốn giữ nhịp sạch sẽ mỗi ngày, nơi những chu trình lặp đi lặp lại được thay thế bằng một guồng vận hành tự động gọn gàng. #Roborock  #Qrevo2Pro  #Robothutbui  #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>118</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>roborockthanhhoa</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@roborockthanhhoa/video/7658844696172596501</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Sao cái gì anh này cũng biết hết ấy nhỉ #2pro #qrevo2pro #robothutbui #thanhhoa #roborockthanhhoa #viralvideotiktok #roborockvietnam #xuhuong #xuhuongtiktok #hutbui #hdpe #otechvietnam #haihuoc #congnghe #robot #trendinghai</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>tm.anh.kitchen.qu</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tm.anh.kitchen.qu/video/7658649213441445128</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot Roborock Qrevo 2 Pro mẫu mới nhất đã có sẵn hàng trưng bày tại Tâm Anh để khách Quảng Trị trải nghiệm trước rồi ạaa 🫶🏻 #Roborock #RoborockVietnam #qrevo2pro #robothutbui #bepquangtri </t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>130</v>
+      </c>
+      <c r="H90" t="n">
+        <v>4</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7658647679970331925</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>#Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>111</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7658883600783297812</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dẫn đầu tính năng chinh phục tầm giá nhanh tay rinh em nó về ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>6</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7658643446319615253</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done em Qrevo 2Pro cho khách yêu #qrevo2pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>91</v>
+      </c>
+      <c r="H93" t="n">
+        <v>7</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>giangchismarthome</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@giangchismarthome/video/7658857183358045460</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seri  #ROBOROCK P1: Vệ sinh màng lọc hepa #giangchirobot #roborock #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>36</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4714,6 +4714,416 @@
         <v>0</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>thuyduonggiadung</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuyduonggiadung/video/7658974968251682056</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#GiaDungThuyDuong #Roborock #robothutbui #Qrevo2Pro #viralvideo </t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>5</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>homecaredigital</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homecaredigital/video/7658888698414632210</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Thiết kế ấn tượng, chống rối tóc tốt nhất phân khúc Ghé ngay Homecare Digital trải nghiệm sản phẩm #Qrevo2Pro #roborock #robothutbui #homecaredigital</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>123</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>homecaredigital</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homecaredigital/video/7658888346411863304</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Đỉnh cao công nghệ trong phân khúc tầm trung - Qrevo 2 Pro #RobotHutBui #Qrevo2Pro #roborock #homecaredigital</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>112</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7658925782911274260</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lái la! Lái la! Roborock qrevo 2pro lái la #roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>49</v>
+      </c>
+      <c r="H98" t="n">
+        <v>3</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7658894927589281045</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rì view qrevo 2 pro xử lý hút bụt và các loại hạt #roborock #Qrevo2Pro #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>77</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7658946352088468757</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hành trình 10 năm gắn bó với nghề kinh doanh Robot - hút bụi lau nhà.#roborock #robothutbui #roborockqrevo2pro #ReviewCongNghe #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>44</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7658941463937551637</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Trùm cuối" robot hút bụi 2026 gọi tên Roborock Qrevo 2 Pro! 😎 🔥 Lực hút "quái vật" 25.000Pa - Chấp mọi loại bụi mịn, thảm dày. ❌ Chống rối tóc 100% - Không lo kẹt chổi, giải phóng đôi tay! 💦 Giặt giẻ nước nóng, sấy khô khép kín, sạch bóng không mùi hôi. 👉 Đầu tư một lần, rảnh tay cả năm. Chốt ngay dưới giỏ hàng! 👇 #roborock #roborockqrevo2pro #robothutbui #ReviewCongNghe #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>37</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7658484781868469524</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Lực hút 25.000 Pa siêu mạnh, Roborock Qrevo 2 Pro chính thức "vô địch" phân khúc! 🤯 ❌ Chổi DuoDivide chia đôi: Hút tóc và lông thú tuồn tuột, KHÔNG lo quấn rối. can góc tường: Giẻ lau FlexiArm chủ động xòe sát mép 1.85mm. 🚿 Dock sạc tối tân: Tự đổ bụi, tự giặt giẻ nước nóng 100°C khử khuẩn đỉnh cao. Đầu tư một lần, rảnh tay cả năm ae ơi! 👇 #Roborock #Qrevo2Pro #robothutbui #giadungthongminh #smarthome</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>290</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7658480835129101588</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quên việc gỡ tóc trên robot hút bụi đi! 🤫 Roborock Qrevo 2 Pro chính thức "out trình" với: 🔥 Lực hút 25.000 Pa – Vô địch thiên hạ hiện tại! ❌ Chổi DuoDivide – Thách thức mọi loại lông tóc, cam kết KHÔNG RỐI. can góc tường – Giẻ lau xòe ra sát rạt 1.85mm. 🚿 Giặt giẻ nước nóng 100°C – Sạch khuẩn, không mùi ẩm mốc. Thân máy siêu mỏng chui gầm cực đỉnh. Gom lúa chốt đơn em này thôi ae ơi! 👇 #Roborock #Qrevo2Pro #RoborockQrevoCurv #robothutbui #giadungthongminh </t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>369</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7658253200633515285</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 Pro#RoborockF25Ultra #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>357</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5124,6 +5124,129 @@
         <v>0</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7658998617058921749</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà sạch ổn định, thao tác tối giản và bạn có thêm thời gian cho những điều thật sự quan trọng. #Roborock #Qrevo2Pro  #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>7</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>homecaredigital</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homecaredigital/video/7658986995707825416</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Ba mê robot hút bụi, con gái cũng mê luôn 😂 Nhà hôm nay có đồ chơi mới cho hai ba con, ba thì nằm dài trên sofa, tay cầm điện thoại mà mắt dõi theo cái Roborock Qrevo 2 Pro chạy vòng vòng dưới sàn. Kiểu như… đang “giám sát công việc” vậy đó 😄 Còn cô nhóc thì khác không ngồi yên được, lại gần cái dock sạc ngồi xuống ngắm nghía, tay rờ rờ như đang khám phá món đồ chơi mới. Nhìn cưng muốn xỉu! Hai ba con nhà người ta mà chung một “gu” đều mê Roborock như nhau, chỉ khác cái là ba thì thích vì… khỏi tự lau nhà 😆 còn con thì thích vì nó tròn tròn đen bóng trông hay ho quá! Cảm ơn gia đình đã tin tưởng gửi gắm việc mệt mỏi khi dọn nhà cho 𝐇𝐨𝐦𝐞𝐜𝐚𝐫𝐞 𝐃𝐢𝐠𝐢𝐭𝐚𝐥 nha. Chúc ba tiếp tục được “nghỉ ngơi có trách nhiệm” và chúc bé tiếp tục xinh yêu như vậy 🥰 #Qrevo2Pro #roborock #robothutbui #homecaredigital</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>43</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7658993474330529044</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔥 Siêu phẩm Roborock Qrevo 2 Pro: Lực hút khủng 25.000Pa, giẻ lau vươn sát góc tường FlexiArm™ và chổi chống rối 100%. Sạch mọi ngóc ngách, rảnh tay tuyệt đối! 🚀 Chốt ngay!#roborock #roborockqrevo2pro #robothutbui #ReviewCongNghe </t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>15</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="videos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="videos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5247,6 +5247,334 @@
         <v>0</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>minhchautestthat</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@minhchautestthat/video/7659030978978925844</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test #013 Robot hút bụi lau nhà Roborock Qrevo 2 Pro có tránh được dây điện, dây sạc nhỏ không? Ae cần test gì cmt xuống nhé, mình tập trung các dòng Robot phổ thông, chủ lực của các hãng #minhchautestthat #Roborock #qrevo2pro #robotlaunhabacgiang </t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>655</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>mi360vn</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mi360vn/video/7659062087011814676</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Trải nghiệm Robot hút bụi Roborock Qrevo 2 Pro #Qrevo2Pro #Roborock #Robothutbui</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>106</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>homecaredigital</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homecaredigital/video/7659056947827576072</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot màu trắng thì nhìn sang nhất đúng không cả nhà nhỉ😋😋 Mọi người cho Homecare biết mình thích màu gì nhé❤️❤️ #roborock #Qrevo2Pro #robothutbui #homecaredigital </t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>32</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>homecaredigital</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homecaredigital/video/7659047138990591250</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có gì bên trong siêu phẩm tầm trung giữa năn 2026🤔🤔 Homecare giới thiệu qua cho quý khách hàng tính năng chính của Qrevo 2 Pro mẫu robot hút bụi mới ra đến từ nhà Roborock #homecaredigital #robothutbui #Qrevo2Pro #roborock </t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>41</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>homecaredigital</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homecaredigital/video/7659045735215795474</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viên ngọc trai đen hạ cánh đầu tiên tại Đà Nẵng cho anh chị chủ yêu công nghệ🌍 Cảm ơn anh chị đã luôn tin chọn Homecare Digital #roborock #Qrevo2Pro #robothutbui #homecaredigital </t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>36</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>homecaredigital</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homecaredigital/video/7659044120563879175</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Những đơn hàng Qrevo 2 Pro đã được Homecare giao tận nhà khách hàng🥳🥳 Ghé ngay trải nghiếm sản phẩm hot giữa năm 2026 nào❤️ #RobotHutBui #homecaredigital #robothutbui #Qrevo2Pro #roborock </t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>41</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>homecaredigital</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homecaredigital/video/7659043835024100615</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot tự động tháo giẻ lau mọi người tin được không - ROBOROCK QREVO 2 PRO đã làm được điều đấy❤️ Ghé ngay Homecare trải nghiệm sản phẩm #Qrevo2Pro #roborock #robothutbui #homecaredigital #RobotHutBui </t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>44</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>homecaredigital</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homecaredigital/video/7659043465900068114</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Một sản phẩm mới ra đến từ nhà Roborock - đến Homecare ngay để trải nghiệm #homecaredigital #robothutbui #roborock #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>3</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5575,6 +5575,416 @@
         <v>0</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>minhchautestthat</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@minhchautestthat/video/7659265956476210453</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Test014 Khả năng làm sạch và né vật cản Dreame L10S ultra gen2 vs Roborock Qrevo 2 pro - phân khúc 13tr Ae cần test thêm gì cmt xuống nhé  #minhchautestthat #robotlaunhabacgiang #qrevo2pro #l10sultragen2 </t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>40</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>anhlinhgroup_73</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@anhlinhgroup_73/video/7659258683691519253</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">em Qrevo2 pro mới về tới cả nhà ơi… #anhlinhgroup #qrevo2pro #Roborock #robothutbui #xuhuong </t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>15</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7659270185303477524</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vệ sinh #Roborock #Qrevo2Pro với 6 bước đơn giản. 😘 #Robothutbui #robothutbuilaunha </t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>4</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7659257060391128340</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Những chiếc #Roborock #Qrevo2Pro đầu tiên đã được giao tới khách hàng tại Buôn Ma Thuột #Robothutbui #robothutbuilaunha </t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>15</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7659276162761379092</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roborock Qrevo 2 Pro (hay còn gọi là Qrevo Curv 2 Pro) là dòng robot hút bụi lau nhà cao cấp với các điểm cốt lõi:  Hiệu năng cực đỉnh: Lực hút kỷ lục 25.000 Pa kết hợp chổi chính chống rối toàn diện, xử lý triệt để tóc và lông thú cưng.  Lau sạch sát mép: Trang bị giẻ lau mở rộng FlexiArm giúp làm sạch sát tường và góc khuất (khoảng cách chỉ 1,85mm).  Thiết kế siêu mỏng &amp; Linh hoạt: Thân máy dày chỉ 7,98cm nhờ cảm biến LiDAR có thể nâng hạ tự động, đi kèm khung gầm nâng hạ thông minh giúp vượt chướng ngại vật cao đến 4cm.#RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>15</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7659271722343959829</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roborock Qrevo 2 Pro là dòng robot hút bụi lau nhà cao cấp sở hữu lực hút HyperForce kỷ lục lên đến 25.000Pa giúp đánh bay mọi bụi mịn và rác vụn. Thiết bị được trang bị hệ thống chổi chính DuoDivide và chổi cạnh dạng vòm, đạt chứng nhận chống rối tóc 100% từ SGS. Điểm nhấn ấn tượng là công nghệ giẻ lau mở rộng FlexiArm™ cùng chổi cạnh đảo chiều thông minh, giúp làm sạch sát mép tường và các góc khuất một cách triệt để. Hệ thống lau xoay kép với tốc độ 200 vòng/phút kết hợp tính năng tự động nâng giẻ 12mm khi gặp thảm, ngăn ngừa tối đa tình trạng làm ướt thảm. Đi kèm là trạm sạc đa năng tự động đổ bụi, giặt giẻ bằng khí nóng và sấy khô 45°C, mang lại trải nghiệm dọn dẹp hoàn toàn rảnh tay lên đến 65 ngày.#RobotHutBui #Roborock #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>22</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7659264913512090901</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roborock F25 Ultra là máy hút bụi lau nhà khô ướt cầm tay cao cấp với 3 điểm cốt lõi:  Lau hơi nước nóng 180°C: Đun nước nóng trực tiếp để đánh tan vết dầu mỡ, mảng bám khô cứng và diệt khuẩn sàn nhà. Lực hút mạnh 22.000 Pa.  Gập phẳng 180° &amp; Trợ lực AI: Thân máy luồn lách sâu vào gầm tủ/giường (chỉ dày 12.5 cm). Bánh xe tự động đẩy/kéo theo lực tay giúp di chuyển nhẹ nhàng.  Dock sấy khô 5 phút: Tự động giặt con lăn bằng nước nóng và sấy khô siêu tốc bằng khí nóng 95°C trong 5 phút, triệt tiêu hoàn toàn mùi hôi và vi khuẩn.#RobotHutBui #Momimart #Roborock #Qrevo2Pro #f25ultra </t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>28</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7659254210474560788</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quá mệt mỏi với cảnh gỡ tóc quấn robot? Đã có Roborock Qrevo 2 Pro "xử đẹp" từ tóc rụng đến bụi mịn! 🤯✨ Chống rối 100%, lực hút 25.000 Pa cao nhất thế giới! Xem ngay👇 #Roborock #Qrevo2Pro #Momimart #GiaDungThongMinh #RobotHutBui </t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>36</v>
+      </c>
+      <c r="H123" t="n">
+        <v>3</v>
+      </c>
+      <c r="I123" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>saigonbephcm</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@saigonbephcm/video/7655526360101686545</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Ngày 7/7/2026 tới đây thì nhà Roborock sẽ cho ra mắt robot hút bụi mới với model mới có tên là Roborock Qrevo 2 Pro với nhiều quà tặng hấp dẫn thêm với đó là giá rất ưu đãi, anh chị nhanh tay chốt lẹ để nhận giá khuyến mãi nhé ❤️ #saigonbep #robothutbui #roborock #roborockqrevo2pro #khuyenmai</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1473</v>
+      </c>
+      <c r="H124" t="n">
+        <v>14</v>
+      </c>
+      <c r="I124" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>saigonbephcm</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@saigonbephcm/video/7654813200650751240</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Một chiếc robot có thể tự giặt giẻ, tự đổ rác, tự tháo giẻ khi hút thảm và lau sát từng mép tường liệu có đáng tiền? 🤔 Cùng Sài Gòn Bếp review Roborock Qrevo 2 Pro để xem vì sao đây đang là một trong những robot hút bụi đáng chú ý nhất hiện nay! ✨ #saigonbep #robothutbui #roborock #roborockqrevo2pro #review</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>726</v>
+      </c>
+      <c r="H125" t="n">
+        <v>18</v>
+      </c>
+      <c r="I125" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -494,20 +494,14 @@
           <t xml:space="preserve">Roborock Qrevo 2 pro , lực hút cao ngất , đầy đủ tính năng vừa mới ra mắt chắn chắc sẽ mang tới cho bạn trải nghiệm tốt nhất . Ghé cửa hàng để trải nghiệm ngay #gihosmarthome #RobotQuangNgai #709QuangTrung #RobotHutBuiLauNha #Roborock </t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G2" t="n">
+        <v>427</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -541,20 +535,14 @@
           <t xml:space="preserve">🏬 Gia dụng Thùy Dương 📞 098 248 93 23 📍 Số 455 Minh Khai 1- Phường Chũ, Bắc Ninh https://maps.app.goo.gl/wsKGGw4Q2i9od31t8  #GiaDungThuyDuong  #Roborock  #robothutbui #Qrevo2Pro </t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G3" t="n">
+        <v>192</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -588,20 +576,14 @@
           <t xml:space="preserve">#giadungthuyduong #Qrevo2Pro #roborock #robothutbui </t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G4" t="n">
+        <v>169</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -635,20 +617,14 @@
           <t xml:space="preserve">Siêu phẩm được chờ đợi nhất #Qrevo2Pro #giadungthuyduong #robothutbui #xuhuong #roborock </t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G5" t="n">
+        <v>156</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -682,20 +658,14 @@
           <t>🔥5 Lý do nên chọn qrevo 2 pro❤️❤️❤️❤️ #Roborock #Qrevo2Pro #robothutbui</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G6" t="n">
+        <v>154</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -729,20 +699,14 @@
           <t>🔥Robot có thực sự biết né vật cản khi nhà cửa quá nhiều đồ đạc...#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G7" t="n">
+        <v>138</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -776,20 +740,14 @@
           <t>🔥Có gì hay ở Qrevo 2 Pro sản phẩm mới ra mắt của nhà Roborock#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G8" t="n">
+        <v>136</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -823,20 +781,14 @@
           <t>👉Dưới 15tr cùng xem robot nào đáng giá nhất...#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G9" t="n">
+        <v>138</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -870,20 +822,14 @@
           <t>👉Hình ảnh Qrevo 2 Pro trên mạng và thực tế....🤔#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G10" t="n">
+        <v>135</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -917,20 +863,14 @@
           <t>👉Cách xử lý những vết bẩn ố bẩn lâu ngày trên sàn nhà....#Roborock #Qrevo2Pro #robothutbui #xuhuong #ahastore #trending #viralvideotiktok #trendingsound</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G11" t="n">
+        <v>111</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -964,20 +904,14 @@
           <t>🔥Giải pháp cho những ngôi nhà nhiều có thảm...#Roborock #robothutbui #xuhuong #Qrevo2Pro #ahastore #trending #viralvideotiktok</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G12" t="n">
+        <v>158</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1011,20 +945,14 @@
           <t>Qrevo 2 Pro của nhà Roborock có gì mà hot đến thế❓#Roborock #robothutbui #xuhuong #ahastore #trending #viralvideotiktok</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G13" t="n">
+        <v>139</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1058,20 +986,14 @@
           <t>🥱Sếp bảo sao mình làm vậy. Mà sao giờ đòi vô họp gấp nhỉ....🤔#Roborock #robothutbui #xuhuong #ahastore #Qrevo2Pro #trendingsound #viralvideotiktok</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G14" t="n">
+        <v>244</v>
+      </c>
+      <c r="H14" t="n">
+        <v>28</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1105,20 +1027,14 @@
           <t>🔥Robot đời cũ hút yếu, hút mãi không sạch....#Roborock #Qrevo2Pro #robothutbui #xuhuong #ahastore</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G15" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1152,20 +1068,14 @@
           <t>🔥Giá tầm trung nhưng công nghệ đỉnh cao.... #Qrevo2Pro #Roborock #robothutbui #xuhuong #ahastore</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G16" t="n">
+        <v>175</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1199,20 +1109,14 @@
           <t>🤣Nay em chạy quảng cáo sản phẩm mới bằng cơm cho các bác xem.....#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="G17" t="n">
+        <v>290</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1246,20 +1150,14 @@
           <t xml:space="preserve">🔥SIÊU PHẨM QREVO 2 PRO ĐÃ CHÍNH THỨC CẬP BẾN AHA STORE. ĐẾN ĐỂ TRẢI NGHIỆM VÀ NHẬN TƯ VẤN NGAY…..#robotrock #ahastore #xuhuong #tiktok #qrevo2pro </t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G18" t="n">
+        <v>180</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1340,20 +1238,14 @@
           <t xml:space="preserve">📍 TigerBot Smart Home  🏠 121F Nguyễn Huệ, Phường Long Châu, Vĩnh Long 📞 Hotline: 0941 861 903 #qrevo2pro #roborock #robothutbui   </t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G20" t="n">
+        <v>154</v>
+      </c>
+      <c r="H20" t="n">
+        <v>11</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1387,20 +1279,14 @@
           <t xml:space="preserve">🏡✨ MỘT CHIẾC ROBOT – GẦN NHƯ LO TRỌN VIỆC NHÀ! Nếu bạn đang tìm một trợ thủ có thể thay mình xử lý hầu hết công việc dọn dẹp hằng ngày, Roborock Qrevo 2 Pro chính là lựa chọn đáng cân nhắc. 🤖 Từ bụi mịn, tóc rụng, lông thú cưng đến các góc khuất hay thảm trải sàn, Qrevo 2 Pro đều được trang bị công nghệ để làm sạch hiệu quả. 💥 Lực hút HyperForce® 25.000Pa hút sạch bụi bẩn và rác vụn chỉ trong một lần di chuyển. 🧹 FlexiArm™ tự động mở rộng chổi cạnh và giẻ lau, làm sạch sát mép tường, góc nhà và những vị trí dễ bị bỏ sót. 🌀 Hệ thống chống rối toàn thân đạt chứng nhận SGS giúp giảm tối đa tóc quấn vào chổi, duy trì hiệu suất ổn định. 🏠 Tự động tháo giẻ khi làm sạch thảm, kết hợp dock đa năng tự giặt giẻ, sấy khô, thu gom bụi và tự làm sạch, mang đến trải nghiệm gần như rảnh tay hoàn toàn. ✨ Việc dọn dẹp giờ đây chỉ còn là một thao tác chạm trên điện thoại. Phần còn lại, hãy để Roborock Qrevo 2 Pro chăm sóc. 📍 TigerBot Smart Home 🏠 121F Nguyễn Huệ, Phường Long Châu, Vĩnh Long 📞 Hotline: 0941 861 903 👉 Inbox ngay để được tư vấn và nhận ưu đãi hấp dẫn! #Roborock #RoborockVietnam #Qrevo2Pro #TigerBotSmartHome #VINHLONG      </t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G21" t="n">
+        <v>130</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1434,20 +1320,14 @@
           <t xml:space="preserve">🏡✨ MỘT CHIẾC ROBOT – GẦN NHƯ LO TRỌN VIỆC NHÀ! Nếu bạn đang tìm một trợ thủ có thể thay mình xử lý hầu hết công việc dọn dẹp hằng ngày, Roborock Qrevo 2 Pro chính là lựa chọn đáng cân nhắc. 🤖 Từ bụi mịn, tóc rụng, lông thú cưng đến các góc khuất hay thảm trải sàn, Qrevo 2 Pro đều được trang bị công nghệ để làm sạch hiệu quả. 💥 Lực hút HyperForce® 25.000Pa hút sạch bụi bẩn và rác vụn chỉ trong một lần di chuyển. 🧹 FlexiArm™ tự động mở rộng chổi cạnh và giẻ lau, làm sạch sát mép tường, góc nhà và những vị trí dễ bị bỏ sót. 🌀 Hệ thống chống rối toàn thân đạt chứng nhận SGS giúp giảm tối đa tóc quấn vào chổi, duy trì hiệu suất ổn định. 🏠 Tự động tháo giẻ khi làm sạch thảm, kết hợp dock đa năng tự giặt giẻ, sấy khô, thu gom bụi và tự làm sạch, mang đến trải nghiệm gần như rảnh tay hoàn toàn. ✨ Việc dọn dẹp giờ đây chỉ còn là một thao tác chạm trên điện thoại. Phần còn lại, hãy để Roborock Qrevo 2 Pro chăm sóc. 📍 TigerBot Smart Home 🏠 121F Nguyễn Huệ, Phường Long Châu, Vĩnh Long 📞 Hotline: 0941 861 903 👉 Inbox ngay để được tư vấn và nhận ưu đãi hấp dẫn! #Roborock #RoborockVietnam #Qrevo2Pro #TigerBotSmartHome #VINHLONG      </t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G22" t="n">
+        <v>103</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1481,20 +1361,14 @@
           <t xml:space="preserve">Test 010: Robot có xử lý được vết bẩn bám từ giày dép sau mưa không? Test này có tâm rồi chứ ae 🤭🤭 ae cần test thêm gì cmt xuống nhé  #minhchautestthat #roborock #roborockqrevo2pro #maylaunha </t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G23" t="n">
+        <v>858</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1528,20 +1402,14 @@
           <t xml:space="preserve">Mấy dòng này oke phết. Combo Vỏ trấu, vỏ hướng dương và tóc- Xử lý cái vèo🤭 Robot hút bụi lau nhà Roborock Qrevo 2 Pro nhé ae #minhchautestthat #roborock #qrevo2pro #minhchausmarthome #roborockqrevo2pro </t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G24" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H24" t="n">
+        <v>11</v>
+      </c>
+      <c r="I24" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -1575,20 +1443,14 @@
           <t xml:space="preserve">Robot hút bụi lau nhà Roborock Qrevo 2 Pro có hút được lông chó mèo không? Mời ace kiểm chứng nhé, ace cần test gì comment xuống dưới nhé #minhchautestthat #robothutbuilaunha #roborockqrevo2pro #roborock #qrevo2pro </t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G25" t="n">
+        <v>505</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1622,20 +1484,14 @@
           <t xml:space="preserve">Robot hút bụi lau nhà có hút sạch tóc không, có bị mắc tóc vào chổi cuốn không?  cùng mình test thực tế nhé 😜 #minhchautestthat #robothuttoc #qrevo2pro #dondep #robothutbuibacgiang </t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G26" t="n">
+        <v>271</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1669,20 +1525,14 @@
           <t xml:space="preserve">Bài test vui giữa 2 em Robot hút bụi lau nhà phân khúc 12-13tr của 2 thương hiệu bán chạy nhất Việt Nam  ae cần test với sp nào cmt xuống dưới nhé  #minhchautestthat #roborock #qrevo2pro #ecovacs #t30c </t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G27" t="n">
+        <v>286</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1716,20 +1566,14 @@
           <t xml:space="preserve">Test #001 Robot hút bụi lau nhà Roborock Qrevo 2 pro vs vỏ hướng dương!  #minhchautestthat #vohuongduong #robothutbuibacgiang </t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G28" t="n">
+        <v>272</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1763,20 +1607,14 @@
           <t xml:space="preserve">Hướng dẫn cài app Robot hút bụi lau nhà Roborock Qrevo 2 pro  #minhchau #huongdan #caiapp  #roborock #qrevo2pro </t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G29" t="n">
+        <v>356</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1810,20 +1648,14 @@
           <t>- Lực hút khủng: 25000pa - Pin: 5200mAh làm việc 200m2 - Robot: chổi chống mắc tóc, nâng khăn, xoè khăn - Trạm sạc: tự thu bụi, giặt nóng, sấy nóng, vệ sinh trạm được cải tiến,. - Robot nói tiếng Việt, app tiếng Việt dễ dùng - Bảo hành chính hãng 2 năm, free ship 2 chiều trong trường hợp cần bảo hành - Mức giá: tầm 13tr anh em thấy sao về em nó. #roborock #qrevo2pro #minhchau #robothutbuibacgiang</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G30" t="n">
+        <v>229</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1857,20 +1689,14 @@
           <t xml:space="preserve">🔥 ĐẬP HỘP ROBOROCK QREVO 2 PRO Robot hút bụi lau nhà được đánh giá sẽ là một trong những sản phẩm chiến lược của Roborock thời gian tới. #Roborock #Qrevo2Pro #MinhChauSmarthome #RobotHutBui #RobotLauNha </t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G31" t="n">
+        <v>424</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1904,20 +1730,14 @@
           <t xml:space="preserve">Tự để lại giẻ tại dock trước khi làm thảm, giữ thảm khô sạch và hạn chế bẩn chéo ✨ Khay giặt tự làm sạch thế hệ 2, giúp dock sạch lâu hơn theo thời gian và giảm công vệ sinh định kỳ ✨ Dock đa năng tự giặt và sấy sau mỗi chu trình, để robot luôn sẵn sàng cho lần chạy tiếp theo #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G32" t="n">
+        <v>132</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1951,20 +1771,14 @@
           <t xml:space="preserve">😮‍💨 Bạn yên tâm, đã có dock của Qrevo 2 Pro với thiết kế bo tròn tinh tế, vì không phải mọi công nghệ đều nằm ở bên trong. Đôi khi, một chi tiết nhỏ như dock bo tròn cũng đủ để mỗi lần đi ngang bớt đi một cú va chạm. Bởi trải nghiệm tốt không chỉ đến từ việc robot dọn sạch, mà còn từ cách mọi chi tiết được thiết kế để sống cùng ngôi nhà của bạn. Luôn nghĩ cho bạn, luôn là Qrevo 2 Pro 💛  #Roborock   #Qrevo2Pro #robothutbui  #thietbithongminh </t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G33" t="n">
+        <v>114</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1998,20 +1812,14 @@
           <t xml:space="preserve">✨ QREVO 2 PRO – CHỌN CÔNG NGHỆ VƯỢT TẦM GIÁ, VIỆC CHĂM NHÀ ĐƯỢC GIAO PHÓ THEO CÁCH THẬT DỄ CHỊU 🤍 Robot hút bụi lau nhà Roborock Qrevo 2 Pro xuất hiện như một lựa chọn dành cho những tổ ấm muốn giữ nhịp sạch sẽ mỗi ngày, nơi những chu trình lặp đi lặp lại được thay thế bằng một guồng vận hành tự động gọn gàng. 🏡 Roborock tập trung vào những tính năng cốt lõi, chắt lọc công nghệ để phục vụ đúng nhu cầu thường nhật, đồng thời mang nhiều trải nghiệm vốn thường gắn với phân khúc cao hơn đến gần hơn với mức giá dễ tiếp cận: ✨ Lực hút HyperForce® 25.000Pa mạnh mẽ, xử lý gọn từ bụi mịn, rác vụn đến tóc rụng và lông thú ✨ Hệ thống chống rối toàn thân có chứng nhận, duy trì hiệu suất ổn định và giảm tối đa thao tác gỡ rối thủ công ✨ FlexiArm™ vươn sát mép, chăm kỹ đường viền và góc cạnh để mặt sàn sạch “đều tay” hơn ✨ Chổi cạnh đảo chiều tối ưu khả năng quét góc, tăng hiệu quả gom bụi sát tường và khe cạnh ✨ Tự để lại giẻ tại dock trước khi làm thảm, giữ thảm khô sạch và hạn chế bẩn chéo ✨ Khay giặt tự làm sạch thế hệ 2, giúp dock sạch lâu hơn theo thời gian và giảm công vệ sinh định kỳ ✨ Dock đa năng tự giặt và sấy sau mỗi chu trình, để robot luôn sẵn sàng cho lần chạy tiếp theo Nhà sạch ổn định, thao tác tối giản và bạn có thêm thời gian cho những điều thật sự quan trọng. #Roborock   #Qrevo2Pro #Robothutbui  #thietbithongminh </t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G34" t="n">
+        <v>109</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2045,20 +1853,14 @@
           <t>🏡✨ Ngoài việc tránh tiếp xúc trực tiếp với nước, robot hút bụi lau nhà Roborock Qrevo 2 Pro tự tin cân trọn hầu hết nhu cầu dọn dẹp trong nhà đấy! 🤖 Thế nên, bụi mịn, tóc rụng, lông thú, khe góc hay thảm trải sàn, cứ giao "em" xử lý. Chủ nhân ơi, hôm nay có nhiệm vụ đặc biệt nào dành cho Qrevo 2 Pro không? #Roborock #RoborockVietnam #OtechVietnam #Qrevo2Pro</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G35" t="n">
+        <v>217</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2092,20 +1894,14 @@
           <t>Tập tành bắt trend thôi hihi #2pro #qrevo2pro #robothutbui #thanhhoa #roborockthanhhoa #viralvideotiktok #roborockvietnam #xuhuong #xuhuongtiktok #hutbui #hdpe #otechvietnam #haihuoc #congnghe #robot</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2139,20 +1935,14 @@
           <t>Sếp bảo ra quay cho anh để chạy quảng cáo em nhé #roborockthanhhoa#viralvideotiktok #roborockvietnam #xuhuong #xuhuongtiktok #hutbui #hdpe #otechvietnam #haihuoc #congnghe #robot #thanhhoa #qrevo2pro #2pro</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G37" t="n">
+        <v>19</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2186,20 +1976,14 @@
           <t>Roborock Qrevo 2 Pro mạnh mẽ hàng đầu phân khúc</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G38" t="n">
+        <v>179</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2233,20 +2017,14 @@
           <t xml:space="preserve">Qrevo 2 Pro có gì hay nào? #Qrevovo2pro #roborock #robothutbui #robotbinhduong </t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G39" t="n">
+        <v>188</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2280,20 +2058,14 @@
           <t xml:space="preserve">Đập hộp robot hút bụi Roborock Qrevo 2 Pro #roborock #congnghe </t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G40" t="n">
+        <v>274</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2374,20 +2146,14 @@
           <t>📷Bàn giao siêu phẩm mới cập bến Roborock Qrevo 2 Pro📷 Qrevo 2 Pro vừa được 𝐇𝐨𝐦𝐞𝐜𝐚𝐫𝐞 𝐃𝐢𝐠𝐢𝐭𝐚𝐥 bàn giao đến tay khách hàng đã lập tức chứng minh vị thế của một "chiến thần" dọn dẹp thực thụ.  Em này tự tin xóa nhòa ranh giới giữa phân khúc tầm trung và cao cấp khi sở hữu trọn vẹn những công nghệ làm sạch đỉnh cao nhất hiện nay. Mỗi góc nhỏ trong ngôi nhà bạn từ nay sẽ luôn bóng bẩy, mang lại trải nghiệm sống thảnh thơi trọn vẹn mà không cần tốn chút sức lực nào. 📷Ghé 𝐇𝐨𝐦𝐞𝐜𝐚𝐫𝐞 𝐃𝐢𝐠𝐢𝐭𝐚𝐥 để được tư vấn chi tiết và sở hữu chiếc robot hút bụi chân ái cho ngôi nhà của bạn! #Qrevo2Pro #Roborock #robothutbui #HomecareDigital #RoborockDaNang</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2421,20 +2187,14 @@
           <t>HOMECARE DIGITAL - ROBOROCK QREVO 2 PRO Dưới 15🥔 thì đây là 1 lựa chọn hoàn toàn xứng đáng với số tiền quý khách hàng đầu tư cho ngồi nhà của mình Ghé ngay Homecare Digital để nhận tư vấn #Qrevo2Pro #Roborock #robothutbui #HomecareDigital #robothutbuilaunha</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G43" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2468,20 +2228,14 @@
           <t>Hot hơn cả thời tiết tháng 6 🔥 Roborock Qrevo 2 Pro đã chính thức mở bán và có sẵn tại Danke rồi đây! Cùng Long khám phá xem Robot phiên bản mới này có gì nâng cấp, có gì đáng tiền và vì sao lại đáng để lên đời nha 😙 #robothutbuilaunha #roborock #qrevo2pro #roborockqrevo2pro #robothutbui</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G44" t="n">
+        <v>148</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2515,20 +2269,14 @@
           <t xml:space="preserve">Roborock Qrevo 2 Pro đã có mặt tại Đà Nẵng. Mọi người xem khả năng hút tóc và đảo chiều chổi của bạn ấy mượt thế nào nha! 😍 #robothutbui #roborock #qrevo2pro #reviewrobot #roborocktaidanang </t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G45" t="n">
+        <v>228</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2562,20 +2310,14 @@
           <t xml:space="preserve">Loading 80% Roborock Krông Nô #roborock  #roborockvietnam  #krôngnô  #qrevo2pro </t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G46" t="n">
+        <v>468</v>
+      </c>
+      <c r="H46" t="n">
+        <v>47</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2609,20 +2351,14 @@
           <t xml:space="preserve">Roborock Qrevo 2 Pro - Đặt hàng ngay để nhận bộ quà tặng 14 món phụ kiện robot Trải nghiệm sản phẩm trực tiếp tại showroom - trung tâm bảo hành Roborok Krông Nô - 30 Nguyễn Tất Thành - Krông Nô - Lâm Đồng hoặc liên hệ 0985.37.47.48 để tư vấn trực tiếp #qrevo2pro  #roborockvietnam  #roborock  #robothutbuilaunha </t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G47" t="n">
+        <v>392</v>
+      </c>
+      <c r="H47" t="n">
+        <v>13</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -2656,20 +2392,14 @@
           <t xml:space="preserve">Đơn nhẹ mùng 2, 2 tầng, 2 em 2 Pro #qrevo2pro  #roborock  #roborockvietnam </t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G48" t="n">
+        <v>235</v>
+      </c>
+      <c r="H48" t="n">
+        <v>11</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -2703,20 +2433,14 @@
           <t>Robot Jutsu nhưng là Roborock Qrevo 2 Pro #transition #mivietnam #Robothutbui #Roborock #Qrevo2Pro</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G49" t="n">
+        <v>589</v>
+      </c>
+      <c r="H49" t="n">
+        <v>20</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -2750,20 +2474,14 @@
           <t>Roborock Qrevo 2 Pro — giao tận nơi, lắp tận nhà, hướng dẫn dùng kỹ bởi #MiVietnam #chuyengiarobothutbui #robothutbui #roborock #Qrevo2Pro</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G50" t="n">
+        <v>1094</v>
+      </c>
+      <c r="H50" t="n">
+        <v>13</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2797,20 +2515,14 @@
           <t>Giặt và Sấy khí nóng - Roborock Qrevo 2 Pro #mivietnam #chuyengiarobothutbui #Roborock #Qrevo2Pro #Qrevo2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G51" t="n">
+        <v>252</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2844,20 +2556,14 @@
           <t xml:space="preserve">Có cải tiến mới Roborock Qrevo 2 Pro #mivietnam #roborock #qrevo2pro #robothutbui </t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G52" t="n">
+        <v>491</v>
+      </c>
+      <c r="H52" t="n">
+        <v>6</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2891,20 +2597,14 @@
           <t>Có thể là đại náo hang ổ "yêu tinh bụi bẩn" đang ẩn nấp luôn #mivietnam #roborock #qrevo2pro #robothutbui Roborock Qrevo 2 Pro</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G53" t="n">
+        <v>713</v>
+      </c>
+      <c r="H53" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2938,20 +2638,14 @@
           <t xml:space="preserve">Lao Công 4.0 khắc nghiệt lắm - Công Nghệ Tự Bảo Vệ của Roborock Qrevo 2 Pro #mivietnam #RobotHutBui #Roborock #qrevo2pro </t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G54" t="n">
+        <v>609</v>
+      </c>
+      <c r="H54" t="n">
+        <v>12</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2985,20 +2679,14 @@
           <t>Vì Sao nói Thiết Kế Roborock Qrevo 2 Pro là 1 thiết kế thân thiện với trẻ em #mivietnam #Robothutbui #Roborock #Qrevo2Pro #Qrevo</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G55" t="n">
+        <v>593</v>
+      </c>
+      <c r="H55" t="n">
+        <v>10</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3126,20 +2814,14 @@
           <t>#Qrevo2Pro #Roborock #robothutbui</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G58" t="n">
+        <v>74</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3173,20 +2855,14 @@
           <t>#Qrevo2Pro #Roborock #robothutbui</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G59" t="n">
+        <v>145</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3220,20 +2896,14 @@
           <t>Quan điểm của mình -  bệ giặt thì cứ phải tháo rời ra như nảy thỉ mới tiện lợi - sạch sẽ - tránh tình trạng đọng bùn đất gây mùi hôi.  Và quan trọng không phải cúi mỏi lưng khi cần chà rửa. 🤭 #Qrevo2Pro #Roborock #robothutbui</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G60" t="n">
+        <v>172</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3267,20 +2937,14 @@
           <t>#Qrevo2Pro #Roborock #robothutbui</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G61" t="n">
+        <v>144</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3314,20 +2978,14 @@
           <t>#Qrevo2Pro #Roborock #robothutbui Hàng sẵn giao ngay lại ____________ ROBOROCK STORE BUÔN MA THUỘT 🏠 Số 29 Trần Phú - Phường Buôn Ma Thuột - Tỉnh Đăk Lăk. ☎️ 0964.642.842 - 097.664.9388</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G62" t="n">
+        <v>137</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3361,20 +3019,14 @@
           <t>Khay giặt giẻ của Qrevo2 Pro có gì mới? #Qrevo2Pro #Roborock #robothutbui</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G63" t="n">
+        <v>150</v>
+      </c>
+      <c r="H63" t="n">
+        <v>6</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3408,20 +3060,14 @@
           <t>Thiết kế mới nhất đến từ Roborock - Một sản phẩm tầm trung nhưng thiết kế sang trọng - tinh tế. #Qrevo2Pro #Roborock #robothutbui</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G64" t="n">
+        <v>143</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3455,20 +3101,14 @@
           <t>Siêu phẩm hothit Roborook Qrevo 2pro. #qrevo2pro #roborockvietnam #hiẹphongtechhome</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G65" t="n">
+        <v>1082</v>
+      </c>
+      <c r="H65" t="n">
+        <v>11</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3502,20 +3142,14 @@
           <t xml:space="preserve">Chạy quảng cáo mới ra đơn Qrevo 2 pro 2026 #quyrobot #Roborock #qrevo2pro #robothutbui </t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="G66" t="n">
+        <v>647</v>
+      </c>
+      <c r="H66" t="n">
+        <v>32</v>
+      </c>
+      <c r="I66" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="67">
@@ -3549,20 +3183,14 @@
           <t xml:space="preserve">Test thực tế mẫu qrevo 2 pro mới rămys cho ace thẩm nhaz #quyrobot #robotvinhphuc #roborock #qrevo2pro </t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G67" t="n">
+        <v>270</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3596,20 +3224,14 @@
           <t xml:space="preserve">Về thêm mã mới qrevo 2 pro 2026 #quyrobot #robotvinhphuc #xuhuong #qrevo2pro #roborock </t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G68" t="n">
+        <v>236</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3643,20 +3265,14 @@
           <t xml:space="preserve">Siêu phẩm tầm trung lực hút cực khủng mang tên Qrevo 2 Pro  #Qrevo2Pro #roborock #robothutbui #smarthomephutho #NhaThongMinh </t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G69" t="n">
+        <v>118</v>
+      </c>
+      <c r="H69" t="n">
+        <v>4</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3690,20 +3306,14 @@
           <t xml:space="preserve">Chiến thần tầm trung mang tên Qrevo 2 pro #Qrevo2Pro #roborock #robothutbui #NhaThongMinh #smarthomephutho </t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G70" t="n">
+        <v>105</v>
+      </c>
+      <c r="H70" t="n">
+        <v>7</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3737,20 +3347,14 @@
           <t>Ship roborock qrevo 2 pro cho khách yêu</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G71" t="n">
+        <v>436</v>
+      </c>
+      <c r="H71" t="n">
+        <v>6</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3784,20 +3388,14 @@
           <t xml:space="preserve">Nhiều bác bảo chạy quảng cáo mới ra đơn, nay em chạy rồi các bác mua hàng cho em đi ạ #Qrevo2pro #roborock #robothutbui #xuhuongtiktok #quyrobot </t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="G72" t="n">
+        <v>247</v>
+      </c>
+      <c r="H72" t="n">
+        <v>49</v>
+      </c>
+      <c r="I72" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="73">
@@ -3831,20 +3429,14 @@
           <t xml:space="preserve">QREVO 2 PRO – CHỌN CÔNG NGHỆ VƯỢT TẦM GIÁ, VIỆC CHĂM NHÀ ĐƯỢC GIAO PHÓ THEO CÁCH THẬT DỄ CHỊU #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G73" t="n">
+        <v>126</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3878,20 +3470,14 @@
           <t xml:space="preserve">Đón chờ siêu phẩm mới đến từ nhà Roborock #robothutbui #qrevo2pro #robothutbuithainguyen  #3tsmart </t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G74" t="n">
+        <v>419</v>
+      </c>
+      <c r="H74" t="n">
+        <v>9</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -3926,7 +3512,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H75" t="n">
         <v>3</v>
@@ -4008,10 +3594,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -4049,13 +3635,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>28</v>
+        <v>51300</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>190</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79">
@@ -4090,10 +3676,10 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>208</v>
+        <v>369</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -4131,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -4172,10 +3758,10 @@
         </is>
       </c>
       <c r="G81" t="n">
+        <v>241</v>
+      </c>
+      <c r="H81" t="n">
         <v>1</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -4213,10 +3799,10 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>7</v>
+        <v>144</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -4254,10 +3840,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -4295,13 +3881,13 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -4336,13 +3922,13 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="H85" t="n">
+        <v>4</v>
+      </c>
+      <c r="I85" t="n">
         <v>2</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -4377,13 +3963,13 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -4418,13 +4004,13 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>420</v>
+        <v>846</v>
       </c>
       <c r="H87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -4459,10 +4045,10 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -4541,10 +4127,10 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>130</v>
+        <v>214</v>
       </c>
       <c r="H90" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -4582,10 +4168,10 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="H91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -4623,10 +4209,10 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -4664,10 +4250,10 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="H93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -4705,13 +4291,13 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -4746,10 +4332,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -4787,7 +4373,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4828,7 +4414,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="H97" t="n">
         <v>1</v>
@@ -4869,10 +4455,10 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="H98" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -4910,7 +4496,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
@@ -4951,10 +4537,10 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>44</v>
+        <v>302</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
@@ -4992,13 +4578,13 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -5033,13 +4619,13 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="H102" t="n">
+        <v>3</v>
+      </c>
+      <c r="I102" t="n">
         <v>1</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5074,13 +4660,13 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -5115,13 +4701,13 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -5156,10 +4742,10 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -5197,7 +4783,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
@@ -5238,10 +4824,10 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -5279,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>655</v>
+        <v>1811</v>
       </c>
       <c r="H108" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
@@ -5320,13 +4906,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>106</v>
+        <v>923</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -5361,10 +4947,10 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -5402,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5443,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5484,10 +5070,10 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -5525,7 +5111,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -5566,10 +5152,10 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -5607,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>40</v>
+        <v>4399</v>
       </c>
       <c r="H116" t="n">
+        <v>29</v>
+      </c>
+      <c r="I116" t="n">
         <v>2</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5648,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5689,10 +5275,10 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -5730,10 +5316,10 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -5771,10 +5357,10 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -5812,10 +5398,10 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -5853,10 +5439,10 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -5894,10 +5480,10 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="H123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I123" t="n">
         <v>3</v>
@@ -5935,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1473</v>
+        <v>1503</v>
       </c>
       <c r="H124" t="n">
         <v>14</v>
@@ -5976,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="videos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="videos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H12" t="n">
         <v>7</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H14" t="n">
         <v>28</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H15" t="n">
         <v>4</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H16" t="n">
         <v>8</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H17" t="n">
         <v>23</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>858</v>
+        <v>886</v>
       </c>
       <c r="H23" t="n">
         <v>7</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1150</v>
+        <v>1178</v>
       </c>
       <c r="H24" t="n">
         <v>11</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="H27" t="n">
         <v>8</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H28" t="n">
         <v>3</v>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="H31" t="n">
         <v>7</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H37" t="n">
         <v>4</v>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H40" t="n">
         <v>3</v>
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="H46" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H48" t="n">
         <v>11</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="H49" t="n">
         <v>20</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1094</v>
+        <v>1105</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H51" t="n">
         <v>6</v>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="H52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="H53" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="H54" t="n">
         <v>12</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="H55" t="n">
         <v>10</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H58" t="n">
         <v>2</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H59" t="n">
         <v>2</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H64" t="n">
         <v>4</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="H65" t="n">
         <v>11</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="H66" t="n">
         <v>32</v>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H72" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I72" t="n">
         <v>60</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>51300</v>
+        <v>55200</v>
       </c>
       <c r="H78" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="I78" t="n">
         <v>53</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I84" t="n">
         <v>2</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>846</v>
+        <v>872</v>
       </c>
       <c r="H87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H91" t="n">
         <v>4</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H95" t="n">
         <v>6</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H97" t="n">
         <v>1</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H98" t="n">
         <v>7</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H100" t="n">
         <v>5</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1811</v>
+        <v>1970</v>
       </c>
       <c r="H108" t="n">
         <v>8</v>
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>923</v>
+        <v>1496</v>
       </c>
       <c r="H109" t="n">
-        <v>256</v>
+        <v>551</v>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H113" t="n">
         <v>2</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H115" t="n">
         <v>1</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>4399</v>
+        <v>6201</v>
       </c>
       <c r="H116" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="H118" t="n">
         <v>2</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>81</v>
+        <v>368</v>
       </c>
       <c r="H120" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>85</v>
+        <v>201</v>
       </c>
       <c r="H121" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="H122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1503</v>
+        <v>1554</v>
       </c>
       <c r="H124" t="n">
         <v>14</v>
@@ -5562,13 +5562,1284 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
       </c>
       <c r="I125" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7659380198932008212</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gái nghệ "Thành Vinh" Gây thương gây nhớ bán robot 😃anh đừng loanh quanh chốt roborock qrevo 2 pro một phát đi anh👏👏👏#Roborock ##Qrevo2Pro ##capcut #ahastore ##tiktok </t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>59</v>
+      </c>
+      <c r="H126" t="n">
+        <v>15</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7659393947168558357</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7/7 đã đến rồi Đến ngay TIGERBOT SMART HOME để tậu robot hút bụi  #qrevo2pro #roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>22</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7659296694642756885</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot hút bụi ngày càng xuất hiện nhiều trong các gia đình hiện đại. Và Roborock Qrevo 2 Pro là một lựa chọn rất đáng để tham khảo lúc này. #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>124</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7659366405183245575</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roborock Qrevo2 Pro phiên bản trắng #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>12</v>
+      </c>
+      <c r="H129" t="n">
+        <v>3</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7659333557625703698</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khám phá từng chi tiết Qrevo2 pro #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>78</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7659326205505654024</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo2 Pro trắng Ngọc Trinh #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>91</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7659293157355474184</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo2 pro dẫn đầu phân khúc #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>99</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7659291275266379015</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo2 pro cần mẫn và tỷ mỹ #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>129</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7659289222553111826</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phẩu thuật Qrevo2 pro mới nhất #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>120</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7659286717026913544</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Sở hữu #qrevo2proQrevo2 Pro mạnh mẽ nhất phân khúc chỉ với hơn 13tr#Roborock #Robothutbui</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>124</v>
+      </c>
+      <c r="H135" t="n">
+        <v>3</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7659283909045226760</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 pro thiết kế đẹp mắt, lực hút mạnh mẽ #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>120</v>
+      </c>
+      <c r="H136" t="n">
+        <v>2</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7659283167630871815</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo2 Pro nhiều tính năng vượt trội trong cùng phân khúc #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>116</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7659281705160707346</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Qrevo 2 pro mạnh mẽ nhất phân khúc #qrevo2pro #Roborock #Robothutbui</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>99</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>t_tech.ninhbinh</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@t_tech.ninhbinh/video/7659317342760963348</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROBOROCK 2pro có gì đáng quan tầm ? ✨ Lực hút HyperForce® 25.000Pa mạnh mẽ ✨ Chổi cạnh đảo chiều thế hệ mới quét sâu vào góc hơn ✨ FlexiArm™ vươn sát mép tường, giảm tối đa khu vực bỏ sót ✨ Hệ thống chống rối toàn thân đạt chứng nhận SGS ✨ Tự động tháo giẻ trước khi làm sạch thảm ✨ Dock đa năng tự giặt, tự sấy, tự làm sạch 📍 :𝐓-𝐭𝐞𝐜𝐡 𝟏𝟓𝟓 𝐋𝐮̛𝐨̛𝐧𝐠 𝐕𝐚̆𝐧 𝐓𝐡𝐚̆𝐧𝐠, 𝐓𝐏𝐍𝐁 ☎️  :𝟎𝟖𝟔𝟓𝟑𝟔𝟑𝟐𝟔𝟖 #qrevo2pro #roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1451</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>tn.robot76</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tn.robot76/video/7659310908673576199</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Sản phẩm Robot tầm trung giá mềm đáng mua nhất hiện tại Qrevo 2 pro #Qrevo2Pro #Roborock #Robothutbui</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>93</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7659313296910159125</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>#Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>86</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7657569311443422485</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Đập hộp #Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>204</v>
+      </c>
+      <c r="H142" t="n">
+        <v>9</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659271674071665940</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chiến minh mới tầm trung nhà roborock lực hút cực khủng điểm 10 cho chất lượng #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>137</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659237445623500053</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chọn đúng robot hút bụi lau nhà  không phải là đặt cược vào may mắn mà là đầu tư cho sự tiện nghi mỗi ngày  Roborock Qrevo 2 pro mang sự cân bằng giữ sức mạnh làm sạch công nghệ thông minh và khả năng tự động hoá vượt trội giúp việc chăm sóc ngôi nhà trở nên dễ dàng hơn #roborock #Qrevo2Pro #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>134</v>
+      </c>
+      <c r="H144" t="n">
+        <v>3</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7659398037382499605</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phiên bản mới của nhà Roborock không còn hình ảnh cứng cáp của dòng Qrevo seri trước đây#RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>26</v>
+      </c>
+      <c r="H145" t="n">
+        <v>2</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>bepphuthai</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bepphuthai/video/7659389488984067348</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>✨ CHƯƠNG TRÌNH TRẢI NGHIỆM TRƯỚC, MUA SAU - QREVO 2 PRO &amp; F25 ULTRA Những quyết định quan trọng nhất cho tổ ấm phải đến từ trải nghiệm thực tế. Từ 07.07.2026 - 31.07.2026, hãy ghé BẾP PHÚ THÁI để tự mình trải nghiệm bộ đôi siêu phẩm dọn dẹp siêu hot: Qrevo 2 Pro &amp; F25 Ultra. ✨ Qrevo 2 Pro: Dòng robot hút bụi mới ra mắt, sở hữu hiệu năng và công nghệ dẫn đầu tầm trung hiện nay, xử lý tốt việc lau dọn hàng ngày. ✨ F25 Ultra: Best seller dòng cầm tay, là mảnh ghép còn lại giúp bạn xử lý nhanh những nơi nhiều dầu mỡ, đồ ăn rơi vãi như khu vực bếp. Đặc quyền dành riêng cho khách hàng: 🚀 Mức giá ưu đãi khi trải nghiệm Qrevo 2 Pro 🚀 Nhận ngay combo quà tặng lên tới 14 sản phẩm 🚀 Trải nghiệm công nghệ mới hiện nay 🚀 Được tư vấn 1:1 giải pháp làm sạch phù hợp với cấu trúc nhà bạn Số lượng quà tặng có giới hạn. Hãy trở thành những người đầu tiên trải nghiệm và lựa chọn đúng sản phẩm cho ngôi nhà của mình! ___________ BẾP PHÚ THÁI 📍 : 262 Lê Thánh Tông P.Hạc Thành TP Thanh Hóa ☎️ : 0945.248.165 #Roborock 2pro</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>22</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7659245802417671445</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌌 QREVO 2 PRO | SỨ MỆNH NÂNG TẦM SỨC MẠNH DỌN DẸP TẦM TRUNG CHÍNH THỨC CẤT CÁNH Roborock Qrevo 2 Pro xuất hiện như một cú phóng mới cho chuẩn sạch tầm trung.  🌪️ Một - Lực hút 25.000Pa đánh thức sức mạnh làm sạch toàn diện, cuốn gọn bụi mịn, tóc rụng và mảnh vụn trong từng lần di chuyển. 🌪️ Hai - Giẻ lau FlexiArm cùng chổi cạnh đảo chiều mở rộng giới hạn làm sạch, len sát mép tường, chạm đến những góc nhỏ thường bị bỏ quên. 🌪️ Ba - Hệ thống chống rối 3 lớp giúp hành trình vận hành mượt mà hơn, để tóc và lông thú không còn là lý do khiến bạn phải cúi xuống gỡ thủ công. 🌪️ Bốn - Dock tự giặt giẻ, sấy nóng 45°C và làm sạch khay giặt, giữ chu trình sau mỗi lần lau luôn khô thoáng, gọn gàng và an tâm. 🌪️ Năm - Khi gặp thảm, robot tự để giẻ lại dock, chỉ tập trung hút sạch mà không kéo ẩm lên bề mặt vải. Chuẩn sạch mới chính thức bắt đầu cùng Roborock Qrevo 2 Pro. #Roborock #RoborockVietnam   #Qrevo2Pro #Roborock #Robothutbui </t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>125</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7657567801011473684</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>𝐐𝐫𝐞𝐯𝐨 𝟐 𝐏𝐫𝐨  👉Lực hút HyperForce: 25.000 Pa 👉Chổi cạnh đảo chiều: Tăng 30% diện tích phủ góc so với chổi cạnh cố định thông thường 👉Giẻ lau cạnh FlexiArm vươn ra sát tường 👉Hệ thống giẻ lau xoay kép 👉Dock sạc đa năng - tự làm sạch bệ giặt giẻ #Qrevo2Pro #Roborock #RobotLauNha #RobotDucTrong</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>111</v>
+      </c>
+      <c r="H148" t="n">
+        <v>4</v>
+      </c>
+      <c r="I148" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7657349734994038037</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Siêu phẩm dọn nhà thế hệ mới Roborock Qrevo 2 Pro! 🖤 Gôm trọn công nghệ đỉnh: 👉 Lực hút khủng 25.000 Pa 👉 Lau sát cạnh 1.85mm,  👉 Chổi cạnh đảo chiều sạch 100% góc chết và AI SmartPlan 3.0 tự tối ưu phòng. Giá cực tốt cho những vị khách đầu tiên, inbox em tư vấn liền tay nhé ạ! 💞 #Roborock #Qrevo2Pro #RobotLauNha #RobotDucTrong #RobotHutBuiLauNha</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>366</v>
+      </c>
+      <c r="H149" t="n">
+        <v>3</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7656613783372074261</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>🏡✨ Ngoài việc tránh tiếp xúc trực tiếp với nước, robot hút bụi lau nhà Roborock Qrevo 2 Pro tự tin cân trọn hầu hết nhu cầu dọn dẹp trong nhà đấy! 🤖 Thế nên, bụi mịn, tóc rụng, lông thú, khe góc hay thảm trải sàn, cứ giao "em" xử lý. 😚 #Roborock #RoborockVietnam #docongnghe#docovo2Pro #robothutbui</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>113</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7656233166637731093</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loanh quanh 13 🍠 - ra mắt tặng thêm rất nhiều 🎁 ✅Lực hút cực mạnh - giá tầm trung ✅Có chổi ven đảo chiều  ✅Có bệ tự vệ sinh  Đừng chần chừ gì nữa mà ib em tư vấn ngay nhé 👌#mytechfavs #qrevo2pro #roborock #robotductrong #test </t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>252</v>
+      </c>
+      <c r="H151" t="n">
+        <v>5</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7655621454356057365</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅Qrevo 2 Pro - Vừa mở bán đã hot hit điên đảo các bác ơi.  🎉Model 2026 với phân khúc giá chỉ loanh quanh 13 triệu thì em này xứng đáng mua nha 👉 Lực hút 25,000Pa (ngang ngửa với dòng cao cấp Qrevo Edge 2 luôn nè)🥹 👉 Giẻ xoè được sát tường, chổi thì xoay đảo chiều - khay giặt tự vệ sinh làm sạch như Edge2 👉 Có cả tính năng tự vệ sinh bệ giặt luôn nhé 👌 ... ❤️Quá hời để hốt về đó ạ.  💰💰💰Giá đang ưu đãi vì ra mắt sản phẩm mới của nhà Roborock nên KH hãy mua nhanhhhhh nhanhhh lên nha.  🏡 H&amp;T Smart Home Đức Trọng - 384 Thống Nhất ☎️ 0988607072 #Qrevo2Pro #2Pro #roborock #robotductrong #robotlaunhaductrong </t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>144</v>
+      </c>
+      <c r="H152" t="n">
+        <v>3</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>domotekvietnam</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@domotekvietnam/video/7659412665927896328</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7/7-31/7 có gì tại Domotek Việt Nam  #Qrevo2Pro #Roborock #Robothutbui #DomotekVietNam #đungdongvaianh </t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>5</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>domotekvietnam</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@domotekvietnam/video/7658694688303533320</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Với Domotek Việt Nam, bán hàng chỉ là khởi đầu – đồng hành và hỗ trợ khách hàng mới là cam kết lâu dài. Tận tâm trước, trong và sau bán, để mỗi sản phẩm đến tay khách đều mang lại sự an tâm tuyệt đối. #DomotekVietNam #DichVuKhachHang #RobotHutBui #ChamSocKhachHang #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>123</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>domotekvietnam</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@domotekvietnam/video/7658306093189385480</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Trải nghiệm trước mua sau cùng Roborock Qrevo 2 Pro và F25ultra #F25UItra #RoborockQrevo2Pro #DomotekVietnam #TraiNghiemTruocMuaSau #RobotHutBuiThongMinh</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>124</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>domotekvietnam</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@domotekvietnam/video/7655242449303948562</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📦 Unboxing siêu phẩm **Roborock Qrevo 2 Pro** 🔥 #DomotekVietNam #Roborock #Unbox #Unboxing #xuhuong   </t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>155</v>
+      </c>
+      <c r="H156" t="n">
+        <v>4</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="videos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="videos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H16" t="n">
         <v>8</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="H17" t="n">
         <v>23</v>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H18" t="n">
         <v>7</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>886</v>
+        <v>1183</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1178</v>
+        <v>1537</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I24" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>520</v>
+        <v>659</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>292</v>
+        <v>348</v>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>276</v>
+        <v>319</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="H29" t="n">
         <v>7</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="H31" t="n">
         <v>7</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H38" t="n">
         <v>5</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H39" t="n">
         <v>7</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="H40" t="n">
         <v>3</v>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="H46" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="H47" t="n">
         <v>13</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="H49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I49" t="n">
         <v>3</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1105</v>
+        <v>1116</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="H53" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H54" t="n">
         <v>12</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H55" t="n">
         <v>10</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H58" t="n">
         <v>2</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1085</v>
+        <v>1120</v>
       </c>
       <c r="H65" t="n">
         <v>11</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>656</v>
+        <v>669</v>
       </c>
       <c r="H66" t="n">
         <v>32</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H75" t="n">
         <v>3</v>
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>55200</v>
+        <v>63000</v>
       </c>
       <c r="H78" t="n">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="I78" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79">
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H83" t="n">
         <v>4</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
@@ -4004,13 +4004,13 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>872</v>
+        <v>1183</v>
       </c>
       <c r="H87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H88" t="n">
         <v>2</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H91" t="n">
         <v>4</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H93" t="n">
         <v>8</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="H95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H97" t="n">
         <v>1</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H98" t="n">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H100" t="n">
         <v>5</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H105" t="n">
         <v>2</v>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1970</v>
+        <v>2810</v>
       </c>
       <c r="H108" t="n">
+        <v>11</v>
+      </c>
+      <c r="I108" t="n">
         <v>8</v>
-      </c>
-      <c r="I108" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="109">
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1496</v>
+        <v>1582</v>
       </c>
       <c r="H109" t="n">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="I109" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H113" t="n">
         <v>2</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H115" t="n">
         <v>1</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>6201</v>
+        <v>111300</v>
       </c>
       <c r="H116" t="n">
-        <v>36</v>
+        <v>672</v>
       </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
     </row>
     <row r="117">
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="H117" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H118" t="n">
         <v>2</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="H120" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>201</v>
+        <v>309</v>
       </c>
       <c r="H121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="H122" t="n">
         <v>3</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1554</v>
+        <v>1684</v>
       </c>
       <c r="H124" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I124" t="n">
         <v>10</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5574,24 +5574,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>kimanh_1202</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@kimanh_1202/video/7659380198932008212</t>
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="H126" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I126" t="n">
         <v>3</v>
@@ -5615,24 +5615,24 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>tigerbot.smarthome</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@tigerbot.smarthome/video/7659393947168558357</t>
@@ -5644,10 +5644,10 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -5656,24 +5656,24 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>.hng0863</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@.hng0863/video/7659296694642756885</t>
@@ -5685,10 +5685,10 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -5697,24 +5697,24 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>thietbibepan</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@thietbibepan/video/7659366405183245575</t>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H129" t="n">
         <v>3</v>
@@ -5738,24 +5738,24 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>thietbibepan</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@thietbibepan/video/7659333557625703698</t>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -5779,24 +5779,24 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>thietbibepan</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@thietbibepan/video/7659326205505654024</t>
@@ -5808,10 +5808,10 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -5820,24 +5820,24 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>thietbibepan</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@thietbibepan/video/7659293157355474184</t>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="H132" t="n">
         <v>1</v>
@@ -5861,24 +5861,24 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>thietbibepan</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@thietbibepan/video/7659291275266379015</t>
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
@@ -5902,24 +5902,24 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>thietbibepan</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@thietbibepan/video/7659289222553111826</t>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5943,24 +5943,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>thietbibepan</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@thietbibepan/video/7659286717026913544</t>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -5984,24 +5984,24 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>thietbibepan</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@thietbibepan/video/7659283909045226760</t>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H136" t="n">
         <v>2</v>
@@ -6025,24 +6025,24 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>thietbibepan</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@thietbibepan/video/7659283167630871815</t>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H137" t="n">
         <v>1</v>
@@ -6066,24 +6066,24 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>thietbibepan</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@thietbibepan/video/7659281705160707346</t>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6107,24 +6107,24 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>t_tech.ninhbinh</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>t_tech.ninhbinh</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@t_tech.ninhbinh/video/7659317342760963348</t>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1451</v>
+        <v>2590</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -6148,24 +6148,24 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>tn.robot76</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>tn.robot76</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@tn.robot76/video/7659310908673576199</t>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
@@ -6189,12 +6189,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>thurobot88</t>
+          <t>longrobot_284</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6204,24 +6204,24 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thurobot88/video/7659313296910159125</t>
+          <t>https://www.tiktok.com/@longrobot_284/video/7659608650318761237</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>#Qrevo2Pro #Roborock #robothutbui</t>
+          <t>Lắp đặt combo Roborock F25 Ultra &amp; Qrevo 2 Pro cho khách | Nhà sạch tự động, lau sàn tiện hơn. #roborock #mayhutbuilaunha #robothutbuilaunha #f25ultra #qrevo2pro</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -6230,39 +6230,39 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>thurobot88</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@thurobot88/video/7657569311443422485</t>
+          <t>https://www.tiktok.com/@thurobot88/video/7659313296910159125</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Đập hộp #Qrevo2Pro #Roborock #robothutbui</t>
+          <t>#Qrevo2Pro #Roborock #robothutbui</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c r="H142" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
@@ -6271,12 +6271,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>phanthulan715</t>
+          <t>thurobot88</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6286,24 +6286,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phanthulan715/video/7659271674071665940</t>
+          <t>https://www.tiktok.com/@thurobot88/video/7657569311443422485</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chiến minh mới tầm trung nhà roborock lực hút cực khủng điểm 10 cho chất lượng #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
+          <t>Đập hộp #Qrevo2Pro #Roborock #robothutbui</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -6312,7 +6312,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6327,24 +6327,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@phanthulan715/video/7659237445623500053</t>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659616850015210772</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chọn đúng robot hút bụi lau nhà  không phải là đặt cược vào may mắn mà là đầu tư cho sự tiện nghi mỗi ngày  Roborock Qrevo 2 pro mang sự cân bằng giữ sức mạnh làm sạch công nghệ thông minh và khả năng tự động hoá vượt trội giúp việc chăm sóc ngôi nhà trở nên dễ dàng hơn #roborock #Qrevo2Pro #robothutbui #smarthomephutho #nhathongminh </t>
+          <t xml:space="preserve">Qrevo 2 Pro – Khi chuẩn sạch len lỏi đến từng góc nhà. ✨ 🔹 Lực hút HyperForce 25.000Pa mạnh mẽ, làm sạch hiệu quả bụi bẩn mỗi ngày. 🔹 Chổi cạnh đảo chiều kết hợp giẻ lau FlexiArm giúp tăng khả năng làm sạch góc và lau sát mép tường. 🔹 Reactive Tech nhận diện và tránh vật cản thông minh, cùng dock sạc đa năng tự giặt, sấy giẻ và rảnh tay lên đến 65 ngày. Một trợ thủ dọn dẹp toàn diện trong phân khúc tầm trung, giúp việc chăm sóc ngôi nhà trở nên nhẹ nhàng hơn mỗi ngày. #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="H144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -6353,80 +6353,80 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>momimart.vn</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@momimart.vn/video/7659398037382499605</t>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659431125873331476</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phiên bản mới của nhà Roborock không còn hình ảnh cứng cáp của dòng Qrevo seri trước đây#RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+          <t xml:space="preserve">Hãy để qrevo 2 pro chăn sóc ngôi nhà của bạn #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="H145" t="n">
         <v>2</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>bepphuthai</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bepphuthai/video/7659389488984067348</t>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659424913576480020</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>✨ CHƯƠNG TRÌNH TRẢI NGHIỆM TRƯỚC, MUA SAU - QREVO 2 PRO &amp; F25 ULTRA Những quyết định quan trọng nhất cho tổ ấm phải đến từ trải nghiệm thực tế. Từ 07.07.2026 - 31.07.2026, hãy ghé BẾP PHÚ THÁI để tự mình trải nghiệm bộ đôi siêu phẩm dọn dẹp siêu hot: Qrevo 2 Pro &amp; F25 Ultra. ✨ Qrevo 2 Pro: Dòng robot hút bụi mới ra mắt, sở hữu hiệu năng và công nghệ dẫn đầu tầm trung hiện nay, xử lý tốt việc lau dọn hàng ngày. ✨ F25 Ultra: Best seller dòng cầm tay, là mảnh ghép còn lại giúp bạn xử lý nhanh những nơi nhiều dầu mỡ, đồ ăn rơi vãi như khu vực bếp. Đặc quyền dành riêng cho khách hàng: 🚀 Mức giá ưu đãi khi trải nghiệm Qrevo 2 Pro 🚀 Nhận ngay combo quà tặng lên tới 14 sản phẩm 🚀 Trải nghiệm công nghệ mới hiện nay 🚀 Được tư vấn 1:1 giải pháp làm sạch phù hợp với cấu trúc nhà bạn Số lượng quà tặng có giới hạn. Hãy trở thành những người đầu tiên trải nghiệm và lựa chọn đúng sản phẩm cho ngôi nhà của mình! ___________ BẾP PHÚ THÁI 📍 : 262 Lê Thánh Tông P.Hạc Thành TP Thanh Hóa ☎️ : 0945.248.165 #Roborock 2pro</t>
+          <t>🏡 Một chiếc robot tốt không chỉ dọn sạch sàn mà còn giúp bạn bớt đi hàng loạt việc lặp lại. Qrevo 2 Pro làm được điều đó với lực hút mạnh, giẻ lau cải tiến, chống rối kép SGS và dock tự giặt sấy thông minh. Thảm luôn khô sạch nhờ tính năng tự tháo giẻ trước khi làm sạch. Trải nghiệm cao cấp giờ đã dễ tiếp cận hơn. #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh  --------- Smarthome Phú Thọ 🏠 Showroom: số 663, Nguyễn Du kéo dài, Phường Việt Trì, Tỉnh Phú Thọ</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
@@ -6435,39 +6435,39 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>robothutbuiductrong</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robothutbuiductrong/video/7659245802417671445</t>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659420670412983573</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">🌌 QREVO 2 PRO | SỨ MỆNH NÂNG TẦM SỨC MẠNH DỌN DẸP TẦM TRUNG CHÍNH THỨC CẤT CÁNH Roborock Qrevo 2 Pro xuất hiện như một cú phóng mới cho chuẩn sạch tầm trung.  🌪️ Một - Lực hút 25.000Pa đánh thức sức mạnh làm sạch toàn diện, cuốn gọn bụi mịn, tóc rụng và mảnh vụn trong từng lần di chuyển. 🌪️ Hai - Giẻ lau FlexiArm cùng chổi cạnh đảo chiều mở rộng giới hạn làm sạch, len sát mép tường, chạm đến những góc nhỏ thường bị bỏ quên. 🌪️ Ba - Hệ thống chống rối 3 lớp giúp hành trình vận hành mượt mà hơn, để tóc và lông thú không còn là lý do khiến bạn phải cúi xuống gỡ thủ công. 🌪️ Bốn - Dock tự giặt giẻ, sấy nóng 45°C và làm sạch khay giặt, giữ chu trình sau mỗi lần lau luôn khô thoáng, gọn gàng và an tâm. 🌪️ Năm - Khi gặp thảm, robot tự để giẻ lại dock, chỉ tập trung hút sạch mà không kéo ẩm lên bề mặt vải. Chuẩn sạch mới chính thức bắt đầu cùng Roborock Qrevo 2 Pro. #Roborock #RoborockVietnam   #Qrevo2Pro #Roborock #Robothutbui </t>
+          <t xml:space="preserve">✨ Siêu phẩm tầm trung mới Roborock Qrevo 2 Pro! ✅ Lực hút mạnh mẽ 25.000Pa đánh bay bụi bẩn hiệu quả ✅ Chổi cạnh xoay chiều giúp làm sạch sát mép, hạn chế bỏ sót ✅ Dock sạc đa năng hỗ trợ giặt và sấy giẻ tự động, giảm thiểu công việc thủ công 🔥 Nhanh tay đặt mua ngay để nhận mức giá ưu đãi hấp dẫn cùng COMBO 14 MÓN PHỤ KIỆN cực giá trị. #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -6476,80 +6476,80 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>robothutbuiductrong</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robothutbuiductrong/video/7657567801011473684</t>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659271674071665940</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>𝐐𝐫𝐞𝐯𝐨 𝟐 𝐏𝐫𝐨  👉Lực hút HyperForce: 25.000 Pa 👉Chổi cạnh đảo chiều: Tăng 30% diện tích phủ góc so với chổi cạnh cố định thông thường 👉Giẻ lau cạnh FlexiArm vươn ra sát tường 👉Hệ thống giẻ lau xoay kép 👉Dock sạc đa năng - tự làm sạch bệ giặt giẻ #Qrevo2Pro #Roborock #RobotLauNha #RobotDucTrong</t>
+          <t xml:space="preserve">Chiến minh mới tầm trung nhà roborock lực hút cực khủng điểm 10 cho chất lượng #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="H148" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>robothutbuiductrong</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robothutbuiductrong/video/7657349734994038037</t>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659237445623500053</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Siêu phẩm dọn nhà thế hệ mới Roborock Qrevo 2 Pro! 🖤 Gôm trọn công nghệ đỉnh: 👉 Lực hút khủng 25.000 Pa 👉 Lau sát cạnh 1.85mm,  👉 Chổi cạnh đảo chiều sạch 100% góc chết và AI SmartPlan 3.0 tự tối ưu phòng. Giá cực tốt cho những vị khách đầu tiên, inbox em tư vấn liền tay nhé ạ! 💞 #Roborock #Qrevo2Pro #RobotLauNha #RobotDucTrong #RobotHutBuiLauNha</t>
+          <t xml:space="preserve">Chọn đúng robot hút bụi lau nhà  không phải là đặt cược vào may mắn mà là đầu tư cho sự tiện nghi mỗi ngày  Roborock Qrevo 2 pro mang sự cân bằng giữ sức mạnh làm sạch công nghệ thông minh và khả năng tự động hoá vượt trội giúp việc chăm sóc ngôi nhà trở nên dễ dàng hơn #roborock #Qrevo2Pro #robothutbui #smarthomephutho #nhathongminh </t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>366</v>
+        <v>146</v>
       </c>
       <c r="H149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
@@ -6558,12 +6558,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>robothutbuiductrong</t>
+          <t>bothome_robotgialai</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6573,24 +6573,24 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robothutbuiductrong/video/7656613783372074261</t>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7659620121916230919</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>🏡✨ Ngoài việc tránh tiếp xúc trực tiếp với nước, robot hút bụi lau nhà Roborock Qrevo 2 Pro tự tin cân trọn hầu hết nhu cầu dọn dẹp trong nhà đấy! 🤖 Thế nên, bụi mịn, tóc rụng, lông thú, khe góc hay thảm trải sàn, cứ giao "em" xử lý. 😚 #Roborock #RoborockVietnam #docongnghe#docovo2Pro #robothutbui</t>
+          <t xml:space="preserve">20 Cù Chính Lan, Pleiku, Gia Lai  0905 095 168 - 0969 960 963  #Qrevo2Pro  #Roborock  #robothutbui  #robothutbuiGiaLai </t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -6599,39 +6599,39 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>robothutbuiductrong</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robothutbuiductrong/video/7656233166637731093</t>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7659431407030160648</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loanh quanh 13 🍠 - ra mắt tặng thêm rất nhiều 🎁 ✅Lực hút cực mạnh - giá tầm trung ✅Có chổi ven đảo chiều  ✅Có bệ tự vệ sinh  Đừng chần chừ gì nữa mà ib em tư vấn ngay nhé 👌#mytechfavs #qrevo2pro #roborock #robotductrong #test </t>
+          <t>Siêu phẩm mới nhà Roborock #Qrevo2Pro #Roborock #robothutbui</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>252</v>
+        <v>362</v>
       </c>
       <c r="H151" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I151" t="n">
         <v>0</v>
@@ -6640,39 +6640,39 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>robothutbuiductrong</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@robothutbuiductrong/video/7655621454356057365</t>
+          <t>https://www.tiktok.com/@momimart.vn/video/7659398037382499605</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅Qrevo 2 Pro - Vừa mở bán đã hot hit điên đảo các bác ơi.  🎉Model 2026 với phân khúc giá chỉ loanh quanh 13 triệu thì em này xứng đáng mua nha 👉 Lực hút 25,000Pa (ngang ngửa với dòng cao cấp Qrevo Edge 2 luôn nè)🥹 👉 Giẻ xoè được sát tường, chổi thì xoay đảo chiều - khay giặt tự vệ sinh làm sạch như Edge2 👉 Có cả tính năng tự vệ sinh bệ giặt luôn nhé 👌 ... ❤️Quá hời để hốt về đó ạ.  💰💰💰Giá đang ưu đãi vì ra mắt sản phẩm mới của nhà Roborock nên KH hãy mua nhanhhhhh nhanhhh lên nha.  🏡 H&amp;T Smart Home Đức Trọng - 384 Thống Nhất ☎️ 0988607072 #Qrevo2Pro #2Pro #roborock #robotductrong #robotlaunhaductrong </t>
+          <t xml:space="preserve">Phiên bản mới của nhà Roborock không còn hình ảnh cứng cáp của dòng Qrevo seri trước đây#RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="H152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
@@ -6681,39 +6681,39 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>bepphuthai</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>domotekvietnam</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@domotekvietnam/video/7659412665927896328</t>
+          <t>https://www.tiktok.com/@bepphuthai/video/7659389488984067348</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7/7-31/7 có gì tại Domotek Việt Nam  #Qrevo2Pro #Roborock #Robothutbui #DomotekVietNam #đungdongvaianh </t>
+          <t>✨ CHƯƠNG TRÌNH TRẢI NGHIỆM TRƯỚC, MUA SAU - QREVO 2 PRO &amp; F25 ULTRA Những quyết định quan trọng nhất cho tổ ấm phải đến từ trải nghiệm thực tế. Từ 07.07.2026 - 31.07.2026, hãy ghé BẾP PHÚ THÁI để tự mình trải nghiệm bộ đôi siêu phẩm dọn dẹp siêu hot: Qrevo 2 Pro &amp; F25 Ultra. ✨ Qrevo 2 Pro: Dòng robot hút bụi mới ra mắt, sở hữu hiệu năng và công nghệ dẫn đầu tầm trung hiện nay, xử lý tốt việc lau dọn hàng ngày. ✨ F25 Ultra: Best seller dòng cầm tay, là mảnh ghép còn lại giúp bạn xử lý nhanh những nơi nhiều dầu mỡ, đồ ăn rơi vãi như khu vực bếp. Đặc quyền dành riêng cho khách hàng: 🚀 Mức giá ưu đãi khi trải nghiệm Qrevo 2 Pro 🚀 Nhận ngay combo quà tặng lên tới 14 sản phẩm 🚀 Trải nghiệm công nghệ mới hiện nay 🚀 Được tư vấn 1:1 giải pháp làm sạch phù hợp với cấu trúc nhà bạn Số lượng quà tặng có giới hạn. Hãy trở thành những người đầu tiên trải nghiệm và lựa chọn đúng sản phẩm cho ngôi nhà của mình! ___________ BẾP PHÚ THÁI 📍 : 262 Lê Thánh Tông P.Hạc Thành TP Thanh Hóa ☎️ : 0945.248.165 #Roborock 2pro</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
@@ -6722,36 +6722,36 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>domotekvietnam</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@domotekvietnam/video/7658694688303533320</t>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7659245802417671445</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Với Domotek Việt Nam, bán hàng chỉ là khởi đầu – đồng hành và hỗ trợ khách hàng mới là cam kết lâu dài. Tận tâm trước, trong và sau bán, để mỗi sản phẩm đến tay khách đều mang lại sự an tâm tuyệt đối. #DomotekVietNam #DichVuKhachHang #RobotHutBui #ChamSocKhachHang #qrevo2pro </t>
+          <t xml:space="preserve">🌌 QREVO 2 PRO | SỨ MỆNH NÂNG TẦM SỨC MẠNH DỌN DẸP TẦM TRUNG CHÍNH THỨC CẤT CÁNH Roborock Qrevo 2 Pro xuất hiện như một cú phóng mới cho chuẩn sạch tầm trung.  🌪️ Một - Lực hút 25.000Pa đánh thức sức mạnh làm sạch toàn diện, cuốn gọn bụi mịn, tóc rụng và mảnh vụn trong từng lần di chuyển. 🌪️ Hai - Giẻ lau FlexiArm cùng chổi cạnh đảo chiều mở rộng giới hạn làm sạch, len sát mép tường, chạm đến những góc nhỏ thường bị bỏ quên. 🌪️ Ba - Hệ thống chống rối 3 lớp giúp hành trình vận hành mượt mà hơn, để tóc và lông thú không còn là lý do khiến bạn phải cúi xuống gỡ thủ công. 🌪️ Bốn - Dock tự giặt giẻ, sấy nóng 45°C và làm sạch khay giặt, giữ chu trình sau mỗi lần lau luôn khô thoáng, gọn gàng và an tâm. 🌪️ Năm - Khi gặp thảm, robot tự để giẻ lại dock, chỉ tập trung hút sạch mà không kéo ẩm lên bề mặt vải. Chuẩn sạch mới chính thức bắt đầu cùng Roborock Qrevo 2 Pro. #Roborock #RoborockVietnam   #Qrevo2Pro #Roborock #Robothutbui </t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6763,12 +6763,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>domotekvietnam</t>
+          <t>robothutbuiductrong</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6778,67 +6778,354 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@domotekvietnam/video/7658306093189385480</t>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7657567801011473684</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Trải nghiệm trước mua sau cùng Roborock Qrevo 2 Pro và F25ultra #F25UItra #RoborockQrevo2Pro #DomotekVietnam #TraiNghiemTruocMuaSau #RobotHutBuiThongMinh</t>
+          <t>𝐐𝐫𝐞𝐯𝐨 𝟐 𝐏𝐫𝐨  👉Lực hút HyperForce: 25.000 Pa 👉Chổi cạnh đảo chiều: Tăng 30% diện tích phủ góc so với chổi cạnh cố định thông thường 👉Giẻ lau cạnh FlexiArm vươn ra sát tường 👉Hệ thống giẻ lau xoay kép 👉Dock sạc đa năng - tự làm sạch bệ giặt giẻ #Qrevo2Pro #Roborock #RobotLauNha #RobotDucTrong</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H155" t="n">
+        <v>4</v>
+      </c>
+      <c r="I155" t="n">
         <v>2</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7657349734994038037</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Siêu phẩm dọn nhà thế hệ mới Roborock Qrevo 2 Pro! 🖤 Gôm trọn công nghệ đỉnh: 👉 Lực hút khủng 25.000 Pa 👉 Lau sát cạnh 1.85mm,  👉 Chổi cạnh đảo chiều sạch 100% góc chết và AI SmartPlan 3.0 tự tối ưu phòng. Giá cực tốt cho những vị khách đầu tiên, inbox em tư vấn liền tay nhé ạ! 💞 #Roborock #Qrevo2Pro #RobotLauNha #RobotDucTrong #RobotHutBuiLauNha</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>367</v>
+      </c>
+      <c r="H156" t="n">
+        <v>3</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7656613783372074261</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>🏡✨ Ngoài việc tránh tiếp xúc trực tiếp với nước, robot hút bụi lau nhà Roborock Qrevo 2 Pro tự tin cân trọn hầu hết nhu cầu dọn dẹp trong nhà đấy! 🤖 Thế nên, bụi mịn, tóc rụng, lông thú, khe góc hay thảm trải sàn, cứ giao "em" xử lý. 😚 #Roborock #RoborockVietnam #docongnghe#docovo2Pro #robothutbui</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>113</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7656233166637731093</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loanh quanh 13 🍠 - ra mắt tặng thêm rất nhiều 🎁 ✅Lực hút cực mạnh - giá tầm trung ✅Có chổi ven đảo chiều  ✅Có bệ tự vệ sinh  Đừng chần chừ gì nữa mà ib em tư vấn ngay nhé 👌#mytechfavs #qrevo2pro #roborock #robotductrong #test </t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>257</v>
+      </c>
+      <c r="H158" t="n">
+        <v>5</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7655621454356057365</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✅Qrevo 2 Pro - Vừa mở bán đã hot hit điên đảo các bác ơi.  🎉Model 2026 với phân khúc giá chỉ loanh quanh 13 triệu thì em này xứng đáng mua nha 👉 Lực hút 25,000Pa (ngang ngửa với dòng cao cấp Qrevo Edge 2 luôn nè)🥹 👉 Giẻ xoè được sát tường, chổi thì xoay đảo chiều - khay giặt tự vệ sinh làm sạch như Edge2 👉 Có cả tính năng tự vệ sinh bệ giặt luôn nhé 👌 ... ❤️Quá hời để hốt về đó ạ.  💰💰💰Giá đang ưu đãi vì ra mắt sản phẩm mới của nhà Roborock nên KH hãy mua nhanhhhhh nhanhhh lên nha.  🏡 H&amp;T Smart Home Đức Trọng - 384 Thống Nhất ☎️ 0988607072 #Qrevo2Pro #2Pro #roborock #robotductrong #robotlaunhaductrong </t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>147</v>
+      </c>
+      <c r="H159" t="n">
+        <v>3</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>domotekvietnam</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@domotekvietnam/video/7659412665927896328</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7/7-31/7 có gì tại Domotek Việt Nam  #Qrevo2Pro #Roborock #Robothutbui #DomotekVietNam #đungdongvaianh </t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>101</v>
+      </c>
+      <c r="H160" t="n">
+        <v>5</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
         <is>
           <t>domotekvietnam</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@domotekvietnam/video/7658694688303533320</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Với Domotek Việt Nam, bán hàng chỉ là khởi đầu – đồng hành và hỗ trợ khách hàng mới là cam kết lâu dài. Tận tâm trước, trong và sau bán, để mỗi sản phẩm đến tay khách đều mang lại sự an tâm tuyệt đối. #DomotekVietNam #DichVuKhachHang #RobotHutBui #ChamSocKhachHang #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>123</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>domotekvietnam</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@domotekvietnam/video/7658306093189385480</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Trải nghiệm trước mua sau cùng Roborock Qrevo 2 Pro và F25ultra #F25UItra #RoborockQrevo2Pro #DomotekVietnam #TraiNghiemTruocMuaSau #RobotHutBuiThongMinh</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>124</v>
+      </c>
+      <c r="H162" t="n">
+        <v>2</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>domotekvietnam</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@domotekvietnam/video/7655242449303948562</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t xml:space="preserve">📦 Unboxing siêu phẩm **Roborock Qrevo 2 Pro** 🔥 #DomotekVietNam #Roborock #Unbox #Unboxing #xuhuong   </t>
         </is>
       </c>
-      <c r="G156" t="n">
-        <v>155</v>
-      </c>
-      <c r="H156" t="n">
+      <c r="G163" t="n">
+        <v>157</v>
+      </c>
+      <c r="H163" t="n">
         <v>4</v>
       </c>
-      <c r="I156" t="n">
+      <c r="I163" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="videos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="videos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -908,7 +908,7 @@
         <v>159</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H14" t="n">
         <v>29</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H16" t="n">
         <v>8</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H20" t="n">
         <v>11</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1183</v>
+        <v>5175</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1537</v>
+        <v>3362</v>
       </c>
       <c r="H24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>659</v>
+        <v>758</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>335</v>
+        <v>386</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="H27" t="n">
         <v>9</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="H29" t="n">
         <v>7</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="H31" t="n">
         <v>7</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H36" t="n">
         <v>3</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H37" t="n">
         <v>4</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H39" t="n">
         <v>7</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="H40" t="n">
         <v>3</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="H46" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I46" t="n">
         <v>8</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H47" t="n">
         <v>13</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="H48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H51" t="n">
         <v>6</v>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H52" t="n">
         <v>7</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H54" t="n">
         <v>12</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H58" t="n">
         <v>2</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H59" t="n">
         <v>2</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H61" t="n">
         <v>3</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1120</v>
+        <v>1145</v>
       </c>
       <c r="H65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>669</v>
+        <v>692</v>
       </c>
       <c r="H66" t="n">
         <v>32</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>63000</v>
+        <v>68500</v>
       </c>
       <c r="H78" t="n">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="I78" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79">
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H84" t="n">
         <v>3</v>
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H86" t="n">
         <v>4</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1183</v>
+        <v>1386</v>
       </c>
       <c r="H87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I87" t="n">
         <v>3</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H91" t="n">
         <v>4</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H93" t="n">
         <v>8</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="H95" t="n">
         <v>7</v>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H97" t="n">
         <v>1</v>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H100" t="n">
         <v>5</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2810</v>
+        <v>4753</v>
       </c>
       <c r="H108" t="n">
+        <v>13</v>
+      </c>
+      <c r="I108" t="n">
         <v>11</v>
-      </c>
-      <c r="I108" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="109">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1582</v>
+        <v>1712</v>
       </c>
       <c r="H109" t="n">
         <v>560</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H113" t="n">
         <v>2</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>111300</v>
+        <v>188700</v>
       </c>
       <c r="H116" t="n">
-        <v>672</v>
+        <v>1244</v>
       </c>
       <c r="I116" t="n">
-        <v>112</v>
+        <v>167</v>
       </c>
     </row>
     <row r="117">
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H117" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H118" t="n">
         <v>2</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="H122" t="n">
         <v>3</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1684</v>
+        <v>1723</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>751</v>
+        <v>768</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="H126" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I126" t="n">
         <v>3</v>
@@ -5644,10 +5644,10 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="H127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H128" t="n">
         <v>3</v>
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H132" t="n">
         <v>1</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="H136" t="n">
         <v>2</v>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H137" t="n">
         <v>1</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,10 +6218,10 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="H141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H143" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="H144" t="n">
         <v>2</v>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H145" t="n">
         <v>2</v>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H146" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H148" t="n">
         <v>1</v>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H149" t="n">
         <v>4</v>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>17</v>
+        <v>260</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="H151" t="n">
         <v>4</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>180</v>
+        <v>299</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="H153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H159" t="n">
         <v>3</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H160" t="n">
         <v>5</v>
@@ -7126,6 +7126,826 @@
         <v>4</v>
       </c>
       <c r="I163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>homesmediant99</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homesmediant99/video/7659607622709939464</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có Qrevo 2 pro không gì là không thể💪💪 Bụi bẩn ư🤔 Chuyện nhỏ luôn☝️☝️#roborock #Qrevo2pro #robothutbui </t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>111</v>
+      </c>
+      <c r="H164" t="n">
+        <v>2</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>homesmediant99</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homesmediant99/video/7659371144524467463</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Roborock #Qrevo2pro#robothutbui </t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>94</v>
+      </c>
+      <c r="H165" t="n">
+        <v>2</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>homesmediant99</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homesmediant99/video/7658504980025920776</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot Roborock qrevo 2 pro có gì??🤔 Cùng xem nhé #RoborockMediaHomesNhaTrang #roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>111</v>
+      </c>
+      <c r="H166" t="n">
+        <v>3</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>homesmediant99</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homesmediant99/video/7658501309468773639</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khắc tinh của bụi bẩn 🤩#roborock #qrevo2pro #RoborockMediaHomesNhaTrang </t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>119</v>
+      </c>
+      <c r="H167" t="n">
+        <v>4</v>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>tm.anh.kitchen.qu</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tm.anh.kitchen.qu/video/7659638627168685319</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Roborock Qrevo 2 Pro đã chính thức mở bán từ ngày hôm nay tại Tâm Anh Kitchen 44 Tôn Thất Thuyết Quảng Trị 🫶🏻  #bepquangtri #Roborock #robockvietnam #Qrevo2Pro</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>399</v>
+      </c>
+      <c r="H168" t="n">
+        <v>7</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>mivietnam_chuyengiarobot</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mivietnam_chuyengiarobot/video/7659726057729182996</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>khi ngủ 8 tiếng trong 2 tiếng kiểu #mivietnam #Roborock #Qrevo2Pro #Robothutbui #fyp</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>277</v>
+      </c>
+      <c r="H169" t="n">
+        <v>6</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>quyrobot</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@quyrobot/video/7659730708952288520</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Qrevo 2 pro trắng đẹp lắm nhé quý vị, tầm giá hơn 13củ thì quá hợp lý rồi ạh #quyrobot #qrevo2pro #robothutbui #roborock</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>38</v>
+      </c>
+      <c r="H170" t="n">
+        <v>2</v>
+      </c>
+      <c r="I170" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>quyrobot</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@quyrobot/video/7659717455098465543</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 pro 2026 màu trắng cực đẹp ace nhé, tin tôi đi🫶🫶 #quyrobot #Roborock #qrevo2pro #robothutbui </t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>47</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659734334227631380</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hãy sờ tận tay nhìn tận mắt để thấy em nó đáng mua cỡ nào #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>35</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659712793259543829</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mời quý vị ghé QUÝ ROBOT để trải nghiệm 2 mã sảnn phẩmm hót hít nhất 2026 ạ. 🤩 #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>52</v>
+      </c>
+      <c r="H173" t="n">
+        <v>2</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659711497689468181</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tính năng hay thế này chỉ có thể là #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>51</v>
+      </c>
+      <c r="H174" t="n">
+        <v>2</v>
+      </c>
+      <c r="I174" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659710504775978260</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mê quá các bác ơi #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>2</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659710008883531028</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mời quý vị #Qrevo2pro #robothutbui #roborock #nghiennha #quyrobot </t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>52</v>
+      </c>
+      <c r="H176" t="n">
+        <v>2</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659708092464008468</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chạy sạch cỡ này không mua không đc quý vị ơi #Qrevo2pro #robothutbui #roborock #quyrobot #nghiennha </t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>53</v>
+      </c>
+      <c r="H177" t="n">
+        <v>2</v>
+      </c>
+      <c r="I177" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7659707318879128839</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghé BOT Home, Trải nghiệm miễn phí sản phấm mới nhà Roborock #Qrevo2Pro  #Roborock  #robothutbui  </t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>64</v>
+      </c>
+      <c r="H178" t="n">
+        <v>4</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>ecomi.vn.roborock</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ecomi.vn.roborock/video/7659670243274411271</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>#Qrevo2Pro #Roborock #Robothutbui #RoborockVn</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>86</v>
+      </c>
+      <c r="H179" t="n">
+        <v>2</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ecomi.vn.roborock</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@ecomi.vn.roborock/video/7659669443374484743</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>#Qrevo2Pro #Roborock #Robothutbui #RoborockVn</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>90</v>
+      </c>
+      <c r="H180" t="n">
+        <v>2</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7659740024879009031</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🎁 Mở bán robot Qrevo 2 Pro roborock đỉnh cao lực hút, giá chỉ tầm trung tại Xiaomi Phú Thọ 🚘 Các bác qua 05 Nguyễn Du, Nông Trang, Việt Trì, Phú Thọ #qrevo2pro #roborock #robothutbui #robotlaunha #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>46</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7656709011747654930</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot cao cấp hơn 20tr thì chỉ là cái tên sau khi Qrevo 2 pro ra mắt 🙈 Hàng sẵn tại shop cho A/C trải nghiệm muốn lấy luôn ạ 🥰 Số 05 Nguyễn Du, Nông Trang, Việt Trì ạ  #roborock #robotlaunha #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>484</v>
+      </c>
+      <c r="H182" t="n">
+        <v>11</v>
+      </c>
+      <c r="I182" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7655314935366438162</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đế chế robot ra mắt bản Qrevo 2 pro cực đỉnh giá chỉ hơn 12 đồng bảo hành tại nhà luôn ạ  #roborock #robotlaunha #roborockqrevo </t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>347</v>
+      </c>
+      <c r="H183" t="n">
+        <v>7</v>
+      </c>
+      <c r="I183" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="videos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="videos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I183"/>
+  <dimension ref="A1:I192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="H14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -1031,7 +1031,7 @@
         <v>151</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>183</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5175</v>
+        <v>13600</v>
       </c>
       <c r="H23" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3362</v>
+        <v>9150</v>
       </c>
       <c r="H24" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>758</v>
+        <v>869</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>390</v>
+        <v>429</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="H31" t="n">
         <v>7</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H36" t="n">
         <v>3</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H37" t="n">
         <v>4</v>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H38" t="n">
         <v>5</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H39" t="n">
         <v>7</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="H40" t="n">
         <v>3</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="H46" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I46" t="n">
         <v>8</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="H47" t="n">
         <v>13</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H48" t="n">
         <v>12</v>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="H49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I49" t="n">
         <v>3</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1129</v>
+        <v>1141</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H54" t="n">
         <v>12</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H58" t="n">
         <v>2</v>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H64" t="n">
         <v>4</v>
@@ -3102,13 +3102,13 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1145</v>
+        <v>1201</v>
       </c>
       <c r="H65" t="n">
         <v>12</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="H66" t="n">
         <v>32</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H71" t="n">
         <v>6</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>68500</v>
+        <v>72000</v>
       </c>
       <c r="H78" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="I78" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79">
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H86" t="n">
         <v>4</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1386</v>
+        <v>1586</v>
       </c>
       <c r="H87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I87" t="n">
         <v>3</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H88" t="n">
         <v>2</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H89" t="n">
         <v>2</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="H95" t="n">
         <v>7</v>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H100" t="n">
         <v>5</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H103" t="n">
         <v>6</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H104" t="n">
         <v>2</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>4753</v>
+        <v>6416</v>
       </c>
       <c r="H108" t="n">
+        <v>21</v>
+      </c>
+      <c r="I108" t="n">
         <v>13</v>
-      </c>
-      <c r="I108" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="109">
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1712</v>
+        <v>2011</v>
       </c>
       <c r="H109" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="I109" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H113" t="n">
         <v>2</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>188700</v>
+        <v>254200</v>
       </c>
       <c r="H116" t="n">
-        <v>1244</v>
+        <v>1688</v>
       </c>
       <c r="I116" t="n">
-        <v>167</v>
+        <v>223</v>
       </c>
     </row>
     <row r="117">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H118" t="n">
         <v>2</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1723</v>
+        <v>1754</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>768</v>
+        <v>787</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H126" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I126" t="n">
         <v>3</v>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H127" t="n">
         <v>5</v>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H128" t="n">
         <v>3</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H136" t="n">
         <v>2</v>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H137" t="n">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,10 +6218,10 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="H141" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H143" t="n">
         <v>10</v>
@@ -6341,13 +6341,13 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="H144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H145" t="n">
         <v>2</v>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H146" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
@@ -6464,13 +6464,13 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I148" t="n">
         <v>0</v>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>260</v>
+        <v>379</v>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="H151" t="n">
         <v>4</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H153" t="n">
         <v>3</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H155" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I155" t="n">
         <v>2</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H159" t="n">
         <v>3</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H160" t="n">
         <v>5</v>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H162" t="n">
         <v>2</v>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="H164" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -7202,13 +7202,13 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H167" t="n">
         <v>4</v>
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>399</v>
+        <v>458</v>
       </c>
       <c r="H168" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>277</v>
+        <v>375</v>
       </c>
       <c r="H169" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="H170" t="n">
         <v>2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
@@ -7480,22 +7480,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659734334227631380</t>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659776166856822036</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hãy sờ tận tay nhìn tận mắt để thấy em nó đáng mua cỡ nào #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+          <t xml:space="preserve">Qua QUÝ ROBOT TRẢI NGHIỆM SP #Qrevo2pro #robothutbui #roborock #xuhuongtiktok #quyrobot </t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="H172" t="n">
         <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -7521,22 +7521,22 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659712793259543829</t>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659734334227631380</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mời quý vị ghé QUÝ ROBOT để trải nghiệm 2 mã sảnn phẩmm hót hít nhất 2026 ạ. 🤩 #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+          <t xml:space="preserve">Hãy sờ tận tay nhìn tận mắt để thấy em nó đáng mua cỡ nào #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="H173" t="n">
         <v>2</v>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659711497689468181</t>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659712793259543829</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tính năng hay thế này chỉ có thể là #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+          <t xml:space="preserve">Mời quý vị ghé QUÝ ROBOT để trải nghiệm 2 mã sảnn phẩmm hót hít nhất 2026 ạ. 🤩 #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="H174" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -7603,22 +7603,22 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659710504775978260</t>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659711497689468181</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mê quá các bác ơi #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+          <t xml:space="preserve">Tính năng hay thế này chỉ có thể là #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="H175" t="n">
         <v>2</v>
       </c>
       <c r="I175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -7644,16 +7644,16 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659710008883531028</t>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659710504775978260</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mời quý vị #Qrevo2pro #robothutbui #roborock #nghiennha #quyrobot </t>
+          <t xml:space="preserve">Mê quá các bác ơi #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="H176" t="n">
         <v>2</v>
@@ -7685,22 +7685,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659708092464008468</t>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659710008883531028</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chạy sạch cỡ này không mua không đc quý vị ơi #Qrevo2pro #robothutbui #roborock #quyrobot #nghiennha </t>
+          <t xml:space="preserve">Mời quý vị #Qrevo2pro #robothutbui #roborock #nghiennha #quyrobot </t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="H177" t="n">
         <v>2</v>
       </c>
       <c r="I177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>bothome_robotgialai</t>
+          <t>nc.nh.qu.robot</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -7726,22 +7726,22 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@bothome_robotgialai/video/7659707318879128839</t>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659708092464008468</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ghé BOT Home, Trải nghiệm miễn phí sản phấm mới nhà Roborock #Qrevo2Pro  #Roborock  #robothutbui  </t>
+          <t xml:space="preserve">Chạy sạch cỡ này không mua không đc quý vị ơi #Qrevo2pro #robothutbui #roborock #quyrobot #nghiennha </t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="H178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ecomi.vn.roborock</t>
+          <t>bothome_robotgialai</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7767,19 +7767,19 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ecomi.vn.roborock/video/7659670243274411271</t>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7659707318879128839</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>#Qrevo2Pro #Roborock #Robothutbui #RoborockVn</t>
+          <t xml:space="preserve">Ghé BOT Home, Trải nghiệm miễn phí sản phấm mới nhà Roborock #Qrevo2Pro  #Roborock  #robothutbui  </t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>86</v>
+        <v>382</v>
       </c>
       <c r="H179" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@ecomi.vn.roborock/video/7659669443374484743</t>
+          <t>https://www.tiktok.com/@ecomi.vn.roborock/video/7659670243274411271</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="H180" t="n">
         <v>2</v>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>xiaomi.phu.tho</t>
+          <t>ecomi.vn.roborock</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7849,19 +7849,19 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7659740024879009031</t>
+          <t>https://www.tiktok.com/@ecomi.vn.roborock/video/7659669443374484743</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">🎁 Mở bán robot Qrevo 2 Pro roborock đỉnh cao lực hút, giá chỉ tầm trung tại Xiaomi Phú Thọ 🚘 Các bác qua 05 Nguyễn Du, Nông Trang, Việt Trì, Phú Thọ #qrevo2pro #roborock #robothutbui #robotlaunha #xiaomiphutho </t>
+          <t>#Qrevo2Pro #Roborock #Robothutbui #RoborockVn</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="H181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>xiaomi.phu.tho</t>
+          <t>roborock.smart.li</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7885,67 +7885,436 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7656709011747654930</t>
+          <t>https://www.tiktok.com/@roborock.smart.li/video/7659770145505578260</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robot cao cấp hơn 20tr thì chỉ là cái tên sau khi Qrevo 2 pro ra mắt 🙈 Hàng sẵn tại shop cho A/C trải nghiệm muốn lấy luôn ạ 🥰 Số 05 Nguyễn Du, Nông Trang, Việt Trì ạ  #roborock #robotlaunha #qrevo2pro </t>
+          <t>#QRevo2Pro #Roborock #RoborockVN</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>484</v>
+        <v>225</v>
       </c>
       <c r="H182" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7660035263992827156</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hot hot 🔥 Roborock Qrevo 2 Pro - Mới nhất #mistorebienhoa #roborock #qrevo2pro #robothutbui </t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>11</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659970700031085845</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qua em trải nghiệm thực tế sản phẩm robot hút bụi lau nhà nha các bác #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>70</v>
+      </c>
+      <c r="H184" t="n">
+        <v>5</v>
+      </c>
+      <c r="I184" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659923695204420884</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có gì nổi bật ở chiến thần Qrevo 2 Pro #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>96</v>
+      </c>
+      <c r="H185" t="n">
+        <v>6</v>
+      </c>
+      <c r="I185" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659798411520298260</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Còn băn khoăn nên chọn dòng robot nào cho nhà mình thì các bác ghé qua Smarthome Phú Thọ em tư vấn nha #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>133</v>
+      </c>
+      <c r="H186" t="n">
+        <v>7</v>
+      </c>
+      <c r="I186" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7659790627864907028</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🔥 TRẢI NGHIỆM TRƯỚC, MUA SAU – CHỐT SIÊU PHẨM NHẬN QUÀ KHỦNG NGAY HÔM NAY! Trực tiếp trải nghiệm và rinh bộ đôi dọn dẹp nhà cửa hot nhất hiện nay: Qrevo 2 Pro &amp; F25 Ultra với chương trình cực kỳ hấp dẫn. ✨ Qrevo 2 Pro: Robot hút bụi mới ra mắt, sở hữu hàng loạt cải tiến công nghệ ấn tượng trong phân khúc tầm trung, để giữ nhà sạch, bạn luôn rảnh tay. ✨ F25 Ultra: Dòng máy lau sàn "best-seller" giúp bạn giải quyết nhanh gọn các sự cố bất chợt, vết bẩn bết dính hay dầu mỡ cứng đầu trong tích tắc 💥 ĐẶC QUYỀN CHỈ ÁP DỤNG TỪ 07.07.2026 - 31.07.2026: Giá trải nghiệm Qrevo 2 Pro: Chỉ còn 13.490.000đ Combo quà tặng độc quyền: Nhận ngay bộ phụ kiện lên tới 14 sản phẩm tiện ích đi kèm khi chốt đơn thành công Hỗ trợ chuyên sâu: Tư vấn giải pháp dọn dẹp và hướng dẫn 1:1 trực tiếp Mắt thấy, tai nghe, tay chạm thực tế để chọn đúng trợ thủ thông minh cho gia đình mình. 👉Số lượng quà tặng có hạn! Ghé ngay cửa hàng hôm nay để không bỏ lỡ nhé! ___________ SMARTHOME PHÚ THỌ #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>153</v>
+      </c>
+      <c r="H187" t="n">
+        <v>9</v>
+      </c>
+      <c r="I187" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7659976937284062485</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mời quý vị #Qrevo2pro #robothutbui #roborock #xuhuongtiktok #quyrobot </t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>6</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7659991460531408136</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 Pro: Phân khúc tầm trung, mẫu mới, công nghệ mới, nhưng giá vẫn cực hấp dẫn. Sẵn tại 20 Cù Chính Lan, Pleiku #Qrevo2Pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>47</v>
+      </c>
+      <c r="H189" t="n">
+        <v>1</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
         <is>
           <t>xiaomi.phu.tho</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>qrevo 2 pro</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7659740024879009031</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🎁 Mở bán robot Qrevo 2 Pro roborock đỉnh cao lực hút, giá chỉ tầm trung tại Xiaomi Phú Thọ 🚘 Các bác qua 05 Nguyễn Du, Nông Trang, Việt Trì, Phú Thọ #qrevo2pro #roborock #robothutbui #robotlaunha #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>172</v>
+      </c>
+      <c r="H190" t="n">
+        <v>4</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7656709011747654930</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot cao cấp hơn 20tr thì chỉ là cái tên sau khi Qrevo 2 pro ra mắt 🙈 Hàng sẵn tại shop cho A/C trải nghiệm muốn lấy luôn ạ 🥰 Số 05 Nguyễn Du, Nông Trang, Việt Trì ạ  #roborock #robotlaunha #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>487</v>
+      </c>
+      <c r="H191" t="n">
+        <v>11</v>
+      </c>
+      <c r="I191" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7655314935366438162</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F192" t="inlineStr">
         <is>
           <t xml:space="preserve">Đế chế robot ra mắt bản Qrevo 2 pro cực đỉnh giá chỉ hơn 12 đồng bảo hành tại nhà luôn ạ  #roborock #robotlaunha #roborockqrevo </t>
         </is>
       </c>
-      <c r="G183" t="n">
-        <v>347</v>
-      </c>
-      <c r="H183" t="n">
+      <c r="G192" t="n">
+        <v>350</v>
+      </c>
+      <c r="H192" t="n">
         <v>7</v>
       </c>
-      <c r="I183" t="n">
+      <c r="I192" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="videos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="videos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I192"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H13" t="n">
         <v>11</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="H14" t="n">
         <v>30</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H16" t="n">
         <v>9</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>13600</v>
+        <v>20700</v>
       </c>
       <c r="H23" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>9150</v>
+        <v>9880</v>
       </c>
       <c r="H24" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>869</v>
+        <v>910</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="H29" t="n">
         <v>8</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H38" t="n">
         <v>5</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H40" t="n">
         <v>3</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H46" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I46" t="n">
         <v>8</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H47" t="n">
         <v>13</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="H49" t="n">
         <v>22</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H51" t="n">
         <v>6</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H58" t="n">
         <v>2</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H59" t="n">
         <v>3</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H61" t="n">
         <v>3</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1201</v>
+        <v>1220</v>
       </c>
       <c r="H65" t="n">
         <v>12</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="H66" t="n">
         <v>32</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H71" t="n">
         <v>6</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H73" t="n">
         <v>3</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H77" t="n">
         <v>5</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>72000</v>
+        <v>73400</v>
       </c>
       <c r="H78" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="I78" t="n">
         <v>71</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H83" t="n">
         <v>5</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1586</v>
+        <v>1641</v>
       </c>
       <c r="H87" t="n">
         <v>13</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H95" t="n">
         <v>7</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H98" t="n">
         <v>9</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H100" t="n">
         <v>5</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H102" t="n">
         <v>3</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H103" t="n">
         <v>6</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>6416</v>
+        <v>7047</v>
       </c>
       <c r="H108" t="n">
         <v>21</v>
       </c>
       <c r="I108" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2011</v>
+        <v>2161</v>
       </c>
       <c r="H109" t="n">
         <v>563</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>254200</v>
+        <v>268300</v>
       </c>
       <c r="H116" t="n">
-        <v>1688</v>
+        <v>1760</v>
       </c>
       <c r="I116" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
     </row>
     <row r="117">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H118" t="n">
         <v>2</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H122" t="n">
         <v>3</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H126" t="n">
         <v>24</v>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H128" t="n">
         <v>3</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H143" t="n">
         <v>10</v>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H146" t="n">
         <v>6</v>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H147" t="n">
         <v>3</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H150" t="n">
         <v>3</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="H151" t="n">
         <v>4</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H153" t="n">
         <v>3</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H157" t="n">
         <v>1</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H159" t="n">
         <v>3</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H164" t="n">
         <v>4</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="H168" t="n">
         <v>10</v>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="H169" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H170" t="n">
         <v>2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H172" t="n">
         <v>1</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H173" t="n">
         <v>2</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H174" t="n">
         <v>4</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H175" t="n">
         <v>2</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H176" t="n">
         <v>2</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H177" t="n">
         <v>2</v>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I178" t="n">
         <v>2</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H179" t="n">
         <v>10</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H180" t="n">
         <v>2</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H181" t="n">
         <v>2</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>225</v>
+        <v>319</v>
       </c>
       <c r="H182" t="n">
         <v>1</v>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="H184" t="n">
         <v>5</v>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="H185" t="n">
         <v>6</v>
@@ -8063,13 +8063,13 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H186" t="n">
         <v>7</v>
       </c>
       <c r="I186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H187" t="n">
         <v>9</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="H189" t="n">
         <v>1</v>
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="H190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H191" t="n">
         <v>11</v>
@@ -8315,6 +8315,334 @@
         <v>7</v>
       </c>
       <c r="I192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7660114055167806738</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roborock Qrevo 2Pro đã cập bến tại Vua Robot 3T Smart rồi mọi người ơi #VuARobot #Robothutbuilaunhathainguyen #xuhuong #roborockvietnam </t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>25</v>
+      </c>
+      <c r="H193" t="n">
+        <v>1</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7660083906003176712</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo2 pro giá tầm trung nhưng sở hữu nhiều tính năng cao cấp #qrevo2pro #Roborock #robothutbui #creatorsearchinsights </t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>38</v>
+      </c>
+      <c r="H194" t="n">
+        <v>3</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>caothienphat.official</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@caothienphat.official/video/7660063763491458312</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Running Test Qrevo 2 Pro 🤪 #caothienphat #CTP #robothutbui #qrevo2pro #roborock </t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>61</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>mivietnam_chuyengiarobot</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mivietnam_chuyengiarobot/video/7660091255338093844</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>khi ngủ 8 tiếng trong 2 tiếng kiểu #mivietnam #Roborock #Qrevo2Pro #Robothutbui #fyp</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>342</v>
+      </c>
+      <c r="H196" t="n">
+        <v>10</v>
+      </c>
+      <c r="I196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7660095512929897749</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Qrevo2pro #robothutbui #roborock #quyrobot </t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>28</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7660082668410899730</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chỉ với già chục triệu sở hữu ngay lực hút 25000pa quá đỉnh 🚘 Trải nghiệm ngay tại 05 Nguyễn Du, Nông Trang, Việt Trì nhé ạ #qrevo2pro #robothutbui #robotlaunha #xiaomiphutho #roborock </t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>42</v>
+      </c>
+      <c r="H198" t="n">
+        <v>1</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>nhadepbepxinh.camxuyen</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nhadepbepxinh.camxuyen/video/7660096585396849938</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghé ngay NHÀ ĐẸP BẾP XINH CẨM XUYÊN để trải nghiệm em robot xịn sò này các bác nhé #qrevo2pro #roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>36</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>nhadepbepxinh.camxuyen</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nhadepbepxinh.camxuyen/video/7657744544179506439</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 Pro và những con số biết nói#nhadepbepxinhthongminh #qrevo2pro #roborock </t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>123</v>
+      </c>
+      <c r="H200" t="n">
+        <v>1</v>
+      </c>
+      <c r="I200" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="videos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="videos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H13" t="n">
         <v>11</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="H14" t="n">
         <v>30</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H16" t="n">
         <v>9</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>20700</v>
+        <v>13600</v>
       </c>
       <c r="H23" t="n">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="I23" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>9880</v>
+        <v>9150</v>
       </c>
       <c r="H24" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>910</v>
+        <v>869</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="H29" t="n">
         <v>8</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H38" t="n">
         <v>5</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H40" t="n">
         <v>3</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="H46" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I46" t="n">
         <v>8</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="H47" t="n">
         <v>13</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="H49" t="n">
         <v>22</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H51" t="n">
         <v>6</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H58" t="n">
         <v>2</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H59" t="n">
         <v>3</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H61" t="n">
         <v>3</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1220</v>
+        <v>1201</v>
       </c>
       <c r="H65" t="n">
         <v>12</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="H66" t="n">
         <v>32</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H71" t="n">
         <v>6</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H73" t="n">
         <v>3</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H77" t="n">
         <v>5</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>73400</v>
+        <v>72000</v>
       </c>
       <c r="H78" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I78" t="n">
         <v>71</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H83" t="n">
         <v>5</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1641</v>
+        <v>1586</v>
       </c>
       <c r="H87" t="n">
         <v>13</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H95" t="n">
         <v>7</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H98" t="n">
         <v>9</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H100" t="n">
         <v>5</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H102" t="n">
         <v>3</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H103" t="n">
         <v>6</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>7047</v>
+        <v>6416</v>
       </c>
       <c r="H108" t="n">
         <v>21</v>
       </c>
       <c r="I108" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109">
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2161</v>
+        <v>2011</v>
       </c>
       <c r="H109" t="n">
         <v>563</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>268300</v>
+        <v>254200</v>
       </c>
       <c r="H116" t="n">
-        <v>1760</v>
+        <v>1688</v>
       </c>
       <c r="I116" t="n">
-        <v>242</v>
+        <v>223</v>
       </c>
     </row>
     <row r="117">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H118" t="n">
         <v>2</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H122" t="n">
         <v>3</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H126" t="n">
         <v>24</v>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H128" t="n">
         <v>3</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H143" t="n">
         <v>10</v>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H146" t="n">
         <v>6</v>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H147" t="n">
         <v>3</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H150" t="n">
         <v>3</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="H151" t="n">
         <v>4</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H153" t="n">
         <v>3</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H157" t="n">
         <v>1</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H159" t="n">
         <v>3</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H164" t="n">
         <v>4</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="H168" t="n">
         <v>10</v>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="H169" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H170" t="n">
         <v>2</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="H171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H172" t="n">
         <v>1</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H173" t="n">
         <v>2</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H174" t="n">
         <v>4</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H175" t="n">
         <v>2</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H176" t="n">
         <v>2</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H177" t="n">
         <v>2</v>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="H178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I178" t="n">
         <v>2</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="H179" t="n">
         <v>10</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H180" t="n">
         <v>2</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H181" t="n">
         <v>2</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>319</v>
+        <v>225</v>
       </c>
       <c r="H182" t="n">
         <v>1</v>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="H183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="H184" t="n">
         <v>5</v>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H185" t="n">
         <v>6</v>
@@ -8063,13 +8063,13 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H186" t="n">
         <v>7</v>
       </c>
       <c r="I186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187">
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H187" t="n">
         <v>9</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="H189" t="n">
         <v>1</v>
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="H190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H191" t="n">
         <v>11</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="H196" t="n">
         <v>10</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H197" t="n">
         <v>1</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H198" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H199" t="n">
         <v>1</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:I214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H10" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H13" t="n">
         <v>11</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="H14" t="n">
         <v>30</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H15" t="n">
         <v>5</v>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H20" t="n">
         <v>11</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>13600</v>
+        <v>30600</v>
       </c>
       <c r="H23" t="n">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>9150</v>
+        <v>10500</v>
       </c>
       <c r="H24" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>869</v>
+        <v>977</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>434</v>
+        <v>481</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>429</v>
+        <v>487</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>453</v>
+        <v>482</v>
       </c>
       <c r="H29" t="n">
         <v>8</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H38" t="n">
         <v>5</v>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="H40" t="n">
         <v>3</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="H46" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I46" t="n">
         <v>8</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="H47" t="n">
         <v>13</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="H49" t="n">
         <v>22</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1141</v>
+        <v>1162</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H51" t="n">
         <v>6</v>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H52" t="n">
         <v>7</v>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H61" t="n">
         <v>3</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1201</v>
+        <v>1279</v>
       </c>
       <c r="H65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>704</v>
+        <v>717</v>
       </c>
       <c r="H66" t="n">
         <v>32</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H69" t="n">
         <v>4</v>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H70" t="n">
         <v>7</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H71" t="n">
         <v>6</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H73" t="n">
         <v>3</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H77" t="n">
         <v>5</v>
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>72000</v>
+        <v>75100</v>
       </c>
       <c r="H78" t="n">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="I78" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79">
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H83" t="n">
         <v>5</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H84" t="n">
         <v>3</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H86" t="n">
         <v>4</v>
@@ -4004,13 +4004,13 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1586</v>
+        <v>1712</v>
       </c>
       <c r="H87" t="n">
         <v>13</v>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H88" t="n">
         <v>2</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H95" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H97" t="n">
         <v>1</v>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H100" t="n">
         <v>5</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H102" t="n">
         <v>3</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H103" t="n">
         <v>6</v>
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>6416</v>
+        <v>7929</v>
       </c>
       <c r="H108" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I108" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109">
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2011</v>
+        <v>2379</v>
       </c>
       <c r="H109" t="n">
         <v>563</v>
       </c>
       <c r="I109" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H115" t="n">
         <v>1</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>254200</v>
+        <v>294600</v>
       </c>
       <c r="H116" t="n">
-        <v>1688</v>
+        <v>1942</v>
       </c>
       <c r="I116" t="n">
-        <v>223</v>
+        <v>283</v>
       </c>
     </row>
     <row r="117">
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H117" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H118" t="n">
         <v>2</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H122" t="n">
         <v>3</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>787</v>
+        <v>810</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H126" t="n">
         <v>24</v>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H128" t="n">
         <v>3</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H132" t="n">
         <v>2</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H136" t="n">
         <v>2</v>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H137" t="n">
         <v>1</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H143" t="n">
         <v>10</v>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H144" t="n">
         <v>4</v>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H145" t="n">
         <v>2</v>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I147" t="n">
         <v>1</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="H150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="H151" t="n">
         <v>4</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H153" t="n">
         <v>3</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H157" t="n">
         <v>1</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H159" t="n">
         <v>3</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H160" t="n">
         <v>5</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H162" t="n">
         <v>2</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H164" t="n">
         <v>4</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H167" t="n">
         <v>4</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="H168" t="n">
         <v>10</v>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="H169" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="H170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I170" t="n">
         <v>1</v>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="H172" t="n">
         <v>1</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="H173" t="n">
         <v>2</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H174" t="n">
         <v>4</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H175" t="n">
         <v>2</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H176" t="n">
         <v>2</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H177" t="n">
         <v>2</v>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="H178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I178" t="n">
         <v>2</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>382</v>
+        <v>436</v>
       </c>
       <c r="H179" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
@@ -7858,10 +7858,10 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>225</v>
+        <v>343</v>
       </c>
       <c r="H182" t="n">
         <v>1</v>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="H184" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I184" t="n">
         <v>2</v>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="H185" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I185" t="n">
         <v>2</v>
@@ -8063,13 +8063,13 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="H186" t="n">
         <v>7</v>
       </c>
       <c r="I186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187">
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="H187" t="n">
         <v>9</v>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="H189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="H190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="H191" t="n">
         <v>11</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H192" t="n">
         <v>7</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>25</v>
+        <v>316</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="H194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I194" t="n">
         <v>1</v>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>62</v>
+        <v>282</v>
       </c>
       <c r="H195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
@@ -8473,13 +8473,13 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>347</v>
+        <v>436</v>
       </c>
       <c r="H196" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="H197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I197" t="n">
         <v>1</v>
@@ -8555,10 +8555,10 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="H198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>43</v>
+        <v>220</v>
       </c>
       <c r="H199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I199" t="n">
         <v>0</v>
@@ -8644,6 +8644,580 @@
       </c>
       <c r="I200" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7660352139872521493</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TigerBot Smart Home  #robothutbui #roborock #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>53</v>
+      </c>
+      <c r="H201" t="n">
+        <v>4</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7660371530378906901</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liên hệ và đến trải nghiệm sản phẩm nha khách yêu của em #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>36</v>
+      </c>
+      <c r="H202" t="n">
+        <v>3</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7660366627724217621</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cùng mình khui thùng em robot hút hụi mới của nhà Roborock nhé #robothutbui #qrevo2pro #roborock #mistorebienhoa </t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>46</v>
+      </c>
+      <c r="H203" t="n">
+        <v>1</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>roborock.krng.n</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@roborock.krng.n/video/7660325976261299477</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#roborock  #qrevo2pro  #roborockvietnam  #krongno #robothutbui </t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>87</v>
+      </c>
+      <c r="H204" t="n">
+        <v>3</v>
+      </c>
+      <c r="I204" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7660330402774666516</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Chương trình trải nghiệm thực tế tại: ____________ ROBOROCK STORE BUÔN MA THUỘT 🏠 Số 29 Trần Phú - Phường Buôn Ma Thuột - Tỉnh Đăk Lăk #Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>73</v>
+      </c>
+      <c r="H205" t="n">
+        <v>2</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7660143026190241045</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qua em trải nghiệm thực tế robot nha các bác #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>105</v>
+      </c>
+      <c r="H206" t="n">
+        <v>2</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7660137920774409493</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Còn băn khoăn gì mà chưa chọn Qrevo 2 Pro ạ #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>116</v>
+      </c>
+      <c r="H207" t="n">
+        <v>5</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7660396252508589332</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siêu sạch và tiện lợi #Qrevo2pro #robothutbui #roborock #xuhuongtiktok #quyrobot </t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>22</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7660160172777590037</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>140</v>
+      </c>
+      <c r="H209" t="n">
+        <v>2</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7660155112341392660</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quả con xoay đỉnh cấp của em #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>134</v>
+      </c>
+      <c r="H210" t="n">
+        <v>2</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7660356666117901576</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lực hút khủng long của em QRevo 2 Pro. Đến BOT HOME để trải nghiệm thực tế em nó, đảm bảo mê nha khách ơi 😝 #Qrevo2Pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>56</v>
+      </c>
+      <c r="H211" t="n">
+        <v>4</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7660178941407202581</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 Pro đã có mặt tại Momimart Quận 2. Mời anh chị đến trải nghiệm để nhận quà nhé #RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>154</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7660390181530275092</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>📦🖤 HÀNG VỀ RỒI! Roborock Qrevo 2 Pro  🔥 Review nhanh về Roborock Qrevo 2 Pro: ✅ Lực hút siêu mạnh 25.000Pa, làm sạch hiệu quả trên mọi bề mặt. ✅ Chổi chống rối kép, cực kỳ phù hợp với gia đình có tóc dài hoặc nuôi thú cưng. ✅ Giẻ lau xoay kép kết hợp cánh tay FlexiArm giúp lau sát mép tường, góc cạnh sạch hơn. ✅ Dock đa năng: Tự giặt giẻ – sấy khô – tự đổ rác, giảm tối đa công việc dọn dẹp hàng ngày. ✅ Điều hướng thông minh, hoạt động ổn định và rất ít phải can thiệp trong quá trình sử dụng. 💯 Một trong những mẫu robot đáng mua nhất ở phân khúc cận cao cấp, hội tụ đầy đủ những tính năng mà đa số người dùng cần với mức giá cực kỳ hợp lý. 📩 Inbox ngay để được tư vấn chi tiết, báo giá tốt và nhận những ưu đãi hấp dẫn. #reviewrobot #Qrevo2pro #Robotlaunha #Robothutbui #Roborock</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>15</v>
+      </c>
+      <c r="H213" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7660149973018889490</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không dùng mẫu này thì dùng mẫu nào nữa các bác  #qrevo2pro #robotlaunha #roborock #robothutbui #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>165</v>
+      </c>
+      <c r="H214" t="n">
+        <v>4</v>
+      </c>
+      <c r="I214" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I214"/>
+  <dimension ref="A1:I226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>529</v>
+        <v>563</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="H13" t="n">
         <v>11</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="H14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H16" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>30600</v>
+        <v>35300</v>
       </c>
       <c r="H23" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="I23" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>10500</v>
+        <v>11300</v>
       </c>
       <c r="H24" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>977</v>
+        <v>1039</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="H29" t="n">
         <v>8</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="H31" t="n">
         <v>8</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H39" t="n">
         <v>8</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="H46" t="n">
         <v>53</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H47" t="n">
         <v>13</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H48" t="n">
         <v>13</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H49" t="n">
         <v>22</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1162</v>
+        <v>1179</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1279</v>
+        <v>1353</v>
       </c>
       <c r="H65" t="n">
         <v>13</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="H66" t="n">
         <v>32</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>75100</v>
+        <v>76600</v>
       </c>
       <c r="H78" t="n">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="I78" t="n">
         <v>72</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H84" t="n">
         <v>3</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H86" t="n">
         <v>4</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1712</v>
+        <v>1791</v>
       </c>
       <c r="H87" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I87" t="n">
         <v>5</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="H100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>7929</v>
+        <v>8873</v>
       </c>
       <c r="H108" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I108" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109">
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2379</v>
+        <v>2640</v>
       </c>
       <c r="H109" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="I109" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110">
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H113" t="n">
         <v>2</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>294600</v>
+        <v>319000</v>
       </c>
       <c r="H116" t="n">
-        <v>1942</v>
+        <v>2112</v>
       </c>
       <c r="I116" t="n">
-        <v>283</v>
+        <v>326</v>
       </c>
     </row>
     <row r="117">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H118" t="n">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1758</v>
+        <v>1764</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>810</v>
+        <v>828</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H126" t="n">
         <v>24</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H132" t="n">
         <v>2</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H137" t="n">
         <v>1</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H144" t="n">
         <v>4</v>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H145" t="n">
         <v>2</v>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H146" t="n">
         <v>7</v>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H147" t="n">
         <v>4</v>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H149" t="n">
         <v>6</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="H150" t="n">
         <v>4</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H151" t="n">
         <v>4</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H153" t="n">
         <v>3</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H159" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H167" t="n">
         <v>4</v>
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="H168" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="H169" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="H170" t="n">
         <v>4</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="H171" t="n">
         <v>3</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H172" t="n">
         <v>1</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H173" t="n">
         <v>2</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H175" t="n">
         <v>2</v>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H178" t="n">
         <v>3</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="H179" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H180" t="n">
         <v>3</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H182" t="n">
         <v>1</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H183" t="n">
         <v>4</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H184" t="n">
         <v>6</v>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H185" t="n">
         <v>7</v>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H186" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I186" t="n">
         <v>6</v>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H187" t="n">
         <v>9</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="H190" t="n">
         <v>5</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H191" t="n">
         <v>11</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H192" t="n">
         <v>7</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>316</v>
+        <v>373</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="H194" t="n">
         <v>4</v>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>282</v>
+        <v>345</v>
       </c>
       <c r="H195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="H196" t="n">
         <v>17</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H197" t="n">
         <v>3</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="H198" t="n">
         <v>3</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>220</v>
+        <v>301</v>
       </c>
       <c r="H199" t="n">
         <v>2</v>
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="H201" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="H202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="H203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
@@ -8801,10 +8801,10 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>87</v>
+        <v>355</v>
       </c>
       <c r="H204" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I204" t="n">
         <v>2</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="H205" t="n">
         <v>2</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="H206" t="n">
         <v>2</v>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="H207" t="n">
         <v>5</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9006,10 +9006,10 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="H209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="H210" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>56</v>
+        <v>349</v>
       </c>
       <c r="H211" t="n">
         <v>4</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>154</v>
+        <v>258</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,13 +9211,505 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>165</v>
+        <v>237</v>
       </c>
       <c r="H214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I214" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7660526024853212436</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot hút bụi lau nhà Roborock Qrevo 2 Pro xuất hiện như một lựa chọn dành cho những tổ ấm muốn giữ nhịp sạch sẽ mỗi ngày, nơi những chu trình lặp đi lặp lại được thay thế bằng một guồng vận hành tự động gọn gàng.#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>47</v>
+      </c>
+      <c r="H215" t="n">
+        <v>3</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>tn.robot76</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tn.robot76/video/7660453171411635463</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Khách tới xem trải nghiệm có 🎁 chốt ngay giao liền trong đêm Qrevo 2 Pro #Qrevo2Pro #Roborock #Robothutbui #robotbinhduong #roborockrobotbinhduong</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>247</v>
+      </c>
+      <c r="H216" t="n">
+        <v>4</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>homecaredigital</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homecaredigital/video/7660421487974714625</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>🚀Đừng chỉ nghe đồn, hãy xem Qrevo 2 Pro dọn dẹp đỉnh thế nào Roborock Qrevo 2 Pro chính là công nghệ khuấy đảo phân khúc tầm trung với khả năng cuốn trôi mọi vết bẩn, trả lại mặt sàn sạch sang sáng bóng. Nhờ sở hữu tầm nhìn sắc bén, robot dễ dàng nhận diện và tránh né thông minh các vật cản trong nhà, đồng thời len lỏi làm sạch sâu sát mép tường mà không bỏ sót bất kỳ ngóc ngách nào.  👉Để tận hưởng không gian sống thảnh thơi, hãy ghé ngay 𝐇𝐨𝐦𝐞𝐜𝐚𝐫𝐞 𝐃𝐢𝐠𝐢𝐭𝐚𝐥 để được tư vấn chi tiết và rinh ngay siêu phẩm này về nhà!</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>mivietnam_chuyengiarobot</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mivietnam_chuyengiarobot/video/7660467805049048341</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>khi ngủ 8 tiếng trong 2 tiếng kiểu #mivietnam #Roborock #Qrevo2Pro #Robothutbui #fyp</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>443</v>
+      </c>
+      <c r="H218" t="n">
+        <v>7</v>
+      </c>
+      <c r="I218" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7660570109743746324</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Hướng dẫn kết nối Roborock 2 Pro với điện thoại. #Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>11</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7660559797263076628</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghé shop em trải nghiệm trước mua sau nha các bác #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>28</v>
+      </c>
+      <c r="H220" t="n">
+        <v>2</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7660471988644777237</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vẫn còn nhiều xuất trải nghiệm robot nha các bác ghé Smarthome Phú Thọ nha #Qrevo2Pro #roborock #robothutbui #smarthomephutho #NhaThongMinh </t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>77</v>
+      </c>
+      <c r="H221" t="n">
+        <v>4</v>
+      </c>
+      <c r="I221" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7660417288608238869</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qua em trải nghiệm robot nha các bác #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>106</v>
+      </c>
+      <c r="H222" t="n">
+        <v>3</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7660514008818011413</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có em nó quá nhàn luôn #Qrevo2pro #robothutbui #roborock #xuhuongtiktok #quyrobot </t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>80</v>
+      </c>
+      <c r="H223" t="n">
+        <v>3</v>
+      </c>
+      <c r="I223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7660420517073014023</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mẫu máy đang rất hot tại nhà BOT #Qrevo2Pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>307</v>
+      </c>
+      <c r="H224" t="n">
+        <v>3</v>
+      </c>
+      <c r="I224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7660517122824604935</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bác nào tìm hiểu robot đừng bỏ qua nhé em này nhé ạ 🤩 🚘 Ngay Xiaomi Phú Thọ: 05 Nguyễn Du, Nông Trang, Việt Trì, Phú Thọ 0862505508 để được xem sản phẩm và tư vấn ạ.  #qrevo2pro #robothutbui #roborock #robotlaunha #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>65</v>
+      </c>
+      <c r="H225" t="n">
+        <v>2</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7660456277914455304</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bác nào không tìm hiểu em này Qrevo 2 Pro chỉ có tiếc 🤩  #qrevo2pro #roborock #robothutbui #robotlaunha #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>109</v>
+      </c>
+      <c r="H226" t="n">
+        <v>4</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="videos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="videos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I226"/>
+  <dimension ref="A1:I255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>563</v>
+        <v>595</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H13" t="n">
         <v>11</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>350</v>
+        <v>392</v>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H16" t="n">
         <v>10</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I17" t="n">
         <v>10</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>35300</v>
+        <v>39700</v>
       </c>
       <c r="H23" t="n">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="I23" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>11300</v>
+        <v>12100</v>
       </c>
       <c r="H24" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1039</v>
+        <v>1128</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>505</v>
+        <v>554</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>512</v>
+        <v>564</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="H29" t="n">
         <v>8</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="H31" t="n">
         <v>8</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H39" t="n">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="H46" t="n">
         <v>53</v>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="H47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H48" t="n">
         <v>13</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="H49" t="n">
         <v>22</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1179</v>
+        <v>1204</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H51" t="n">
         <v>6</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H59" t="n">
         <v>5</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1353</v>
+        <v>1403</v>
       </c>
       <c r="H65" t="n">
         <v>13</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="H66" t="n">
         <v>32</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H70" t="n">
         <v>7</v>
@@ -3389,13 +3389,13 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H72" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I72" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>76600</v>
+        <v>77400</v>
       </c>
       <c r="H78" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I78" t="n">
         <v>72</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H83" t="n">
         <v>5</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H86" t="n">
         <v>4</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1791</v>
+        <v>1915</v>
       </c>
       <c r="H87" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I87" t="n">
         <v>5</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H92" t="n">
         <v>4</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H93" t="n">
         <v>9</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H98" t="n">
         <v>10</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H99" t="n">
         <v>2</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H102" t="n">
         <v>3</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H103" t="n">
         <v>6</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H104" t="n">
         <v>2</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H105" t="n">
         <v>3</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>8873</v>
+        <v>9588</v>
       </c>
       <c r="H108" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I108" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109">
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2640</v>
+        <v>2907</v>
       </c>
       <c r="H109" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="I109" t="n">
         <v>27</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>319000</v>
+        <v>369600</v>
       </c>
       <c r="H116" t="n">
-        <v>2112</v>
+        <v>2441</v>
       </c>
       <c r="I116" t="n">
-        <v>326</v>
+        <v>392</v>
       </c>
     </row>
     <row r="117">
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H122" t="n">
         <v>3</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>828</v>
+        <v>842</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H126" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I126" t="n">
         <v>3</v>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H128" t="n">
         <v>3</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H132" t="n">
         <v>2</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H143" t="n">
         <v>10</v>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I144" t="n">
         <v>3</v>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I145" t="n">
         <v>2</v>
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H146" t="n">
         <v>7</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H147" t="n">
         <v>4</v>
@@ -6505,13 +6505,13 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H149" t="n">
         <v>6</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H150" t="n">
         <v>4</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="H151" t="n">
         <v>4</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H159" t="n">
         <v>3</v>
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H160" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H164" t="n">
         <v>4</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="H168" t="n">
         <v>11</v>
@@ -7366,13 +7366,13 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="H169" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="H170" t="n">
         <v>4</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H171" t="n">
         <v>3</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H174" t="n">
         <v>4</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H175" t="n">
         <v>2</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H176" t="n">
         <v>2</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H177" t="n">
         <v>2</v>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H178" t="n">
         <v>3</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="H179" t="n">
         <v>12</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H180" t="n">
         <v>3</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H181" t="n">
         <v>3</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H183" t="n">
         <v>4</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H184" t="n">
         <v>6</v>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="H185" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I185" t="n">
         <v>2</v>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H186" t="n">
         <v>8</v>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H187" t="n">
         <v>9</v>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H188" t="n">
         <v>2</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H189" t="n">
         <v>2</v>
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H190" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H192" t="n">
         <v>7</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="H194" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I194" t="n">
         <v>1</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="H195" t="n">
         <v>3</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="H196" t="n">
         <v>17</v>
@@ -8555,10 +8555,10 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="H198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="H199" t="n">
         <v>2</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H201" t="n">
         <v>7</v>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>138</v>
+        <v>356</v>
       </c>
       <c r="H202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="H203" t="n">
         <v>3</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="H204" t="n">
         <v>4</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H205" t="n">
         <v>2</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H207" t="n">
         <v>5</v>
@@ -8965,13 +8965,13 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H209" t="n">
         <v>3</v>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H210" t="n">
         <v>4</v>
@@ -9088,10 +9088,10 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="H211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,10 +9252,10 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>47</v>
+        <v>367</v>
       </c>
       <c r="H215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I215" t="n">
         <v>0</v>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>247</v>
+        <v>350</v>
       </c>
       <c r="H216" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I216" t="n">
         <v>1</v>
@@ -9375,13 +9375,13 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>443</v>
+        <v>885</v>
       </c>
       <c r="H218" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -9416,10 +9416,10 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>11</v>
+        <v>161</v>
       </c>
       <c r="H219" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I219" t="n">
         <v>0</v>
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>28</v>
+        <v>239</v>
       </c>
       <c r="H220" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I220" t="n">
         <v>0</v>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="H221" t="n">
         <v>4</v>
@@ -9539,10 +9539,10 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>106</v>
+        <v>363</v>
       </c>
       <c r="H222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I222" t="n">
         <v>0</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="H223" t="n">
         <v>3</v>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>307</v>
+        <v>377</v>
       </c>
       <c r="H224" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I224" t="n">
         <v>1</v>
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>65</v>
+        <v>229</v>
       </c>
       <c r="H225" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I225" t="n">
         <v>0</v>
@@ -9703,12 +9703,1201 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="H226" t="n">
         <v>4</v>
       </c>
       <c r="I226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7660860650763160853</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Chương trình trải nghiệm trước mua sau là gì❓#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>33</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7660859272317701396</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Đâu mới là sản phẩm hợp với nhà bạn❓#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>40</v>
+      </c>
+      <c r="H228" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7660858983569198357</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>👉Quảng cáo liệu có hay như lời đồn..#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>47</v>
+      </c>
+      <c r="H229" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7660858670590348564</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>🔥Sản phẩm mới của Roborock có gì mà nhiều người review đến vậy#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>41</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7660796826668535060</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>👉Ghé ngay AHA để tham dự chương trình mới trong tháng 7 này...#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>103</v>
+      </c>
+      <c r="H231" t="n">
+        <v>7</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7660795084635376916</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>❓Có gì hay ở Qrevo 2 Pro mà nhiều người muốn tới AHA trải nghiệm#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>107</v>
+      </c>
+      <c r="H232" t="n">
+        <v>4</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7660794775708159253</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>⭐️Sự khác nhau khi đã có với chưa có robot hút bụi...#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>114</v>
+      </c>
+      <c r="H233" t="n">
+        <v>6</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7660794517313899796</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>❓Bạn đang phân giữa robot hút bụi và máy hút bụi cầm tay🤔#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>111</v>
+      </c>
+      <c r="H234" t="n">
+        <v>5</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7660794241345391892</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>🔥POV: Bạn đi trải nghiệm dòng sản phẩm mới ra mắt của nhà Roborock#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok #trendingsound</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>110</v>
+      </c>
+      <c r="H235" t="n">
+        <v>7</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>minhchautestthat</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@minhchautestthat/video/7660755888197602581</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Test021 Câu hỏi đơn giản nhưng nhiều khách chưa hình dung ra thế nào là chống rơi của Robot hút bụi  Anh em cần test tính năng gì cmt mình lên video nhé #minhchautestthat #robothutbuilaunha  #roborock #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>1767</v>
+      </c>
+      <c r="H236" t="n">
+        <v>16</v>
+      </c>
+      <c r="I236" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7660857484583767317</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đến ngày cửa hàng em để được trải nghiệm cũng như được tư vấn và hỗ trợ về các dòng của Roborock nào#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>31</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7660853480596311316</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà sạch ổn định, thao tác tối giản và bạn có thêm thời gian cho những điều thật sự quan trọng.#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>30</v>
+      </c>
+      <c r="H238" t="n">
+        <v>1</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7660855134213180679</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đâu mới là sự lựa chọn hàng đầu dành cho gia đình bạn #robothutbui #qrevo2pro #roborock #fyp #robothutbuilaunhathainguyen </t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>28</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7660676462822935826</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>07.07 này là đã biết đi đâu rồi đó #robothutbui #robothutbuilaunhathainguyen #qrevo2pro #roborock #fyp</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>344</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7660754481725836562</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhẹ nhàng lướt qua nhau #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>208</v>
+      </c>
+      <c r="H241" t="n">
+        <v>2</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7660700044315659527</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo2 pro sự khác biệt trong cùng phân khúc #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>169</v>
+      </c>
+      <c r="H242" t="n">
+        <v>4</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7660698676767018247</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Để dép ở lại không được đưa ra ngoài #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>169</v>
+      </c>
+      <c r="H243" t="n">
+        <v>3</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7660587495742278933</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Tính năng để lại giẻ lau khi robot đi hút bụi sẽ giúp thảm  không bị ướt trong quá trình robot làm việc #Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>152</v>
+      </c>
+      <c r="H244" t="n">
+        <v>3</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7660835795540004117</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chưa chọn được mẫu nào ưng thì qua em nha các bác #Qrevo2Pro #roborock #robothutbui #smarthomephutho #NhaThongMinh </t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>33</v>
+      </c>
+      <c r="H245" t="n">
+        <v>4</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7660824262122523924</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Các bác biết chọn gì cho nhà mình chưa ạ #Qrevo2Pro #roborock #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>46</v>
+      </c>
+      <c r="H246" t="n">
+        <v>3</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7660747866427641108</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vẫn chưa biết chọn robot nào phù hợp cho gia đình thì qua em nha #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>88</v>
+      </c>
+      <c r="H247" t="n">
+        <v>4</v>
+      </c>
+      <c r="I247" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7660716972161830164</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghé đi! Ghé đi! Ghé shop em đi còn nhiều quà của trải nghiệm tháng 7 nha các bác #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>111</v>
+      </c>
+      <c r="H248" t="n">
+        <v>6</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7660851524767091988</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mời quý vị xem để biết nhà mình hợp em nào #Qrevo2pro #robothutbui #roborock #f25ultra #quyrobot </t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>55</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7660811772676361493</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>#RobotHutBui #Roborock #Qrevo2Pro #Momimart #Roborock Qrevo 2 Pro là dòng robot hút bụi lau nhà thuộc phân khúc cận cao cấp, nổi bật với khả năng làm sạch vượt trội và mức độ tự động hóa cực kỳ cao:  Hiệu suất làm sạch cực khủng: Sở hữu lực hút HyperForce lên tới 25.000 Pa kết hợp với hệ thống chổi chính DuoDivide và chổi cạnh dạng vòm cho khả năng chống rối tóc gần như tuyệt đối.  Lau nhà sát mép: Công nghệ FlexiArm Edge Mopping cho phép giẻ lau xoay (tốc độ 200 vòng/phút) tự động mở rộng, áp sát mép tường với khoảng cách chỉ 1.85 mm, giúp bao phủ toàn bộ các góc khuất.  Xử lý thảm thông minh: Robot tự động nâng giẻ lau lên 12mm hoặc thậm chí tự động tháo rời giẻ tại dock trước khi đi hút bụi trên thảm, đảm bảo thảm không bao giờ bị ẩm ướt.  Dock sạc toàn năng: Tự động đổ bụi, tự châm nước, giặt giẻ bằng khí nóng và sấy khô bằng khí ấm 45°C để khử mùi, hạn chế tối đa việc phải vệ sinh thủ công (rảnh tay lên đến 65 ngày).  Điều hướng chính xác: Sử dụng hệ thống tránh vật cản Reactive Tech giúp né tránh đồ nội thất, dây điện mượt mà và hỗ trợ kết nối qua app Roborock (tương thích chuẩn Matter).</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>90</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7660742603058482453</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>#RobotHutBui #Momimart #Roborock #Qrevo2Pro ở khu vực Thảo điền Quận 2 thì nên mua robot ở đâu??</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>138</v>
+      </c>
+      <c r="H251" t="n">
+        <v>4</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7660723908009561365</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đến ngay cửa hàng Momimart để được trải nghiệm Qrevo 2 Pro và nhận nhiều quà tặng hấp dẫn nhé ạ   #RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>147</v>
+      </c>
+      <c r="H252" t="n">
+        <v>3</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7660845191305383175</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qua shop trải nghiệm nhận quà thui ạ 🎁🎁🎁 🏠 Số 05 Nguyễn Du, Nông Trang, Việt Trì, Phú Thọ #roborock #qrevo2pro #robotlaunha #robothutbui #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>49</v>
+      </c>
+      <c r="H253" t="n">
+        <v>2</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7660833597250751751</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sản phẩm đang được trưng bày tại Xiaomi Phú Thọ 🚘 Các bác qua shop xem nha: 05 Nguyễn Du, Nông Trang, Việt Trì ạ #qrevo2pro #robothutbui #robotlaunha #roborock #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>42</v>
+      </c>
+      <c r="H254" t="n">
+        <v>1</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7660756036101475591</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bỏ qua em này là tiếc lắm nha các bác 🤩 🚘 qua luôn Xiaomi Phú Thọ: 05 Nguyễn Du, Nông Trang, Việt Trì để trải nghiệm ạ 😍 #qrevo2pro #robotlaunha #robothutbui #roborock #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>101</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I255"/>
+  <dimension ref="A1:I278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>595</v>
+        <v>657</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="H14" t="n">
         <v>33</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H15" t="n">
         <v>5</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H17" t="n">
         <v>25</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H20" t="n">
         <v>11</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>39700</v>
+        <v>44400</v>
       </c>
       <c r="H23" t="n">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="I23" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>12100</v>
+        <v>13200</v>
       </c>
       <c r="H24" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1128</v>
+        <v>1226</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>554</v>
+        <v>608</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>541</v>
+        <v>575</v>
       </c>
       <c r="H29" t="n">
         <v>8</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>546</v>
+        <v>568</v>
       </c>
       <c r="H31" t="n">
         <v>8</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="H46" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I46" t="n">
         <v>9</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="H47" t="n">
         <v>14</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="H48" t="n">
         <v>13</v>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="H49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I49" t="n">
         <v>3</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1204</v>
+        <v>1236</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H51" t="n">
         <v>6</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H59" t="n">
         <v>5</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1403</v>
+        <v>1442</v>
       </c>
       <c r="H65" t="n">
         <v>13</v>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="H66" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I66" t="n">
         <v>26</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H72" t="n">
         <v>51</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H77" t="n">
         <v>5</v>
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>77400</v>
+        <v>77900</v>
       </c>
       <c r="H78" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I78" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79">
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3881,13 +3881,13 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H84" t="n">
+        <v>4</v>
+      </c>
+      <c r="I84" t="n">
         <v>3</v>
-      </c>
-      <c r="I84" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1915</v>
+        <v>2053</v>
       </c>
       <c r="H87" t="n">
         <v>15</v>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H98" t="n">
         <v>10</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>9588</v>
+        <v>10200</v>
       </c>
       <c r="H108" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I108" t="n">
         <v>22</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2907</v>
+        <v>3154</v>
       </c>
       <c r="H109" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="I109" t="n">
         <v>27</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H115" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H118" t="n">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>842</v>
+        <v>858</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H126" t="n">
         <v>25</v>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H127" t="n">
         <v>5</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H132" t="n">
         <v>2</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H136" t="n">
         <v>3</v>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H137" t="n">
         <v>1</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H143" t="n">
         <v>10</v>
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H146" t="n">
         <v>7</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H147" t="n">
         <v>4</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="H151" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I151" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H159" t="n">
         <v>3</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H160" t="n">
         <v>6</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H162" t="n">
         <v>2</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H164" t="n">
         <v>4</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="H168" t="n">
         <v>11</v>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="H169" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I169" t="n">
         <v>1</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="H170" t="n">
         <v>4</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="H171" t="n">
         <v>3</v>
@@ -7489,13 +7489,13 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H172" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" t="n">
         <v>1</v>
-      </c>
-      <c r="I172" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -7530,13 +7530,13 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174">
@@ -7571,13 +7571,13 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -7612,13 +7612,13 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176">
@@ -7653,13 +7653,13 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H178" t="n">
+        <v>4</v>
+      </c>
+      <c r="I178" t="n">
         <v>3</v>
-      </c>
-      <c r="I178" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="H179" t="n">
         <v>12</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H180" t="n">
         <v>3</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H181" t="n">
         <v>3</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="H183" t="n">
         <v>4</v>
@@ -7981,13 +7981,13 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H184" t="n">
         <v>6</v>
       </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -8145,13 +8145,13 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H189" t="n">
         <v>2</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="H191" t="n">
         <v>11</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H192" t="n">
         <v>7</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,13 +8391,13 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="H194" t="n">
         <v>6</v>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="H195" t="n">
         <v>3</v>
@@ -8473,13 +8473,13 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="H196" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197">
@@ -8514,13 +8514,13 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H199" t="n">
         <v>2</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H200" t="n">
         <v>1</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H201" t="n">
         <v>7</v>
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
@@ -8801,10 +8801,10 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="H204" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I204" t="n">
         <v>2</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H206" t="n">
         <v>3</v>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H207" t="n">
         <v>5</v>
@@ -8965,13 +8965,13 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -9006,13 +9006,13 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -9047,13 +9047,13 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H210" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H211" t="n">
         <v>5</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="H215" t="n">
         <v>4</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="H216" t="n">
         <v>5</v>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>885</v>
+        <v>936</v>
       </c>
       <c r="H218" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I218" t="n">
         <v>3</v>
@@ -9416,10 +9416,10 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="H219" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I219" t="n">
         <v>0</v>
@@ -9457,13 +9457,13 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="H220" t="n">
         <v>3</v>
       </c>
       <c r="I220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H221" t="n">
         <v>4</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H222" t="n">
         <v>4</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H223" t="n">
+        <v>4</v>
+      </c>
+      <c r="I223" t="n">
         <v>3</v>
-      </c>
-      <c r="I223" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H224" t="n">
         <v>4</v>
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="H225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I225" t="n">
         <v>0</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H226" t="n">
         <v>4</v>
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="H227" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
@@ -9785,10 +9785,10 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="H228" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="H229" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I229" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="H230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="H231" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="H232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="H233" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="H234" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -10072,10 +10072,10 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="H235" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -10113,13 +10113,13 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1767</v>
+        <v>5045</v>
       </c>
       <c r="H236" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I236" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="237">
@@ -10154,10 +10154,10 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>31</v>
+        <v>274</v>
       </c>
       <c r="H237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
@@ -10195,10 +10195,10 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>30</v>
+        <v>315</v>
       </c>
       <c r="H238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>28</v>
+        <v>348</v>
       </c>
       <c r="H239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>208</v>
+        <v>361</v>
       </c>
       <c r="H241" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I241" t="n">
         <v>0</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="H242" t="n">
         <v>4</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>169</v>
+        <v>260</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H244" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I244" t="n">
         <v>0</v>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="H245" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I245" t="n">
         <v>0</v>
@@ -10523,10 +10523,10 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>46</v>
+        <v>158</v>
       </c>
       <c r="H246" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I246" t="n">
         <v>0</v>
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="H247" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I247" t="n">
         <v>3</v>
@@ -10605,10 +10605,10 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="H248" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I248" t="n">
         <v>0</v>
@@ -10646,13 +10646,13 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="H249" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>147</v>
+        <v>199</v>
       </c>
       <c r="H252" t="n">
         <v>3</v>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>49</v>
+        <v>254</v>
       </c>
       <c r="H253" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I253" t="n">
         <v>0</v>
@@ -10851,10 +10851,10 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>42</v>
+        <v>221</v>
       </c>
       <c r="H254" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I254" t="n">
         <v>0</v>
@@ -10892,12 +10892,955 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="H255" t="n">
+        <v>3</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7661125651956534549</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">So sánh robot hút bụi và cây lau nhà  #robothutbui #qrevo2pro #roborock </t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>122</v>
+      </c>
+      <c r="H256" t="n">
+        <v>3</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7661184898564230421</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tự nhiên thấy suy thấy lụy mà thấy hợp cảnh quá trời😆😆#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>45</v>
+      </c>
+      <c r="H257" t="n">
+        <v>3</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7661180385392463124</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cùng mình tìm hiểu thêm tính năng của Roborock Quevo 2 Pro nhé #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>50</v>
+      </c>
+      <c r="H258" t="n">
+        <v>1</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7660887258148457736</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Từ ngày có em sen robot, nhà lúc nào cũng sạch bong. Hàng xóm bàn tán còn nhiều hơn chuyện giá vàng. Chị em mê sạch mà chưa biết chọn robot nào thì đừng lướt qua! #VuaRobot #Robothutbuilaunhathainguyen #Qrevo2Pro #roborockthainguyen #Nhasach</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>351</v>
+      </c>
+      <c r="H259" t="n">
+        <v>3</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>mivietnam_chuyengiarobot</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mivietnam_chuyengiarobot/video/7661212940925668628</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Cuối tuần này bạn đã biết đi đâu chưa? 👀 Nếu đang muốn trải nghiệm robot hút bụi "xịn" trước khi xuống tiền thì đây là dịp không nên bỏ lỡ! Đến trực tiếp các chi nhánh tại Mi Việt Nam, trải nghiệm Roborock Qrevo 2 Pro hoặc Roborock F25 Ultra, bạn sẽ được tặng thêm những phần quà chính hãng từ Roborock như balo, bình giữ nhiệt, túi đeo chéo, mũ, dù, gấu bông... 🎁 📍 Áp dụng tại tất cả chi nhánh Mi Việt Nam 📅 07/07 - 31/07/2026 Hẹn bạn cuối tuần này tại Mi Việt Nam nhé💙 #mivietnam #chuyengiarobothutbui #Roborock #mayhutbuilausan</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>51</v>
+      </c>
+      <c r="H260" t="n">
+        <v>4</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7661209574782881045</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Quay Clip quảng cáo ❌ Phá cửa hàng ✅ 🤣🤣🤣 #Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>24</v>
+      </c>
+      <c r="H261" t="n">
+        <v>3</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7661156138116779284</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuối tuần rồi qua em trải nghiệm nha các bác #Qrevo2Pro #roborock #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>49</v>
+      </c>
+      <c r="H262" t="n">
         <v>2</v>
       </c>
-      <c r="I255" t="n">
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7661143571449318677</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop em sẵn nha các bác qua em trải nghiệm ạ #Qrevo2Pro #roborock #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>73</v>
+      </c>
+      <c r="H263" t="n">
+        <v>2</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7660881959463259413</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghé Smarthome Phú Thọ trải nghiệm thực tế robot và chổi lau nhà roborock nha các bác #Qrevo2Pro #roborock #robothutbui  #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>132</v>
+      </c>
+      <c r="H264" t="n">
+        <v>3</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7661206808031251732</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lắp đặt và hướng dẫn tại nhà #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>50</v>
+      </c>
+      <c r="H265" t="n">
+        <v>1</v>
+      </c>
+      <c r="I265" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7661105481154563349</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xem là mê- mà mê là chốt #Qrevo2pro #robothutbui #roborock #quyrobot #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>120</v>
+      </c>
+      <c r="H266" t="n">
+        <v>6</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7661189581924207880</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đu trend biến hình ra Qrevo 2 Pro 😛 #Qrevo2Pro #Roborock #robothutbui  </t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>77</v>
+      </c>
+      <c r="H267" t="n">
+        <v>3</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7661144227564342535</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theo dõi máy làm việc thực tế qua app  #Qrevo2Pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>98</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7661088902647680263</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bạn phân vân khi có quá nhiều mẫu máy robot hút bụi ⁉️💥 BOT Home sẽ giúp bạn lựa chọn robot phù hợp với gia đình #Qrevo2Pro #Roborock #robothutbui  </t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>131</v>
+      </c>
+      <c r="H269" t="n">
+        <v>2</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>hatechz</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hatechz/video/7661196321335954706</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghé Hatechz sờ tận tay - rinh ngay siêu phẩm cùng nhiều món quà nhỏ xing iu ❤️ #robothutbui #qrevo2pro #roborock #F25Ultra #f25series </t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>35</v>
+      </c>
+      <c r="H270" t="n">
+        <v>1</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>hatechz</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hatechz/video/7661174527149264136</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Một lựa chọn vừa túi cho các bác ạ 💕 #qrevo2pro #roborock #qrevo #viral #robothutbui </t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>61</v>
+      </c>
+      <c r="H271" t="n">
+        <v>1</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7661150208344018196</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>104</v>
+      </c>
+      <c r="H272" t="n">
+        <v>4</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7661136584531578132</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nên chọn mua robot nào hiệu quả?#RobotHutBui #Roborock #Qrevo2Pro #curv2flow #Momimart </t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>107</v>
+      </c>
+      <c r="H273" t="n">
+        <v>3</v>
+      </c>
+      <c r="I273" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7661119084867767573</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hãy đến cửa hàng Momimart để trải nghiệm sản phẩm mới của Roborock xem có đáng sở hữu nó không nhé mn ơi…quà trải nghiệm vẫn đang ngập tràn #RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>86</v>
+      </c>
+      <c r="H274" t="n">
+        <v>3</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7661135733352041749</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không chỉ nhìn thông số, H&amp;T SmartHome luôn test thực tế để xem Roborock Qrevo 2 Pro làm sạch đến đâu. Với lực hút lên đến 25.000Pa cùng giẻ lau xoay kép, Qrevo 2 Pro mang lại hiệu quả làm sạch ấn tượng ngay trong những tình huống thực tế.   🎥 Xem hết video để thấy khả năng làm sạch của Qrevo 2 Pro có đúng như kỳ vọng không nhé! 📩 Muốn trải nghiệm trực tiếp hoặc cần tư vấn, cứ nhắn H&amp;T SmartHome Đức Trọng để được hỗ trợ. #Robotlaunha #qrevo2pro #roborock #robotductrong #reviewrobot </t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>68</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7660921507715075348</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bạn đang phân vân có nên mua robot hút bụi lau nhà? Đừng chỉ xem video – hãy đến trực tiếp trải nghiệm sức mạnh của Roborock Qrevo 2 Pro! ✨ Tận mắt kiểm chứng: ✅ Lực hút HyperForce 25.000Pa siêu mạnh ✅ Giẻ lau cạnh FlexiArm™ tự động mở rộng sát mép tường và chân nội thất, chăm kỹ những vị trí thường dễ bị bỏ sót ✅ Chổi chống rối, cực hợp nhà có tóc dài &amp; thú cưng ✅ Khay giặt tự làm sạch thế hệ 2 giúp dock sạch lâu hơn, giảm công sức vệ sinh định kỳ ✅ Tự động tháo rời giẻ lau trước khi làm sạch thảm, giúp hạn chế bẩn chéo và giữ thảm luôn khô ráo ✅  Dock đa năng tự giặt và sấy sau mỗi chu trình, để robot luôn sẵn sàng cho lần làm sạch tiếp theo 🔥 Đặc biệt khi mua máy tại sự kiện: 🎁 Nhận ngay ưu đãi cực hấp dẫn 🎁 Tặng thêm nhiều phần quà giá trị chỉ dành cho khách đến tham gia trải nghiệm. 🎁 Được tư vấn trực tiếp để chọn đúng mẫu máy phù hợp với nhu cầu. 📍 Đến trải nghiệm miễn phí – Cảm nhận thực tế – Săn ưu đãi lớn – Quà mang về liền tay! 👉 Inbox ngay để nhận thông tin chi tiết chương trình.  #Robotlaunha #roborock #qrevo2pro #robotductrong #reviewrobot </t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>168</v>
+      </c>
+      <c r="H276" t="n">
+        <v>1</v>
+      </c>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7661195487575362834</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deal này chưa sâu còn deal nào sâu hơn cho Qrevo 2 pro nữa ạ  #qrevo2pro #robothutbui #roborock #robotlaunha #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>53</v>
+      </c>
+      <c r="H277" t="n">
+        <v>2</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>homebotvietnam</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homebotvietnam/video/7661151281343483157</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Nhà sạch hơn mà mình lại nhàn hơn ✨🤖 Qrevo 2 Pro lo từ hút đến lau, để bạn dành thời gian cho những điều quan trọng hơn! 🏡💙 #Qrevo2Pro #Roborock #robothutbui #ReviewCongNghe #NhaThongMinh</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>86</v>
+      </c>
+      <c r="H278" t="n">
+        <v>2</v>
+      </c>
+      <c r="I278" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I278"/>
+  <dimension ref="A1:I305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>657</v>
+        <v>731</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="H14" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H16" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H17" t="n">
         <v>25</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H20" t="n">
         <v>11</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>44400</v>
+        <v>52100</v>
       </c>
       <c r="H23" t="n">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="I23" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>13200</v>
+        <v>21600</v>
       </c>
       <c r="H24" t="n">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="I24" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1226</v>
+        <v>1323</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>618</v>
+        <v>660</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>575</v>
+        <v>616</v>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>568</v>
+        <v>590</v>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>399</v>
+        <v>428</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="H46" t="n">
         <v>54</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="H47" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I47" t="n">
         <v>3</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H48" t="n">
         <v>13</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1236</v>
+        <v>1268</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H51" t="n">
         <v>6</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H59" t="n">
         <v>5</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H64" t="n">
         <v>4</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1442</v>
+        <v>1493</v>
       </c>
       <c r="H65" t="n">
         <v>13</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="H66" t="n">
         <v>33</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H69" t="n">
         <v>5</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H72" t="n">
         <v>51</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H73" t="n">
         <v>4</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H77" t="n">
         <v>5</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>77900</v>
+        <v>78500</v>
       </c>
       <c r="H78" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I78" t="n">
         <v>73</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H83" t="n">
         <v>5</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H84" t="n">
         <v>4</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H86" t="n">
         <v>5</v>
@@ -4004,13 +4004,13 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2053</v>
+        <v>2165</v>
       </c>
       <c r="H87" t="n">
         <v>15</v>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H88" t="n">
         <v>3</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H92" t="n">
         <v>4</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H93" t="n">
         <v>9</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H98" t="n">
         <v>10</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H99" t="n">
         <v>2</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H105" t="n">
         <v>3</v>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>10200</v>
+        <v>10700</v>
       </c>
       <c r="H108" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I108" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109">
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3154</v>
+        <v>3699</v>
       </c>
       <c r="H109" t="n">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="I109" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="110">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>369600</v>
+        <v>448200</v>
       </c>
       <c r="H116" t="n">
-        <v>2441</v>
+        <v>3022</v>
       </c>
       <c r="I116" t="n">
-        <v>392</v>
+        <v>471</v>
       </c>
     </row>
     <row r="117">
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H117" t="n">
         <v>1</v>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1767</v>
+        <v>1772</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>858</v>
+        <v>880</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H126" t="n">
         <v>25</v>
@@ -5685,10 +5685,10 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I128" t="n">
         <v>1</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H143" t="n">
         <v>10</v>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I144" t="n">
         <v>3</v>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H145" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I145" t="n">
         <v>2</v>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="H146" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I146" t="n">
         <v>2</v>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H147" t="n">
         <v>4</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H149" t="n">
         <v>6</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="H150" t="n">
         <v>4</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="H151" t="n">
         <v>5</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H157" t="n">
         <v>1</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H159" t="n">
         <v>3</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H160" t="n">
         <v>6</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H163" t="n">
         <v>4</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H167" t="n">
         <v>4</v>
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="H168" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="H169" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I169" t="n">
         <v>1</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="H170" t="n">
         <v>4</v>
@@ -7448,13 +7448,13 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H171" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H175" t="n">
         <v>3</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H176" t="n">
         <v>3</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="H179" t="n">
         <v>12</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H181" t="n">
         <v>3</v>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="H184" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I184" t="n">
         <v>3</v>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H185" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I185" t="n">
         <v>2</v>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H186" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I186" t="n">
         <v>6</v>
@@ -8104,13 +8104,13 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H187" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H189" t="n">
         <v>2</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H191" t="n">
         <v>11</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H192" t="n">
         <v>7</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="H194" t="n">
         <v>6</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="H195" t="n">
         <v>3</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="H196" t="n">
         <v>18</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H197" t="n">
         <v>4</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H199" t="n">
         <v>2</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="H201" t="n">
         <v>7</v>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H202" t="n">
         <v>5</v>
@@ -8801,10 +8801,10 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="H204" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I204" t="n">
         <v>2</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H205" t="n">
         <v>3</v>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H206" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H207" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H210" t="n">
         <v>5</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="H211" t="n">
         <v>5</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="H215" t="n">
         <v>4</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="H216" t="n">
         <v>5</v>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>936</v>
+        <v>950</v>
       </c>
       <c r="H218" t="n">
         <v>11</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H219" t="n">
         <v>6</v>
@@ -9457,13 +9457,13 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="H220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I220" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221">
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H221" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I221" t="n">
         <v>2</v>
@@ -9539,10 +9539,10 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="H222" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I222" t="n">
         <v>0</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H223" t="n">
         <v>4</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="H224" t="n">
         <v>4</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,10 +9703,10 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I226" t="n">
         <v>1</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="H227" t="n">
         <v>6</v>
@@ -9785,10 +9785,10 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H228" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H229" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I229" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="H230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H231" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="H233" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="H234" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -10072,10 +10072,10 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="H235" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -10113,13 +10113,13 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>5045</v>
+        <v>6997</v>
       </c>
       <c r="H236" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I236" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="237">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H237" t="n">
         <v>2</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H238" t="n">
         <v>2</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H239" t="n">
         <v>3</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10318,13 +10318,13 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H241" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H242" t="n">
         <v>4</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="H244" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I244" t="n">
         <v>0</v>
@@ -10482,13 +10482,13 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H245" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
@@ -10523,10 +10523,10 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H246" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I246" t="n">
         <v>0</v>
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H247" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I247" t="n">
         <v>3</v>
@@ -10605,10 +10605,10 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H248" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I248" t="n">
         <v>0</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H249" t="n">
         <v>3</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H252" t="n">
         <v>3</v>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="H253" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I253" t="n">
         <v>0</v>
@@ -10851,10 +10851,10 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H254" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I254" t="n">
         <v>0</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>122</v>
+        <v>316</v>
       </c>
       <c r="H256" t="n">
         <v>3</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>45</v>
+        <v>384</v>
       </c>
       <c r="H257" t="n">
         <v>3</v>
@@ -11015,10 +11015,10 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>50</v>
+        <v>356</v>
       </c>
       <c r="H258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I258" t="n">
         <v>0</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>51</v>
+        <v>360</v>
       </c>
       <c r="H260" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I260" t="n">
         <v>0</v>
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>24</v>
+        <v>190</v>
       </c>
       <c r="H261" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I261" t="n">
         <v>0</v>
@@ -11179,10 +11179,10 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="H262" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I262" t="n">
         <v>0</v>
@@ -11220,10 +11220,10 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="H263" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I263" t="n">
         <v>0</v>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="H264" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I264" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="H265" t="n">
         <v>1</v>
@@ -11343,13 +11343,13 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="H266" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -11384,13 +11384,13 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>77</v>
+        <v>417</v>
       </c>
       <c r="H267" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11466,7 +11466,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H269" t="n">
         <v>2</v>
@@ -11548,10 +11548,10 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="H271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I271" t="n">
         <v>0</v>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="H272" t="n">
         <v>4</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="H273" t="n">
         <v>3</v>
@@ -11671,10 +11671,10 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="H274" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I274" t="n">
         <v>0</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,10 +11753,10 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="H276" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I276" t="n">
         <v>0</v>
@@ -11794,13 +11794,13 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>53</v>
+        <v>155</v>
       </c>
       <c r="H277" t="n">
+        <v>4</v>
+      </c>
+      <c r="I277" t="n">
         <v>2</v>
-      </c>
-      <c r="I277" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -11835,13 +11835,1120 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>86</v>
+        <v>185</v>
       </c>
       <c r="H278" t="n">
+        <v>3</v>
+      </c>
+      <c r="I278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7661509710729743637</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thêm 1 tính năng muốn khách hàng hiểu rõ hơn về em Quevo 2pro#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>104</v>
+      </c>
+      <c r="H279" t="n">
+        <v>3</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7661427932539260180</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không muốn robot gặp lỗi thường xuyên thì không nên bỏ qua video này #qrevo2pro #roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>231</v>
+      </c>
+      <c r="H280" t="n">
+        <v>1</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7661305885108555028</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lưu ý để không mất tiền oan khi dùng robot lau nhà #qrevo2pro #roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>187</v>
+      </c>
+      <c r="H281" t="n">
         <v>2</v>
       </c>
-      <c r="I278" t="n">
-        <v>0</v>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7661305749364034836</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mùa nồm ẩm robot tự động có hiệu quả không #qrevo2pro #roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>328</v>
+      </c>
+      <c r="H282" t="n">
+        <v>7</v>
+      </c>
+      <c r="I282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7661250883543518472</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đâu là lựa chọn phù hợp cho ngôi nhà của bạn #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>341</v>
+      </c>
+      <c r="H283" t="n">
+        <v>3</v>
+      </c>
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7661249160171064583</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo2 Pro thách thức mọi ngóc ngách #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>269</v>
+      </c>
+      <c r="H284" t="n">
+        <v>1</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7661245395942509842</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trải nghiệm khi chưa có robot lau nhà và khi có robot lau nhà #qrevo2pro #Roborock #robothutbui  </t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>364</v>
+      </c>
+      <c r="H285" t="n">
+        <v>2</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7661469978004180244</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không gian trải nghiệm chuyên nghiệp tại: ____________ ROBOROCK STORE BUÔN MA THUỘT 🏠 Số 29 Trần Phú - Phường Buôn Ma Thuột - Tỉnh Đăk Lăk. #Qrevo2Pro #Roborock #robothutbui #robotlaunhadaklak </t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>115</v>
+      </c>
+      <c r="H286" t="n">
+        <v>3</v>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7661312931505720596</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>#Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>174</v>
+      </c>
+      <c r="H287" t="n">
+        <v>2</v>
+      </c>
+      <c r="I287" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7661272339232886037</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Khách em đã xài 3 đời nhà Roborock - review về sản phẩm. #Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>139</v>
+      </c>
+      <c r="H288" t="n">
+        <v>2</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7661255680904531221</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>#Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>110</v>
+      </c>
+      <c r="H289" t="n">
+        <v>1</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7661249311178919189</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Em mời Anh/chị ghé trải nghiệm máy tại showroom: ___________ ROBOROCK STORE BUÔN MA THUỘT 🏠 Số 29 Trần Phú - Phường Buôn Ma Thuột - Tỉnh Đăk Lăk. ☎️ 0964.642.842 - 097.664.9388 #Qrevo2Pro #Roborock #robothutbui #robotlaunhadaklak </t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>124</v>
+      </c>
+      <c r="H290" t="n">
+        <v>7</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7661231784289537300</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>#Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>137</v>
+      </c>
+      <c r="H291" t="n">
+        <v>3</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>quyrobot</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@quyrobot/video/7661298317313248519</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 pro bình xuyên vĩnh phúc cũ #suarobothutbui #qrevo2pro #quyrobot #robothutbui #roborock </t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>145</v>
+      </c>
+      <c r="H292" t="n">
+        <v>1</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7661602014954016021</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cứ gọi là hót hòn họt luôn ạ #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhướng </t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>2</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7661473046783364373</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roborock Qrevo 2 Pro chiến binh tầm trung siêu đỉnh qua em trải nghiệm nha các bác #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>99</v>
+      </c>
+      <c r="H294" t="n">
+        <v>4</v>
+      </c>
+      <c r="I294" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7661307834373508373</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qua em nha các bác #Qrevo2Pro #roborock #robothutbui #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>109</v>
+      </c>
+      <c r="H295" t="n">
+        <v>4</v>
+      </c>
+      <c r="I295" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7661303356194852116</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có robot cái rảnh cả ngày luôn #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>118</v>
+      </c>
+      <c r="H296" t="n">
+        <v>5</v>
+      </c>
+      <c r="I296" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7661598736014986504</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Các hai yêu ghé BOT để nhận tùm lum quà nha 😝😝 #Qrevo2Pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>24</v>
+      </c>
+      <c r="H297" t="n">
+        <v>1</v>
+      </c>
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7661520928689376519</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đã có đệ tử, dễ gì tui phải dọn nhà 😝 #Qrevo2Pro #Roborock #robothutbui  </t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>187</v>
+      </c>
+      <c r="H298" t="n">
+        <v>8</v>
+      </c>
+      <c r="I298" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>hatechz</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hatechz/video/7661450885398105352</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quà xing iu đã lên kệ chờ mọi ngừi ghé ạ 🫶🏻 #robothutbui #roborock #qrevo2pro #F25Ultra #f25series </t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>232</v>
+      </c>
+      <c r="H299" t="n">
+        <v>1</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7661542089586396437</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>103</v>
+      </c>
+      <c r="H300" t="n">
+        <v>1</v>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7661503102960405781</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#RobotHutBui #Roborock #Qrevo2Pro ##Momimart </t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>403</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7661443193581341973</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà có nhiều đồ thì có Sài robot được không?#RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>342</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7661605943527869716</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Video hướng dẫn cài app Qrevo 2 Pro. Đơn giản, chi tiết mà ai cũng làm được nhé cả nhà #Roborock #Qrevo2pro #Robotlaunha #huongdancaidat #RobotDucTrong</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>6</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7661289962519809300</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">“Robot hay cây đẩy?” – Câu hỏi khiến nhiều gia đình đau đầu hơn cả… tối nay ăn gì! 🤣 Thực ra chẳng có sản phẩm nào thắng sản phẩm nào cả. ✅ Nhà nhiều người đi làm, muốn lúc nào về cũng thấy sàn sạch → Robot  ✅ Nhà có con nhỏ, thú cưng, hay đổ nước, rơi cơm, bẩn bất chợt → Cây đẩy  👉 Đừng mua theo trend. 👉 Đừng mua vì người khác khen. Hãy mua vì nó phù hợp với chính gia đình mình. Còn nếu điều kiện cho phép… Robot lo việc hằng ngày, cây đẩy xử lý việc phát sinh. Hai đứa này không phải đối thủ, mà là đồng đội. 😆 #roborock #qrevo2pro #robotlaunha #f25ultra #trainghiemthucte </t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>134</v>
+      </c>
+      <c r="H304" t="n">
+        <v>2</v>
+      </c>
+      <c r="I304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7661243254192475399</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ai mà tìm hiểu robot mà bỏ qua thì tiếc cho Qrevo 2 pro lắm đó ạ #qrevo2pro #roborock #robotlaunha #robothutbui #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>250</v>
+      </c>
+      <c r="H305" t="n">
+        <v>3</v>
+      </c>
+      <c r="I305" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I305"/>
+  <dimension ref="A1:I310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>731</v>
+        <v>810</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="H14" t="n">
         <v>34</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H16" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H17" t="n">
         <v>25</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>52100</v>
+        <v>55000</v>
       </c>
       <c r="H23" t="n">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="I23" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>21600</v>
+        <v>24000</v>
       </c>
       <c r="H24" t="n">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="I24" t="n">
         <v>34</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1323</v>
+        <v>1408</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>660</v>
+        <v>694</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="H28" t="n">
         <v>5</v>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>616</v>
+        <v>653</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="H31" t="n">
         <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>428</v>
+        <v>457</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="H46" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I46" t="n">
         <v>9</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H49" t="n">
         <v>23</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1268</v>
+        <v>1293</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H59" t="n">
         <v>5</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1493</v>
+        <v>1542</v>
       </c>
       <c r="H65" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="H66" t="n">
         <v>33</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="H72" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I72" t="n">
         <v>61</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>78500</v>
+        <v>78800</v>
       </c>
       <c r="H78" t="n">
         <v>284</v>
       </c>
       <c r="I78" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79">
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2165</v>
+        <v>2252</v>
       </c>
       <c r="H87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I87" t="n">
         <v>7</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H93" t="n">
         <v>9</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H97" t="n">
         <v>1</v>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H103" t="n">
         <v>6</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H104" t="n">
         <v>2</v>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>10700</v>
+        <v>10900</v>
       </c>
       <c r="H108" t="n">
         <v>39</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3699</v>
+        <v>4349</v>
       </c>
       <c r="H109" t="n">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="I109" t="n">
         <v>29</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H113" t="n">
         <v>2</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H115" t="n">
         <v>1</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>448200</v>
+        <v>454700</v>
       </c>
       <c r="H116" t="n">
-        <v>3022</v>
+        <v>3067</v>
       </c>
       <c r="I116" t="n">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="117">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H119" t="n">
         <v>2</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H132" t="n">
         <v>2</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H146" t="n">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H149" t="n">
         <v>6</v>
@@ -6587,13 +6587,13 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="H150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -6628,13 +6628,13 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="H151" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H153" t="n">
         <v>3</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H159" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H160" t="n">
         <v>6</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="H168" t="n">
         <v>12</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="H169" t="n">
         <v>16</v>
@@ -7407,13 +7407,13 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="H171" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I171" t="n">
         <v>2</v>
@@ -7489,10 +7489,10 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H172" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I172" t="n">
         <v>1</v>
@@ -7530,13 +7530,13 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I173" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H174" t="n">
         <v>5</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H175" t="n">
         <v>3</v>
@@ -7776,13 +7776,13 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="H179" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H182" t="n">
         <v>1</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H183" t="n">
         <v>4</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H184" t="n">
         <v>7</v>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H186" t="n">
         <v>10</v>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H187" t="n">
         <v>11</v>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I188" t="n">
         <v>1</v>
@@ -8186,13 +8186,13 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H189" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="H191" t="n">
         <v>11</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H192" t="n">
         <v>7</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,13 +8391,13 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="H194" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195">
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H195" t="n">
         <v>3</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="H196" t="n">
         <v>18</v>
@@ -8514,13 +8514,13 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H197" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I197" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H199" t="n">
         <v>2</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H201" t="n">
         <v>7</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="H204" t="n">
         <v>7</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H205" t="n">
         <v>3</v>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H207" t="n">
         <v>7</v>
@@ -8965,13 +8965,13 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -9006,13 +9006,13 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -9047,13 +9047,13 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H210" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="H211" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="H215" t="n">
         <v>4</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="H216" t="n">
         <v>5</v>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>950</v>
+        <v>963</v>
       </c>
       <c r="H218" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I218" t="n">
         <v>3</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="H219" t="n">
         <v>6</v>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H220" t="n">
         <v>5</v>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="H224" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I224" t="n">
         <v>1</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H227" t="n">
         <v>6</v>
@@ -9785,10 +9785,10 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H228" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H229" t="n">
         <v>7</v>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H230" t="n">
         <v>3</v>
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H231" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H233" t="n">
         <v>9</v>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H234" t="n">
         <v>9</v>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H235" t="n">
         <v>10</v>
@@ -10113,10 +10113,10 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>6997</v>
+        <v>7587</v>
       </c>
       <c r="H236" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I236" t="n">
         <v>22</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H239" t="n">
         <v>3</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10318,10 +10318,10 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H241" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I241" t="n">
         <v>1</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H242" t="n">
         <v>4</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H244" t="n">
         <v>6</v>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H245" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I245" t="n">
         <v>2</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H247" t="n">
         <v>8</v>
@@ -10605,7 +10605,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H248" t="n">
         <v>11</v>
@@ -10646,13 +10646,13 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H249" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H252" t="n">
         <v>3</v>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="H253" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I253" t="n">
         <v>0</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="H256" t="n">
         <v>3</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="H257" t="n">
         <v>3</v>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H258" t="n">
         <v>2</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="H260" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I260" t="n">
         <v>0</v>
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="H261" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I261" t="n">
         <v>0</v>
@@ -11179,10 +11179,10 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="H262" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I262" t="n">
         <v>0</v>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H264" t="n">
         <v>6</v>
@@ -11302,13 +11302,13 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
@@ -11343,13 +11343,13 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="H266" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
@@ -11384,13 +11384,13 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>417</v>
+        <v>755</v>
       </c>
       <c r="H267" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I267" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
@@ -11425,13 +11425,13 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="H268" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -11466,13 +11466,13 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="H269" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -11548,13 +11548,13 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H271" t="n">
         <v>2</v>
       </c>
       <c r="I271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H272" t="n">
         <v>4</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="H273" t="n">
         <v>3</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="H274" t="n">
         <v>4</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="H277" t="n">
         <v>4</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="H278" t="n">
         <v>3</v>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>104</v>
+        <v>357</v>
       </c>
       <c r="H279" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I279" t="n">
         <v>0</v>
@@ -11917,13 +11917,13 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>231</v>
+        <v>374</v>
       </c>
       <c r="H280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -11958,10 +11958,10 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="H281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I281" t="n">
         <v>0</v>
@@ -11999,10 +11999,10 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="H282" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I282" t="n">
         <v>0</v>
@@ -12040,10 +12040,10 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="H283" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I283" t="n">
         <v>0</v>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="H284" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I284" t="n">
         <v>0</v>
@@ -12122,10 +12122,10 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="H285" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I285" t="n">
         <v>0</v>
@@ -12163,10 +12163,10 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H286" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I286" t="n">
         <v>0</v>
@@ -12204,10 +12204,10 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="H287" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I287" t="n">
         <v>2</v>
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="H288" t="n">
         <v>2</v>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H289" t="n">
         <v>1</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="H290" t="n">
         <v>7</v>
@@ -12368,7 +12368,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="H291" t="n">
         <v>3</v>
@@ -12409,10 +12409,10 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="H292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I292" t="n">
         <v>0</v>
@@ -12450,13 +12450,13 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="H293" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
@@ -12491,10 +12491,10 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="H294" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I294" t="n">
         <v>2</v>
@@ -12532,10 +12532,10 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H295" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I295" t="n">
         <v>5</v>
@@ -12573,10 +12573,10 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H296" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I296" t="n">
         <v>2</v>
@@ -12614,13 +12614,13 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>24</v>
+        <v>206</v>
       </c>
       <c r="H297" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I297" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -12655,13 +12655,13 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>187</v>
+        <v>378</v>
       </c>
       <c r="H298" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I298" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299">
@@ -12696,13 +12696,13 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>232</v>
+        <v>388</v>
       </c>
       <c r="H299" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I299" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="300">
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="H300" t="n">
         <v>1</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>403</v>
+        <v>432</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="H302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I302" t="n">
         <v>0</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>6</v>
+        <v>133</v>
       </c>
       <c r="H303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I303" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="H304" t="n">
         <v>2</v>
@@ -12942,13 +12942,218 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="H305" t="n">
         <v>3</v>
       </c>
       <c r="I305" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>longrobot_284</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@longrobot_284/video/7661927210483223829</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Lại là người đầu tiên, đập hộp sản phẩm mới của Roborock, lần này là bạn Qrevo 2 Pro, dự kiến là tâm điểm nửa cuối năm 2026 đây ạ!😍 #roborock #robothutbuilaunha #qrevo2pro #reviewrobot #longrobot</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>109</v>
+      </c>
+      <c r="H306" t="n">
+        <v>3</v>
+      </c>
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7661639131579043093</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chọn qrevo 2 pro uy tín luôn ạ #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhướng </t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>201</v>
+      </c>
+      <c r="H307" t="n">
+        <v>6</v>
+      </c>
+      <c r="I307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7661862783620762887</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test lực hút của Roborock Qrevo 2 Pro #Qrevo2Pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>139</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7661994026698198292</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bên mình luôn có sẵn những mẫu robot hút bụi lau nhà HOT nhất tại kho, không cần chờ order, không phải đợi cả tuần mới có máy. ✅ Hàng sẵn kho ✅ Xem máy trực tiếp ✅ Chốt là có thể lắp đặt ngay trong ngày (khi sắp xếp được lịch) Cần robot là có robot. Muốn nhà sạch là bên mình lên đường ngay! 🚗✨ Inbox để được tư vấn mẫu phù hợp và đặt lịch lắp đặt nhanh nhất nhé! #Roborock #Qrevo2pro #Robotlaunha #f25ultra✨ #qrevoedge2 </t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>5</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7661963630685998354</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lực hút đỉnh 25000pa phân khúc tầm trung khó bỏ qua Qrevo 2 pro có sẵn tại Xiaomi Phú Thọ ạ   #qrevo2pro #robothutbui #robotlaunha #roborock #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>40</v>
+      </c>
+      <c r="H310" t="n">
+        <v>1</v>
+      </c>
+      <c r="I310" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I310"/>
+  <dimension ref="A1:I322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>810</v>
+        <v>875</v>
       </c>
       <c r="H2" t="n">
         <v>5</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="H14" t="n">
         <v>34</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H17" t="n">
         <v>25</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>55000</v>
+        <v>57000</v>
       </c>
       <c r="H23" t="n">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="I23" t="n">
         <v>84</v>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="H24" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I24" t="n">
         <v>34</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1408</v>
+        <v>1457</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>694</v>
+        <v>708</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="H28" t="n">
         <v>5</v>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>653</v>
+        <v>682</v>
       </c>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="H31" t="n">
         <v>9</v>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H39" t="n">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="H46" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I46" t="n">
         <v>9</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="H49" t="n">
         <v>23</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1293</v>
+        <v>1322</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H59" t="n">
         <v>5</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H63" t="n">
         <v>6</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1542</v>
+        <v>3286</v>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>771</v>
+        <v>784</v>
       </c>
       <c r="H66" t="n">
         <v>33</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H77" t="n">
         <v>5</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>78800</v>
+        <v>80200</v>
       </c>
       <c r="H78" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I78" t="n">
         <v>78</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H84" t="n">
         <v>4</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H86" t="n">
         <v>6</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2252</v>
+        <v>2301</v>
       </c>
       <c r="H87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I87" t="n">
         <v>7</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H88" t="n">
         <v>3</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H98" t="n">
         <v>10</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H105" t="n">
         <v>3</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>10900</v>
+        <v>11000</v>
       </c>
       <c r="H108" t="n">
         <v>39</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>4349</v>
+        <v>4640</v>
       </c>
       <c r="H109" t="n">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I109" t="n">
         <v>29</v>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>454700</v>
+        <v>459900</v>
       </c>
       <c r="H116" t="n">
-        <v>3067</v>
+        <v>3092</v>
       </c>
       <c r="I116" t="n">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="117">
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H117" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H118" t="n">
         <v>4</v>
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H122" t="n">
         <v>3</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>900</v>
+        <v>977</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H136" t="n">
         <v>3</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H142" t="n">
         <v>2</v>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H145" t="n">
         <v>4</v>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H146" t="n">
         <v>8</v>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H147" t="n">
         <v>4</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H150" t="n">
         <v>6</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="H151" t="n">
         <v>7</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H157" t="n">
         <v>1</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H159" t="n">
         <v>4</v>
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H164" t="n">
         <v>4</v>
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="H168" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="H169" t="n">
         <v>16</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H173" t="n">
         <v>4</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H174" t="n">
         <v>5</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H175" t="n">
         <v>3</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H176" t="n">
         <v>3</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H177" t="n">
         <v>3</v>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H178" t="n">
         <v>4</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="H179" t="n">
         <v>15</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H180" t="n">
         <v>3</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H183" t="n">
         <v>4</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H184" t="n">
         <v>7</v>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H185" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H186" t="n">
         <v>10</v>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H188" t="n">
         <v>4</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H189" t="n">
         <v>5</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="H191" t="n">
         <v>11</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H192" t="n">
         <v>7</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="H194" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I194" t="n">
         <v>4</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="H195" t="n">
         <v>3</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="H196" t="n">
         <v>18</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H197" t="n">
         <v>5</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H199" t="n">
         <v>2</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H201" t="n">
         <v>7</v>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H202" t="n">
         <v>5</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H203" t="n">
         <v>4</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="H204" t="n">
         <v>7</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H206" t="n">
         <v>5</v>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H207" t="n">
         <v>7</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H208" t="n">
         <v>3</v>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H209" t="n">
         <v>5</v>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H210" t="n">
         <v>7</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H211" t="n">
         <v>8</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="H215" t="n">
         <v>4</v>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H216" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I216" t="n">
         <v>1</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>963</v>
+        <v>978</v>
       </c>
       <c r="H218" t="n">
         <v>12</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="H219" t="n">
         <v>6</v>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H220" t="n">
         <v>5</v>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H221" t="n">
         <v>6</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H222" t="n">
         <v>6</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H223" t="n">
+        <v>5</v>
+      </c>
+      <c r="I223" t="n">
         <v>4</v>
-      </c>
-      <c r="I223" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="224">
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="H224" t="n">
         <v>8</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H227" t="n">
         <v>6</v>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H230" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -9908,7 +9908,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H231" t="n">
         <v>12</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H233" t="n">
         <v>9</v>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H234" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -10072,10 +10072,10 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H235" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -10113,13 +10113,13 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>7587</v>
+        <v>7775</v>
       </c>
       <c r="H236" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I236" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="237">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H237" t="n">
         <v>2</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H238" t="n">
         <v>2</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="H241" t="n">
         <v>8</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H242" t="n">
         <v>4</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H244" t="n">
         <v>6</v>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H245" t="n">
         <v>8</v>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H246" t="n">
         <v>7</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H247" t="n">
         <v>8</v>
@@ -10605,7 +10605,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H248" t="n">
         <v>11</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H249" t="n">
         <v>4</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H252" t="n">
         <v>3</v>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="H253" t="n">
         <v>7</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -10933,13 +10933,13 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="H257" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I257" t="n">
         <v>0</v>
@@ -11015,10 +11015,10 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="H258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I258" t="n">
         <v>0</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="H260" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I260" t="n">
         <v>0</v>
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="H261" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I261" t="n">
         <v>0</v>
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H262" t="n">
         <v>5</v>
@@ -11220,7 +11220,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H263" t="n">
         <v>4</v>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H264" t="n">
         <v>6</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
@@ -11384,10 +11384,10 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>755</v>
+        <v>840</v>
       </c>
       <c r="H267" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I267" t="n">
         <v>3</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H268" t="n">
         <v>4</v>
@@ -11466,7 +11466,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H269" t="n">
         <v>6</v>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="H272" t="n">
         <v>4</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="H273" t="n">
         <v>3</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H274" t="n">
         <v>4</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H277" t="n">
         <v>4</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="H278" t="n">
         <v>3</v>
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="H279" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I279" t="n">
         <v>0</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="H280" t="n">
         <v>3</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,13 +11999,13 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="H282" t="n">
         <v>8</v>
       </c>
       <c r="I282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="H283" t="n">
         <v>4</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12163,10 +12163,10 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="H286" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I286" t="n">
         <v>0</v>
@@ -12204,10 +12204,10 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="H287" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I287" t="n">
         <v>2</v>
@@ -12245,10 +12245,10 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H288" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I288" t="n">
         <v>0</v>
@@ -12286,10 +12286,10 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I289" t="n">
         <v>0</v>
@@ -12327,10 +12327,10 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="H290" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I290" t="n">
         <v>0</v>
@@ -12368,10 +12368,10 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H291" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I291" t="n">
         <v>0</v>
@@ -12409,10 +12409,10 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I292" t="n">
         <v>0</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H293" t="n">
         <v>5</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H294" t="n">
         <v>5</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H295" t="n">
         <v>5</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H296" t="n">
         <v>6</v>
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>206</v>
+        <v>402</v>
       </c>
       <c r="H297" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I297" t="n">
         <v>2</v>
@@ -12655,10 +12655,10 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>378</v>
+        <v>490</v>
       </c>
       <c r="H298" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I298" t="n">
         <v>5</v>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="H299" t="n">
         <v>7</v>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="H300" t="n">
         <v>1</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="H302" t="n">
         <v>1</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="H303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I303" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H304" t="n">
         <v>2</v>
@@ -12942,10 +12942,10 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="H305" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I305" t="n">
         <v>1</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H307" t="n">
         <v>6</v>
@@ -13065,10 +13065,10 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="H308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I308" t="n">
         <v>0</v>
@@ -13106,10 +13106,10 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>5</v>
+        <v>166</v>
       </c>
       <c r="H309" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I309" t="n">
         <v>0</v>
@@ -13147,12 +13147,504 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>40</v>
+        <v>361</v>
       </c>
       <c r="H310" t="n">
+        <v>3</v>
+      </c>
+      <c r="I310" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7662251037633285384</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quà tặng bất ngờ #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>128</v>
+      </c>
+      <c r="H311" t="n">
+        <v>3</v>
+      </c>
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7662057108481019157</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Thực tế Roborock Qrevo 2 Pro khi leo thảm chùi chân #htsmarthome #roborock #robothutbui #Qrevo2Pro #robotlaunhadaklak </t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>269</v>
+      </c>
+      <c r="H312" t="n">
+        <v>2</v>
+      </c>
+      <c r="I312" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7662052868844686613</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tớ thân hình phụ nữ chứ mà về khoản nghịch phá thì mấy ổng thua xa. 🤣🤣 #roborock #Qrevo2Pro #robothutbui </t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>186</v>
+      </c>
+      <c r="H313" t="n">
+        <v>3</v>
+      </c>
+      <c r="I313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7662051722814033172</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#robothutbui #Qrevo2Pro #roborock </t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>172</v>
+      </c>
+      <c r="H314" t="n">
         <v>1</v>
       </c>
-      <c r="I310" t="n">
+      <c r="I314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7662045528770809108</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thông số pin của #roborock #Qrevo2Pro #robothutbui </t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>141</v>
+      </c>
+      <c r="H315" t="n">
+        <v>1</v>
+      </c>
+      <c r="I315" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7662044493251726612</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chi tiết từng bộ phận #robothutbui #roborock #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>182</v>
+      </c>
+      <c r="H316" t="n">
+        <v>3</v>
+      </c>
+      <c r="I316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7662042762996452628</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rất ấn tượng về cách sắp xếp các bộ phận của #roborock #Qrevo2Pro #robothutbui </t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>193</v>
+      </c>
+      <c r="H317" t="n">
+        <v>2</v>
+      </c>
+      <c r="I317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7662040418091044116</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cùng mình khám phá bên trong #roborock  #robothutbui #Qrevo2Pro có gì nhé. </t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>246</v>
+      </c>
+      <c r="H318" t="n">
+        <v>5</v>
+      </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662029235443240213</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghé shop em trải nghiệm thực tế nha các bác #Qrevo2Pro #roborock #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>196</v>
+      </c>
+      <c r="H319" t="n">
+        <v>5</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662020010134539541</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 pro xử lý vết bẩn dễ dàng #Qrevo2Pro #roborock #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>361</v>
+      </c>
+      <c r="H320" t="n">
+        <v>4</v>
+      </c>
+      <c r="I320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7662298436829515026</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bác nào muốn test hút tóc xem chống dối chổi chính không ạ. để em xin cmt bên dưới nhé ạ  #qrevo2pro #robothutbui #roborock #robotlaunha #xuhuong </t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>47</v>
+      </c>
+      <c r="H321" t="n">
+        <v>2</v>
+      </c>
+      <c r="I321" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7662220442446351624</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Các bác muốn test thêm tính năng gì cmt bên dưới em làm nhé ạ  #qrevo2pro #robothutbui #roborock #robotlaunha #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>106</v>
+      </c>
+      <c r="H322" t="n">
+        <v>1</v>
+      </c>
+      <c r="I322" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I322"/>
+  <dimension ref="A1:I342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>875</v>
+        <v>981</v>
       </c>
       <c r="H2" t="n">
         <v>5</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="H14" t="n">
         <v>34</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H16" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H17" t="n">
         <v>25</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H20" t="n">
         <v>11</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>57000</v>
+        <v>57600</v>
       </c>
       <c r="H23" t="n">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="I23" t="n">
         <v>84</v>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>25000</v>
+        <v>25400</v>
       </c>
       <c r="H24" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I24" t="n">
         <v>34</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1457</v>
+        <v>1524</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>679</v>
+        <v>700</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>708</v>
+        <v>739</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="H28" t="n">
         <v>5</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="H29" t="n">
         <v>11</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="H31" t="n">
         <v>9</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H39" t="n">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="H46" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I46" t="n">
         <v>9</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H48" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="H49" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I49" t="n">
         <v>3</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1322</v>
+        <v>1338</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H64" t="n">
         <v>4</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>3286</v>
+        <v>15100</v>
       </c>
       <c r="H65" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="H66" t="n">
         <v>33</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H69" t="n">
         <v>5</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H71" t="n">
         <v>6</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H73" t="n">
         <v>4</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>80200</v>
+        <v>82300</v>
       </c>
       <c r="H78" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I78" t="n">
         <v>78</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H83" t="n">
         <v>5</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2301</v>
+        <v>2364</v>
       </c>
       <c r="H87" t="n">
         <v>17</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H88" t="n">
         <v>3</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H93" t="n">
         <v>9</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,13 +4578,13 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H105" t="n">
         <v>3</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>4640</v>
+        <v>4925</v>
       </c>
       <c r="H109" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="I109" t="n">
         <v>29</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>459900</v>
+        <v>463000</v>
       </c>
       <c r="H116" t="n">
-        <v>3092</v>
+        <v>3118</v>
       </c>
       <c r="I116" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="117">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H119" t="n">
         <v>3</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>977</v>
+        <v>1071</v>
       </c>
       <c r="H125" t="n">
         <v>18</v>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H128" t="n">
         <v>4</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H136" t="n">
         <v>3</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H143" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H147" t="n">
         <v>4</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
@@ -6587,10 +6587,10 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H150" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I150" t="n">
         <v>1</v>
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="H151" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I151" t="n">
         <v>1</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H153" t="n">
         <v>4</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H157" t="n">
         <v>1</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H159" t="n">
         <v>4</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H161" t="n">
         <v>1</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="H168" t="n">
         <v>13</v>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="H169" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I169" t="n">
         <v>1</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="H179" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I179" t="n">
         <v>1</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H184" t="n">
         <v>7</v>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H186" t="n">
         <v>10</v>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H187" t="n">
         <v>11</v>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H189" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I189" t="n">
         <v>1</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H191" t="n">
         <v>11</v>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H192" t="n">
         <v>7</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H194" t="n">
         <v>8</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H195" t="n">
         <v>3</v>
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H196" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I196" t="n">
         <v>4</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H197" t="n">
         <v>5</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H200" t="n">
         <v>1</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H201" t="n">
         <v>7</v>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H202" t="n">
         <v>5</v>
@@ -8801,10 +8801,10 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="H204" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I204" t="n">
         <v>2</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H205" t="n">
         <v>4</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H206" t="n">
         <v>5</v>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H209" t="n">
         <v>5</v>
@@ -9088,10 +9088,10 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H211" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I211" t="n">
         <v>1</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="H215" t="n">
         <v>4</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="H216" t="n">
         <v>6</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="H218" t="n">
         <v>12</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H219" t="n">
         <v>6</v>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H220" t="n">
         <v>5</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H222" t="n">
         <v>6</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H223" t="n">
         <v>5</v>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="H224" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I224" t="n">
         <v>1</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H227" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H228" t="n">
         <v>7</v>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H229" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I229" t="n">
         <v>0</v>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H230" t="n">
         <v>4</v>
@@ -9908,7 +9908,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H231" t="n">
         <v>12</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H232" t="n">
         <v>5</v>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H233" t="n">
         <v>9</v>
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>7775</v>
+        <v>7947</v>
       </c>
       <c r="H236" t="n">
         <v>38</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H238" t="n">
         <v>2</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H239" t="n">
         <v>3</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H241" t="n">
         <v>8</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H242" t="n">
         <v>4</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H244" t="n">
         <v>6</v>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H245" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I245" t="n">
         <v>2</v>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H246" t="n">
         <v>7</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H247" t="n">
         <v>8</v>
@@ -10605,7 +10605,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H248" t="n">
         <v>11</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H249" t="n">
         <v>4</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H252" t="n">
         <v>3</v>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H253" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I253" t="n">
         <v>0</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -10933,10 +10933,10 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H256" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I256" t="n">
         <v>1</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="H260" t="n">
         <v>9</v>
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="H261" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I261" t="n">
         <v>0</v>
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H262" t="n">
         <v>5</v>
@@ -11220,7 +11220,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H263" t="n">
         <v>4</v>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H264" t="n">
         <v>6</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
@@ -11384,13 +11384,13 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>840</v>
+        <v>886</v>
       </c>
       <c r="H267" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="268">
@@ -11425,10 +11425,10 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H268" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I268" t="n">
         <v>1</v>
@@ -11466,10 +11466,10 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H269" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I269" t="n">
         <v>1</v>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H271" t="n">
         <v>2</v>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="H272" t="n">
         <v>4</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H273" t="n">
         <v>3</v>
@@ -11671,10 +11671,10 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H274" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I274" t="n">
         <v>0</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H277" t="n">
         <v>4</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="H278" t="n">
         <v>3</v>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="H279" t="n">
         <v>6</v>
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="H280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I280" t="n">
         <v>2</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,10 +11999,10 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="H282" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I282" t="n">
         <v>1</v>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="H283" t="n">
         <v>4</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="H286" t="n">
         <v>5</v>
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H288" t="n">
         <v>3</v>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H289" t="n">
         <v>2</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H290" t="n">
         <v>8</v>
@@ -12368,7 +12368,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H291" t="n">
         <v>4</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H293" t="n">
         <v>5</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H294" t="n">
         <v>5</v>
@@ -12532,13 +12532,13 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H295" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I295" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="296">
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H296" t="n">
         <v>6</v>
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>402</v>
+        <v>496</v>
       </c>
       <c r="H297" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I297" t="n">
         <v>2</v>
@@ -12655,10 +12655,10 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>490</v>
+        <v>550</v>
       </c>
       <c r="H298" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I298" t="n">
         <v>5</v>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H299" t="n">
         <v>7</v>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H300" t="n">
         <v>1</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H302" t="n">
         <v>1</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H303" t="n">
         <v>2</v>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H304" t="n">
         <v>2</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="H307" t="n">
         <v>6</v>
@@ -13065,10 +13065,10 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="H308" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I308" t="n">
         <v>0</v>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="H309" t="n">
         <v>3</v>
@@ -13147,13 +13147,13 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
       </c>
       <c r="I310" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311">
@@ -13188,10 +13188,10 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="H311" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I311" t="n">
         <v>0</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>269</v>
+        <v>426</v>
       </c>
       <c r="H312" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I312" t="n">
         <v>4</v>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="H313" t="n">
         <v>3</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="H314" t="n">
         <v>1</v>
@@ -13352,7 +13352,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="H315" t="n">
         <v>1</v>
@@ -13393,10 +13393,10 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="H316" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I316" t="n">
         <v>0</v>
@@ -13434,13 +13434,13 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="H317" t="n">
+        <v>4</v>
+      </c>
+      <c r="I317" t="n">
         <v>2</v>
-      </c>
-      <c r="I317" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>246</v>
+        <v>335</v>
       </c>
       <c r="H318" t="n">
         <v>5</v>
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="H319" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I319" t="n">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="H320" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I320" t="n">
         <v>0</v>
@@ -13598,13 +13598,13 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>47</v>
+        <v>359</v>
       </c>
       <c r="H321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I321" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -13639,12 +13639,832 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>106</v>
+        <v>261</v>
       </c>
       <c r="H322" t="n">
+        <v>4</v>
+      </c>
+      <c r="I322" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7662603103866244372</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chắc là robot lau không sạch đâu. Làm sao mà nó ghi nhớ đuo2cj. Đây là những câu nói mk khách nói khi nghe về Robot hút bụi lau nhà. Và đây chắc không sạch đâu🤭🤭 em cho khách thấy sự chăm chỉ,sạch sẽ và khả năng ghi nhớ của Roborock🥰🥰🥰#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>134</v>
+      </c>
+      <c r="H323" t="n">
+        <v>0</v>
+      </c>
+      <c r="I323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7662599216698494228</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Làm cái video giới thiệu QUevo 2pro mà thấy hơn phim hành động😆😆#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>126</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0</v>
+      </c>
+      <c r="I324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7662703051794435346</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QRevo 2 Pro có gì mà lại được lòng mọi người đến vậy. Thử xem nhé #robothutbui #qrevo2pro #roborock #fyp #3tsmart </t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>30</v>
+      </c>
+      <c r="H325" t="n">
+        <v>0</v>
+      </c>
+      <c r="I325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7662571805814639890</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hướng dẫn cách giảm stress #robothutbui #qrevo2pro #roborock #3tsmart </t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>337</v>
+      </c>
+      <c r="H326" t="n">
+        <v>9</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662706826248506645</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Như này các chị đẹp đã ưng em chưa ạ #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G327" t="n">
+        <v>17</v>
+      </c>
+      <c r="H327" t="n">
+        <v>3</v>
+      </c>
+      <c r="I327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662691854332218645</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roborock Qrevo 2 Pro chiến binh tầm trung đáng lưu tâm #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G328" t="n">
+        <v>25</v>
+      </c>
+      <c r="H328" t="n">
+        <v>4</v>
+      </c>
+      <c r="I328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662591587871902997</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Với 25.000 Pa Qrevo 2 pro làm được những gì #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G329" t="n">
+        <v>168</v>
+      </c>
+      <c r="H329" t="n">
+        <v>2</v>
+      </c>
+      <c r="I329" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662405485471042837</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dọn nhà không còn là vấn  nan giải khi có roborock qrevo 2 pro #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhướng </t>
+        </is>
+      </c>
+      <c r="G330" t="n">
+        <v>367</v>
+      </c>
+      <c r="H330" t="n">
+        <v>8</v>
+      </c>
+      <c r="I330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662383873250217237</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tìm hiểu các tính năng làm sạch của qrevo 2 pro #Qrevo2Pro #roborock #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G331" t="n">
+        <v>140</v>
+      </c>
+      <c r="H331" t="n">
+        <v>4</v>
+      </c>
+      <c r="I331" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662367285104971029</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Các bác nào còn thắc mắc là nhà nhiều đồ có dùng được robot không thì qua em trải nghiệm thực tế nhé #Qrevo2Pro #roborock #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>369</v>
+      </c>
+      <c r="H332" t="n">
+        <v>4</v>
+      </c>
+      <c r="I332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7662598767866252564</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cứ sắm e sen là hết cãi nhau các bác ạ. #Qrevo2pro #roborock #robothutbui #quyrobot </t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>131</v>
+      </c>
+      <c r="H333" t="n">
+        <v>2</v>
+      </c>
+      <c r="I333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7662561459939069192</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ok chị iuu 😝 mời khách ghé BOT trải nghiệm sản phẩm ạ #Qrevo2Pro #Roborock #robothutbui #robothutbuiGiaLai </t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>154</v>
+      </c>
+      <c r="H334" t="n">
+        <v>3</v>
+      </c>
+      <c r="I334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>bothome_robotgialai</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@bothome_robotgialai/video/7662402343652183314</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test độ làm sạch của robot  #Qrevo2Pro #Roborock #robothutbui #robothutbuiGiaLai </t>
+        </is>
+      </c>
+      <c r="G335" t="n">
+        <v>154</v>
+      </c>
+      <c r="H335" t="n">
+        <v>6</v>
+      </c>
+      <c r="I335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7662560798732012820</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mắc roborock Edge 2 là mắc bán chạy nhất của nhà bên em luôn nhé an#RobotHutBui #Roborock #Qrevo2Pro #Momimart #edge2 </t>
+        </is>
+      </c>
+      <c r="G336" t="n">
+        <v>119</v>
+      </c>
+      <c r="H336" t="n">
+        <v>0</v>
+      </c>
+      <c r="I336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7662368026364300565</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kỹ thuật có kinh nghiệm 8 năm trong nghề hướng dẫn lắp đặt máy tại nhà khách. Roborock#RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G337" t="n">
+        <v>132</v>
+      </c>
+      <c r="H337" t="n">
         <v>1</v>
       </c>
-      <c r="I322" t="n">
+      <c r="I337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7662366026897624340</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🚨 Đừng mua robot hay máy hút bụi cầm tay một cách mơ hồ! Rất nhiều khách hàng đã từng chọn theo review, theo quảng cáo hoặc theo lời giới thiệu… nhưng đến khi trải nghiệm thực tế mới nhận ra: mình suýt mua nhầm! 🔥 Từ 15/07, H&amp;T Smart Home Đức Trọng mở chương trình TRẢI NGHIỆM THỰC TẾ. Đến để: ✅ Test trực tiếp robot hút bụi và máy hút bụi cầm tay. ✅ So sánh khả năng làm sạch trên nhiều loại bề mặt. ✅ Được tư vấn đúng nhu cầu, không mua dư tính năng, không lãng phí tiền. Chỉ cần trải nghiệm vài phút, bạn sẽ biết đâu mới là lựa chọn phù hợp nhất cho gia đình mình. 📍 H&amp;T Smart Home Đức Trọng 🏠 384 Thống Nhất ⚠️ Đừng để đến khi đã mua rồi mới biết: “Giá như mình đến trải nghiệm trước!” #Roborock #Qrevo2pro #Robotlaunha #f25ultra✨ #trainghiemthucte </t>
+        </is>
+      </c>
+      <c r="G338" t="n">
+        <v>382</v>
+      </c>
+      <c r="H338" t="n">
+        <v>5</v>
+      </c>
+      <c r="I338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7662680383766416648</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 pro phân khúc giá tầm trung nhưng có tính năng như dòng 20tr 🤩 🚘 Các bác qua 05 Nguyễn Du, Nông Trang, Việt Trì trải nghiệm nhé ạ  #qrevo2pro #robothutbui #robotlaunha #roborock #xuhuong </t>
+        </is>
+      </c>
+      <c r="G339" t="n">
+        <v>52</v>
+      </c>
+      <c r="H339" t="n">
+        <v>0</v>
+      </c>
+      <c r="I339" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7662597427123211528</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giặt giẻ nước nóng, tự vệ sinh dock sạc mà giá hơn 12 đồng 😳 Qua luôn 05 Nguyễn Du, Nông Trang, Việt Trì trải nghiệm mua sắm đơn vị to uy tín luôn ạ  #qrevo2pro #roborock #robothutbui #robotlaunha #xuhuong </t>
+        </is>
+      </c>
+      <c r="G340" t="n">
+        <v>269</v>
+      </c>
+      <c r="H340" t="n">
+        <v>3</v>
+      </c>
+      <c r="I340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7662535498015051026</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">có robot nhàn tênh luôn, ko có thấy mệt liền.  #qrevo2pro #robothutbui #roborock #xuhuong #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G341" t="n">
+        <v>242</v>
+      </c>
+      <c r="H341" t="n">
+        <v>2</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>homebotvietnam</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homebotvietnam/video/7662393380043066644</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Ai bận rộn chắc sẽ mê em này! ⏰🤖 Dọn nhà thông minh, tiết kiệm thời gian mỗi ngày. ✨🏠 #Qrevo2Pro #Roborock #robothutbui #SmartHome #ReviewCongNghe</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
+        <v>372</v>
+      </c>
+      <c r="H342" t="n">
+        <v>0</v>
+      </c>
+      <c r="I342" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I342"/>
+  <dimension ref="A1:I358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>981</v>
+        <v>1096</v>
       </c>
       <c r="H2" t="n">
         <v>5</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>499</v>
+        <v>575</v>
       </c>
       <c r="H14" t="n">
         <v>34</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H15" t="n">
         <v>5</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H16" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H17" t="n">
         <v>25</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H20" t="n">
         <v>11</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>57600</v>
+        <v>57800</v>
       </c>
       <c r="H23" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I23" t="n">
         <v>84</v>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>25400</v>
+        <v>25600</v>
       </c>
       <c r="H24" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I24" t="n">
         <v>34</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1524</v>
+        <v>1550</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="H28" t="n">
         <v>5</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="H29" t="n">
         <v>11</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="H46" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I46" t="n">
         <v>9</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1338</v>
+        <v>1354</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H59" t="n">
         <v>6</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H63" t="n">
         <v>7</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H64" t="n">
         <v>4</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>15100</v>
+        <v>24900</v>
       </c>
       <c r="H65" t="n">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>795</v>
+        <v>811</v>
       </c>
       <c r="H66" t="n">
         <v>33</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H69" t="n">
         <v>5</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H77" t="n">
         <v>5</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>82300</v>
+        <v>83600</v>
       </c>
       <c r="H78" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I78" t="n">
         <v>78</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H86" t="n">
         <v>6</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2364</v>
+        <v>2383</v>
       </c>
       <c r="H87" t="n">
         <v>17</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H88" t="n">
         <v>3</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H98" t="n">
         <v>10</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H102" t="n">
         <v>3</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H105" t="n">
         <v>3</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>11000</v>
+        <v>11100</v>
       </c>
       <c r="H108" t="n">
         <v>39</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>4925</v>
+        <v>5137</v>
       </c>
       <c r="H109" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I109" t="n">
         <v>29</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>463000</v>
+        <v>465400</v>
       </c>
       <c r="H116" t="n">
-        <v>3118</v>
+        <v>3132</v>
       </c>
       <c r="I116" t="n">
         <v>486</v>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H117" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H118" t="n">
         <v>5</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H126" t="n">
         <v>25</v>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H128" t="n">
         <v>4</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H136" t="n">
         <v>3</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H142" t="n">
         <v>3</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H143" t="n">
         <v>11</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H150" t="n">
         <v>7</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="H151" t="n">
         <v>10</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="H159" t="n">
         <v>4</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H160" t="n">
         <v>6</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H161" t="n">
         <v>1</v>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H162" t="n">
         <v>2</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H168" t="n">
         <v>13</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H173" t="n">
         <v>4</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H174" t="n">
         <v>5</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H175" t="n">
         <v>3</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H176" t="n">
         <v>3</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H177" t="n">
         <v>3</v>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H178" t="n">
         <v>4</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H179" t="n">
         <v>17</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H180" t="n">
         <v>3</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H181" t="n">
         <v>3</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H184" t="n">
         <v>7</v>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H188" t="n">
         <v>4</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="H191" t="n">
         <v>11</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,13 +8391,13 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="H194" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195">
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="H195" t="n">
         <v>3</v>
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="H196" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I196" t="n">
         <v>4</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H197" t="n">
         <v>5</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H199" t="n">
         <v>2</v>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H202" t="n">
         <v>5</v>
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H203" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H205" t="n">
         <v>4</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H208" t="n">
         <v>3</v>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H209" t="n">
         <v>5</v>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H210" t="n">
         <v>7</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="H215" t="n">
         <v>4</v>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H216" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I216" t="n">
         <v>1</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="H218" t="n">
         <v>12</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H219" t="n">
         <v>6</v>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H220" t="n">
         <v>5</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H222" t="n">
         <v>6</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H223" t="n">
         <v>5</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H224" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H227" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
@@ -9785,10 +9785,10 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H228" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H229" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I229" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H230" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H231" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="H232" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H233" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H234" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -10072,10 +10072,10 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H235" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>7947</v>
+        <v>8060</v>
       </c>
       <c r="H236" t="n">
         <v>38</v>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H237" t="n">
         <v>2</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H238" t="n">
         <v>2</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H239" t="n">
         <v>3</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H241" t="n">
         <v>8</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H242" t="n">
         <v>4</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H244" t="n">
         <v>6</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H247" t="n">
         <v>8</v>
@@ -10605,7 +10605,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H248" t="n">
         <v>11</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H249" t="n">
         <v>4</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H252" t="n">
         <v>3</v>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H253" t="n">
         <v>8</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H256" t="n">
         <v>5</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H257" t="n">
         <v>4</v>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H258" t="n">
         <v>3</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="H260" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I260" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H261" t="n">
         <v>18</v>
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H262" t="n">
         <v>5</v>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H264" t="n">
         <v>6</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>886</v>
+        <v>908</v>
       </c>
       <c r="H267" t="n">
         <v>26</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H268" t="n">
         <v>5</v>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H271" t="n">
         <v>2</v>
@@ -11589,10 +11589,10 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H272" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I272" t="n">
         <v>0</v>
@@ -11630,10 +11630,10 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="H273" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I273" t="n">
         <v>2</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H277" t="n">
         <v>4</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="H278" t="n">
         <v>3</v>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="H279" t="n">
         <v>6</v>
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="H280" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I280" t="n">
         <v>2</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,10 +11999,10 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="H282" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I282" t="n">
         <v>1</v>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="H283" t="n">
         <v>4</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="H287" t="n">
         <v>6</v>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H289" t="n">
         <v>2</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H290" t="n">
         <v>8</v>
@@ -12368,10 +12368,10 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H291" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I291" t="n">
         <v>0</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H293" t="n">
         <v>5</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H294" t="n">
         <v>5</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H295" t="n">
         <v>6</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H296" t="n">
         <v>6</v>
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>496</v>
+        <v>530</v>
       </c>
       <c r="H297" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I297" t="n">
         <v>2</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="H298" t="n">
         <v>22</v>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H299" t="n">
         <v>7</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H302" t="n">
         <v>1</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H303" t="n">
         <v>2</v>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H304" t="n">
         <v>2</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H307" t="n">
         <v>6</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H308" t="n">
         <v>4</v>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H309" t="n">
         <v>3</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
@@ -13188,10 +13188,10 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H311" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I311" t="n">
         <v>0</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>426</v>
+        <v>490</v>
       </c>
       <c r="H312" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I312" t="n">
         <v>4</v>
@@ -13270,10 +13270,10 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="H313" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I313" t="n">
         <v>0</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="H314" t="n">
         <v>1</v>
@@ -13352,7 +13352,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H315" t="n">
         <v>1</v>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="H316" t="n">
         <v>7</v>
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="H317" t="n">
         <v>4</v>
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="H318" t="n">
         <v>5</v>
@@ -13516,7 +13516,7 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H319" t="n">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="H320" t="n">
         <v>6</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="H321" t="n">
         <v>3</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="H322" t="n">
         <v>4</v>
@@ -13680,10 +13680,10 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>134</v>
+        <v>378</v>
       </c>
       <c r="H323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I323" t="n">
         <v>0</v>
@@ -13721,10 +13721,10 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>126</v>
+        <v>315</v>
       </c>
       <c r="H324" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I324" t="n">
         <v>0</v>
@@ -13762,13 +13762,13 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>30</v>
+        <v>303</v>
       </c>
       <c r="H325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="H326" t="n">
         <v>9</v>
@@ -13844,10 +13844,10 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>17</v>
+        <v>254</v>
       </c>
       <c r="H327" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I327" t="n">
         <v>0</v>
@@ -13885,13 +13885,13 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="H328" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I328" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -13926,10 +13926,10 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>168</v>
+        <v>296</v>
       </c>
       <c r="H329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I329" t="n">
         <v>2</v>
@@ -13967,7 +13967,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="H330" t="n">
         <v>8</v>
@@ -14008,10 +14008,10 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="H331" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I331" t="n">
         <v>2</v>
@@ -14049,7 +14049,7 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="H332" t="n">
         <v>4</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="H333" t="n">
         <v>2</v>
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="H334" t="n">
         <v>3</v>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="H335" t="n">
         <v>6</v>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="H337" t="n">
         <v>1</v>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="H338" t="n">
         <v>5</v>
@@ -14336,10 +14336,10 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="H339" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I339" t="n">
         <v>0</v>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>269</v>
+        <v>372</v>
       </c>
       <c r="H340" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I340" t="n">
         <v>0</v>
@@ -14418,10 +14418,10 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="H341" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I341" t="n">
         <v>0</v>
@@ -14459,12 +14459,668 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
       </c>
       <c r="I342" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7662997467893353749</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thay vì phải đau lưng lau nhà thì mình chọn chill chill ngồi nhìn con sen nó lau nhà đi thôi🤭🤭#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G343" t="n">
+        <v>101</v>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7662993805758565653</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G344" t="n">
+        <v>119</v>
+      </c>
+      <c r="H344" t="n">
+        <v>1</v>
+      </c>
+      <c r="I344" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7663024544826969352</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhìn là mê ngay thiết kế này #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G345" t="n">
+        <v>64</v>
+      </c>
+      <c r="H345" t="n">
+        <v>0</v>
+      </c>
+      <c r="I345" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7662916180155338004</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ưu và nhược điểm của Robot hút bụi lau nhà tự động và robot hút bụi lau nhà cầm tay #qrevo2pro #roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G346" t="n">
+        <v>124</v>
+      </c>
+      <c r="H346" t="n">
+        <v>2</v>
+      </c>
+      <c r="I346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7662759839638113556</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Black or white? #roborock #robothutbui #Qrevo2Pro #robotlaunhadaklak </t>
+        </is>
+      </c>
+      <c r="G347" t="n">
+        <v>150</v>
+      </c>
+      <c r="H347" t="n">
+        <v>3</v>
+      </c>
+      <c r="I347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7662747537794731284</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#CapCut #robothutbui #roborock #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G348" t="n">
+        <v>144</v>
+      </c>
+      <c r="H348" t="n">
+        <v>6</v>
+      </c>
+      <c r="I348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7662746458482920725</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Qrevo2Pro #robotlaunhadaklak #robothutbui #roborock </t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>135</v>
+      </c>
+      <c r="H349" t="n">
+        <v>3</v>
+      </c>
+      <c r="I349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7663055009147653396</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cứ gọi là không chê vào đâu được ạ #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhướng </t>
+        </is>
+      </c>
+      <c r="G350" t="n">
+        <v>45</v>
+      </c>
+      <c r="H350" t="n">
+        <v>3</v>
+      </c>
+      <c r="I350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662947057757392149</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Các bác đã biết tháo lắp chổi chính của robot chưa ạ #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhướng </t>
+        </is>
+      </c>
+      <c r="G351" t="n">
+        <v>101</v>
+      </c>
+      <c r="H351" t="n">
+        <v>1</v>
+      </c>
+      <c r="I351" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662941692269497621</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roborock Qrevo 2 Pro làm được gì với lực hút 25.000 pa #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G352" t="n">
+        <v>169</v>
+      </c>
+      <c r="H352" t="n">
+        <v>2</v>
+      </c>
+      <c r="I352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7662736356698836245</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cứ gọi là ngon bổ tài chisnh trong tầm tay ạ #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G353" t="n">
+        <v>166</v>
+      </c>
+      <c r="H353" t="n">
+        <v>6</v>
+      </c>
+      <c r="I353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7663081242031836437</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cứ nhấc e nó các bác nhé #Qrevo2pro #robothutbui #roborock #xuhuongtiktok #quyrobot </t>
+        </is>
+      </c>
+      <c r="G354" t="n">
+        <v>14</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7663075933972155669</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Không cần mức giá cao để sở hữu trải nghiệm dọn dẹp thông minh, trong những màn đấu với rác bụi và những thử thách trên sàn, Qrevo 2 Pro vô địch trong tầm giá khi sở hữu hàng loạt hiệu năng khủng: ✨ Lực hút HyperForce 25.000Pa mạnh mẽ, xử lý gọn từ bụi mịn, rác vụn đến tóc rụng và lông thú cưng ✨ Hệ thống chống rối toàn thân được chứng nhận, giúp duy trì hiệu suất làm sạch ổn định và giảm thiểu thao tác gỡ tóc thủ công ✨ Giẻ lau cạnh FlexiArm™ tự động mở rộng sát mép tường và chân nội thất, chăm kỹ những vị trí thường dễ bị bỏ sót ✨ Chổi cạnh đảo chiều thế hệ mới tối ưu khả năng gom bụi sát góc, tăng độ bao phủ làm sạch ✨ Tự động tháo rời giẻ lau trước khi làm sạch thảm, giúp hạn chế bẩn chéo và giữ thảm luôn khô ráo ✨  Khay giặt tự làm sạch thế hệ 2 giúp dock sạch lâu hơn, giảm công sức vệ sinh định kỳ ✨  Dock đa năng tự giặt và sấy sau mỗi chu trình, để robot luôn sẵn sàng cho lần làm sạch tiếp theo Bạn đã sẵn sàng cùng Qrevo 2 Pro nâng cúp cho chuẩn sống thảnh thơi mới ✨ #Roborock ##RobotDucTrong#Qrevo2Pro #roborock</t>
+        </is>
+      </c>
+      <c r="G355" t="n">
+        <v>24</v>
+      </c>
+      <c r="H355" t="n">
+        <v>1</v>
+      </c>
+      <c r="I355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7662759380080790804</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot ngon không thiếu, nhưng Qrevo 2 Pro là mẫu đáng để trải nghiệm trực tiếp nhất lúc này! Đừng mua robot chỉ qua video! Đến ngay H&amp;T Smart Home Đức Trọng - 384 Thống Nhất trải nghiệm thực tế để thấy khác biệt về lực hút và khả năng lau nhà so với các dòng robot khác trước khi chọn mua nhé! #Roborock #Qrevo2pro #Robotlaunha #trainghiemthucte #RobotDucTrong </t>
+        </is>
+      </c>
+      <c r="G356" t="n">
+        <v>309</v>
+      </c>
+      <c r="H356" t="n">
+        <v>2</v>
+      </c>
+      <c r="I356" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7663081686124547335</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 pro lực hút 25000pa giá chỉ hơn chục thôi 😳😳😳 🏠 Trải nghiệm tại Xiaomi Phú Thọ nhé các bác 🚘 05 Nguyễn Du, Nông Trang, Việt Trì ạ: 0862505508 #qrevo2pro #robothutbui #roborock #robotlaunha #xuhuong </t>
+        </is>
+      </c>
+      <c r="G357" t="n">
+        <v>21</v>
+      </c>
+      <c r="H357" t="n">
+        <v>1</v>
+      </c>
+      <c r="I357" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>nhadepbepxinh.camxuyen</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nhadepbepxinh.camxuyen/video/7662932971392994578</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Let go💪 🚗🏡 Hành trình đi lắp đặt Roborock Qrevo 2 Pro cho khách yêu! Mỗi đơn hàng không chỉ là giao máy, mà còn là mang đến một trải nghiệm sử dụng trọn vẹn. ❤️</t>
+        </is>
+      </c>
+      <c r="G358" t="n">
+        <v>128</v>
+      </c>
+      <c r="H358" t="n">
+        <v>4</v>
+      </c>
+      <c r="I358" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I358"/>
+  <dimension ref="A1:I390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1096</v>
+        <v>1194</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>575</v>
+        <v>639</v>
       </c>
       <c r="H14" t="n">
         <v>34</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H16" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H17" t="n">
         <v>25</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>57800</v>
+        <v>58000</v>
       </c>
       <c r="H23" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I23" t="n">
         <v>84</v>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>25600</v>
+        <v>25700</v>
       </c>
       <c r="H24" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I24" t="n">
         <v>34</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1550</v>
+        <v>1580</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>751</v>
+        <v>770</v>
       </c>
       <c r="H27" t="n">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="H28" t="n">
         <v>5</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H39" t="n">
         <v>9</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="H46" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I46" t="n">
         <v>9</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H48" t="n">
         <v>15</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1354</v>
+        <v>1377</v>
       </c>
       <c r="H50" t="n">
         <v>13</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H63" t="n">
         <v>7</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H64" t="n">
         <v>4</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>24900</v>
+        <v>35800</v>
       </c>
       <c r="H65" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>811</v>
+        <v>833</v>
       </c>
       <c r="H66" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I66" t="n">
         <v>26</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>83600</v>
+        <v>84200</v>
       </c>
       <c r="H78" t="n">
         <v>292</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H80" t="n">
         <v>1</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2383</v>
+        <v>2416</v>
       </c>
       <c r="H87" t="n">
         <v>17</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>5137</v>
+        <v>5299</v>
       </c>
       <c r="H109" t="n">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I109" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>465400</v>
+        <v>467500</v>
       </c>
       <c r="H116" t="n">
-        <v>3132</v>
+        <v>3137</v>
       </c>
       <c r="I116" t="n">
         <v>486</v>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H117" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H118" t="n">
         <v>5</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5439,13 +5439,13 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="H124" t="n">
         <v>15</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H126" t="n">
         <v>25</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2600</v>
+        <v>2603</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H143" t="n">
         <v>11</v>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H145" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H153" t="n">
         <v>4</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H159" t="n">
         <v>4</v>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H162" t="n">
         <v>2</v>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H167" t="n">
         <v>4</v>
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="H168" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H180" t="n">
         <v>3</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H181" t="n">
         <v>3</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H183" t="n">
         <v>4</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="H191" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I191" t="n">
         <v>2</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="H194" t="n">
         <v>9</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H195" t="n">
         <v>3</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H203" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H215" t="n">
         <v>4</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="H216" t="n">
         <v>7</v>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="H218" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I218" t="n">
         <v>3</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H219" t="n">
         <v>6</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H224" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H227" t="n">
         <v>8</v>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H228" t="n">
         <v>9</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H229" t="n">
         <v>9</v>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H230" t="n">
         <v>5</v>
@@ -9908,7 +9908,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H231" t="n">
         <v>13</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="H232" t="n">
         <v>6</v>
@@ -10113,13 +10113,13 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>8060</v>
+        <v>8157</v>
       </c>
       <c r="H236" t="n">
         <v>38</v>
       </c>
       <c r="I236" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="237">
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H238" t="n">
         <v>2</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H239" t="n">
         <v>3</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H244" t="n">
         <v>6</v>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H246" t="n">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H252" t="n">
         <v>3</v>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="H253" t="n">
         <v>8</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H258" t="n">
         <v>3</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="H260" t="n">
         <v>10</v>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H261" t="n">
         <v>18</v>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H264" t="n">
         <v>6</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>908</v>
+        <v>921</v>
       </c>
       <c r="H267" t="n">
         <v>26</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H268" t="n">
         <v>5</v>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H272" t="n">
         <v>5</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H273" t="n">
         <v>4</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H274" t="n">
         <v>5</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H277" t="n">
         <v>4</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="H278" t="n">
         <v>3</v>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="H279" t="n">
         <v>6</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="H280" t="n">
         <v>5</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="H282" t="n">
         <v>10</v>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H283" t="n">
         <v>4</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12163,10 +12163,10 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H286" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I286" t="n">
         <v>0</v>
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H287" t="n">
         <v>6</v>
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H288" t="n">
         <v>3</v>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H289" t="n">
         <v>2</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H290" t="n">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H294" t="n">
         <v>5</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H295" t="n">
         <v>6</v>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>530</v>
+        <v>556</v>
       </c>
       <c r="H297" t="n">
         <v>25</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="H298" t="n">
         <v>22</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H303" t="n">
         <v>2</v>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H304" t="n">
         <v>2</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H308" t="n">
         <v>4</v>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H309" t="n">
         <v>3</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H311" t="n">
         <v>5</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="H312" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I312" t="n">
         <v>4</v>
@@ -13270,10 +13270,10 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H313" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I313" t="n">
         <v>0</v>
@@ -13311,10 +13311,10 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="H314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I314" t="n">
         <v>0</v>
@@ -13352,10 +13352,10 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I315" t="n">
         <v>0</v>
@@ -13393,10 +13393,10 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="H316" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I316" t="n">
         <v>0</v>
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="H317" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I317" t="n">
         <v>2</v>
@@ -13475,10 +13475,10 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="H318" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I318" t="n">
         <v>0</v>
@@ -13516,7 +13516,7 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H319" t="n">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H320" t="n">
         <v>6</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="H321" t="n">
         <v>3</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="H322" t="n">
         <v>4</v>
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="H323" t="n">
         <v>1</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H324" t="n">
         <v>2</v>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="H325" t="n">
         <v>2</v>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H326" t="n">
         <v>9</v>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="H327" t="n">
         <v>6</v>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H328" t="n">
         <v>10</v>
@@ -13926,7 +13926,7 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H329" t="n">
         <v>3</v>
@@ -13967,7 +13967,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H330" t="n">
         <v>8</v>
@@ -14049,7 +14049,7 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H332" t="n">
         <v>4</v>
@@ -14090,13 +14090,13 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H334" t="n">
         <v>3</v>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H335" t="n">
         <v>6</v>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H337" t="n">
         <v>1</v>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H338" t="n">
         <v>5</v>
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H339" t="n">
         <v>3</v>
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="H340" t="n">
         <v>4</v>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="H341" t="n">
         <v>4</v>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -14500,7 +14500,7 @@
         </is>
       </c>
       <c r="G343" t="n">
-        <v>101</v>
+        <v>363</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -14541,7 +14541,7 @@
         </is>
       </c>
       <c r="G344" t="n">
-        <v>119</v>
+        <v>249</v>
       </c>
       <c r="H344" t="n">
         <v>1</v>
@@ -14582,10 +14582,10 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="H345" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I345" t="n">
         <v>0</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="H346" t="n">
         <v>2</v>
@@ -14664,10 +14664,10 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="H347" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I347" t="n">
         <v>0</v>
@@ -14705,10 +14705,10 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="H348" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I348" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="H349" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I349" t="n">
         <v>0</v>
@@ -14787,7 +14787,7 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="H350" t="n">
         <v>3</v>
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="H351" t="n">
         <v>1</v>
@@ -14869,10 +14869,10 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>169</v>
+        <v>260</v>
       </c>
       <c r="H352" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I352" t="n">
         <v>0</v>
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="H353" t="n">
         <v>6</v>
@@ -14951,10 +14951,10 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="H354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I354" t="n">
         <v>0</v>
@@ -14992,7 +14992,7 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>24</v>
+        <v>206</v>
       </c>
       <c r="H355" t="n">
         <v>1</v>
@@ -15033,7 +15033,7 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="H356" t="n">
         <v>2</v>
@@ -15074,10 +15074,10 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="H357" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I357" t="n">
         <v>0</v>
@@ -15115,12 +15115,1324 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="H358" t="n">
         <v>4</v>
       </c>
       <c r="I358" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7663394455847718165</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>👉Sở hữu lực hút tới 25.000Pa liệu có hot#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>64</v>
+      </c>
+      <c r="H359" t="n">
+        <v>0</v>
+      </c>
+      <c r="I359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7663394202142723349</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>🔥Cùng test lực hút cực khủng của Qrevo 2 Pro#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>70</v>
+      </c>
+      <c r="H360" t="n">
+        <v>1</v>
+      </c>
+      <c r="I360" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7663393984106073365</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>🔥Chổi cạnh đảo chiều - Tự động xoè giẻ có gì hot#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok</t>
+        </is>
+      </c>
+      <c r="G361" t="n">
+        <v>65</v>
+      </c>
+      <c r="H361" t="n">
+        <v>0</v>
+      </c>
+      <c r="I361" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7663393743260618004</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>✅POV: Khi bạn lười chảy thây nhưng vẫn muốn nhà sạch#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>64</v>
+      </c>
+      <c r="H362" t="n">
+        <v>0</v>
+      </c>
+      <c r="I362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7663393379727854868</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Qrevo 2 pro xử lý ngóc nghách như thế nào?#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>68</v>
+      </c>
+      <c r="H363" t="n">
+        <v>1</v>
+      </c>
+      <c r="I363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7663331209589624085</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>✅POV: Bạn không cần làm mọi thứ vì đã có Qrevo 2 Pro#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>115</v>
+      </c>
+      <c r="H364" t="n">
+        <v>3</v>
+      </c>
+      <c r="I364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7663330690716585236</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>👉POV: Khi bạn vắng nhà#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending #viralvideotiktok</t>
+        </is>
+      </c>
+      <c r="G365" t="n">
+        <v>126</v>
+      </c>
+      <c r="H365" t="n">
+        <v>5</v>
+      </c>
+      <c r="I365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7663330572600642837</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>❓Vợ chồng cãi nhau vì việc dọn nhà....#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending</t>
+        </is>
+      </c>
+      <c r="G366" t="n">
+        <v>122</v>
+      </c>
+      <c r="H366" t="n">
+        <v>4</v>
+      </c>
+      <c r="I366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7663330347714628884</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>👉Giải pháp đi làm về còn không cần phải dọn dẹp..#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending</t>
+        </is>
+      </c>
+      <c r="G367" t="n">
+        <v>115</v>
+      </c>
+      <c r="H367" t="n">
+        <v>1</v>
+      </c>
+      <c r="I367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>kimanh_1202</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@kimanh_1202/video/7663329977714216213</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>🔥Nếu cần robot ngon, thử em này nhé....#Roborock #Qrevo2Pro #robothutbui #ahastore #xuhuong #trending</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>126</v>
+      </c>
+      <c r="H368" t="n">
+        <v>1</v>
+      </c>
+      <c r="I368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7663304399392869652</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chủ vắng nhà là Robot dọn dẹp ngay😃😃😃 Không bao giờ than phiền hay khó chịu mà luôn ân cần,vui vẻ dọn dẹp🤭🤭🤭 #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>382</v>
+      </c>
+      <c r="H369" t="n">
+        <v>2</v>
+      </c>
+      <c r="I369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7663110646178843925</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theo mọi người, con robot này đang dọn nhà hay đang kéo cả tổ nhện đi du lịch? 🤣🕸️” #Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G370" t="n">
+        <v>447</v>
+      </c>
+      <c r="H370" t="n">
+        <v>1</v>
+      </c>
+      <c r="I370" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7663093365684112661</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Còn chần chừ gì nữa😀😀😀 Cho e lên xu hướng đi mấy chị😆😆 Em bán Robot giá rẻ nà🥰🥰🥰🥰#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G371" t="n">
+        <v>366</v>
+      </c>
+      <c r="H371" t="n">
+        <v>2</v>
+      </c>
+      <c r="I371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7663106921028734215</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có điều gì hay ở QRevo 2Pro? #robothutbui #roborock #qrevo2pro #fyp #3tsmart </t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>368</v>
+      </c>
+      <c r="H372" t="n">
+        <v>0</v>
+      </c>
+      <c r="I372" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7663094834416291090</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Có cô tiên dọn nhà giúp #robothutbui #roborock #qrevo2pro #fyp #3tsmart</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>348</v>
+      </c>
+      <c r="H373" t="n">
+        <v>2</v>
+      </c>
+      <c r="I373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7663463397580721429</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chụp hình em 2 Pro thì khép cái chân lại nha mí ní. Nó bóng nó soi gương được luôn á. 🤭 #Qrevo2Pro #roborock #robothutbui #robotlaunhadaklak </t>
+        </is>
+      </c>
+      <c r="G374" t="n">
+        <v>6</v>
+      </c>
+      <c r="H374" t="n">
+        <v>0</v>
+      </c>
+      <c r="I374" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7663459959610363157</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Test thực tế #robothutbui #roborock #Qrevo2Pro hút tóc</t>
+        </is>
+      </c>
+      <c r="G375" t="n">
+        <v>11</v>
+      </c>
+      <c r="H375" t="n">
+        <v>1</v>
+      </c>
+      <c r="I375" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7663452048561573140</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Như này đã hài lòng các bác chưa ạ #robothutbui #roborock #Qrevo2Pro #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G376" t="n">
+        <v>10</v>
+      </c>
+      <c r="H376" t="n">
+        <v>3</v>
+      </c>
+      <c r="I376" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7663366772220841236</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sàn nào thì em cũng cân được hết ạ #xuhuong #Qrevo2Pro #robothutbui #roborock #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G377" t="n">
+        <v>85</v>
+      </c>
+      <c r="H377" t="n">
+        <v>3</v>
+      </c>
+      <c r="I377" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7663355424074157332</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không chỉ ngon mà tài chính trong tầm tay nha các bác #xuhuong #Qrevo2Pro #robothutbui #roborock #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G378" t="n">
+        <v>91</v>
+      </c>
+      <c r="H378" t="n">
+        <v>2</v>
+      </c>
+      <c r="I378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7663321914437455125</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hướng dẫn lắp lại phụ kiện robot sau khi tháo ra vệ sinh #roborock #robothutbuithongminh #Qrevo2Pro #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G379" t="n">
+        <v>189</v>
+      </c>
+      <c r="H379" t="n">
+        <v>4</v>
+      </c>
+      <c r="I379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7663136340053298453</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Từ khi có em sen gia đình hoà thuận hẳn #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhướng </t>
+        </is>
+      </c>
+      <c r="G380" t="n">
+        <v>384</v>
+      </c>
+      <c r="H380" t="n">
+        <v>5</v>
+      </c>
+      <c r="I380" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7663402887036341525</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nâng tầm trải nghiệm với Dock sạc đa năng! Sở hữu Roborock Qrevo 2 Pro là bạn đang sở hữu giải pháp giải phóng đôi tay tuyệt đối. Không cần tốn sức, Dock sạc đa năng sẽ tự động vận hành trọn gói mọi công đoạn chăm sóc robot và sàn nhà: 💧 Tự động châm nước: Robot tự quay về dock để bổ sung nước sạch khi cần, giúp duy trì hiệu quả lau dọn liên tục. 🧼 Tự động giặt sấy: Dock tự động giặt giẻ bằng khí nóng và sấy khô bằng khí ấm, giúp hạn chế mùi hôi và ẩm mốc. 🗑️ Tự động gom bụi: Bụi bẩn được chuyển từ robot vào túi chứa lớn, giúp giảm tần suất vệ sinh thủ công. Nâng cấp công nghệ, tận hưởng cuộc sống tiện nghi xứng tầm với bạn! ✨ #RoborockVietnam #Roborock #Qrevo2Pro#RobotHutBui #robothutbuiquan2 </t>
+        </is>
+      </c>
+      <c r="G381" t="n">
+        <v>147</v>
+      </c>
+      <c r="H381" t="n">
+        <v>0</v>
+      </c>
+      <c r="I381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7663393180070579476</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>QREVO 2 PRO - VÔ ĐỊCH TRONG TẦM GIÁ 🏆 Không cần mức giá cao để sở hữu trải nghiệm dọn dẹp thông minh, trong những màn đấu với rác bụi và những thử thách trên sàn, Qrevo 2 Pro vô địch trong tầm giá khi sở hữu hàng loạt hiệu năng khủng: ✨ Lực hút HyperForce 25.000Pa mạnh mẽ, xử lý gọn từ bụi mịn, rác vụn đến tóc rụng và lông thú cưng ✨ Hệ thống chống rối toàn thân được chứng nhận, giúp duy trì hiệu suất làm sạch ổn định và giảm thiểu thao tác gỡ tóc thủ công ✨ Giẻ lau cạnh FlexiArm™ tự động mở rộng sát mép tường và chân nội thất, chăm kỹ những vị trí thường dễ bị bỏ sót ✨ Chổi cạnh đảo chiều thế hệ mới tối ưu khả năng gom bụi sát góc, tăng độ bao phủ làm sạch ✨ Tự động tháo rời giẻ lau trước khi làm sạch thảm, giúp hạn chế bẩn chéo và giữ thảm luôn khô ráo ✨  Khay giặt tự làm sạch thế hệ 2 giúp dock sạch lâu hơn, giảm công sức vệ sinh định kỳ ✨  Dock đa năng tự giặt và sấy sau mỗi chu trình, để robot luôn sẵn sàng cho lần làm sạch tiếp theo Bạn đã sẵn sàng cùng Qrevo 2 Pro nâng cúp cho chuẩn sống thảnh thơi mới ✨ #Roborock #RoborockVietnam #robothutbuilaunhachinhhang ##robothutbuilaunhathongminh #Qrevo2Pro</t>
+        </is>
+      </c>
+      <c r="G382" t="n">
+        <v>155</v>
+      </c>
+      <c r="H382" t="n">
+        <v>2</v>
+      </c>
+      <c r="I382" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7663388628449496340</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nâng tầm trải nghiệm với Dock sạc đa năng! Sở hữu Roborock Qrevo 2 Pro là bạn đang sở hữu giải pháp giải phóng đôi tay tuyệt đối. Không cần tốn sức, Dock sạc đa năng sẽ tự động vận hành trọn gói mọi công đoạn chăm sóc robot và sàn nhà: 💧 Tự động châm nước: Robot tự quay về dock để bổ sung nước sạch khi cần, giúp duy trì hiệu quả lau dọn liên tục. 🧼 Tự động giặt sấy: Dock tự động giặt giẻ bằng khí nóng và sấy khô bằng khí ấm, giúp hạn chế mùi hôi và ẩm mốc. 🗑️ Tự động gom bụi: Bụi bẩn được chuyển từ robot vào túi chứa lớn, giúp giảm tần suất vệ sinh thủ công. Nâng cấp công nghệ, tận hưởng cuộc sống tiện nghi xứng tầm với bạn! ✨ #RoborockVietnam #Roborock #Qrevo2Pro#RobotHutBui </t>
+        </is>
+      </c>
+      <c r="G383" t="n">
+        <v>92</v>
+      </c>
+      <c r="H383" t="n">
+        <v>2</v>
+      </c>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7663357161237515540</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot Qrevo 2 Pro không làm@Bạn Thất vọng#RobotHutBui #Roborock #Qrevo2Pro #trend </t>
+        </is>
+      </c>
+      <c r="G384" t="n">
+        <v>185</v>
+      </c>
+      <c r="H384" t="n">
+        <v>3</v>
+      </c>
+      <c r="I384" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7663334566941248789</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G385" t="n">
+        <v>361</v>
+      </c>
+      <c r="H385" t="n">
+        <v>0</v>
+      </c>
+      <c r="I385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7663331582580641044</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Những lý do nên mua Robot Qrevo2Pro#RobotHutBui #Roborock #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G386" t="n">
+        <v>98</v>
+      </c>
+      <c r="H386" t="n">
+        <v>0</v>
+      </c>
+      <c r="I386" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7663119936411454740</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POV: Khi bạn vắng nhà… 🏡🤖 Bạn đi làm. Bạn đưa con đi học. Bạn đi cà phê, gặp bạn bè hay vi vu cuối tuần. Đến khi bạn mở cửa trở về… Không còn cảnh sàn đầy bụi hay phải cầm chổi ngay sau giờ làm. Chỉ còn một căn nhà sạch sẽ, thơm tho và cảm giác được “đón về” sau một ngày dài. Đó là điều tuyệt vời nhất của robot hút bụi: không phải nó dọn nhà thay bạn, mà nó trả lại cho bạn nhiều thời gian hơn dành cho bản thân và gia đình. ❤️ 📍Trải nghiệm trực tiếp các dòng robot mới nhất tại H&amp;T Smart Home Đức Trọng – 384 Thống Nhất.  #Roborock #Qrevo2Pro #Robotlaunha #trainghiemthucte #RobotDucTrong </t>
+        </is>
+      </c>
+      <c r="G387" t="n">
+        <v>363</v>
+      </c>
+      <c r="H387" t="n">
+        <v>5</v>
+      </c>
+      <c r="I387" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7663412387705261319</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tìm hiểu mua robot mà bỏ qua em Qrevo 2 pro là tiếc lắm nha các bác 🚘 Ghé qua Xiaomi Phú Thọ trải nghiệm nhận quà ạ 🏠 05 Nguyễn Du, Nông Trang, Việt Trì nhé các bác  #qrevo2pro #robothutbui #roborock #robotlaunha #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G388" t="n">
+        <v>48</v>
+      </c>
+      <c r="H388" t="n">
+        <v>3</v>
+      </c>
+      <c r="I388" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7663336181286915346</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giá nhỉnh 12 củ, có sẵn tại shop trải nghiệm và ring em nó về nha các bác  #qrevo2pro #robothutbui #roborock #robotlaunha #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G389" t="n">
+        <v>119</v>
+      </c>
+      <c r="H389" t="n">
+        <v>4</v>
+      </c>
+      <c r="I389" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>homebotvietnam</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homebotvietnam/video/7663437010949917973</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Chỉ một chiếc robot nhưng xử lý cả đống việc trong nhà! 🤩🧹 Bạn chấm em này bao nhiêu điểm? 💬👇 #Qrevo2Pro #Roborock #robothutbui #NhaSach #ReviewCongNghe</t>
+        </is>
+      </c>
+      <c r="G390" t="n">
+        <v>26</v>
+      </c>
+      <c r="H390" t="n">
+        <v>1</v>
+      </c>
+      <c r="I390" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I390"/>
+  <dimension ref="A1:I404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1194</v>
+        <v>1304</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>639</v>
+        <v>660</v>
       </c>
       <c r="H14" t="n">
         <v>34</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>58000</v>
+        <v>58400</v>
       </c>
       <c r="H23" t="n">
         <v>355</v>
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>25700</v>
+        <v>25800</v>
       </c>
       <c r="H24" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I24" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1580</v>
+        <v>1625</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H39" t="n">
         <v>9</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="H46" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I46" t="n">
         <v>9</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H63" t="n">
         <v>7</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>35800</v>
+        <v>55000</v>
       </c>
       <c r="H65" t="n">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>833</v>
+        <v>847</v>
       </c>
       <c r="H66" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I66" t="n">
         <v>26</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H67" t="n">
         <v>2</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>84200</v>
+        <v>84600</v>
       </c>
       <c r="H78" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I78" t="n">
         <v>78</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H86" t="n">
         <v>6</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2416</v>
+        <v>2474</v>
       </c>
       <c r="H87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I87" t="n">
         <v>7</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H98" t="n">
         <v>10</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H107" t="n">
         <v>4</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="H108" t="n">
         <v>39</v>
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>5299</v>
+        <v>5456</v>
       </c>
       <c r="H109" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I109" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H113" t="n">
         <v>2</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>467500</v>
+        <v>470200</v>
       </c>
       <c r="H116" t="n">
-        <v>3137</v>
+        <v>3155</v>
       </c>
       <c r="I116" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="117">
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H117" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H118" t="n">
         <v>5</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H122" t="n">
         <v>4</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H136" t="n">
         <v>3</v>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H137" t="n">
         <v>1</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2603</v>
+        <v>2606</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H142" t="n">
         <v>3</v>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H146" t="n">
         <v>8</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H151" t="n">
         <v>10</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H153" t="n">
         <v>4</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H161" t="n">
         <v>1</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H168" t="n">
         <v>14</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H173" t="n">
         <v>4</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H174" t="n">
         <v>5</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H175" t="n">
         <v>3</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H183" t="n">
         <v>4</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H184" t="n">
         <v>7</v>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H185" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H186" t="n">
         <v>10</v>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H188" t="n">
         <v>4</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H189" t="n">
         <v>7</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H191" t="n">
         <v>12</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H194" t="n">
         <v>9</v>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="H195" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="H196" t="n">
         <v>20</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H197" t="n">
         <v>5</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H200" t="n">
         <v>1</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H201" t="n">
         <v>7</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H203" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H205" t="n">
         <v>4</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H206" t="n">
         <v>5</v>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H207" t="n">
         <v>7</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H208" t="n">
         <v>3</v>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H209" t="n">
         <v>5</v>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H210" t="n">
         <v>7</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H215" t="n">
         <v>4</v>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1004</v>
+        <v>1013</v>
       </c>
       <c r="H218" t="n">
         <v>13</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H219" t="n">
         <v>6</v>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H220" t="n">
         <v>5</v>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H221" t="n">
         <v>6</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H222" t="n">
         <v>6</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H223" t="n">
         <v>5</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="H224" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H229" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I229" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H231" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H232" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H234" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -10113,10 +10113,10 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>8157</v>
+        <v>8284</v>
       </c>
       <c r="H236" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I236" t="n">
         <v>27</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H244" t="n">
         <v>6</v>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H245" t="n">
         <v>9</v>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H246" t="n">
         <v>7</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H247" t="n">
         <v>8</v>
@@ -10605,7 +10605,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H248" t="n">
         <v>11</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H249" t="n">
         <v>4</v>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H253" t="n">
         <v>8</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H257" t="n">
         <v>4</v>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H258" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="H260" t="n">
         <v>10</v>
@@ -11138,10 +11138,10 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H261" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I261" t="n">
         <v>0</v>
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H262" t="n">
         <v>5</v>
@@ -11220,7 +11220,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H263" t="n">
         <v>4</v>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H264" t="n">
         <v>6</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>921</v>
+        <v>938</v>
       </c>
       <c r="H267" t="n">
         <v>26</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H268" t="n">
         <v>5</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H273" t="n">
         <v>4</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H274" t="n">
         <v>5</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H277" t="n">
         <v>4</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="H278" t="n">
         <v>3</v>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="H279" t="n">
         <v>6</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="H280" t="n">
         <v>5</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="H282" t="n">
         <v>10</v>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H283" t="n">
         <v>4</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H286" t="n">
         <v>6</v>
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H287" t="n">
         <v>6</v>
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H288" t="n">
         <v>3</v>
@@ -12286,10 +12286,10 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I289" t="n">
         <v>0</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H290" t="n">
         <v>8</v>
@@ -12368,7 +12368,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H291" t="n">
         <v>5</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H293" t="n">
         <v>5</v>
@@ -12532,13 +12532,13 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H295" t="n">
         <v>6</v>
       </c>
       <c r="I295" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="296">
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H296" t="n">
         <v>6</v>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="H297" t="n">
         <v>25</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="H298" t="n">
         <v>22</v>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H299" t="n">
         <v>7</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="H303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I303" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H304" t="n">
         <v>2</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H307" t="n">
         <v>6</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H308" t="n">
         <v>4</v>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H309" t="n">
         <v>3</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H311" t="n">
         <v>5</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="H312" t="n">
         <v>7</v>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H314" t="n">
         <v>3</v>
@@ -13352,7 +13352,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H315" t="n">
         <v>3</v>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H316" t="n">
         <v>10</v>
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="H317" t="n">
         <v>7</v>
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="H318" t="n">
         <v>7</v>
@@ -13516,7 +13516,7 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H319" t="n">
         <v>7</v>
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="H320" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I320" t="n">
         <v>0</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="H321" t="n">
         <v>3</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="H322" t="n">
         <v>4</v>
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="H323" t="n">
         <v>1</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H324" t="n">
         <v>2</v>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H325" t="n">
         <v>2</v>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="H326" t="n">
         <v>9</v>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="H327" t="n">
         <v>6</v>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H328" t="n">
         <v>10</v>
@@ -13926,7 +13926,7 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H329" t="n">
         <v>3</v>
@@ -13967,7 +13967,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H330" t="n">
         <v>8</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H331" t="n">
         <v>5</v>
@@ -14049,7 +14049,7 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H332" t="n">
         <v>4</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H333" t="n">
         <v>3</v>
@@ -14131,10 +14131,10 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="H334" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I334" t="n">
         <v>0</v>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H335" t="n">
         <v>6</v>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="H338" t="n">
         <v>5</v>
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H339" t="n">
         <v>3</v>
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H340" t="n">
         <v>4</v>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="H341" t="n">
         <v>4</v>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -14500,10 +14500,10 @@
         </is>
       </c>
       <c r="G343" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I343" t="n">
         <v>0</v>
@@ -14541,7 +14541,7 @@
         </is>
       </c>
       <c r="G344" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H344" t="n">
         <v>1</v>
@@ -14582,10 +14582,10 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I345" t="n">
         <v>0</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H346" t="n">
         <v>2</v>
@@ -14664,10 +14664,10 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H347" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I347" t="n">
         <v>0</v>
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H348" t="n">
         <v>8</v>
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H349" t="n">
         <v>5</v>
@@ -14787,10 +14787,10 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H350" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I350" t="n">
         <v>0</v>
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H351" t="n">
         <v>1</v>
@@ -14869,7 +14869,7 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H352" t="n">
         <v>3</v>
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H353" t="n">
         <v>6</v>
@@ -14951,7 +14951,7 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H354" t="n">
         <v>1</v>
@@ -14992,7 +14992,7 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H355" t="n">
         <v>1</v>
@@ -15033,13 +15033,13 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="H356" t="n">
         <v>2</v>
       </c>
       <c r="I356" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="357">
@@ -15074,7 +15074,7 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="H357" t="n">
         <v>6</v>
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="H358" t="n">
         <v>4</v>
@@ -15156,10 +15156,10 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="H359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I359" t="n">
         <v>0</v>
@@ -15197,10 +15197,10 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="H360" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I360" t="n">
         <v>0</v>
@@ -15238,10 +15238,10 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="H361" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I361" t="n">
         <v>0</v>
@@ -15279,10 +15279,10 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="H362" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I362" t="n">
         <v>0</v>
@@ -15320,10 +15320,10 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="H363" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I363" t="n">
         <v>0</v>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="H364" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I364" t="n">
         <v>0</v>
@@ -15402,10 +15402,10 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H365" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I365" t="n">
         <v>0</v>
@@ -15443,10 +15443,10 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="H366" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I366" t="n">
         <v>0</v>
@@ -15484,10 +15484,10 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="H367" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I367" t="n">
         <v>0</v>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="H368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I368" t="n">
         <v>0</v>
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>382</v>
+        <v>472</v>
       </c>
       <c r="H369" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I369" t="n">
         <v>0</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H370" t="n">
         <v>1</v>
@@ -15648,7 +15648,7 @@
         </is>
       </c>
       <c r="G371" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H371" t="n">
         <v>2</v>
@@ -15689,13 +15689,13 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="H372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H373" t="n">
         <v>2</v>
@@ -15771,10 +15771,10 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="H374" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I374" t="n">
         <v>0</v>
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="H375" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I375" t="n">
         <v>0</v>
@@ -15853,10 +15853,10 @@
         </is>
       </c>
       <c r="G376" t="n">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="H376" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I376" t="n">
         <v>0</v>
@@ -15894,10 +15894,10 @@
         </is>
       </c>
       <c r="G377" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="H377" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I377" t="n">
         <v>0</v>
@@ -15935,7 +15935,7 @@
         </is>
       </c>
       <c r="G378" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="H378" t="n">
         <v>2</v>
@@ -15976,10 +15976,10 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>189</v>
+        <v>322</v>
       </c>
       <c r="H379" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I379" t="n">
         <v>0</v>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="H380" t="n">
         <v>5</v>
@@ -16058,10 +16058,10 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>147</v>
+        <v>367</v>
       </c>
       <c r="H381" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I381" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>155</v>
+        <v>342</v>
       </c>
       <c r="H382" t="n">
         <v>2</v>
@@ -16140,10 +16140,10 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="H383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I383" t="n">
         <v>0</v>
@@ -16181,13 +16181,13 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>185</v>
+        <v>379</v>
       </c>
       <c r="H384" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I384" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="385">
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -16263,7 +16263,7 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -16304,10 +16304,10 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="H387" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I387" t="n">
         <v>0</v>
@@ -16345,10 +16345,10 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="H388" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I388" t="n">
         <v>0</v>
@@ -16386,10 +16386,10 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="H389" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I389" t="n">
         <v>0</v>
@@ -16427,12 +16427,586 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>26</v>
+        <v>317</v>
       </c>
       <c r="H390" t="n">
+        <v>4</v>
+      </c>
+      <c r="I390" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>thuyduonggiadung</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuyduonggiadung/video/7663811464016203015</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Bàn giao và lắp đặt Robot lau nhà cho chị khách yêu Phường Chũ#roborock #qrevo2pro #robotlaunha #GiaDungThuyDuong</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>21</v>
+      </c>
+      <c r="H391" t="n">
+        <v>0</v>
+      </c>
+      <c r="I391" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7663753251665366292</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ngày bé cứ nghĩ nhà luôn sạch là vì mẹ thích dọn dẹp. Lớn lên mới hiểu, đó là vì mẹ chẳng có lựa chọn nào khác. Giờ công nghệ đã khác. Roborock Quevo 2Pro với lực hút 25.000Pa Để những người phụ nữ trong gia đình có thêm thời gian nghỉ ngơi thay vì dành hàng giờ cho việc lau dọn. Nhà sạch không phải đánh đổi bằng sự mệt mỏi. #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>74</v>
+      </c>
+      <c r="H392" t="n">
         <v>1</v>
       </c>
-      <c r="I390" t="n">
+      <c r="I392" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7663743038375677204</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giờ có gia tiên nào độ cho con bán lần 5 con Roborock Quevo 2 Pro là con mua heo về úng liền😆😆😆😆😆# #Roborock  #Qrevo2Pro  #Robothutbui  #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G393" t="n">
+        <v>91</v>
+      </c>
+      <c r="H393" t="n">
+        <v>0</v>
+      </c>
+      <c r="I393" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7663503149243632916</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cùng mình vệ sinh em Roborock Quevo 2 pro nhé❤️❤️❤️#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>397</v>
+      </c>
+      <c r="H394" t="n">
+        <v>5</v>
+      </c>
+      <c r="I394" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7663709706468248850</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ông cha ta đã nói #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>117</v>
+      </c>
+      <c r="H395" t="n">
+        <v>0</v>
+      </c>
+      <c r="I395" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7663490061631048967</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vệ sinh Qrevo 2 Pro #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>150</v>
+      </c>
+      <c r="H396" t="n">
+        <v>3</v>
+      </c>
+      <c r="I396" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>xiaomitiengiang.vn</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomitiengiang.vn/video/7663517065793391892</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>#roborock2pro #xiaomitiengiang #robotxiaomitiengiang #robotthongminhhutbuiban #tivixiaomithongminh  robot Roborock Qrevo 2 Pro mã mới, lau nhà và hút bụi thông minh🥰</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>98</v>
+      </c>
+      <c r="H397" t="n">
+        <v>1</v>
+      </c>
+      <c r="I397" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7663487409463577877</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cảm ơn khách iu đã luôn ủng hộ shop em #robotlaunhadaklak #robothutbui #roborock #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>166</v>
+      </c>
+      <c r="H398" t="n">
+        <v>6</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7663700018708090132</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cũng hưởng ứng world Cup ạ #robothutbui #Qrevo2Pro #roborock #xuhuong #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G399" t="n">
+        <v>121</v>
+      </c>
+      <c r="H399" t="n">
+        <v>6</v>
+      </c>
+      <c r="I399" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7663640270642171156</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cần tìm 1 em robot ngon thì Qrevo 2 Pro không thể bỏ qua ạ #robothutbui #roborock #Qrevo2Pro #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>164</v>
+      </c>
+      <c r="H400" t="n">
+        <v>8</v>
+      </c>
+      <c r="I400" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7663500377538563348</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trải nghiệm cái mua luôn giao lắp em Qrevo 2 Pro cho chị đẹp #robothutbui #roborock #Qrevo2Pro #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G401" t="n">
+        <v>309</v>
+      </c>
+      <c r="H401" t="n">
+        <v>10</v>
+      </c>
+      <c r="I401" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>nc.nh.qu.robot</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@nc.nh.qu.robot/video/7663819236254469397</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#quyrobot #Qrevo2pro #roborock #robothutbui #xuhuongtiktok </t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>17</v>
+      </c>
+      <c r="H402" t="n">
+        <v>0</v>
+      </c>
+      <c r="I402" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7663509818367560981</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có những sản phẩm không cần nói quá nhiều, trải nghiệm một lần là đủ để quyết định. 📍 Ghé H&amp;T Smart Home Đức Trọng – 384 Thống Nhất để tự mình trải nghiệm và chọn đúng thiết bị phù hợp với gia đình nhé! #Roborock #Qrevo2Pro #trainghiemthucte #Robotlaunha #f25ultra✨ </t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>365</v>
+      </c>
+      <c r="H403" t="n">
+        <v>0</v>
+      </c>
+      <c r="I403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7663699976798735634</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Săn sale mùa WORLD CUP cùng Qrevo 2 Pro nhé  #qrevo2pro #robothutbui #roborock #robotlaunha #xuhuong </t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>105</v>
+      </c>
+      <c r="H404" t="n">
+        <v>2</v>
+      </c>
+      <c r="I404" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I404"/>
+  <dimension ref="A1:I421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1304</v>
+        <v>1456</v>
       </c>
       <c r="H2" t="n">
         <v>7</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H13" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="H14" t="n">
         <v>34</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H15" t="n">
         <v>5</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H16" t="n">
         <v>10</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>58400</v>
+        <v>58700</v>
       </c>
       <c r="H23" t="n">
         <v>355</v>
@@ -1406,7 +1406,7 @@
         <v>25800</v>
       </c>
       <c r="H24" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I24" t="n">
         <v>35</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1625</v>
+        <v>1659</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>746</v>
+        <v>768</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
         <v>2</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>676</v>
+        <v>689</v>
       </c>
       <c r="H46" t="n">
         <v>61</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H48" t="n">
         <v>15</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H59" t="n">
         <v>6</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H63" t="n">
         <v>7</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H64" t="n">
         <v>4</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>55000</v>
+        <v>73800</v>
       </c>
       <c r="H65" t="n">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="H66" t="n">
         <v>35</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>84600</v>
+        <v>84800</v>
       </c>
       <c r="H78" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I78" t="n">
         <v>78</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2474</v>
+        <v>2504</v>
       </c>
       <c r="H87" t="n">
         <v>18</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H92" t="n">
         <v>4</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H93" t="n">
         <v>9</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H98" t="n">
         <v>10</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>11200</v>
+        <v>11300</v>
       </c>
       <c r="H108" t="n">
         <v>39</v>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>5456</v>
+        <v>5638</v>
       </c>
       <c r="H109" t="n">
         <v>589</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>470200</v>
+        <v>472600</v>
       </c>
       <c r="H116" t="n">
-        <v>3155</v>
+        <v>3173</v>
       </c>
       <c r="I116" t="n">
-        <v>487</v>
+        <v>496</v>
       </c>
     </row>
     <row r="117">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H118" t="n">
         <v>5</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H119" t="n">
         <v>3</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H142" t="n">
         <v>3</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H143" t="n">
         <v>11</v>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H144" t="n">
         <v>6</v>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H145" t="n">
         <v>4</v>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H149" t="n">
         <v>6</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H151" t="n">
         <v>10</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H168" t="n">
         <v>14</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H173" t="n">
         <v>4</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H174" t="n">
         <v>5</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H175" t="n">
         <v>3</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H183" t="n">
         <v>4</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H184" t="n">
         <v>7</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H191" t="n">
         <v>12</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H195" t="n">
         <v>4</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H196" t="n">
         <v>20</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H203" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H205" t="n">
         <v>4</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H206" t="n">
         <v>5</v>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H207" t="n">
         <v>7</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H215" t="n">
         <v>4</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="H216" t="n">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1013</v>
+        <v>1018</v>
       </c>
       <c r="H218" t="n">
         <v>13</v>
@@ -9416,10 +9416,10 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H219" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I219" t="n">
         <v>0</v>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H221" t="n">
         <v>6</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H222" t="n">
         <v>6</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="H224" t="n">
         <v>10</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H227" t="n">
         <v>8</v>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H228" t="n">
         <v>9</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H232" t="n">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H235" t="n">
         <v>13</v>
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>8284</v>
+        <v>8361</v>
       </c>
       <c r="H236" t="n">
         <v>39</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H241" t="n">
         <v>8</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H244" t="n">
         <v>6</v>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H246" t="n">
         <v>7</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H247" t="n">
         <v>8</v>
@@ -10605,7 +10605,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H248" t="n">
         <v>11</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H249" t="n">
         <v>4</v>
@@ -10769,10 +10769,10 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H252" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I252" t="n">
         <v>0</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="H260" t="n">
         <v>10</v>
@@ -11138,13 +11138,13 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H261" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
@@ -11220,7 +11220,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H263" t="n">
         <v>4</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="H267" t="n">
         <v>26</v>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H271" t="n">
         <v>2</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H273" t="n">
         <v>4</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H274" t="n">
         <v>5</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H278" t="n">
         <v>3</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="H280" t="n">
         <v>5</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="H282" t="n">
         <v>10</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H286" t="n">
         <v>6</v>
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H287" t="n">
         <v>6</v>
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H288" t="n">
         <v>3</v>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H289" t="n">
         <v>3</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H290" t="n">
         <v>8</v>
@@ -12368,7 +12368,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H291" t="n">
         <v>5</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H294" t="n">
         <v>5</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H295" t="n">
         <v>6</v>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="H297" t="n">
         <v>25</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="H298" t="n">
         <v>22</v>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H299" t="n">
         <v>7</v>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H300" t="n">
         <v>1</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="H303" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I303" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H304" t="n">
         <v>2</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H308" t="n">
         <v>4</v>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H309" t="n">
         <v>3</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H311" t="n">
         <v>5</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="H312" t="n">
         <v>7</v>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H314" t="n">
         <v>3</v>
@@ -13352,7 +13352,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H315" t="n">
         <v>3</v>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H316" t="n">
         <v>10</v>
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H317" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I317" t="n">
         <v>2</v>
@@ -13475,10 +13475,10 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="H318" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I318" t="n">
         <v>0</v>
@@ -13516,7 +13516,7 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H319" t="n">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H320" t="n">
         <v>7</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H321" t="n">
         <v>3</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H322" t="n">
         <v>4</v>
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H323" t="n">
         <v>1</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H324" t="n">
         <v>2</v>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H325" t="n">
         <v>2</v>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H326" t="n">
         <v>9</v>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="H327" t="n">
         <v>6</v>
@@ -13967,7 +13967,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H330" t="n">
         <v>8</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="H333" t="n">
         <v>3</v>
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H334" t="n">
         <v>4</v>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H335" t="n">
         <v>6</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H337" t="n">
         <v>1</v>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H338" t="n">
         <v>5</v>
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="H339" t="n">
         <v>3</v>
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H340" t="n">
         <v>4</v>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H341" t="n">
         <v>4</v>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -14500,7 +14500,7 @@
         </is>
       </c>
       <c r="G343" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H343" t="n">
         <v>1</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H346" t="n">
         <v>2</v>
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H347" t="n">
         <v>7</v>
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H348" t="n">
         <v>8</v>
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H349" t="n">
         <v>5</v>
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H351" t="n">
         <v>1</v>
@@ -14869,7 +14869,7 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H352" t="n">
         <v>3</v>
@@ -14951,10 +14951,10 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I354" t="n">
         <v>0</v>
@@ -14992,10 +14992,10 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I355" t="n">
         <v>0</v>
@@ -15033,7 +15033,7 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="H356" t="n">
         <v>2</v>
@@ -15074,7 +15074,7 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H357" t="n">
         <v>6</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H359" t="n">
         <v>2</v>
@@ -15197,10 +15197,10 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H360" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I360" t="n">
         <v>0</v>
@@ -15238,10 +15238,10 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I361" t="n">
         <v>0</v>
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H362" t="n">
         <v>2</v>
@@ -15361,7 +15361,7 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H364" t="n">
         <v>4</v>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H365" t="n">
         <v>6</v>
@@ -15443,7 +15443,7 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H366" t="n">
         <v>5</v>
@@ -15484,7 +15484,7 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H367" t="n">
         <v>4</v>
@@ -15525,7 +15525,7 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H368" t="n">
         <v>2</v>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="H369" t="n">
         <v>3</v>
@@ -15648,7 +15648,7 @@
         </is>
       </c>
       <c r="G371" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H371" t="n">
         <v>2</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H372" t="n">
         <v>1</v>
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H373" t="n">
         <v>2</v>
@@ -15771,10 +15771,10 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="H374" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I374" t="n">
         <v>0</v>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="H375" t="n">
         <v>4</v>
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="G376" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H376" t="n">
         <v>7</v>
@@ -15894,10 +15894,10 @@
         </is>
       </c>
       <c r="G377" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H377" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I377" t="n">
         <v>0</v>
@@ -15935,10 +15935,10 @@
         </is>
       </c>
       <c r="G378" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H378" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I378" t="n">
         <v>0</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H379" t="n">
         <v>6</v>
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H380" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I380" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="H381" t="n">
         <v>2</v>
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H383" t="n">
         <v>3</v>
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="H384" t="n">
         <v>5</v>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -16263,7 +16263,7 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H387" t="n">
         <v>6</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H388" t="n">
         <v>4</v>
@@ -16386,10 +16386,10 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H389" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I389" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="H390" t="n">
         <v>4</v>
@@ -16468,13 +16468,13 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="H391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392">
@@ -16509,10 +16509,10 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>74</v>
+        <v>364</v>
       </c>
       <c r="H392" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I392" t="n">
         <v>0</v>
@@ -16550,10 +16550,10 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>91</v>
+        <v>348</v>
       </c>
       <c r="H393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I393" t="n">
         <v>0</v>
@@ -16591,7 +16591,7 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="H394" t="n">
         <v>5</v>
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="H395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I395" t="n">
         <v>0</v>
@@ -16673,13 +16673,13 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="H396" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
@@ -16714,7 +16714,7 @@
         </is>
       </c>
       <c r="G397" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H397" t="n">
         <v>1</v>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="H398" t="n">
         <v>6</v>
@@ -16796,10 +16796,10 @@
         </is>
       </c>
       <c r="G399" t="n">
-        <v>121</v>
+        <v>266</v>
       </c>
       <c r="H399" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I399" t="n">
         <v>0</v>
@@ -16837,13 +16837,13 @@
         </is>
       </c>
       <c r="G400" t="n">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="H400" t="n">
         <v>8</v>
       </c>
       <c r="I400" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="401">
@@ -16878,13 +16878,13 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>309</v>
+        <v>365</v>
       </c>
       <c r="H401" t="n">
         <v>10</v>
       </c>
       <c r="I401" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="402">
@@ -16919,10 +16919,10 @@
         </is>
       </c>
       <c r="G402" t="n">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="H402" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I402" t="n">
         <v>0</v>
@@ -16960,10 +16960,10 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="H403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I403" t="n">
         <v>0</v>
@@ -17001,12 +17001,709 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="H404" t="n">
         <v>2</v>
       </c>
       <c r="I404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>homesmediant99</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homesmediant99/video/7664043460101426439</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mẫu robot nhà Roborock đang được săn đón hiện nay #Roborock#qrevo2pro#robothutbui #mediahomesnhatrang </t>
+        </is>
+      </c>
+      <c r="G405" t="n">
+        <v>126</v>
+      </c>
+      <c r="H405" t="n">
+        <v>1</v>
+      </c>
+      <c r="I405" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7664094568580926740</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghé trực tiếp cửa hàng để trải nghiệm thực tế Roborock Qrevo 2 Pro ạ. Bên em sẽ tư vấn chi tiết các tính năng, hướng dẫn sử dụng và giải đáp mọi thắc mắc để anh/chị dễ dàng lựa chọn sản phẩm phù hợp. #Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>110</v>
+      </c>
+      <c r="H406" t="n">
+        <v>2</v>
+      </c>
+      <c r="I406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7663870285048794389</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cùng mình vệ sinh cho cục cưng nhé🤭🤭🤭 Cục cưng này chạy bằng pin chớ ngoan và thông minh lắm🥰🥰 #Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>358</v>
+      </c>
+      <c r="H407" t="n">
+        <v>0</v>
+      </c>
+      <c r="I407" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7664178629961731335</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unbox QRevo 2Pro cùng 3T SMART #robothutbui #roborock #qrevo2pro #fyp #3tsmart </t>
+        </is>
+      </c>
+      <c r="G408" t="n">
+        <v>21</v>
+      </c>
+      <c r="H408" t="n">
+        <v>0</v>
+      </c>
+      <c r="I408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7664195254064647431</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khả năng xoè dẻ lau sát cạnh hiệu quả #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>16</v>
+      </c>
+      <c r="H409" t="n">
+        <v>0</v>
+      </c>
+      <c r="I409" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7664152106927951112</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test khả năng lau hút Qrevo2 Pro #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>91</v>
+      </c>
+      <c r="H410" t="n">
+        <v>0</v>
+      </c>
+      <c r="I410" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7664149893119888648</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test làm sạch với tương ớt #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G411" t="n">
+        <v>110</v>
+      </c>
+      <c r="H411" t="n">
+        <v>0</v>
+      </c>
+      <c r="I411" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7664145698937425159</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tháo lắp robot có dễ không #qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G412" t="n">
+        <v>112</v>
+      </c>
+      <c r="H412" t="n">
+        <v>0</v>
+      </c>
+      <c r="I412" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>thietbibepan</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thietbibepan/video/7664133102645611794</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 pro quét cạnh hóc hiệu quả#qrevo2pro #Roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G413" t="n">
+        <v>229</v>
+      </c>
+      <c r="H413" t="n">
+        <v>2</v>
+      </c>
+      <c r="I413" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7664163515120323860</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done em qrevo 2 pro cho khách yêu #robothutbui #Qrevo2Pro #robothutbui #xuhuong </t>
+        </is>
+      </c>
+      <c r="G414" t="n">
+        <v>36</v>
+      </c>
+      <c r="H414" t="n">
+        <v>3</v>
+      </c>
+      <c r="I414" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7663870941709045012</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chiến thần lực hút giá tầm trung không thể bỏ qua #robothutbui #Qrevo2Pro #roborock #xuhuong #xuhuong </t>
+        </is>
+      </c>
+      <c r="G415" t="n">
+        <v>149</v>
+      </c>
+      <c r="H415" t="n">
+        <v>3</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7664137979606174996</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#RobotHutBui #RoborockVietnam #robothutbuiquan2 #Qrevo2Pro #Roborock </t>
+        </is>
+      </c>
+      <c r="G416" t="n">
+        <v>109</v>
+      </c>
+      <c r="H416" t="n">
+        <v>0</v>
+      </c>
+      <c r="I416" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7664125393594535189</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#RoborockVietnam #RobotHutBui #robothutbuiquan2 #Qrevo2Pro #Roborock </t>
+        </is>
+      </c>
+      <c r="G417" t="n">
+        <v>113</v>
+      </c>
+      <c r="H417" t="n">
+        <v>0</v>
+      </c>
+      <c r="I417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7664123562436889876</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#RoborockVietnam #RobotHutBui #robothutbuiquan2 #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G418" t="n">
+        <v>112</v>
+      </c>
+      <c r="H418" t="n">
+        <v>1</v>
+      </c>
+      <c r="I418" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7663885617536830740</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Giảm bớt đồ đạc không dùng tới trong vòng 1/2 năm. Bạn hãy tin mình đi hơn 1/2 đồ đạc trong nhà là hơn 2-3 năm rồi mình không dùng đến 2. Hay sắm các thiết bị thông minh, giúp rút ngắn thời gian dọn dẹp lại#RoborockVietnam #RobotHutBui #robothutbuiquan2 #Qrevo2Pro #Momimart </t>
+        </is>
+      </c>
+      <c r="G419" t="n">
+        <v>389</v>
+      </c>
+      <c r="H419" t="n">
+        <v>0</v>
+      </c>
+      <c r="I419" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7663878901826997525</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#RoborockVietnam #Roborock #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G420" t="n">
+        <v>319</v>
+      </c>
+      <c r="H420" t="n">
+        <v>1</v>
+      </c>
+      <c r="I420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7663878304650349845</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiếp tục seri giao 2 em Robot về 2 nhà khách gần nhau. Robot Qrevo S Pro#RoborockVietnam #Roborock #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G421" t="n">
+        <v>346</v>
+      </c>
+      <c r="H421" t="n">
+        <v>1</v>
+      </c>
+      <c r="I421" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I421"/>
+  <dimension ref="A1:I429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1456</v>
+        <v>1628</v>
       </c>
       <c r="H2" t="n">
         <v>7</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H7" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="H14" t="n">
         <v>34</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H17" t="n">
         <v>25</v>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>58700</v>
+        <v>58800</v>
       </c>
       <c r="H23" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I23" t="n">
         <v>84</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>25800</v>
+        <v>26000</v>
       </c>
       <c r="H24" t="n">
         <v>138</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1659</v>
+        <v>1713</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H39" t="n">
         <v>9</v>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="H46" t="n">
         <v>61</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H59" t="n">
         <v>6</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>73800</v>
+        <v>89800</v>
       </c>
       <c r="H65" t="n">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="H66" t="n">
         <v>35</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>84800</v>
+        <v>85400</v>
       </c>
       <c r="H78" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="I78" t="n">
         <v>78</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2504</v>
+        <v>2572</v>
       </c>
       <c r="H87" t="n">
         <v>18</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H98" t="n">
         <v>10</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>5638</v>
+        <v>5890</v>
       </c>
       <c r="H109" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="I109" t="n">
         <v>33</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>472600</v>
+        <v>475600</v>
       </c>
       <c r="H116" t="n">
-        <v>3173</v>
+        <v>3189</v>
       </c>
       <c r="I116" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="117">
@@ -5234,13 +5234,13 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H117" t="n">
+        <v>4</v>
+      </c>
+      <c r="I117" t="n">
         <v>1</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H118" t="n">
         <v>5</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H119" t="n">
         <v>3</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H127" t="n">
         <v>5</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H142" t="n">
         <v>3</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H150" t="n">
         <v>7</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H160" t="n">
         <v>6</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H168" t="n">
         <v>14</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H173" t="n">
         <v>4</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H175" t="n">
         <v>3</v>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H178" t="n">
         <v>4</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H183" t="n">
         <v>4</v>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H188" t="n">
         <v>4</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H194" t="n">
         <v>9</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H195" t="n">
         <v>4</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H196" t="n">
         <v>20</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H201" t="n">
         <v>7</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H203" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H205" t="n">
         <v>4</v>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H210" t="n">
         <v>7</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H215" t="n">
         <v>4</v>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="H218" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I218" t="n">
         <v>3</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H219" t="n">
         <v>7</v>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H221" t="n">
         <v>6</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H223" t="n">
         <v>5</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H224" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H230" t="n">
         <v>5</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="H232" t="n">
         <v>7</v>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H234" t="n">
         <v>12</v>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H235" t="n">
         <v>13</v>
@@ -10113,10 +10113,10 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>8361</v>
+        <v>8477</v>
       </c>
       <c r="H236" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I236" t="n">
         <v>27</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H239" t="n">
         <v>3</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H242" t="n">
         <v>4</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H244" t="n">
         <v>6</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H249" t="n">
         <v>4</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H253" t="n">
         <v>8</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H256" t="n">
         <v>5</v>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H258" t="n">
         <v>3</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="H260" t="n">
         <v>10</v>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H261" t="n">
         <v>20</v>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H264" t="n">
         <v>6</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>950</v>
+        <v>959</v>
       </c>
       <c r="H267" t="n">
         <v>26</v>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H272" t="n">
         <v>5</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H273" t="n">
         <v>4</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H277" t="n">
         <v>4</v>
@@ -11835,10 +11835,10 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H278" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I278" t="n">
         <v>0</v>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H279" t="n">
         <v>6</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H280" t="n">
         <v>5</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="H282" t="n">
         <v>10</v>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H283" t="n">
         <v>4</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H286" t="n">
         <v>6</v>
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H287" t="n">
         <v>6</v>
@@ -12368,7 +12368,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H291" t="n">
         <v>5</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H295" t="n">
         <v>6</v>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="H297" t="n">
         <v>25</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="H298" t="n">
         <v>22</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H302" t="n">
         <v>1</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H308" t="n">
         <v>4</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H311" t="n">
         <v>5</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="H312" t="n">
         <v>7</v>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H314" t="n">
         <v>3</v>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H316" t="n">
         <v>10</v>
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="H317" t="n">
         <v>8</v>
@@ -13475,10 +13475,10 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="H318" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I318" t="n">
         <v>0</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H320" t="n">
         <v>7</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H321" t="n">
         <v>3</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H322" t="n">
         <v>4</v>
@@ -13721,7 +13721,7 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H324" t="n">
         <v>2</v>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H325" t="n">
         <v>2</v>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H326" t="n">
         <v>9</v>
@@ -13967,7 +13967,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H330" t="n">
         <v>8</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H333" t="n">
         <v>3</v>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H338" t="n">
         <v>5</v>
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H339" t="n">
         <v>3</v>
@@ -14377,10 +14377,10 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="H340" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I340" t="n">
         <v>0</v>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H341" t="n">
         <v>4</v>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H345" t="n">
         <v>3</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H346" t="n">
         <v>2</v>
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H347" t="n">
         <v>7</v>
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="H348" t="n">
         <v>8</v>
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H349" t="n">
         <v>5</v>
@@ -14787,7 +14787,7 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H350" t="n">
         <v>4</v>
@@ -14951,10 +14951,10 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I354" t="n">
         <v>0</v>
@@ -14992,7 +14992,7 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H355" t="n">
         <v>2</v>
@@ -15033,7 +15033,7 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="H356" t="n">
         <v>2</v>
@@ -15074,10 +15074,10 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H357" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I357" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H359" t="n">
         <v>2</v>
@@ -15197,7 +15197,7 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H360" t="n">
         <v>4</v>
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="H361" t="n">
         <v>3</v>
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H362" t="n">
         <v>2</v>
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H363" t="n">
         <v>4</v>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H364" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I364" t="n">
         <v>0</v>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H365" t="n">
         <v>6</v>
@@ -15443,7 +15443,7 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H366" t="n">
         <v>5</v>
@@ -15484,7 +15484,7 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H367" t="n">
         <v>4</v>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I368" t="n">
         <v>0</v>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="H369" t="n">
         <v>3</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H370" t="n">
         <v>1</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H372" t="n">
         <v>1</v>
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H373" t="n">
         <v>2</v>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H374" t="n">
         <v>3</v>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H375" t="n">
         <v>4</v>
@@ -15935,7 +15935,7 @@
         </is>
       </c>
       <c r="G378" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H378" t="n">
         <v>3</v>
@@ -15976,10 +15976,10 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H379" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I379" t="n">
         <v>0</v>
@@ -16017,10 +16017,10 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H380" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I380" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H381" t="n">
         <v>2</v>
@@ -16099,7 +16099,7 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H382" t="n">
         <v>2</v>
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H383" t="n">
         <v>3</v>
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="H384" t="n">
         <v>5</v>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -16263,7 +16263,7 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="H387" t="n">
         <v>6</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H388" t="n">
         <v>4</v>
@@ -16386,7 +16386,7 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H389" t="n">
         <v>6</v>
@@ -16427,7 +16427,7 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="H390" t="n">
         <v>4</v>
@@ -16468,13 +16468,13 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>448</v>
+        <v>509</v>
       </c>
       <c r="H391" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I391" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="392">
@@ -16509,7 +16509,7 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="H392" t="n">
         <v>2</v>
@@ -16550,7 +16550,7 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -16591,10 +16591,10 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="H394" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I394" t="n">
         <v>0</v>
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H395" t="n">
         <v>1</v>
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H396" t="n">
         <v>4</v>
@@ -16714,7 +16714,7 @@
         </is>
       </c>
       <c r="G397" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H397" t="n">
         <v>1</v>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="H398" t="n">
         <v>6</v>
@@ -16796,7 +16796,7 @@
         </is>
       </c>
       <c r="G399" t="n">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H399" t="n">
         <v>8</v>
@@ -16837,7 +16837,7 @@
         </is>
       </c>
       <c r="G400" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H400" t="n">
         <v>8</v>
@@ -16878,13 +16878,13 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="H401" t="n">
         <v>10</v>
       </c>
       <c r="I401" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="402">
@@ -16919,7 +16919,7 @@
         </is>
       </c>
       <c r="G402" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H402" t="n">
         <v>2</v>
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="H403" t="n">
         <v>1</v>
@@ -17001,7 +17001,7 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H404" t="n">
         <v>2</v>
@@ -17042,7 +17042,7 @@
         </is>
       </c>
       <c r="G405" t="n">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="H405" t="n">
         <v>1</v>
@@ -17083,10 +17083,10 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>110</v>
+        <v>301</v>
       </c>
       <c r="H406" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I406" t="n">
         <v>0</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="G407" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17165,10 +17165,10 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="H408" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I408" t="n">
         <v>0</v>
@@ -17206,10 +17206,10 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="H409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I409" t="n">
         <v>0</v>
@@ -17247,10 +17247,10 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>91</v>
+        <v>355</v>
       </c>
       <c r="H410" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I410" t="n">
         <v>0</v>
@@ -17288,7 +17288,7 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>110</v>
+        <v>359</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -17329,10 +17329,10 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>112</v>
+        <v>379</v>
       </c>
       <c r="H412" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I412" t="n">
         <v>0</v>
@@ -17370,10 +17370,10 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>229</v>
+        <v>360</v>
       </c>
       <c r="H413" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I413" t="n">
         <v>0</v>
@@ -17411,10 +17411,10 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="H414" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I414" t="n">
         <v>0</v>
@@ -17452,10 +17452,10 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="H415" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I415" t="n">
         <v>2</v>
@@ -17493,10 +17493,10 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="H416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I416" t="n">
         <v>0</v>
@@ -17534,10 +17534,10 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I417" t="n">
         <v>0</v>
@@ -17575,10 +17575,10 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="H418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I418" t="n">
         <v>0</v>
@@ -17616,10 +17616,10 @@
         </is>
       </c>
       <c r="G419" t="n">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="H419" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I419" t="n">
         <v>0</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="H420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I420" t="n">
         <v>0</v>
@@ -17698,12 +17698,340 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H421" t="n">
         <v>1</v>
       </c>
       <c r="I421" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7664235129853775125</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Fan anh Messi #roborock#qrevo2pro #robothutbui#worldcup2026🏆</t>
+        </is>
+      </c>
+      <c r="G422" t="n">
+        <v>366</v>
+      </c>
+      <c r="H422" t="n">
+        <v>6</v>
+      </c>
+      <c r="I422" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7664537475943025938</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khách hàng đến trải nghiệm trực tiếp tại cửa hàng và chốt ngay 1 em Qrevo 2 Pro  #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G423" t="n">
+        <v>53</v>
+      </c>
+      <c r="H423" t="n">
+        <v>1</v>
+      </c>
+      <c r="I423" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7664534659556019464</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khách hàng sau khi được tư vấn và trải nghiệm thực tế đã chốt đơn luôn🥰 #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G424" t="n">
+        <v>63</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0</v>
+      </c>
+      <c r="I424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7664522197632830728</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G425" t="n">
+        <v>59</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0</v>
+      </c>
+      <c r="I425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7664521273258691858</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giao QRevo 2Pro cùng 3T SMART #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G426" t="n">
+        <v>63</v>
+      </c>
+      <c r="H426" t="n">
+        <v>1</v>
+      </c>
+      <c r="I426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7664518454531165458</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chiếc robot được khách hàng tin dùng #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G427" t="n">
+        <v>61</v>
+      </c>
+      <c r="H427" t="n">
+        <v>1</v>
+      </c>
+      <c r="I427" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7664445841675078933</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Các bác thấy sao hay để lại bình luận cho em biết với nhé 😘#mistorebienhoa #roborock #robothutbui #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G428" t="n">
+        <v>112</v>
+      </c>
+      <c r="H428" t="n">
+        <v>2</v>
+      </c>
+      <c r="I428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7664217914542738708</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khách chốt luôn COMBO: Robot lau nhà Qrevo 2 Pro + Robot lau kính 🤩 ✔️Một chiếc robot hút bụi lau nhà lo sàn nhà sạch bóng. ✔️Một chiếc robot lau kính giúp cửa kính trong veo mà không cần leo trèo nguy hiểm. ✨ Chỉ một lần đầu tư, cả ngôi nhà được chăm sóc từ sàn đến kính. Cảm ơn gia đình Thầy Hoàn và cô Sao Trần đã tin tưởng lựa chọn combo robot tại H&amp;T Smart Home Đức Trọng nghen. 📍 Robot luôn có sẵn tại cửa hàng, không cần chờ order. ✅ Trải nghiệm trực tiếp trước khi mua. ✅ Hướng dẫn sử dụng tận tình. ✅ Hỗ trợ lắp đặt và bảo hành nhanh chóng. Đừng mua theo quảng cáo, hãy đến trải nghiệm để chọn đúng chiếc robot phù hợp nhất với ngôi nhà của bạn! 📍 H&amp;T Smart Home – 384 Thống Nhất, Đức Trọng #Roborock #Qrevo2Pro #Robotlaunha #RobotDucTrong #lapdattannoi </t>
+        </is>
+      </c>
+      <c r="G429" t="n">
+        <v>347</v>
+      </c>
+      <c r="H429" t="n">
+        <v>2</v>
+      </c>
+      <c r="I429" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I429"/>
+  <dimension ref="A1:I446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1628</v>
+        <v>1809</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="H14" t="n">
         <v>34</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H20" t="n">
         <v>11</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>58800</v>
+        <v>59100</v>
       </c>
       <c r="H23" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="I23" t="n">
         <v>84</v>
@@ -1409,7 +1409,7 @@
         <v>138</v>
       </c>
       <c r="I24" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1713</v>
+        <v>1751</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H39" t="n">
         <v>9</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>701</v>
+        <v>725</v>
       </c>
       <c r="H46" t="n">
         <v>61</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>282</v>
+        <v>344</v>
       </c>
       <c r="H48" t="n">
         <v>16</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H63" t="n">
         <v>7</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>89800</v>
+        <v>105400</v>
       </c>
       <c r="H65" t="n">
-        <v>284</v>
+        <v>331</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="H66" t="n">
         <v>35</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="H77" t="n">
         <v>6</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>85400</v>
+        <v>85900</v>
       </c>
       <c r="H78" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I78" t="n">
         <v>78</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H80" t="n">
         <v>2</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2572</v>
+        <v>2619</v>
       </c>
       <c r="H87" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I87" t="n">
         <v>7</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H104" t="n">
         <v>2</v>
@@ -4865,13 +4865,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>11300</v>
+        <v>11400</v>
       </c>
       <c r="H108" t="n">
         <v>39</v>
       </c>
       <c r="I108" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109">
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>5890</v>
+        <v>6115</v>
       </c>
       <c r="H109" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I109" t="n">
         <v>33</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>475600</v>
+        <v>478400</v>
       </c>
       <c r="H116" t="n">
-        <v>3189</v>
+        <v>3209</v>
       </c>
       <c r="I116" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="117">
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H117" t="n">
         <v>4</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H118" t="n">
         <v>5</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H126" t="n">
         <v>25</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H151" t="n">
         <v>10</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H175" t="n">
         <v>3</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H176" t="n">
         <v>3</v>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H178" t="n">
         <v>4</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H194" t="n">
         <v>9</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H195" t="n">
         <v>4</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="H196" t="n">
         <v>20</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H203" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H205" t="n">
         <v>4</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H211" t="n">
         <v>9</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,10 +9252,10 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="H215" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I215" t="n">
         <v>0</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H216" t="n">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="H218" t="n">
         <v>14</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H219" t="n">
         <v>7</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H230" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H232" t="n">
         <v>7</v>
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H233" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>8477</v>
+        <v>8549</v>
       </c>
       <c r="H236" t="n">
         <v>40</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H239" t="n">
         <v>3</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H242" t="n">
         <v>4</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H243" t="n">
         <v>3</v>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H247" t="n">
         <v>8</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="H260" t="n">
         <v>10</v>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H261" t="n">
         <v>20</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="H267" t="n">
         <v>26</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H268" t="n">
         <v>5</v>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H272" t="n">
         <v>5</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H273" t="n">
         <v>4</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H274" t="n">
         <v>5</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,10 +11794,10 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H277" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I277" t="n">
         <v>2</v>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H279" t="n">
         <v>6</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H280" t="n">
         <v>5</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="H282" t="n">
         <v>10</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12204,10 +12204,10 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H287" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I287" t="n">
         <v>2</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H290" t="n">
         <v>8</v>
@@ -12368,7 +12368,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H291" t="n">
         <v>5</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>630</v>
+        <v>653</v>
       </c>
       <c r="H297" t="n">
         <v>25</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="H298" t="n">
         <v>22</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H303" t="n">
         <v>4</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H309" t="n">
         <v>3</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H311" t="n">
         <v>5</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H312" t="n">
         <v>7</v>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H314" t="n">
         <v>3</v>
@@ -13352,7 +13352,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H315" t="n">
         <v>3</v>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H316" t="n">
         <v>10</v>
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H317" t="n">
         <v>8</v>
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="H318" t="n">
         <v>9</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H322" t="n">
         <v>4</v>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H325" t="n">
         <v>2</v>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H326" t="n">
         <v>9</v>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H327" t="n">
         <v>6</v>
@@ -13967,7 +13967,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H330" t="n">
         <v>8</v>
@@ -14131,10 +14131,10 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H334" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I334" t="n">
         <v>0</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H337" t="n">
         <v>1</v>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H338" t="n">
         <v>5</v>
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H339" t="n">
         <v>3</v>
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H340" t="n">
         <v>5</v>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H341" t="n">
         <v>4</v>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H345" t="n">
         <v>3</v>
@@ -14623,10 +14623,10 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H346" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I346" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H347" t="n">
         <v>7</v>
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H348" t="n">
         <v>8</v>
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H349" t="n">
         <v>5</v>
@@ -14951,7 +14951,7 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H354" t="n">
         <v>3</v>
@@ -14992,7 +14992,7 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H355" t="n">
         <v>2</v>
@@ -15033,7 +15033,7 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H356" t="n">
         <v>2</v>
@@ -15074,7 +15074,7 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H357" t="n">
         <v>7</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H359" t="n">
         <v>2</v>
@@ -15197,10 +15197,10 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H360" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I360" t="n">
         <v>0</v>
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H361" t="n">
         <v>3</v>
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H362" t="n">
         <v>2</v>
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H363" t="n">
         <v>4</v>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H364" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I364" t="n">
         <v>0</v>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H365" t="n">
         <v>6</v>
@@ -15443,7 +15443,7 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H366" t="n">
         <v>5</v>
@@ -15484,7 +15484,7 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H367" t="n">
         <v>4</v>
@@ -15525,10 +15525,10 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H368" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I368" t="n">
         <v>0</v>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H369" t="n">
         <v>3</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H370" t="n">
         <v>1</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H372" t="n">
         <v>1</v>
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H373" t="n">
         <v>2</v>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H374" t="n">
         <v>3</v>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H375" t="n">
         <v>4</v>
@@ -15894,7 +15894,7 @@
         </is>
       </c>
       <c r="G377" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H377" t="n">
         <v>6</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H379" t="n">
         <v>7</v>
@@ -16058,7 +16058,7 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="H381" t="n">
         <v>2</v>
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H383" t="n">
         <v>3</v>
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H384" t="n">
         <v>5</v>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="H387" t="n">
         <v>6</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H388" t="n">
         <v>4</v>
@@ -16386,7 +16386,7 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H389" t="n">
         <v>6</v>
@@ -16427,7 +16427,7 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="H390" t="n">
         <v>4</v>
@@ -16468,10 +16468,10 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>509</v>
+        <v>562</v>
       </c>
       <c r="H391" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I391" t="n">
         <v>3</v>
@@ -16509,10 +16509,10 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H392" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I392" t="n">
         <v>0</v>
@@ -16550,7 +16550,7 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -16591,7 +16591,7 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="H394" t="n">
         <v>7</v>
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H396" t="n">
         <v>4</v>
@@ -16714,10 +16714,10 @@
         </is>
       </c>
       <c r="G397" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I397" t="n">
         <v>0</v>
@@ -16755,10 +16755,10 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="H398" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I398" t="n">
         <v>0</v>
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="H401" t="n">
         <v>10</v>
@@ -16919,7 +16919,7 @@
         </is>
       </c>
       <c r="G402" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H402" t="n">
         <v>2</v>
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="H403" t="n">
         <v>1</v>
@@ -17001,7 +17001,7 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H404" t="n">
         <v>2</v>
@@ -17042,7 +17042,7 @@
         </is>
       </c>
       <c r="G405" t="n">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="H405" t="n">
         <v>1</v>
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="H406" t="n">
         <v>4</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="G407" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="H408" t="n">
         <v>4</v>
@@ -17206,7 +17206,7 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H409" t="n">
         <v>1</v>
@@ -17247,10 +17247,10 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="H410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I410" t="n">
         <v>0</v>
@@ -17288,7 +17288,7 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="H412" t="n">
         <v>1</v>
@@ -17370,7 +17370,7 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H413" t="n">
         <v>4</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H414" t="n">
         <v>4</v>
@@ -17452,7 +17452,7 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H415" t="n">
         <v>4</v>
@@ -17493,7 +17493,7 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="H416" t="n">
         <v>1</v>
@@ -17534,7 +17534,7 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H417" t="n">
         <v>1</v>
@@ -17575,7 +17575,7 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H418" t="n">
         <v>2</v>
@@ -17616,7 +17616,7 @@
         </is>
       </c>
       <c r="G419" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H419" t="n">
         <v>1</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H420" t="n">
         <v>2</v>
@@ -17698,7 +17698,7 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H421" t="n">
         <v>1</v>
@@ -17739,7 +17739,7 @@
         </is>
       </c>
       <c r="G422" t="n">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="H422" t="n">
         <v>6</v>
@@ -17780,10 +17780,10 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>53</v>
+        <v>344</v>
       </c>
       <c r="H423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I423" t="n">
         <v>0</v>
@@ -17821,10 +17821,10 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>63</v>
+        <v>373</v>
       </c>
       <c r="H424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I424" t="n">
         <v>0</v>
@@ -17862,10 +17862,10 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>59</v>
+        <v>352</v>
       </c>
       <c r="H425" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I425" t="n">
         <v>0</v>
@@ -17903,10 +17903,10 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>63</v>
+        <v>343</v>
       </c>
       <c r="H426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I426" t="n">
         <v>0</v>
@@ -17944,10 +17944,10 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>61</v>
+        <v>319</v>
       </c>
       <c r="H427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I427" t="n">
         <v>0</v>
@@ -17985,13 +17985,13 @@
         </is>
       </c>
       <c r="G428" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="H428" t="n">
         <v>2</v>
       </c>
       <c r="I428" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -18026,12 +18026,709 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="H429" t="n">
+        <v>3</v>
+      </c>
+      <c r="I429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7664871694196116756</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tui chọn tận hưởng🫢🫢🫢 Còn mấy bà chọn gì😂😂😂😂😂#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G430" t="n">
+        <v>86</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0</v>
+      </c>
+      <c r="I430" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7664848549317709076</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mỗi ngày em chọn một niềm vui🥰🥰 Và hôm nay niềm vui em chọn là nhận được sự yêu thương và tin tưởng của khách hàng như vậy thui❤️❤️❤️#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G431" t="n">
+        <v>240</v>
+      </c>
+      <c r="H431" t="n">
         <v>2</v>
       </c>
-      <c r="I429" t="n">
+      <c r="I431" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7664841853790948616</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Robot hút bụi có thật sự chỉ là chiêu trò PR?  #Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G432" t="n">
+        <v>117</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0</v>
+      </c>
+      <c r="I432" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7664624521655110930</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Dù là hoàng tử hay công chúa thì khách chỉ cần chốt đơn là chúng em cũng sẵn sàng vào vị trí phục vụ tận nơi luôn ạ🛵🛵 Khách hàng để ý chúng em nhiều chút nhé ạ ❤️❤️ ━━━━━━━━━━━━━━ VUA ROBOT – 3T SMART ☎ Hotline: 0️⃣3️⃣6️⃣5️⃣ 319 688 📍 272 Phan Đình Phùng, TP. Thái Nguyên #3TSmart  #Qrevo2Pro #Roborock #robothutbui</t>
+        </is>
+      </c>
+      <c r="G433" t="n">
+        <v>383</v>
+      </c>
+      <c r="H433" t="n">
+        <v>2</v>
+      </c>
+      <c r="I433" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7664802918696045845</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc tư vấn giải đáp thắc mắc cho các anh chị đang phân vân chọn những mẫu mã hay thương hiệu nào sử dụng bền #robothutbui #roborock #mistorebienhoa #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G434" t="n">
+        <v>127</v>
+      </c>
+      <c r="H434" t="n">
+        <v>3</v>
+      </c>
+      <c r="I434" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7664929323555605781</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhất định phải có 1 thứ nha các bác #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G435" t="n">
+        <v>27</v>
+      </c>
+      <c r="H435" t="n">
+        <v>2</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7664884038754143508</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Màu trắng mẹ mắng cũng mua 🤭 #Qrevo2Pro #roborock #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G436" t="n">
+        <v>61</v>
+      </c>
+      <c r="H436" t="n">
+        <v>2</v>
+      </c>
+      <c r="I436" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7664864380932115733</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không có điểm chê luôn ạ #Qrevo2Pro #roborock #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G437" t="n">
+        <v>67</v>
+      </c>
+      <c r="H437" t="n">
+        <v>2</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7664805976142286101</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pov chị đẹp sau khi trải nghiệm Qrevo 2Pro #Qrevo2Pro #robothutbui #roborock #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G438" t="n">
+        <v>86</v>
+      </c>
+      <c r="H438" t="n">
+        <v>5</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7664804108993400084</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Từ ngày biết đến roborock chú mới mua 6 con thôi #Qrevo2Pro #robothutbui #roborock #smarthomephutho #nhathongminh </t>
+        </is>
+      </c>
+      <c r="G439" t="n">
+        <v>92</v>
+      </c>
+      <c r="H439" t="n">
+        <v>1</v>
+      </c>
+      <c r="I439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7664799422798204180</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chị đẹp dễ thương gì đâu #robothutbui #Qrevo2Pro #roborock #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G440" t="n">
+        <v>184</v>
+      </c>
+      <c r="H440" t="n">
+        <v>1</v>
+      </c>
+      <c r="I440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7664630788620832021</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Câu chuyện đáng iu với chị đẹp #robothutbui #Qrevo2Pro #roborock #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G441" t="n">
+        <v>362</v>
+      </c>
+      <c r="H441" t="n">
+        <v>2</v>
+      </c>
+      <c r="I441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7664626822822317332</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lại thêm 1 em 2 Pro cho chị đẹp ở Văn Lang Sky #robothutbui #Qrevo2Pro #roborock #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G442" t="n">
+        <v>172</v>
+      </c>
+      <c r="H442" t="n">
+        <v>2</v>
+      </c>
+      <c r="I442" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7664652863259397396</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✨ Feedback chân thật từ khách sau lần lau đầu tiên #Roborock #Qrevo2Pro #Robotlaunha #RobotDucTrong #trainghiemthucte </t>
+        </is>
+      </c>
+      <c r="G443" t="n">
+        <v>185</v>
+      </c>
+      <c r="H443" t="n">
+        <v>3</v>
+      </c>
+      <c r="I443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>homebotvietnam</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homebotvietnam/video/7664646144634539285</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Dọn nhà chưa bao giờ "chill" đến vậy! 🤖✨ Xem Qrevo 2 Pro xử lý mọi thứ gọn gàng chỉ trong vài phút. 🏡💙 #Qrevo2Pro #Roborock #robothutbui #ReviewCongNghe #SmartHome</t>
+        </is>
+      </c>
+      <c r="G444" t="n">
+        <v>246</v>
+      </c>
+      <c r="H444" t="n">
+        <v>3</v>
+      </c>
+      <c r="I444" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>hinhnendep7777</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hinhnendep7777/video/7664936936766754056</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trợ thủ khi bạn vắng nhà. #Roborock #Qrevo2Pro #robothutbui #gialai </t>
+        </is>
+      </c>
+      <c r="G445" t="n">
+        <v>0</v>
+      </c>
+      <c r="H445" t="n">
+        <v>1</v>
+      </c>
+      <c r="I445" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>hinhnendep7777</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hinhnendep7777/video/7664936537762647314</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Top 5 thứ đang tiền mua nhất trong nhà  #Qrevo2Pro #Roborock #robothutbui #gialai </t>
+        </is>
+      </c>
+      <c r="G446" t="n">
+        <v>0</v>
+      </c>
+      <c r="H446" t="n">
+        <v>0</v>
+      </c>
+      <c r="I446" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I446"/>
+  <dimension ref="A1:I460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1809</v>
+        <v>2009</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H10" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H11" t="n">
         <v>6</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="H14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H15" t="n">
         <v>5</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H20" t="n">
         <v>11</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>59100</v>
+        <v>59900</v>
       </c>
       <c r="H23" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I23" t="n">
         <v>84</v>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="H24" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I24" t="n">
         <v>38</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1751</v>
+        <v>1777</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H39" t="n">
         <v>9</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>725</v>
+        <v>762</v>
       </c>
       <c r="H46" t="n">
         <v>61</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>344</v>
+        <v>395</v>
       </c>
       <c r="H48" t="n">
         <v>16</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>105400</v>
+        <v>122200</v>
       </c>
       <c r="H65" t="n">
-        <v>331</v>
+        <v>396</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="H66" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I66" t="n">
         <v>26</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="H77" t="n">
         <v>6</v>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>85900</v>
+        <v>86000</v>
       </c>
       <c r="H78" t="n">
         <v>302</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2619</v>
+        <v>2660</v>
       </c>
       <c r="H87" t="n">
         <v>19</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>6115</v>
+        <v>6358</v>
       </c>
       <c r="H109" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="I109" t="n">
         <v>33</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>478400</v>
+        <v>480900</v>
       </c>
       <c r="H116" t="n">
-        <v>3209</v>
+        <v>3222</v>
       </c>
       <c r="I116" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="117">
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H117" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H118" t="n">
         <v>5</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2607</v>
+        <v>2610</v>
       </c>
       <c r="H139" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H151" t="n">
         <v>10</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H153" t="n">
         <v>4</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H155" t="n">
         <v>5</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H168" t="n">
         <v>14</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H183" t="n">
         <v>4</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H194" t="n">
         <v>9</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H195" t="n">
         <v>4</v>
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H196" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I196" t="n">
         <v>4</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H203" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H205" t="n">
         <v>4</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H208" t="n">
         <v>3</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H211" t="n">
         <v>9</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="H218" t="n">
         <v>14</v>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H220" t="n">
         <v>5</v>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H222" t="n">
         <v>6</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H224" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H228" t="n">
         <v>9</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H229" t="n">
         <v>10</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="H232" t="n">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H235" t="n">
         <v>13</v>
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>8549</v>
+        <v>8624</v>
       </c>
       <c r="H236" t="n">
         <v>40</v>
@@ -10277,10 +10277,10 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
@@ -10400,10 +10400,10 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="H243" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I243" t="n">
         <v>0</v>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H244" t="n">
         <v>6</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H253" t="n">
         <v>8</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -10933,10 +10933,10 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H256" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I256" t="n">
         <v>1</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="H260" t="n">
         <v>10</v>
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H262" t="n">
         <v>5</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11384,10 +11384,10 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="H267" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I267" t="n">
         <v>4</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H268" t="n">
         <v>5</v>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H272" t="n">
         <v>5</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H273" t="n">
         <v>4</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H274" t="n">
         <v>5</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H278" t="n">
         <v>4</v>
@@ -11876,7 +11876,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H279" t="n">
         <v>6</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="H280" t="n">
         <v>5</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="H282" t="n">
         <v>10</v>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="H283" t="n">
         <v>4</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H287" t="n">
         <v>7</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H290" t="n">
         <v>8</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H294" t="n">
         <v>5</v>
@@ -12573,10 +12573,10 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H296" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I296" t="n">
         <v>2</v>
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>653</v>
+        <v>667</v>
       </c>
       <c r="H297" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I297" t="n">
         <v>2</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="H298" t="n">
         <v>22</v>
@@ -12696,7 +12696,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H299" t="n">
         <v>7</v>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H300" t="n">
         <v>1</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H302" t="n">
         <v>1</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="H303" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I303" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H304" t="n">
         <v>2</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H308" t="n">
         <v>4</v>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H309" t="n">
         <v>3</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H311" t="n">
         <v>5</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="H312" t="n">
         <v>7</v>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H314" t="n">
         <v>3</v>
@@ -13352,7 +13352,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H315" t="n">
         <v>3</v>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H316" t="n">
         <v>10</v>
@@ -13434,10 +13434,10 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="H317" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I317" t="n">
         <v>2</v>
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H318" t="n">
         <v>9</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H321" t="n">
         <v>3</v>
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H323" t="n">
         <v>1</v>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H325" t="n">
         <v>2</v>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="H327" t="n">
         <v>6</v>
@@ -13967,7 +13967,7 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H330" t="n">
         <v>8</v>
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H334" t="n">
         <v>5</v>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H335" t="n">
         <v>6</v>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14254,10 +14254,10 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="H337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I337" t="n">
         <v>0</v>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H338" t="n">
         <v>5</v>
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H339" t="n">
         <v>3</v>
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H340" t="n">
         <v>5</v>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H341" t="n">
         <v>4</v>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -14500,7 +14500,7 @@
         </is>
       </c>
       <c r="G343" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H343" t="n">
         <v>1</v>
@@ -14541,7 +14541,7 @@
         </is>
       </c>
       <c r="G344" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H344" t="n">
         <v>1</v>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H345" t="n">
         <v>3</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H346" t="n">
         <v>3</v>
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H347" t="n">
         <v>7</v>
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H348" t="n">
         <v>8</v>
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H349" t="n">
         <v>5</v>
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H351" t="n">
         <v>1</v>
@@ -14951,7 +14951,7 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H354" t="n">
         <v>3</v>
@@ -14992,7 +14992,7 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H355" t="n">
         <v>2</v>
@@ -15033,7 +15033,7 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H356" t="n">
         <v>2</v>
@@ -15074,7 +15074,7 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H357" t="n">
         <v>7</v>
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H358" t="n">
         <v>4</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H359" t="n">
         <v>2</v>
@@ -15197,7 +15197,7 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H360" t="n">
         <v>5</v>
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H361" t="n">
         <v>3</v>
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H362" t="n">
         <v>2</v>
@@ -15361,7 +15361,7 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H364" t="n">
         <v>6</v>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H365" t="n">
         <v>6</v>
@@ -15443,7 +15443,7 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H366" t="n">
         <v>5</v>
@@ -15484,7 +15484,7 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H367" t="n">
         <v>4</v>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H369" t="n">
         <v>3</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H370" t="n">
         <v>1</v>
@@ -15648,7 +15648,7 @@
         </is>
       </c>
       <c r="G371" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H371" t="n">
         <v>2</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="H372" t="n">
         <v>1</v>
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H373" t="n">
         <v>2</v>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H374" t="n">
         <v>3</v>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H375" t="n">
         <v>4</v>
@@ -15935,7 +15935,7 @@
         </is>
       </c>
       <c r="G378" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H378" t="n">
         <v>3</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H379" t="n">
         <v>7</v>
@@ -16058,7 +16058,7 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H381" t="n">
         <v>2</v>
@@ -16099,7 +16099,7 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H382" t="n">
         <v>2</v>
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H383" t="n">
         <v>3</v>
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H384" t="n">
         <v>5</v>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -16263,7 +16263,7 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="H387" t="n">
         <v>6</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H388" t="n">
         <v>4</v>
@@ -16386,7 +16386,7 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H389" t="n">
         <v>6</v>
@@ -16427,10 +16427,10 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="H390" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I390" t="n">
         <v>0</v>
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="H391" t="n">
         <v>5</v>
@@ -16509,7 +16509,7 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H392" t="n">
         <v>3</v>
@@ -16550,7 +16550,7 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -16591,7 +16591,7 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="H394" t="n">
         <v>7</v>
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H395" t="n">
         <v>1</v>
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H396" t="n">
         <v>4</v>
@@ -16714,7 +16714,7 @@
         </is>
       </c>
       <c r="G397" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H397" t="n">
         <v>2</v>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="H398" t="n">
         <v>7</v>
@@ -16796,7 +16796,7 @@
         </is>
       </c>
       <c r="G399" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H399" t="n">
         <v>8</v>
@@ -16878,10 +16878,10 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H401" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I401" t="n">
         <v>15</v>
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H403" t="n">
         <v>1</v>
@@ -17001,7 +17001,7 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H404" t="n">
         <v>2</v>
@@ -17042,7 +17042,7 @@
         </is>
       </c>
       <c r="G405" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H405" t="n">
         <v>1</v>
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H406" t="n">
         <v>4</v>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H408" t="n">
         <v>4</v>
@@ -17206,7 +17206,7 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="H409" t="n">
         <v>1</v>
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="H410" t="n">
         <v>2</v>
@@ -17288,10 +17288,10 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="H411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I411" t="n">
         <v>0</v>
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="H412" t="n">
         <v>1</v>
@@ -17370,7 +17370,7 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="H413" t="n">
         <v>4</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H414" t="n">
         <v>4</v>
@@ -17493,7 +17493,7 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="H416" t="n">
         <v>1</v>
@@ -17534,7 +17534,7 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H417" t="n">
         <v>1</v>
@@ -17575,7 +17575,7 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H418" t="n">
         <v>2</v>
@@ -17616,7 +17616,7 @@
         </is>
       </c>
       <c r="G419" t="n">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H419" t="n">
         <v>1</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H420" t="n">
         <v>2</v>
@@ -17698,7 +17698,7 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H421" t="n">
         <v>1</v>
@@ -17739,10 +17739,10 @@
         </is>
       </c>
       <c r="G422" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H422" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I422" t="n">
         <v>0</v>
@@ -17780,7 +17780,7 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="H423" t="n">
         <v>2</v>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="H424" t="n">
         <v>1</v>
@@ -17862,7 +17862,7 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H425" t="n">
         <v>3</v>
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H426" t="n">
         <v>3</v>
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="H427" t="n">
         <v>2</v>
@@ -17985,7 +17985,7 @@
         </is>
       </c>
       <c r="G428" t="n">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="H428" t="n">
         <v>2</v>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H429" t="n">
         <v>3</v>
@@ -18067,10 +18067,10 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>86</v>
+        <v>386</v>
       </c>
       <c r="H430" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I430" t="n">
         <v>0</v>
@@ -18108,10 +18108,10 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>240</v>
+        <v>373</v>
       </c>
       <c r="H431" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I431" t="n">
         <v>0</v>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>117</v>
+        <v>356</v>
       </c>
       <c r="H432" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I432" t="n">
         <v>0</v>
@@ -18190,10 +18190,10 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>383</v>
+        <v>412</v>
       </c>
       <c r="H433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I433" t="n">
         <v>0</v>
@@ -18231,7 +18231,7 @@
         </is>
       </c>
       <c r="G434" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="H434" t="n">
         <v>3</v>
@@ -18272,10 +18272,10 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="H435" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I435" t="n">
         <v>0</v>
@@ -18313,13 +18313,13 @@
         </is>
       </c>
       <c r="G436" t="n">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="H436" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I436" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -18354,13 +18354,13 @@
         </is>
       </c>
       <c r="G437" t="n">
-        <v>67</v>
+        <v>148</v>
       </c>
       <c r="H437" t="n">
+        <v>4</v>
+      </c>
+      <c r="I437" t="n">
         <v>2</v>
-      </c>
-      <c r="I437" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -18395,7 +18395,7 @@
         </is>
       </c>
       <c r="G438" t="n">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="H438" t="n">
         <v>5</v>
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="G439" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="H439" t="n">
         <v>1</v>
@@ -18477,13 +18477,13 @@
         </is>
       </c>
       <c r="G440" t="n">
-        <v>184</v>
+        <v>331</v>
       </c>
       <c r="H440" t="n">
         <v>1</v>
       </c>
       <c r="I440" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="441">
@@ -18518,10 +18518,10 @@
         </is>
       </c>
       <c r="G441" t="n">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="H441" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I441" t="n">
         <v>0</v>
@@ -18559,7 +18559,7 @@
         </is>
       </c>
       <c r="G442" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="H442" t="n">
         <v>2</v>
@@ -18600,7 +18600,7 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="H443" t="n">
         <v>3</v>
@@ -18641,10 +18641,10 @@
         </is>
       </c>
       <c r="G444" t="n">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="H444" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I444" t="n">
         <v>0</v>
@@ -18682,10 +18682,10 @@
         </is>
       </c>
       <c r="G445" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H445" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I445" t="n">
         <v>0</v>
@@ -18723,13 +18723,587 @@
         </is>
       </c>
       <c r="G446" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I446" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7664989262433078549</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Top 5 thứ đáng mua trong nhà  #robothutbui #roborock #qrevo2pro #woldcup2026#VINHLONG </t>
+        </is>
+      </c>
+      <c r="G447" t="n">
+        <v>389</v>
+      </c>
+      <c r="H447" t="n">
+        <v>6</v>
+      </c>
+      <c r="I447" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7665234962735533332</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot có thể “đình công”, nhưng shop thì không! 😄 Máy gặp lỗi cứ mang về, bảo hành có shop lo. Mua Roborock là mua cả sự yên tâm! 🤖#Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G448" t="n">
+        <v>183</v>
+      </c>
+      <c r="H448" t="n">
+        <v>0</v>
+      </c>
+      <c r="I448" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7664991994996919572</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiền có thể mua hạnh phúc… Ít nhất là mua được Roborock Qrevo 2 Pro, để khỏi phải quét nhà mỗi ngày! 😍🤖 #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>409</v>
+      </c>
+      <c r="H449" t="n">
+        <v>7</v>
+      </c>
+      <c r="I449" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7664960629219839253</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Từng là một cô gái đầy nhiệt huyết, năng động. Sau 5 năm bắt đầu lại từ con số 0 với bán hàng và tư vấn lại. Nghĩ rằng mình không thể, nhưng cố gắng nỗ lực và thành quả của mình là sự tin tưởng của khách hàng. Ngày ngày nhận được lời khen của khách hàng❤️ Nhận được tình yêu thương của khách hàng❤️❤️❤️❤️ Mình thành công quá rực rỡ r đúng không mọi người!!! #Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G450" t="n">
+        <v>358</v>
+      </c>
+      <c r="H450" t="n">
+        <v>3</v>
+      </c>
+      <c r="I450" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7664955877694180628</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đừng ai đùa với cái gương soi của em Quevo 2 pro này nha🤣🤣🤣🤣🤣 Chụp ảnh nhớ khép khép lại nha mấy ní🤭🤭🤭#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G451" t="n">
+        <v>378</v>
+      </c>
+      <c r="H451" t="n">
+        <v>3</v>
+      </c>
+      <c r="I451" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7665318694972673288</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hầu hết mọi người đều đã sở hữu cho mình 1 em Q Revo 2 Pro. Còn bạn thì sao? #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G452" t="n">
+        <v>13</v>
+      </c>
+      <c r="H452" t="n">
+        <v>1</v>
+      </c>
+      <c r="I452" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7665314936570039560</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Top 5 những thứ đáng mua cho nhà bạn #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G453" t="n">
+        <v>14</v>
+      </c>
+      <c r="H453" t="n">
+        <v>1</v>
+      </c>
+      <c r="I453" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7665312754038836498</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trải nghiệm thực tế của khách tại cửa hàng #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>14</v>
+      </c>
+      <c r="H454" t="n">
+        <v>1</v>
+      </c>
+      <c r="I454" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7665322502213651733</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QR 2 Pro ra trận #roborock #mistorebienhoa #qrevo2pro #robothutbui </t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>6</v>
+      </c>
+      <c r="H455" t="n">
+        <v>1</v>
+      </c>
+      <c r="I455" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7665257959307447572</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 pro quá hợp lý luôn ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G456" t="n">
+        <v>70</v>
+      </c>
+      <c r="H456" t="n">
+        <v>3</v>
+      </c>
+      <c r="I456" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7665251541938474260</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhạc nào em cũng chiều được luôn ạ #roborock #robothutbui #Qrevo2Pro #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>87</v>
+      </c>
+      <c r="H457" t="n">
+        <v>2</v>
+      </c>
+      <c r="I457" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7665184644320464148</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Còn gì lăn tăn nữa ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G458" t="n">
+        <v>93</v>
+      </c>
+      <c r="H458" t="n">
+        <v>3</v>
+      </c>
+      <c r="I458" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7665154123968302357</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Mua Robot hút bụi để rảnh tay pha một ly cafe Laura 😆 #Roborock #Qrevo2Pro #Robotlaunha #RobotDucTrong #xuhuong</t>
+        </is>
+      </c>
+      <c r="G459" t="n">
+        <v>154</v>
+      </c>
+      <c r="H459" t="n">
+        <v>1</v>
+      </c>
+      <c r="I459" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7664993003664182548</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không mua cũng phải mua 😆 #Roborock #Qrevo2Pro #Robotlaunha #RobotDucTrong #xuhuong  </t>
+        </is>
+      </c>
+      <c r="G460" t="n">
+        <v>150</v>
+      </c>
+      <c r="H460" t="n">
+        <v>3</v>
+      </c>
+      <c r="I460" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I460"/>
+  <dimension ref="A1:I467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2009</v>
+        <v>2205</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H11" t="n">
         <v>6</v>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H12" t="n">
         <v>10</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H13" t="n">
         <v>11</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="H14" t="n">
         <v>35</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>59900</v>
+        <v>60500</v>
       </c>
       <c r="H23" t="n">
         <v>361</v>
       </c>
       <c r="I23" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>26100</v>
+        <v>26200</v>
       </c>
       <c r="H24" t="n">
         <v>140</v>
       </c>
       <c r="I24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>762</v>
+        <v>780</v>
       </c>
       <c r="H46" t="n">
         <v>61</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="H48" t="n">
         <v>16</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H58" t="n">
         <v>3</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="H61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H64" t="n">
         <v>4</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>122200</v>
+        <v>132600</v>
       </c>
       <c r="H65" t="n">
-        <v>396</v>
+        <v>430</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>874</v>
+        <v>884</v>
       </c>
       <c r="H66" t="n">
         <v>36</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H77" t="n">
         <v>6</v>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>86000</v>
+        <v>86200</v>
       </c>
       <c r="H78" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I78" t="n">
         <v>78</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H80" t="n">
         <v>2</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2660</v>
+        <v>2681</v>
       </c>
       <c r="H87" t="n">
         <v>19</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H102" t="n">
         <v>3</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>11400</v>
+        <v>11500</v>
       </c>
       <c r="H108" t="n">
         <v>39</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>6358</v>
+        <v>6559</v>
       </c>
       <c r="H109" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="I109" t="n">
         <v>33</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>480900</v>
+        <v>482900</v>
       </c>
       <c r="H116" t="n">
-        <v>3222</v>
+        <v>3239</v>
       </c>
       <c r="I116" t="n">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="117">
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H117" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H118" t="n">
         <v>5</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H126" t="n">
         <v>25</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H135" t="n">
         <v>3</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H142" t="n">
         <v>3</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H173" t="n">
         <v>4</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H179" t="n">
         <v>17</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H180" t="n">
         <v>3</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H181" t="n">
         <v>3</v>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H183" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H194" t="n">
         <v>9</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="H195" t="n">
         <v>4</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="H196" t="n">
         <v>21</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H197" t="n">
         <v>5</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H199" t="n">
         <v>2</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H200" t="n">
         <v>1</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H203" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H205" t="n">
         <v>4</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H208" t="n">
         <v>3</v>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H209" t="n">
         <v>5</v>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H210" t="n">
         <v>7</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H215" t="n">
         <v>5</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H216" t="n">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="H218" t="n">
         <v>14</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H223" t="n">
         <v>5</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H224" t="n">
         <v>10</v>
@@ -9908,7 +9908,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H231" t="n">
         <v>14</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="H232" t="n">
         <v>7</v>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H234" t="n">
         <v>12</v>
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>8624</v>
+        <v>8659</v>
       </c>
       <c r="H236" t="n">
         <v>40</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H239" t="n">
         <v>3</v>
@@ -10277,10 +10277,10 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="H240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H241" t="n">
         <v>8</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H243" t="n">
         <v>4</v>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H253" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I253" t="n">
         <v>0</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H257" t="n">
         <v>4</v>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H258" t="n">
         <v>3</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="H260" t="n">
         <v>10</v>
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H262" t="n">
         <v>5</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>973</v>
+        <v>985</v>
       </c>
       <c r="H267" t="n">
         <v>27</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H273" t="n">
         <v>4</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H277" t="n">
         <v>5</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H278" t="n">
         <v>4</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="H280" t="n">
         <v>5</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="H282" t="n">
         <v>10</v>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="H283" t="n">
         <v>4</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H286" t="n">
         <v>6</v>
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H287" t="n">
         <v>7</v>
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H288" t="n">
         <v>3</v>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H289" t="n">
         <v>3</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H290" t="n">
         <v>8</v>
@@ -12368,7 +12368,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H291" t="n">
         <v>5</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H295" t="n">
         <v>6</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H296" t="n">
         <v>7</v>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="H297" t="n">
         <v>26</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="H298" t="n">
         <v>22</v>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H300" t="n">
         <v>1</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="H303" t="n">
         <v>5</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H311" t="n">
         <v>5</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="H312" t="n">
         <v>7</v>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H314" t="n">
         <v>3</v>
@@ -13352,7 +13352,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H315" t="n">
         <v>3</v>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H316" t="n">
         <v>10</v>
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="H317" t="n">
         <v>9</v>
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H318" t="n">
         <v>9</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="H321" t="n">
         <v>3</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H322" t="n">
         <v>4</v>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H325" t="n">
         <v>2</v>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H326" t="n">
         <v>9</v>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H327" t="n">
         <v>6</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H333" t="n">
         <v>3</v>
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H334" t="n">
         <v>5</v>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H335" t="n">
         <v>6</v>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H337" t="n">
         <v>2</v>
@@ -14336,10 +14336,10 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I339" t="n">
         <v>0</v>
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H340" t="n">
         <v>5</v>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H341" t="n">
         <v>4</v>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -14500,7 +14500,7 @@
         </is>
       </c>
       <c r="G343" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H343" t="n">
         <v>1</v>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H345" t="n">
         <v>3</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H346" t="n">
         <v>3</v>
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H347" t="n">
         <v>7</v>
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H348" t="n">
         <v>8</v>
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H349" t="n">
         <v>5</v>
@@ -14869,7 +14869,7 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H352" t="n">
         <v>3</v>
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H353" t="n">
         <v>6</v>
@@ -14951,10 +14951,10 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H354" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I354" t="n">
         <v>0</v>
@@ -14992,7 +14992,7 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H355" t="n">
         <v>2</v>
@@ -15033,7 +15033,7 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H356" t="n">
         <v>2</v>
@@ -15074,7 +15074,7 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H357" t="n">
         <v>7</v>
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H358" t="n">
         <v>4</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H359" t="n">
         <v>2</v>
@@ -15197,10 +15197,10 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H360" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I360" t="n">
         <v>0</v>
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H361" t="n">
         <v>3</v>
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H362" t="n">
         <v>2</v>
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H363" t="n">
         <v>4</v>
@@ -15361,7 +15361,7 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H364" t="n">
         <v>6</v>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H365" t="n">
         <v>6</v>
@@ -15443,7 +15443,7 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H366" t="n">
         <v>5</v>
@@ -15525,7 +15525,7 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H368" t="n">
         <v>4</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="H372" t="n">
         <v>1</v>
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="H373" t="n">
         <v>2</v>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H374" t="n">
         <v>3</v>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H375" t="n">
         <v>4</v>
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="G376" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H376" t="n">
         <v>7</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="H379" t="n">
         <v>7</v>
@@ -16058,7 +16058,7 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H381" t="n">
         <v>2</v>
@@ -16099,7 +16099,7 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H382" t="n">
         <v>2</v>
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H383" t="n">
         <v>3</v>
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H384" t="n">
         <v>5</v>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H387" t="n">
         <v>6</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H388" t="n">
         <v>4</v>
@@ -16386,10 +16386,10 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H389" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I389" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="H390" t="n">
         <v>5</v>
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="H391" t="n">
         <v>5</v>
@@ -16509,7 +16509,7 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H392" t="n">
         <v>3</v>
@@ -16550,7 +16550,7 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -16591,10 +16591,10 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="H394" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I394" t="n">
         <v>0</v>
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H395" t="n">
         <v>1</v>
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H396" t="n">
         <v>4</v>
@@ -16714,7 +16714,7 @@
         </is>
       </c>
       <c r="G397" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H397" t="n">
         <v>2</v>
@@ -16755,10 +16755,10 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="H398" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I398" t="n">
         <v>0</v>
@@ -16796,7 +16796,7 @@
         </is>
       </c>
       <c r="G399" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H399" t="n">
         <v>8</v>
@@ -16837,7 +16837,7 @@
         </is>
       </c>
       <c r="G400" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H400" t="n">
         <v>8</v>
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="H401" t="n">
         <v>11</v>
@@ -16919,7 +16919,7 @@
         </is>
       </c>
       <c r="G402" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H402" t="n">
         <v>2</v>
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H403" t="n">
         <v>1</v>
@@ -17001,7 +17001,7 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H404" t="n">
         <v>2</v>
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="H406" t="n">
         <v>4</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="G407" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H408" t="n">
         <v>4</v>
@@ -17206,7 +17206,7 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H409" t="n">
         <v>1</v>
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H410" t="n">
         <v>2</v>
@@ -17288,13 +17288,13 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="H411" t="n">
+        <v>2</v>
+      </c>
+      <c r="I411" t="n">
         <v>1</v>
-      </c>
-      <c r="I411" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H412" t="n">
         <v>1</v>
@@ -17370,7 +17370,7 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="H413" t="n">
         <v>4</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H414" t="n">
         <v>4</v>
@@ -17452,7 +17452,7 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H415" t="n">
         <v>4</v>
@@ -17493,7 +17493,7 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H416" t="n">
         <v>1</v>
@@ -17534,7 +17534,7 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H417" t="n">
         <v>1</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="H420" t="n">
         <v>2</v>
@@ -17698,7 +17698,7 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H421" t="n">
         <v>1</v>
@@ -17780,7 +17780,7 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H423" t="n">
         <v>2</v>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H424" t="n">
         <v>1</v>
@@ -17862,7 +17862,7 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H425" t="n">
         <v>3</v>
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H426" t="n">
         <v>3</v>
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="H427" t="n">
         <v>2</v>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H429" t="n">
         <v>3</v>
@@ -18067,7 +18067,7 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H430" t="n">
         <v>2</v>
@@ -18108,7 +18108,7 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H431" t="n">
         <v>3</v>
@@ -18149,10 +18149,10 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I432" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="H433" t="n">
         <v>3</v>
@@ -18272,10 +18272,10 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="H435" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I435" t="n">
         <v>0</v>
@@ -18313,10 +18313,10 @@
         </is>
       </c>
       <c r="G436" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H436" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I436" t="n">
         <v>3</v>
@@ -18354,10 +18354,10 @@
         </is>
       </c>
       <c r="G437" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H437" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I437" t="n">
         <v>2</v>
@@ -18395,7 +18395,7 @@
         </is>
       </c>
       <c r="G438" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H438" t="n">
         <v>5</v>
@@ -18436,10 +18436,10 @@
         </is>
       </c>
       <c r="G439" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I439" t="n">
         <v>0</v>
@@ -18518,10 +18518,10 @@
         </is>
       </c>
       <c r="G441" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H441" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I441" t="n">
         <v>0</v>
@@ -18559,10 +18559,10 @@
         </is>
       </c>
       <c r="G442" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I442" t="n">
         <v>2</v>
@@ -18600,7 +18600,7 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H443" t="n">
         <v>3</v>
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="G445" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H445" t="n">
         <v>2</v>
@@ -18764,13 +18764,13 @@
         </is>
       </c>
       <c r="G447" t="n">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="H447" t="n">
         <v>6</v>
       </c>
       <c r="I447" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -18805,10 +18805,10 @@
         </is>
       </c>
       <c r="G448" t="n">
-        <v>183</v>
+        <v>373</v>
       </c>
       <c r="H448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I448" t="n">
         <v>0</v>
@@ -18846,7 +18846,7 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="H449" t="n">
         <v>7</v>
@@ -18887,10 +18887,10 @@
         </is>
       </c>
       <c r="G450" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H450" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I450" t="n">
         <v>0</v>
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="G451" t="n">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="H451" t="n">
         <v>3</v>
@@ -18969,13 +18969,13 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>13</v>
+        <v>334</v>
       </c>
       <c r="H452" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I452" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="453">
@@ -19010,10 +19010,10 @@
         </is>
       </c>
       <c r="G453" t="n">
-        <v>14</v>
+        <v>352</v>
       </c>
       <c r="H453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I453" t="n">
         <v>2</v>
@@ -19051,10 +19051,10 @@
         </is>
       </c>
       <c r="G454" t="n">
-        <v>14</v>
+        <v>338</v>
       </c>
       <c r="H454" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I454" t="n">
         <v>0</v>
@@ -19092,10 +19092,10 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>6</v>
+        <v>144</v>
       </c>
       <c r="H455" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I455" t="n">
         <v>0</v>
@@ -19133,10 +19133,10 @@
         </is>
       </c>
       <c r="G456" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="H456" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I456" t="n">
         <v>0</v>
@@ -19174,10 +19174,10 @@
         </is>
       </c>
       <c r="G457" t="n">
-        <v>87</v>
+        <v>272</v>
       </c>
       <c r="H457" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I457" t="n">
         <v>0</v>
@@ -19215,10 +19215,10 @@
         </is>
       </c>
       <c r="G458" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="H458" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I458" t="n">
         <v>2</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="G459" t="n">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="H459" t="n">
         <v>1</v>
@@ -19297,13 +19297,300 @@
         </is>
       </c>
       <c r="G460" t="n">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="H460" t="n">
         <v>3</v>
       </c>
       <c r="I460" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7665569884570389780</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bảo dưỡng robot  #qrevo2pro #robothutbui #roborock#vinhlong #dongthap </t>
+        </is>
+      </c>
+      <c r="G461" t="n">
+        <v>176</v>
+      </c>
+      <c r="H461" t="n">
+        <v>3</v>
+      </c>
+      <c r="I461" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7665614101850180885</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Người yêu có thể chưa có, nhưng robot dọn nhà thì nên có! 🤣 Roborock Qrevo 2 Pro lo từ hút bụi đến lau nhà, bạn chỉ việc nằm nghỉ. Ai cần “trợ lý việc nhà” thì inbox em ngay!  #Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G462" t="n">
+        <v>126</v>
+      </c>
+      <c r="H462" t="n">
+        <v>0</v>
+      </c>
+      <c r="I462" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7665610196600769812</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ý là bán Robot nhàn lắm các bác🤭🤭🤭  Ít là 3 là 4 chớ nhiều là 9 là 10 ghệ lận đó🤣🤣🤣 Nên các bác cứ nhiệt tình hỏi em đi🤭🤭🤭 Em làm clip giải đáp cho các bác từng cái lun🥰🥰🥰 Cmt cho em bận rộn đi ạ❤️❤️❤️❤️ #Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G463" t="n">
+        <v>348</v>
+      </c>
+      <c r="H463" t="n">
+        <v>0</v>
+      </c>
+      <c r="I463" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>longrobot_284</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@longrobot_284/video/7665669646963559700</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Gầm 12cm? Robot Qrevo 2 Pro chui hút lau vô tư nha!✌🏻 #roborock #robothutbuilaunha #qrevo2pro #longrobot #reviewrobot</t>
+        </is>
+      </c>
+      <c r="G464" t="n">
+        <v>60</v>
+      </c>
+      <c r="H464" t="n">
+        <v>2</v>
+      </c>
+      <c r="I464" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7665666322595908884</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quá hợp lý luôn ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G465" t="n">
+        <v>54</v>
+      </c>
+      <c r="H465" t="n">
+        <v>0</v>
+      </c>
+      <c r="I465" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7665644113248718101</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hàng hot về liên tục phục vụ khách yêu #roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G466" t="n">
+        <v>65</v>
+      </c>
+      <c r="H466" t="n">
+        <v>3</v>
+      </c>
+      <c r="I466" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7665368075428203797</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21h vẫn đi lắp robot cho khách là chuyện bình thường ở H&amp;T Smart Home. 🚗✨ 📍H&amp;T Smart Home Đức Trọng #Roborock #Qrevo2Pro #RobotHutBui #LapDatTanNoi #HTSmartHome   </t>
+        </is>
+      </c>
+      <c r="G467" t="n">
+        <v>203</v>
+      </c>
+      <c r="H467" t="n">
+        <v>0</v>
+      </c>
+      <c r="I467" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I467"/>
+  <dimension ref="A1:I474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>60500</v>
+        <v>60800</v>
       </c>
       <c r="H23" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I23" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="H46" t="n">
         <v>61</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="H47" t="n">
         <v>16</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H59" t="n">
         <v>6</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="H61" t="n">
         <v>5</v>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H63" t="n">
         <v>7</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H64" t="n">
         <v>4</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>132600</v>
+        <v>142700</v>
       </c>
       <c r="H65" t="n">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="I65" t="n">
         <v>3</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="H66" t="n">
         <v>36</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H72" t="n">
         <v>50</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H74" t="n">
         <v>9</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="H77" t="n">
         <v>6</v>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>86200</v>
+        <v>86300</v>
       </c>
       <c r="H78" t="n">
         <v>304</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2681</v>
+        <v>2708</v>
       </c>
       <c r="H87" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I87" t="n">
         <v>7</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H88" t="n">
         <v>3</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>6559</v>
+        <v>6739</v>
       </c>
       <c r="H109" t="n">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="I109" t="n">
         <v>33</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>482900</v>
+        <v>484000</v>
       </c>
       <c r="H116" t="n">
-        <v>3239</v>
+        <v>3243</v>
       </c>
       <c r="I116" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="117">
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H117" t="n">
         <v>7</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H118" t="n">
         <v>5</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="H135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H142" t="n">
         <v>3</v>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H146" t="n">
         <v>8</v>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H147" t="n">
         <v>4</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H153" t="n">
         <v>5</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H173" t="n">
         <v>4</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H177" t="n">
         <v>3</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H179" t="n">
         <v>17</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H183" t="n">
         <v>5</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H184" t="n">
         <v>7</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H194" t="n">
         <v>9</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H195" t="n">
         <v>4</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H197" t="n">
         <v>5</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H203" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -8842,13 +8842,13 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H205" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H207" t="n">
         <v>7</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H208" t="n">
         <v>3</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H219" t="n">
         <v>7</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H224" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
@@ -9908,7 +9908,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H231" t="n">
         <v>14</v>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>287</v>
+        <v>406</v>
       </c>
       <c r="H232" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>8659</v>
+        <v>8678</v>
       </c>
       <c r="H236" t="n">
         <v>40</v>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H239" t="n">
         <v>3</v>
@@ -10277,7 +10277,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H249" t="n">
         <v>4</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H253" t="n">
         <v>9</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H256" t="n">
         <v>6</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H257" t="n">
         <v>4</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="H260" t="n">
         <v>10</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="H267" t="n">
         <v>27</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H268" t="n">
         <v>5</v>
@@ -11466,7 +11466,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H269" t="n">
         <v>8</v>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H272" t="n">
         <v>5</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H273" t="n">
         <v>4</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H274" t="n">
         <v>5</v>
@@ -11712,7 +11712,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H277" t="n">
         <v>5</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H280" t="n">
         <v>5</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="H282" t="n">
         <v>10</v>
@@ -12040,7 +12040,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="H283" t="n">
         <v>4</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H287" t="n">
         <v>7</v>
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H288" t="n">
         <v>3</v>
@@ -12327,10 +12327,10 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H290" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I290" t="n">
         <v>0</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="H297" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I297" t="n">
         <v>2</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="H298" t="n">
         <v>22</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H303" t="n">
         <v>5</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H308" t="n">
         <v>4</v>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H309" t="n">
         <v>3</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H311" t="n">
         <v>5</v>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="H312" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I312" t="n">
         <v>4</v>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H314" t="n">
         <v>3</v>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H316" t="n">
         <v>10</v>
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H317" t="n">
         <v>9</v>
@@ -13475,10 +13475,10 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="H318" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I318" t="n">
         <v>0</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H320" t="n">
         <v>7</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H321" t="n">
         <v>3</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H322" t="n">
         <v>4</v>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="H325" t="n">
         <v>2</v>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H326" t="n">
         <v>9</v>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H327" t="n">
         <v>6</v>
@@ -13926,7 +13926,7 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H329" t="n">
         <v>3</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H333" t="n">
         <v>3</v>
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H334" t="n">
         <v>5</v>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H335" t="n">
         <v>6</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H337" t="n">
         <v>2</v>
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H339" t="n">
         <v>4</v>
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="H340" t="n">
         <v>5</v>
@@ -14418,10 +14418,10 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H341" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I341" t="n">
         <v>0</v>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H345" t="n">
         <v>3</v>
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H349" t="n">
         <v>5</v>
@@ -14869,7 +14869,7 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H352" t="n">
         <v>3</v>
@@ -14951,7 +14951,7 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H354" t="n">
         <v>4</v>
@@ -15074,7 +15074,7 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H357" t="n">
         <v>7</v>
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H358" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I358" t="n">
         <v>0</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H359" t="n">
         <v>2</v>
@@ -15197,7 +15197,7 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H360" t="n">
         <v>6</v>
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H361" t="n">
         <v>3</v>
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H363" t="n">
         <v>4</v>
@@ -15361,7 +15361,7 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H364" t="n">
         <v>6</v>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H365" t="n">
         <v>6</v>
@@ -15443,7 +15443,7 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H366" t="n">
         <v>5</v>
@@ -15484,7 +15484,7 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H367" t="n">
         <v>4</v>
@@ -15525,7 +15525,7 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H368" t="n">
         <v>4</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H370" t="n">
         <v>1</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="H372" t="n">
         <v>1</v>
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H373" t="n">
         <v>2</v>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H374" t="n">
         <v>3</v>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H375" t="n">
         <v>4</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="H379" t="n">
         <v>7</v>
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H383" t="n">
         <v>3</v>
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H384" t="n">
         <v>5</v>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H387" t="n">
         <v>6</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H388" t="n">
         <v>4</v>
@@ -16386,7 +16386,7 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H389" t="n">
         <v>7</v>
@@ -16427,7 +16427,7 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H390" t="n">
         <v>5</v>
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="H391" t="n">
         <v>5</v>
@@ -16550,7 +16550,7 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -16591,7 +16591,7 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H394" t="n">
         <v>8</v>
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H395" t="n">
         <v>1</v>
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H396" t="n">
         <v>4</v>
@@ -16755,10 +16755,10 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="H398" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I398" t="n">
         <v>0</v>
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="H401" t="n">
         <v>11</v>
@@ -16919,7 +16919,7 @@
         </is>
       </c>
       <c r="G402" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H402" t="n">
         <v>2</v>
@@ -16960,7 +16960,7 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="H403" t="n">
         <v>1</v>
@@ -17001,7 +17001,7 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="H404" t="n">
         <v>2</v>
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H406" t="n">
         <v>4</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="G407" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17165,10 +17165,10 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="H408" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I408" t="n">
         <v>0</v>
@@ -17206,7 +17206,7 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H409" t="n">
         <v>1</v>
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H410" t="n">
         <v>2</v>
@@ -17288,7 +17288,7 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H411" t="n">
         <v>2</v>
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="H412" t="n">
         <v>1</v>
@@ -17370,7 +17370,7 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="H413" t="n">
         <v>4</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H414" t="n">
         <v>4</v>
@@ -17452,7 +17452,7 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H415" t="n">
         <v>4</v>
@@ -17493,7 +17493,7 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H416" t="n">
         <v>1</v>
@@ -17534,7 +17534,7 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H417" t="n">
         <v>1</v>
@@ -17575,7 +17575,7 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H418" t="n">
         <v>2</v>
@@ -17616,7 +17616,7 @@
         </is>
       </c>
       <c r="G419" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H419" t="n">
         <v>1</v>
@@ -17739,7 +17739,7 @@
         </is>
       </c>
       <c r="G422" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H422" t="n">
         <v>7</v>
@@ -17780,7 +17780,7 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H423" t="n">
         <v>2</v>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H424" t="n">
         <v>1</v>
@@ -17862,7 +17862,7 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H425" t="n">
         <v>3</v>
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H426" t="n">
         <v>3</v>
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H427" t="n">
         <v>2</v>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H429" t="n">
         <v>3</v>
@@ -18067,7 +18067,7 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H430" t="n">
         <v>2</v>
@@ -18108,7 +18108,7 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H431" t="n">
         <v>3</v>
@@ -18149,7 +18149,7 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H432" t="n">
         <v>3</v>
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="H433" t="n">
         <v>3</v>
@@ -18272,10 +18272,10 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H435" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I435" t="n">
         <v>0</v>
@@ -18313,7 +18313,7 @@
         </is>
       </c>
       <c r="G436" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H436" t="n">
         <v>4</v>
@@ -18354,7 +18354,7 @@
         </is>
       </c>
       <c r="G437" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H437" t="n">
         <v>5</v>
@@ -18395,7 +18395,7 @@
         </is>
       </c>
       <c r="G438" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H438" t="n">
         <v>5</v>
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="G439" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H439" t="n">
         <v>2</v>
@@ -18477,7 +18477,7 @@
         </is>
       </c>
       <c r="G440" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H440" t="n">
         <v>1</v>
@@ -18518,7 +18518,7 @@
         </is>
       </c>
       <c r="G441" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H441" t="n">
         <v>4</v>
@@ -18559,7 +18559,7 @@
         </is>
       </c>
       <c r="G442" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H442" t="n">
         <v>3</v>
@@ -18600,7 +18600,7 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H443" t="n">
         <v>3</v>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G444" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H444" t="n">
         <v>4</v>
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="G445" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H445" t="n">
         <v>2</v>
@@ -18764,7 +18764,7 @@
         </is>
       </c>
       <c r="G447" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H447" t="n">
         <v>6</v>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="G448" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H448" t="n">
         <v>1</v>
@@ -18846,7 +18846,7 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="H449" t="n">
         <v>7</v>
@@ -18928,10 +18928,10 @@
         </is>
       </c>
       <c r="G451" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H451" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I451" t="n">
         <v>0</v>
@@ -18969,10 +18969,10 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="H452" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I452" t="n">
         <v>4</v>
@@ -19010,10 +19010,10 @@
         </is>
       </c>
       <c r="G453" t="n">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I453" t="n">
         <v>2</v>
@@ -19051,7 +19051,7 @@
         </is>
       </c>
       <c r="G454" t="n">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H454" t="n">
         <v>4</v>
@@ -19092,10 +19092,10 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H455" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I455" t="n">
         <v>0</v>
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="G456" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="H456" t="n">
         <v>4</v>
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="G457" t="n">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H457" t="n">
         <v>3</v>
@@ -19215,7 +19215,7 @@
         </is>
       </c>
       <c r="G458" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H458" t="n">
         <v>5</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="G459" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H459" t="n">
         <v>1</v>
@@ -19297,7 +19297,7 @@
         </is>
       </c>
       <c r="G460" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H460" t="n">
         <v>3</v>
@@ -19338,7 +19338,7 @@
         </is>
       </c>
       <c r="G461" t="n">
-        <v>176</v>
+        <v>309</v>
       </c>
       <c r="H461" t="n">
         <v>3</v>
@@ -19379,13 +19379,13 @@
         </is>
       </c>
       <c r="G462" t="n">
-        <v>126</v>
+        <v>330</v>
       </c>
       <c r="H462" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="G463" t="n">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -19461,10 +19461,10 @@
         </is>
       </c>
       <c r="G464" t="n">
-        <v>60</v>
+        <v>183</v>
       </c>
       <c r="H464" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I464" t="n">
         <v>0</v>
@@ -19502,10 +19502,10 @@
         </is>
       </c>
       <c r="G465" t="n">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="H465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I465" t="n">
         <v>0</v>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="G466" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="H466" t="n">
         <v>3</v>
@@ -19584,12 +19584,299 @@
         </is>
       </c>
       <c r="G467" t="n">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="H467" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I467" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7665979501754469653</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thêm một tính năng cài đặt của Quevo 2 Pro cho mọi người đây ạ!!! #Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G468" t="n">
+        <v>127</v>
+      </c>
+      <c r="H468" t="n">
+        <v>1</v>
+      </c>
+      <c r="I468" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7665945031286607124</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cùng mình check báo lỗi đèn sáng đỏ trên robot nhé #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G469" t="n">
+        <v>358</v>
+      </c>
+      <c r="H469" t="n">
+        <v>1</v>
+      </c>
+      <c r="I469" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7665895793315876103</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G470" t="n">
+        <v>367</v>
+      </c>
+      <c r="H470" t="n">
+        <v>1</v>
+      </c>
+      <c r="I470" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7665698774488042760</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>#Qrevo2Pro #Roborock #robothutbui #3tsmart</t>
+        </is>
+      </c>
+      <c r="G471" t="n">
+        <v>338</v>
+      </c>
+      <c r="H471" t="n">
+        <v>2</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7666029482502786324</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Còn ít quà, anh chị nào nhanh tay đến em rước robot về sẽ được tặng quà ạ#mistorebienhoa #robothutbui #qrevo2pro #roborock </t>
+        </is>
+      </c>
+      <c r="G472" t="n">
+        <v>70</v>
+      </c>
+      <c r="H472" t="n">
+        <v>0</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7665707747933031700</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bác bác đã biết làm sao để robot luôn bền mới chưa ạ #roborock #Qrevo2Pro #robothutbui #xuhuong #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G473" t="n">
+        <v>385</v>
+      </c>
+      <c r="H473" t="n">
+        <v>4</v>
+      </c>
+      <c r="I473" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7665753601993641237</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đèn trên dock đang báo gì? #Roborock #Qrevo2Pro #RobotHutBui #huongdansudung </t>
+        </is>
+      </c>
+      <c r="G474" t="n">
+        <v>159</v>
+      </c>
+      <c r="H474" t="n">
+        <v>1</v>
+      </c>
+      <c r="I474" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I474"/>
+  <dimension ref="A1:I476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>86300</v>
+        <v>86400</v>
       </c>
       <c r="H78" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I78" t="n">
         <v>78</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H82" t="n">
         <v>4</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H84" t="n">
         <v>4</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H85" t="n">
         <v>4</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H86" t="n">
         <v>6</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>2708</v>
+        <v>2725</v>
       </c>
       <c r="H87" t="n">
         <v>20</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H90" t="n">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H91" t="n">
         <v>5</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H97" t="n">
         <v>1</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H106" t="n">
         <v>1</v>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>6739</v>
+        <v>6926</v>
       </c>
       <c r="H109" t="n">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="I109" t="n">
         <v>33</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H110" t="n">
         <v>2</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H113" t="n">
         <v>2</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H115" t="n">
         <v>2</v>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>484000</v>
+        <v>484900</v>
       </c>
       <c r="H116" t="n">
-        <v>3243</v>
+        <v>3248</v>
       </c>
       <c r="I116" t="n">
         <v>508</v>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H129" t="n">
         <v>4</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="H135" t="n">
         <v>4</v>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H137" t="n">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="H139" t="n">
         <v>5</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H140" t="n">
         <v>2</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H141" t="n">
         <v>5</v>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H146" t="n">
         <v>8</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H151" t="n">
         <v>10</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H164" t="n">
         <v>4</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H165" t="n">
         <v>3</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H166" t="n">
         <v>3</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,13 +7448,13 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>366</v>
+        <v>414</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H173" t="n">
         <v>4</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H179" t="n">
         <v>17</v>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H180" t="n">
         <v>3</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H181" t="n">
         <v>3</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H183" t="n">
         <v>5</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H189" t="n">
         <v>7</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H193" t="n">
         <v>1</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H194" t="n">
         <v>9</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="H195" t="n">
         <v>4</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="H196" t="n">
         <v>21</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H201" t="n">
         <v>7</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H203" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H205" t="n">
         <v>5</v>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H207" t="n">
         <v>7</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H208" t="n">
         <v>3</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H211" t="n">
         <v>9</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="H218" t="n">
         <v>14</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H219" t="n">
         <v>7</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H223" t="n">
         <v>5</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H224" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H227" t="n">
         <v>8</v>
@@ -9908,7 +9908,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H231" t="n">
         <v>14</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>406</v>
+        <v>470</v>
       </c>
       <c r="H232" t="n">
         <v>8</v>
@@ -10113,7 +10113,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>8678</v>
+        <v>8691</v>
       </c>
       <c r="H236" t="n">
         <v>40</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H243" t="n">
         <v>4</v>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H244" t="n">
         <v>6</v>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H249" t="n">
         <v>4</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H253" t="n">
         <v>9</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H256" t="n">
         <v>6</v>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H258" t="n">
         <v>3</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H259" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="H260" t="n">
         <v>10</v>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H261" t="n">
         <v>20</v>
@@ -11220,7 +11220,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H263" t="n">
         <v>4</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="H267" t="n">
         <v>27</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="H273" t="n">
         <v>4</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H274" t="n">
         <v>5</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H277" t="n">
         <v>5</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H278" t="n">
         <v>4</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="H280" t="n">
         <v>5</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="H282" t="n">
         <v>10</v>
@@ -12040,10 +12040,10 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="H283" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I283" t="n">
         <v>0</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H286" t="n">
         <v>6</v>
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H287" t="n">
         <v>7</v>
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H288" t="n">
         <v>3</v>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H289" t="n">
         <v>3</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H290" t="n">
         <v>9</v>
@@ -12368,7 +12368,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H291" t="n">
         <v>5</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H296" t="n">
         <v>7</v>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>684</v>
+        <v>704</v>
       </c>
       <c r="H297" t="n">
         <v>27</v>
@@ -12655,10 +12655,10 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="H298" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I298" t="n">
         <v>5</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="H303" t="n">
         <v>5</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H308" t="n">
         <v>4</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="H312" t="n">
         <v>8</v>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H314" t="n">
         <v>3</v>
@@ -13352,7 +13352,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H315" t="n">
         <v>3</v>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H316" t="n">
         <v>10</v>
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H317" t="n">
         <v>9</v>
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="H318" t="n">
         <v>10</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H320" t="n">
         <v>7</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="H321" t="n">
         <v>3</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H322" t="n">
         <v>4</v>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H325" t="n">
         <v>2</v>
@@ -13803,7 +13803,7 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H326" t="n">
         <v>9</v>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H327" t="n">
         <v>6</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H333" t="n">
         <v>3</v>
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H334" t="n">
         <v>5</v>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H335" t="n">
         <v>6</v>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H337" t="n">
         <v>2</v>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H338" t="n">
         <v>5</v>
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H339" t="n">
         <v>4</v>
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="H340" t="n">
         <v>5</v>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H341" t="n">
         <v>5</v>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H345" t="n">
         <v>3</v>
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H347" t="n">
         <v>7</v>
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H348" t="n">
         <v>8</v>
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H349" t="n">
         <v>5</v>
@@ -14828,7 +14828,7 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H351" t="n">
         <v>1</v>
@@ -14869,7 +14869,7 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H352" t="n">
         <v>3</v>
@@ -14951,7 +14951,7 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H354" t="n">
         <v>4</v>
@@ -14992,7 +14992,7 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H355" t="n">
         <v>2</v>
@@ -15033,7 +15033,7 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H356" t="n">
         <v>2</v>
@@ -15074,7 +15074,7 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H357" t="n">
         <v>7</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H359" t="n">
         <v>2</v>
@@ -15197,10 +15197,10 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H360" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I360" t="n">
         <v>0</v>
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H361" t="n">
         <v>3</v>
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H362" t="n">
         <v>2</v>
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H363" t="n">
         <v>4</v>
@@ -15361,7 +15361,7 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H364" t="n">
         <v>6</v>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H365" t="n">
         <v>6</v>
@@ -15443,7 +15443,7 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H366" t="n">
         <v>5</v>
@@ -15484,7 +15484,7 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H367" t="n">
         <v>4</v>
@@ -15525,7 +15525,7 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H368" t="n">
         <v>4</v>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H369" t="n">
         <v>3</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="H372" t="n">
         <v>1</v>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H374" t="n">
         <v>3</v>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H375" t="n">
         <v>4</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="H379" t="n">
         <v>7</v>
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H387" t="n">
         <v>6</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H388" t="n">
         <v>4</v>
@@ -16386,7 +16386,7 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="H389" t="n">
         <v>7</v>
@@ -16427,7 +16427,7 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="H390" t="n">
         <v>5</v>
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="H391" t="n">
         <v>5</v>
@@ -16550,7 +16550,7 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -16591,7 +16591,7 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="H394" t="n">
         <v>8</v>
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H395" t="n">
         <v>1</v>
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H396" t="n">
         <v>4</v>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H398" t="n">
         <v>9</v>
@@ -16796,7 +16796,7 @@
         </is>
       </c>
       <c r="G399" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H399" t="n">
         <v>8</v>
@@ -16878,7 +16878,7 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="H401" t="n">
         <v>11</v>
@@ -16919,7 +16919,7 @@
         </is>
       </c>
       <c r="G402" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H402" t="n">
         <v>2</v>
@@ -17001,7 +17001,7 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="H404" t="n">
         <v>2</v>
@@ -17042,7 +17042,7 @@
         </is>
       </c>
       <c r="G405" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H405" t="n">
         <v>1</v>
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H406" t="n">
         <v>4</v>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H408" t="n">
         <v>5</v>
@@ -17206,7 +17206,7 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H409" t="n">
         <v>1</v>
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H410" t="n">
         <v>2</v>
@@ -17288,7 +17288,7 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H411" t="n">
         <v>2</v>
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H412" t="n">
         <v>1</v>
@@ -17370,7 +17370,7 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="H413" t="n">
         <v>4</v>
@@ -17493,7 +17493,7 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H416" t="n">
         <v>1</v>
@@ -17575,7 +17575,7 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H418" t="n">
         <v>2</v>
@@ -17616,7 +17616,7 @@
         </is>
       </c>
       <c r="G419" t="n">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H419" t="n">
         <v>1</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H420" t="n">
         <v>2</v>
@@ -17698,7 +17698,7 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H421" t="n">
         <v>1</v>
@@ -17739,7 +17739,7 @@
         </is>
       </c>
       <c r="G422" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H422" t="n">
         <v>7</v>
@@ -17780,7 +17780,7 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H423" t="n">
         <v>2</v>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H424" t="n">
         <v>1</v>
@@ -17862,7 +17862,7 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H425" t="n">
         <v>3</v>
@@ -17903,7 +17903,7 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H426" t="n">
         <v>3</v>
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H427" t="n">
         <v>2</v>
@@ -17985,7 +17985,7 @@
         </is>
       </c>
       <c r="G428" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H428" t="n">
         <v>2</v>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H429" t="n">
         <v>3</v>
@@ -18067,10 +18067,10 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="H430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I430" t="n">
         <v>0</v>
@@ -18108,7 +18108,7 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H431" t="n">
         <v>3</v>
@@ -18149,7 +18149,7 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H432" t="n">
         <v>3</v>
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="H433" t="n">
         <v>3</v>
@@ -18272,7 +18272,7 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H435" t="n">
         <v>8</v>
@@ -18313,7 +18313,7 @@
         </is>
       </c>
       <c r="G436" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H436" t="n">
         <v>4</v>
@@ -18354,7 +18354,7 @@
         </is>
       </c>
       <c r="G437" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H437" t="n">
         <v>5</v>
@@ -18395,7 +18395,7 @@
         </is>
       </c>
       <c r="G438" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H438" t="n">
         <v>5</v>
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="G439" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H439" t="n">
         <v>2</v>
@@ -18518,7 +18518,7 @@
         </is>
       </c>
       <c r="G441" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H441" t="n">
         <v>4</v>
@@ -18559,7 +18559,7 @@
         </is>
       </c>
       <c r="G442" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H442" t="n">
         <v>3</v>
@@ -18600,7 +18600,7 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H443" t="n">
         <v>3</v>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G444" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H444" t="n">
         <v>4</v>
@@ -18764,7 +18764,7 @@
         </is>
       </c>
       <c r="G447" t="n">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H447" t="n">
         <v>6</v>
@@ -18846,7 +18846,7 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="H449" t="n">
         <v>7</v>
@@ -18969,7 +18969,7 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="H452" t="n">
         <v>4</v>
@@ -19010,7 +19010,7 @@
         </is>
       </c>
       <c r="G453" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H453" t="n">
         <v>3</v>
@@ -19051,7 +19051,7 @@
         </is>
       </c>
       <c r="G454" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H454" t="n">
         <v>4</v>
@@ -19092,7 +19092,7 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H455" t="n">
         <v>6</v>
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="G456" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H456" t="n">
         <v>4</v>
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="G457" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H457" t="n">
         <v>3</v>
@@ -19215,10 +19215,10 @@
         </is>
       </c>
       <c r="G458" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H458" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I458" t="n">
         <v>2</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="G459" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H459" t="n">
         <v>1</v>
@@ -19297,7 +19297,7 @@
         </is>
       </c>
       <c r="G460" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H460" t="n">
         <v>3</v>
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="G462" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H462" t="n">
         <v>4</v>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="G463" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -19461,7 +19461,7 @@
         </is>
       </c>
       <c r="G464" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H464" t="n">
         <v>4</v>
@@ -19502,7 +19502,7 @@
         </is>
       </c>
       <c r="G465" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H465" t="n">
         <v>1</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="G466" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H466" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I466" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467">
@@ -19584,7 +19584,7 @@
         </is>
       </c>
       <c r="G467" t="n">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="H467" t="n">
         <v>2</v>
@@ -19625,10 +19625,10 @@
         </is>
       </c>
       <c r="G468" t="n">
-        <v>127</v>
+        <v>229</v>
       </c>
       <c r="H468" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I468" t="n">
         <v>0</v>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="G469" t="n">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="H469" t="n">
         <v>1</v>
@@ -19707,10 +19707,10 @@
         </is>
       </c>
       <c r="G470" t="n">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="H470" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I470" t="n">
         <v>0</v>
@@ -19748,10 +19748,10 @@
         </is>
       </c>
       <c r="G471" t="n">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="H471" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I471" t="n">
         <v>0</v>
@@ -19789,7 +19789,7 @@
         </is>
       </c>
       <c r="G472" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -19830,7 +19830,7 @@
         </is>
       </c>
       <c r="G473" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="H473" t="n">
         <v>4</v>
@@ -19871,12 +19871,94 @@
         </is>
       </c>
       <c r="G474" t="n">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="H474" t="n">
+        <v>3</v>
+      </c>
+      <c r="I474" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7666080376439262472</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Top những lý do nên chọn Q Revo 2 Pro #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G475" t="n">
+        <v>353</v>
+      </c>
+      <c r="H475" t="n">
+        <v>2</v>
+      </c>
+      <c r="I475" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7666281991779798293</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Công nghệ đổi chiều chổi cạnh liệu có hiệu quả?#roborock #qrevo2pro #robothutbui #mistorebienhoa </t>
+        </is>
+      </c>
+      <c r="G476" t="n">
+        <v>121</v>
+      </c>
+      <c r="H476" t="n">
         <v>1</v>
       </c>
-      <c r="I474" t="n">
+      <c r="I476" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I476"/>
+  <dimension ref="A1:I481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H95" t="n">
         <v>8</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H100" t="n">
         <v>6</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H101" t="n">
         <v>4</v>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>11500</v>
+        <v>11600</v>
       </c>
       <c r="H108" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I108" t="n">
         <v>25</v>
@@ -4906,13 +4906,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>6926</v>
+        <v>7160</v>
       </c>
       <c r="H109" t="n">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="I109" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110">
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>484900</v>
+        <v>486300</v>
       </c>
       <c r="H116" t="n">
-        <v>3248</v>
+        <v>3258</v>
       </c>
       <c r="I116" t="n">
         <v>508</v>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H117" t="n">
         <v>8</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H118" t="n">
         <v>6</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="H120" t="n">
         <v>7</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H121" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H123" t="n">
         <v>4</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H126" t="n">
         <v>25</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H130" t="n">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H131" t="n">
         <v>3</v>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H132" t="n">
         <v>2</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H133" t="n">
         <v>2</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H135" t="n">
         <v>4</v>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H137" t="n">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2611</v>
+        <v>2613</v>
       </c>
       <c r="H139" t="n">
         <v>5</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H142" t="n">
         <v>3</v>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H147" t="n">
         <v>4</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H150" t="n">
         <v>7</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H151" t="n">
         <v>10</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H152" t="n">
         <v>4</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H153" t="n">
         <v>5</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H168" t="n">
         <v>14</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H169" t="n">
         <v>17</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H170" t="n">
         <v>5</v>
@@ -7448,13 +7448,13 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>414</v>
+        <v>453</v>
       </c>
       <c r="H171" t="n">
         <v>6</v>
       </c>
       <c r="I171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H172" t="n">
         <v>4</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H174" t="n">
         <v>5</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H176" t="n">
         <v>3</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H179" t="n">
         <v>17</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H183" t="n">
         <v>5</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H189" t="n">
         <v>7</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H190" t="n">
         <v>6</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H194" t="n">
         <v>9</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H195" t="n">
         <v>4</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H196" t="n">
         <v>21</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H198" t="n">
         <v>4</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H199" t="n">
         <v>2</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H203" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="H204" t="n">
         <v>8</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H211" t="n">
         <v>9</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H214" t="n">
         <v>5</v>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="H218" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I218" t="n">
         <v>3</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H219" t="n">
         <v>7</v>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H221" t="n">
         <v>6</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H224" t="n">
         <v>10</v>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H225" t="n">
         <v>5</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H226" t="n">
         <v>5</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H229" t="n">
         <v>10</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>470</v>
+        <v>506</v>
       </c>
       <c r="H232" t="n">
         <v>8</v>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H233" t="n">
         <v>11</v>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H234" t="n">
         <v>12</v>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H235" t="n">
         <v>13</v>
@@ -10113,10 +10113,10 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>8691</v>
+        <v>8703</v>
       </c>
       <c r="H236" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I236" t="n">
         <v>27</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H243" t="n">
         <v>4</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H251" t="n">
         <v>4</v>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H253" t="n">
         <v>9</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H254" t="n">
         <v>6</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H255" t="n">
         <v>3</v>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="H260" t="n">
         <v>10</v>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H265" t="n">
         <v>2</v>
@@ -11343,7 +11343,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H266" t="n">
         <v>9</v>
@@ -11384,7 +11384,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>998</v>
+        <v>1014</v>
       </c>
       <c r="H267" t="n">
         <v>27</v>
@@ -11425,10 +11425,10 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H268" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I268" t="n">
         <v>1</v>
@@ -11466,7 +11466,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H269" t="n">
         <v>8</v>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H272" t="n">
         <v>5</v>
@@ -11630,7 +11630,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="H273" t="n">
         <v>4</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H274" t="n">
         <v>5</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H276" t="n">
         <v>4</v>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H277" t="n">
         <v>5</v>
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H278" t="n">
         <v>4</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H280" t="n">
         <v>5</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H281" t="n">
         <v>3</v>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H282" t="n">
         <v>10</v>
@@ -12081,7 +12081,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H284" t="n">
         <v>3</v>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="H285" t="n">
         <v>3</v>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H286" t="n">
         <v>6</v>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H290" t="n">
         <v>9</v>
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>704</v>
+        <v>734</v>
       </c>
       <c r="H297" t="n">
         <v>27</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="H298" t="n">
         <v>23</v>
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H300" t="n">
         <v>1</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H302" t="n">
         <v>1</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="H303" t="n">
         <v>5</v>
@@ -12942,7 +12942,7 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H305" t="n">
         <v>4</v>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H306" t="n">
         <v>3</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H308" t="n">
         <v>4</v>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H309" t="n">
         <v>3</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H310" t="n">
         <v>3</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H311" t="n">
         <v>5</v>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="H312" t="n">
         <v>8</v>
@@ -13270,7 +13270,7 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -13311,7 +13311,7 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H314" t="n">
         <v>3</v>
@@ -13352,7 +13352,7 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H315" t="n">
         <v>3</v>
@@ -13393,10 +13393,10 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H316" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I316" t="n">
         <v>0</v>
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H317" t="n">
         <v>9</v>
@@ -13475,10 +13475,10 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="H318" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I318" t="n">
         <v>0</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H320" t="n">
         <v>7</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H321" t="n">
         <v>3</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H322" t="n">
         <v>4</v>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H327" t="n">
         <v>6</v>
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H334" t="n">
         <v>5</v>
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H335" t="n">
         <v>6</v>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H337" t="n">
         <v>2</v>
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H339" t="n">
         <v>4</v>
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H340" t="n">
         <v>5</v>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H341" t="n">
         <v>5</v>
@@ -14582,7 +14582,7 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H345" t="n">
         <v>3</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H346" t="n">
         <v>3</v>
@@ -14664,10 +14664,10 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H347" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I347" t="n">
         <v>0</v>
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H348" t="n">
         <v>8</v>
@@ -14746,10 +14746,10 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H349" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I349" t="n">
         <v>0</v>
@@ -14951,7 +14951,7 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H354" t="n">
         <v>4</v>
@@ -15074,7 +15074,7 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H357" t="n">
         <v>7</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H359" t="n">
         <v>2</v>
@@ -15197,7 +15197,7 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H360" t="n">
         <v>7</v>
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H361" t="n">
         <v>3</v>
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H362" t="n">
         <v>2</v>
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H363" t="n">
         <v>4</v>
@@ -15361,7 +15361,7 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H364" t="n">
         <v>6</v>
@@ -15402,7 +15402,7 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H365" t="n">
         <v>6</v>
@@ -15443,7 +15443,7 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H366" t="n">
         <v>5</v>
@@ -15484,7 +15484,7 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H367" t="n">
         <v>4</v>
@@ -15525,7 +15525,7 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H368" t="n">
         <v>4</v>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H369" t="n">
         <v>3</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H370" t="n">
         <v>1</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H372" t="n">
         <v>1</v>
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H375" t="n">
         <v>4</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="H379" t="n">
         <v>7</v>
@@ -16058,7 +16058,7 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="H381" t="n">
         <v>2</v>
@@ -16099,7 +16099,7 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H382" t="n">
         <v>2</v>
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H383" t="n">
         <v>3</v>
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H384" t="n">
         <v>5</v>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -16263,7 +16263,7 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -16304,10 +16304,10 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H387" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I387" t="n">
         <v>0</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H388" t="n">
         <v>4</v>
@@ -16386,7 +16386,7 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H389" t="n">
         <v>7</v>
@@ -16427,7 +16427,7 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="H390" t="n">
         <v>5</v>
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H391" t="n">
         <v>5</v>
@@ -16509,7 +16509,7 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H392" t="n">
         <v>3</v>
@@ -16550,10 +16550,10 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="H393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I393" t="n">
         <v>0</v>
@@ -16591,7 +16591,7 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="H394" t="n">
         <v>8</v>
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H395" t="n">
         <v>1</v>
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H396" t="n">
         <v>4</v>
@@ -16714,7 +16714,7 @@
         </is>
       </c>
       <c r="G397" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H397" t="n">
         <v>2</v>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H398" t="n">
         <v>9</v>
@@ -16878,10 +16878,10 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="H401" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I401" t="n">
         <v>15</v>
@@ -16919,7 +16919,7 @@
         </is>
       </c>
       <c r="G402" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H402" t="n">
         <v>2</v>
@@ -17001,7 +17001,7 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H404" t="n">
         <v>2</v>
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H406" t="n">
         <v>4</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="G407" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17206,7 +17206,7 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H409" t="n">
         <v>1</v>
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="H410" t="n">
         <v>2</v>
@@ -17288,7 +17288,7 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H411" t="n">
         <v>2</v>
@@ -17329,7 +17329,7 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="H412" t="n">
         <v>1</v>
@@ -17370,10 +17370,10 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="H413" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I413" t="n">
         <v>0</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H414" t="n">
         <v>4</v>
@@ -17493,7 +17493,7 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="H416" t="n">
         <v>1</v>
@@ -17534,7 +17534,7 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H417" t="n">
         <v>1</v>
@@ -17575,7 +17575,7 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H418" t="n">
         <v>2</v>
@@ -17616,7 +17616,7 @@
         </is>
       </c>
       <c r="G419" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H419" t="n">
         <v>1</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H420" t="n">
         <v>2</v>
@@ -17698,7 +17698,7 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H421" t="n">
         <v>1</v>
@@ -17862,7 +17862,7 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H425" t="n">
         <v>3</v>
@@ -17985,7 +17985,7 @@
         </is>
       </c>
       <c r="G428" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H428" t="n">
         <v>2</v>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H429" t="n">
         <v>3</v>
@@ -18067,7 +18067,7 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="H430" t="n">
         <v>3</v>
@@ -18108,7 +18108,7 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H431" t="n">
         <v>3</v>
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H433" t="n">
         <v>3</v>
@@ -18231,10 +18231,10 @@
         </is>
       </c>
       <c r="G434" t="n">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c r="H434" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I434" t="n">
         <v>0</v>
@@ -18395,7 +18395,7 @@
         </is>
       </c>
       <c r="G438" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H438" t="n">
         <v>5</v>
@@ -18477,7 +18477,7 @@
         </is>
       </c>
       <c r="G440" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H440" t="n">
         <v>1</v>
@@ -18518,7 +18518,7 @@
         </is>
       </c>
       <c r="G441" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H441" t="n">
         <v>4</v>
@@ -18559,7 +18559,7 @@
         </is>
       </c>
       <c r="G442" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H442" t="n">
         <v>3</v>
@@ -18600,7 +18600,7 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H443" t="n">
         <v>3</v>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="G444" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H444" t="n">
         <v>4</v>
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="G445" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H445" t="n">
         <v>2</v>
@@ -18764,7 +18764,7 @@
         </is>
       </c>
       <c r="G447" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H447" t="n">
         <v>6</v>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="G448" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H448" t="n">
         <v>1</v>
@@ -18846,7 +18846,7 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="H449" t="n">
         <v>7</v>
@@ -18887,7 +18887,7 @@
         </is>
       </c>
       <c r="G450" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H450" t="n">
         <v>4</v>
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="G451" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H451" t="n">
         <v>4</v>
@@ -18969,7 +18969,7 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="H452" t="n">
         <v>4</v>
@@ -19010,10 +19010,10 @@
         </is>
       </c>
       <c r="G453" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H453" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I453" t="n">
         <v>2</v>
@@ -19092,10 +19092,10 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="H455" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I455" t="n">
         <v>0</v>
@@ -19215,7 +19215,7 @@
         </is>
       </c>
       <c r="G458" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H458" t="n">
         <v>6</v>
@@ -19297,7 +19297,7 @@
         </is>
       </c>
       <c r="G460" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H460" t="n">
         <v>3</v>
@@ -19338,7 +19338,7 @@
         </is>
       </c>
       <c r="G461" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H461" t="n">
         <v>3</v>
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="G462" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H462" t="n">
         <v>4</v>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="G463" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -19461,7 +19461,7 @@
         </is>
       </c>
       <c r="G464" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H464" t="n">
         <v>4</v>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="G466" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H466" t="n">
         <v>4</v>
@@ -19584,10 +19584,10 @@
         </is>
       </c>
       <c r="G467" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H467" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I467" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="G468" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H468" t="n">
         <v>2</v>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="G469" t="n">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="H469" t="n">
         <v>1</v>
@@ -19707,7 +19707,7 @@
         </is>
       </c>
       <c r="G470" t="n">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H470" t="n">
         <v>2</v>
@@ -19748,7 +19748,7 @@
         </is>
       </c>
       <c r="G471" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H471" t="n">
         <v>3</v>
@@ -19789,7 +19789,7 @@
         </is>
       </c>
       <c r="G472" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -19830,10 +19830,10 @@
         </is>
       </c>
       <c r="G473" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H473" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I473" t="n">
         <v>0</v>
@@ -19871,10 +19871,10 @@
         </is>
       </c>
       <c r="G474" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="H474" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I474" t="n">
         <v>0</v>
@@ -19912,7 +19912,7 @@
         </is>
       </c>
       <c r="G475" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H475" t="n">
         <v>2</v>
@@ -19953,12 +19953,217 @@
         </is>
       </c>
       <c r="G476" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="H476" t="n">
         <v>1</v>
       </c>
       <c r="I476" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7666427796175998229</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mài nào cũng thấy em ấy sang và sáng😁😁😁#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G477" t="n">
+        <v>359</v>
+      </c>
+      <c r="H477" t="n">
+        <v>0</v>
+      </c>
+      <c r="I477" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7666662109920431380</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unbox Robot hút bụi lau nhà Roborock Qrevo 2 Pro #mistorebienhoa #robothutbui #qrevo2pro #roborock </t>
+        </is>
+      </c>
+      <c r="G478" t="n">
+        <v>9756</v>
+      </c>
+      <c r="H478" t="n">
+        <v>9</v>
+      </c>
+      <c r="I478" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7666682737415376148</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Còn đợi gì nữa các bác #roborock #Qrevo2Pro #robothutbui #xuhuong </t>
+        </is>
+      </c>
+      <c r="G479" t="n">
+        <v>97</v>
+      </c>
+      <c r="H479" t="n">
+        <v>1</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7666790803964022037</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Roborock #RoborockVietnam #Qrevo2Pro #RobotHutBui </t>
+        </is>
+      </c>
+      <c r="G480" t="n">
+        <v>28</v>
+      </c>
+      <c r="H480" t="n">
+        <v>0</v>
+      </c>
+      <c r="I480" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7666789595438304532</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌌 QREVO 2 PRO | SỨ MỆNH NÂNG TẦM SỨC MẠNH DỌN DẸP TẦM TRUNG Không cần là flagship mới có trải nghiệm làm sạch vượt trội. Roborock Qrevo 2 Pro mang đến những trải nghiệm vượt trội vốn chỉ nên thuộc về phân khúc cao cấp: 🌪️ 25.000Pa lực hút mạnh mẽ, xử lý bụi mịn, tóc và mảnh vụn. 🌪️ FlexiArm + chổi cạnh đảo chiều làm sạch sát mép, sát góc. 🌪️ Hệ thống chống rối 3 lớp, giảm tóc quấn hiệu quả. 🌪️ Dock tự giặt giẻ, sấy nóng 45°C và làm sạch khay giặt. 🌪️ Tự tháo giẻ khi hút thảm, giữ thảm luôn khô ráo. 💫 Tầm trung nay đã cất cánh. Chuẩn sạch mới chính thức bắt đầu cùng Roborock Qrevo 2 Pro. #Roborock #RoborockVietnam #Qrevo2Pro #RobotHutBui </t>
+        </is>
+      </c>
+      <c r="G481" t="n">
+        <v>30</v>
+      </c>
+      <c r="H481" t="n">
+        <v>0</v>
+      </c>
+      <c r="I481" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I481"/>
+  <dimension ref="A1:I491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17780,7 +17780,7 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H423" t="n">
         <v>2</v>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H424" t="n">
         <v>1</v>
@@ -17862,7 +17862,7 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H425" t="n">
         <v>3</v>
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H427" t="n">
         <v>2</v>
@@ -18067,7 +18067,7 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="H430" t="n">
         <v>3</v>
@@ -18108,7 +18108,7 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H431" t="n">
         <v>3</v>
@@ -18149,7 +18149,7 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H432" t="n">
         <v>3</v>
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="H433" t="n">
         <v>3</v>
@@ -18231,10 +18231,10 @@
         </is>
       </c>
       <c r="G434" t="n">
-        <v>259</v>
+        <v>464</v>
       </c>
       <c r="H434" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I434" t="n">
         <v>0</v>
@@ -18272,7 +18272,7 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H435" t="n">
         <v>8</v>
@@ -18600,7 +18600,7 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H443" t="n">
         <v>3</v>
@@ -18641,10 +18641,10 @@
         </is>
       </c>
       <c r="G444" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H444" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I444" t="n">
         <v>0</v>
@@ -18764,7 +18764,7 @@
         </is>
       </c>
       <c r="G447" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H447" t="n">
         <v>6</v>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="G448" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H448" t="n">
         <v>1</v>
@@ -18846,7 +18846,7 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="H449" t="n">
         <v>7</v>
@@ -18969,7 +18969,7 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="H452" t="n">
         <v>4</v>
@@ -19010,7 +19010,7 @@
         </is>
       </c>
       <c r="G453" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H453" t="n">
         <v>4</v>
@@ -19051,13 +19051,13 @@
         </is>
       </c>
       <c r="G454" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H454" t="n">
         <v>4</v>
       </c>
       <c r="I454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -19092,10 +19092,10 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>240</v>
+        <v>398</v>
       </c>
       <c r="H455" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I455" t="n">
         <v>0</v>
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="G457" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H457" t="n">
         <v>3</v>
@@ -19215,7 +19215,7 @@
         </is>
       </c>
       <c r="G458" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H458" t="n">
         <v>6</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="G459" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H459" t="n">
         <v>1</v>
@@ -19338,7 +19338,7 @@
         </is>
       </c>
       <c r="G461" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H461" t="n">
         <v>3</v>
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="G462" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H462" t="n">
         <v>4</v>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="G463" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -19461,7 +19461,7 @@
         </is>
       </c>
       <c r="G464" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="H464" t="n">
         <v>4</v>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="G466" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H466" t="n">
         <v>4</v>
@@ -19584,7 +19584,7 @@
         </is>
       </c>
       <c r="G467" t="n">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H467" t="n">
         <v>3</v>
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="G468" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H468" t="n">
         <v>2</v>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="G469" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H469" t="n">
         <v>1</v>
@@ -19707,7 +19707,7 @@
         </is>
       </c>
       <c r="G470" t="n">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H470" t="n">
         <v>2</v>
@@ -19748,7 +19748,7 @@
         </is>
       </c>
       <c r="G471" t="n">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H471" t="n">
         <v>3</v>
@@ -19830,7 +19830,7 @@
         </is>
       </c>
       <c r="G473" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="H473" t="n">
         <v>7</v>
@@ -19871,7 +19871,7 @@
         </is>
       </c>
       <c r="G474" t="n">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="H474" t="n">
         <v>4</v>
@@ -19912,7 +19912,7 @@
         </is>
       </c>
       <c r="G475" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="H475" t="n">
         <v>2</v>
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="G476" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H476" t="n">
         <v>1</v>
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="G477" t="n">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -20035,13 +20035,13 @@
         </is>
       </c>
       <c r="G478" t="n">
-        <v>9756</v>
+        <v>11600</v>
       </c>
       <c r="H478" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I478" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G479" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="H479" t="n">
         <v>1</v>
@@ -20117,7 +20117,7 @@
         </is>
       </c>
       <c r="G480" t="n">
-        <v>28</v>
+        <v>350</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -20158,12 +20158,422 @@
         </is>
       </c>
       <c r="G481" t="n">
-        <v>30</v>
+        <v>374</v>
       </c>
       <c r="H481" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I481" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7667175618991213845</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>#roborock#qrevo2pro#robothutbui#vinhlong#dongthap</t>
+        </is>
+      </c>
+      <c r="G482" t="n">
+        <v>49</v>
+      </c>
+      <c r="H482" t="n">
+        <v>5</v>
+      </c>
+      <c r="I482" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7667168980959776021</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Việc nhẹ ấy vậy mà mỗi lần vệ sinh em nó cứ thấy cuốn🤭🤭🤭#Qrevo2Pro #Roborock #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G483" t="n">
+        <v>62</v>
+      </c>
+      <c r="H483" t="n">
+        <v>0</v>
+      </c>
+      <c r="I483" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7667164693403946260</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thêm 1 mẹo vệ sinh nữa cho mọi người đây ạ!#Qrevo2Pro #Roborock #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G484" t="n">
+        <v>72</v>
+      </c>
+      <c r="H484" t="n">
+        <v>4</v>
+      </c>
+      <c r="I484" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7667160679186566420</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Âm thanh chân thực từ việc dọn dẹp em Quevo 2 pro#Roborock  #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G485" t="n">
+        <v>81</v>
+      </c>
+      <c r="H485" t="n">
+        <v>1</v>
+      </c>
+      <c r="I485" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7667154244730146069</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cùng mình thay túi rác mới cho em Quevo 2 pro nhé🥰#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G486" t="n">
+        <v>140</v>
+      </c>
+      <c r="H486" t="n">
+        <v>2</v>
+      </c>
+      <c r="I486" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7667180652566940948</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Em ơi chị muốn dùng nước lau sàn khác được không? Câu trả lời trong video ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G487" t="n">
+        <v>38</v>
+      </c>
+      <c r="H487" t="n">
+        <v>2</v>
+      </c>
+      <c r="I487" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7667169045547863316</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Của bền tại người là có thật ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G488" t="n">
+        <v>47</v>
+      </c>
+      <c r="H488" t="n">
+        <v>1</v>
+      </c>
+      <c r="I488" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7666831913105050900</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🌌 QREVO 2 PRO | SỨ MỆNH NÂNG TẦM SỨC MẠNH DỌN DẸP TẦM TRUNG Không cần là flagship mới có trải nghiệm làm sạch vượt trội. Roborock Qrevo 2 Pro mang đến những trải nghiệm vượt trội vốn chỉ nên thuộc về phân khúc cao cấp: 🌪️ 25.000Pa lực hút mạnh mẽ, xử lý bụi mịn, tóc và mảnh vụn. 🌪️ FlexiArm + chổi cạnh đảo chiều làm sạch sát mép, sát góc. 🌪️ Hệ thống chống rối 3 lớp, giảm tóc quấn hiệu quả. 🌪️ Dock tự giặt giẻ, sấy nóng 45°C và làm sạch khay giặt. 🌪️ Tự tháo giẻ khi hút thảm, giữ thảm luôn khô ráo. 💫 Tầm trung nay đã cất cánh. Chuẩn sạch mới chính thức bắt đầu cùng Roborock Qrevo 2 Pro. #Roborock #RoborockVietnam #Qrevo2Pro#RobotHutBui </t>
+        </is>
+      </c>
+      <c r="G489" t="n">
+        <v>391</v>
+      </c>
+      <c r="H489" t="n">
+        <v>3</v>
+      </c>
+      <c r="I489" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7666862105018027285</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không cần là flagship mới có trải nghiệm làm sạch vượt trội. Roborock Qrevo 2 Pro mang đến những trải nghiệm vượt trội vốn chỉ nên thuộc về phân khúc cao cấp: 🌪️ 25.000Pa lực hút mạnh mẽ, xử lý bụi mịn, tóc và mảnh vụn. 🌪️ FlexiArm + chổi cạnh đảo chiều làm sạch sát mép, sát góc. 🌪️ Hệ thống chống rối 3 lớp, giảm tóc quấn hiệu quả. 🌪️ Dock tự giặt giẻ, sấy nóng 45°C và làm sạch khay giặt. 🌪️ Tự tháo giẻ khi hút thảm, giữ thảm luôn khô ráo. #Roborock #RoborockVietnam #Qrevo2Pro #robotductrong </t>
+        </is>
+      </c>
+      <c r="G490" t="n">
+        <v>142</v>
+      </c>
+      <c r="H490" t="n">
+        <v>3</v>
+      </c>
+      <c r="I490" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>homebotvietnam</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homebotvietnam/video/7666837364261621012</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Tiết kiệm thời gian dọn nhà để làm điều mình thích. ☕🏡 Qrevo 2 Pro đúng là "chân ái" cho người bận rộn! 🤖✨ #Qrevo2Pro #Roborock #robothutbui #SmartHome #TikTokMadeMeBuyIt</t>
+        </is>
+      </c>
+      <c r="G491" t="n">
+        <v>209</v>
+      </c>
+      <c r="H491" t="n">
+        <v>1</v>
+      </c>
+      <c r="I491" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I491"/>
+  <dimension ref="A1:I493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18231,7 +18231,7 @@
         </is>
       </c>
       <c r="G434" t="n">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="H434" t="n">
         <v>32</v>
@@ -18518,7 +18518,7 @@
         </is>
       </c>
       <c r="G441" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H441" t="n">
         <v>4</v>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="G448" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H448" t="n">
         <v>1</v>
@@ -18846,7 +18846,7 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H449" t="n">
         <v>7</v>
@@ -18887,7 +18887,7 @@
         </is>
       </c>
       <c r="G450" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H450" t="n">
         <v>4</v>
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="G451" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H451" t="n">
         <v>4</v>
@@ -18969,7 +18969,7 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H452" t="n">
         <v>4</v>
@@ -19092,10 +19092,10 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="H455" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I455" t="n">
         <v>0</v>
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="G462" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H462" t="n">
         <v>4</v>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="G463" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="G468" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H468" t="n">
         <v>2</v>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="G469" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H469" t="n">
         <v>1</v>
@@ -19871,7 +19871,7 @@
         </is>
       </c>
       <c r="G474" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H474" t="n">
         <v>4</v>
@@ -19912,7 +19912,7 @@
         </is>
       </c>
       <c r="G475" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H475" t="n">
         <v>2</v>
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="G477" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G479" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H479" t="n">
         <v>1</v>
@@ -20117,7 +20117,7 @@
         </is>
       </c>
       <c r="G480" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="G481" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H481" t="n">
         <v>2</v>
@@ -20199,7 +20199,7 @@
         </is>
       </c>
       <c r="G482" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="H482" t="n">
         <v>5</v>
@@ -20240,7 +20240,7 @@
         </is>
       </c>
       <c r="G483" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -20281,7 +20281,7 @@
         </is>
       </c>
       <c r="G484" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="H484" t="n">
         <v>4</v>
@@ -20322,7 +20322,7 @@
         </is>
       </c>
       <c r="G485" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H485" t="n">
         <v>1</v>
@@ -20363,7 +20363,7 @@
         </is>
       </c>
       <c r="G486" t="n">
-        <v>140</v>
+        <v>224</v>
       </c>
       <c r="H486" t="n">
         <v>2</v>
@@ -20404,7 +20404,7 @@
         </is>
       </c>
       <c r="G487" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H487" t="n">
         <v>2</v>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="G488" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="H488" t="n">
         <v>1</v>
@@ -20486,7 +20486,7 @@
         </is>
       </c>
       <c r="G489" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H489" t="n">
         <v>3</v>
@@ -20527,7 +20527,7 @@
         </is>
       </c>
       <c r="G490" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H490" t="n">
         <v>3</v>
@@ -20568,12 +20568,94 @@
         </is>
       </c>
       <c r="G491" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H491" t="n">
         <v>1</v>
       </c>
       <c r="I491" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>hatechz</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hatechz/video/7667207149096881415</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Quà tặng Qrevo 2 Pro #qrevo2pro #roborock #roborockvietnam #hatechz #quangtri</t>
+        </is>
+      </c>
+      <c r="G492" t="n">
+        <v>10</v>
+      </c>
+      <c r="H492" t="n">
+        <v>1</v>
+      </c>
+      <c r="I492" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7667210944690277640</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot Qrevo 2 pro có sẵn tại shop  các KH qua shop xem trải nghiệm nha ạ  🚘🏠 Số 05 Nguyễn Du, Nông Trang, Việt Trì, Phú Thọ #qrevo2pro #robothutbui  #roborock #robotroborock #xuhuong </t>
+        </is>
+      </c>
+      <c r="G493" t="n">
+        <v>6</v>
+      </c>
+      <c r="H493" t="n">
+        <v>0</v>
+      </c>
+      <c r="I493" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I493"/>
+  <dimension ref="A1:I506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18067,7 +18067,7 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="H430" t="n">
         <v>3</v>
@@ -18108,7 +18108,7 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H431" t="n">
         <v>3</v>
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="G445" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H445" t="n">
         <v>2</v>
@@ -18723,7 +18723,7 @@
         </is>
       </c>
       <c r="G446" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H446" t="n">
         <v>1</v>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="G448" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H448" t="n">
         <v>1</v>
@@ -18846,7 +18846,7 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="H449" t="n">
         <v>7</v>
@@ -18887,7 +18887,7 @@
         </is>
       </c>
       <c r="G450" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H450" t="n">
         <v>4</v>
@@ -18969,7 +18969,7 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="H452" t="n">
         <v>4</v>
@@ -19010,7 +19010,7 @@
         </is>
       </c>
       <c r="G453" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H453" t="n">
         <v>4</v>
@@ -19051,13 +19051,13 @@
         </is>
       </c>
       <c r="G454" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H454" t="n">
         <v>4</v>
       </c>
       <c r="I454" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="455">
@@ -19092,10 +19092,10 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>411</v>
+        <v>585</v>
       </c>
       <c r="H455" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="I455" t="n">
         <v>0</v>
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="G457" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H457" t="n">
         <v>3</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="G459" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H459" t="n">
         <v>1</v>
@@ -19297,7 +19297,7 @@
         </is>
       </c>
       <c r="G460" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H460" t="n">
         <v>3</v>
@@ -19338,7 +19338,7 @@
         </is>
       </c>
       <c r="G461" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H461" t="n">
         <v>3</v>
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="G462" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H462" t="n">
         <v>4</v>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="G463" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -19461,10 +19461,10 @@
         </is>
       </c>
       <c r="G464" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H464" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I464" t="n">
         <v>0</v>
@@ -19584,7 +19584,7 @@
         </is>
       </c>
       <c r="G467" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H467" t="n">
         <v>3</v>
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="G468" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H468" t="n">
         <v>2</v>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="G469" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H469" t="n">
         <v>1</v>
@@ -19707,7 +19707,7 @@
         </is>
       </c>
       <c r="G470" t="n">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H470" t="n">
         <v>2</v>
@@ -19748,7 +19748,7 @@
         </is>
       </c>
       <c r="G471" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H471" t="n">
         <v>3</v>
@@ -19789,7 +19789,7 @@
         </is>
       </c>
       <c r="G472" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -19830,7 +19830,7 @@
         </is>
       </c>
       <c r="G473" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H473" t="n">
         <v>7</v>
@@ -19871,7 +19871,7 @@
         </is>
       </c>
       <c r="G474" t="n">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="H474" t="n">
         <v>4</v>
@@ -19912,7 +19912,7 @@
         </is>
       </c>
       <c r="G475" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H475" t="n">
         <v>2</v>
@@ -19953,10 +19953,10 @@
         </is>
       </c>
       <c r="G476" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H476" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I476" t="n">
         <v>0</v>
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="G477" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -20035,10 +20035,10 @@
         </is>
       </c>
       <c r="G478" t="n">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="H478" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I478" t="n">
         <v>1</v>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G479" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H479" t="n">
         <v>1</v>
@@ -20117,7 +20117,7 @@
         </is>
       </c>
       <c r="G480" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="G481" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="H481" t="n">
         <v>2</v>
@@ -20199,10 +20199,10 @@
         </is>
       </c>
       <c r="G482" t="n">
-        <v>64</v>
+        <v>171</v>
       </c>
       <c r="H482" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I482" t="n">
         <v>0</v>
@@ -20240,7 +20240,7 @@
         </is>
       </c>
       <c r="G483" t="n">
-        <v>78</v>
+        <v>376</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -20281,10 +20281,10 @@
         </is>
       </c>
       <c r="G484" t="n">
-        <v>130</v>
+        <v>436</v>
       </c>
       <c r="H484" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I484" t="n">
         <v>0</v>
@@ -20322,10 +20322,10 @@
         </is>
       </c>
       <c r="G485" t="n">
-        <v>100</v>
+        <v>177</v>
       </c>
       <c r="H485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I485" t="n">
         <v>0</v>
@@ -20363,7 +20363,7 @@
         </is>
       </c>
       <c r="G486" t="n">
-        <v>224</v>
+        <v>393</v>
       </c>
       <c r="H486" t="n">
         <v>2</v>
@@ -20404,10 +20404,10 @@
         </is>
       </c>
       <c r="G487" t="n">
-        <v>51</v>
+        <v>376</v>
       </c>
       <c r="H487" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I487" t="n">
         <v>0</v>
@@ -20445,13 +20445,13 @@
         </is>
       </c>
       <c r="G488" t="n">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="H488" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489">
@@ -20486,7 +20486,7 @@
         </is>
       </c>
       <c r="G489" t="n">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="H489" t="n">
         <v>3</v>
@@ -20527,7 +20527,7 @@
         </is>
       </c>
       <c r="G490" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="H490" t="n">
         <v>3</v>
@@ -20568,7 +20568,7 @@
         </is>
       </c>
       <c r="G491" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H491" t="n">
         <v>1</v>
@@ -20609,10 +20609,10 @@
         </is>
       </c>
       <c r="G492" t="n">
-        <v>10</v>
+        <v>389</v>
       </c>
       <c r="H492" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I492" t="n">
         <v>0</v>
@@ -20650,12 +20650,545 @@
         </is>
       </c>
       <c r="G493" t="n">
-        <v>6</v>
+        <v>357</v>
       </c>
       <c r="H493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I493" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7667444195656764693</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hô Lê hê lô các đồng môn Quevo 2pro #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G494" t="n">
+        <v>372</v>
+      </c>
+      <c r="H494" t="n">
+        <v>1</v>
+      </c>
+      <c r="I494" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7667440581517266197</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hãy dùng nước lau sàn chuyên dụng dành cho robot để robot hoạt động tốt và hiệu quả nhất nhé ạ #Roborock #Qrevo2Pro #Robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G495" t="n">
+        <v>205</v>
+      </c>
+      <c r="H495" t="n">
+        <v>0</v>
+      </c>
+      <c r="I495" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7667405333274447124</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Là một clip hề hước🤭🤭🤭🤭 #Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G496" t="n">
+        <v>398</v>
+      </c>
+      <c r="H496" t="n">
+        <v>2</v>
+      </c>
+      <c r="I496" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7667406333683076359</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chỉ cần làm 5 điều này, robot của bạn có thể bền thêm vài năm🥰 #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G497" t="n">
+        <v>120</v>
+      </c>
+      <c r="H497" t="n">
+        <v>0</v>
+      </c>
+      <c r="I497" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7667395341288738055</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G498" t="n">
+        <v>168</v>
+      </c>
+      <c r="H498" t="n">
+        <v>3</v>
+      </c>
+      <c r="I498" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7667220378070109458</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Màu đèn báo trên dock sạc nói lên điều gì? Bạn đã biết chưa? #Qrevo2Pro #Roborock #robothutbui #3tsmart</t>
+        </is>
+      </c>
+      <c r="G499" t="n">
+        <v>357</v>
+      </c>
+      <c r="H499" t="n">
+        <v>3</v>
+      </c>
+      <c r="I499" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7667217699507948808</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tại sao không nên dùng các chất tẩy rửa khác cho robot hút bụi? #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G500" t="n">
+        <v>360</v>
+      </c>
+      <c r="H500" t="n">
+        <v>3</v>
+      </c>
+      <c r="I500" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7667212249894833426</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Chỉ còn 3 ngày nữa thôi... #Qrevo2Pro #Roborock #robothutbui #3tsmart</t>
+        </is>
+      </c>
+      <c r="G501" t="n">
+        <v>260</v>
+      </c>
+      <c r="H501" t="n">
+        <v>2</v>
+      </c>
+      <c r="I501" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7667250005844970772</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#CapCut #Qrevo2Pro #roborock #robothutbui #robotlaunhadaklak </t>
+        </is>
+      </c>
+      <c r="G502" t="n">
+        <v>173</v>
+      </c>
+      <c r="H502" t="n">
+        <v>1</v>
+      </c>
+      <c r="I502" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7667515294360898836</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mấy bác còn lăn tăn thì qua em trải nghiệm trực tiếp nhé #roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G503" t="n">
+        <v>15</v>
+      </c>
+      <c r="H503" t="n">
+        <v>0</v>
+      </c>
+      <c r="I503" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7667512904874265876</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chỉ mất vài phút lắp đặt mà hưởng sự an nhàn lâu dài #roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G504" t="n">
+        <v>39</v>
+      </c>
+      <c r="H504" t="n">
+        <v>2</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7667505593204133127</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Để tăng tuổi thọ robot các bác nên vệ sinh định kì nha #qrevo2pro #roborock #robothutbui #robotlaunha #xuhuong </t>
+        </is>
+      </c>
+      <c r="G505" t="n">
+        <v>75</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7667214029655559442</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bác nào ở Phú Thọ qua shop xem trải nghiệm nhận quà nha 🎁🎁🎁 🚘🏠 Số 05 Nguyễn Du, Nông Trang, Việt Trì, Phú Thọ #qrevo2pro #roborock #robothutbui #xuhuong #robotroborock </t>
+        </is>
+      </c>
+      <c r="G506" t="n">
+        <v>353</v>
+      </c>
+      <c r="H506" t="n">
+        <v>3</v>
+      </c>
+      <c r="I506" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I506"/>
+  <dimension ref="A1:I519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18969,7 +18969,7 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H452" t="n">
         <v>4</v>
@@ -19010,7 +19010,7 @@
         </is>
       </c>
       <c r="G453" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H453" t="n">
         <v>4</v>
@@ -19092,7 +19092,7 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H455" t="n">
         <v>46</v>
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="G456" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H456" t="n">
         <v>4</v>
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="G457" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H457" t="n">
         <v>3</v>
@@ -19215,7 +19215,7 @@
         </is>
       </c>
       <c r="G458" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H458" t="n">
         <v>6</v>
@@ -19338,7 +19338,7 @@
         </is>
       </c>
       <c r="G461" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H461" t="n">
         <v>3</v>
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="G462" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H462" t="n">
         <v>4</v>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="G463" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -19461,7 +19461,7 @@
         </is>
       </c>
       <c r="G464" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="H464" t="n">
         <v>5</v>
@@ -19502,7 +19502,7 @@
         </is>
       </c>
       <c r="G465" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H465" t="n">
         <v>1</v>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="G466" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H466" t="n">
         <v>4</v>
@@ -19584,7 +19584,7 @@
         </is>
       </c>
       <c r="G467" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H467" t="n">
         <v>3</v>
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="G468" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="H468" t="n">
         <v>2</v>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="G469" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H469" t="n">
         <v>1</v>
@@ -19707,7 +19707,7 @@
         </is>
       </c>
       <c r="G470" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H470" t="n">
         <v>2</v>
@@ -19789,7 +19789,7 @@
         </is>
       </c>
       <c r="G472" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -19830,7 +19830,7 @@
         </is>
       </c>
       <c r="G473" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H473" t="n">
         <v>7</v>
@@ -19871,7 +19871,7 @@
         </is>
       </c>
       <c r="G474" t="n">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="H474" t="n">
         <v>4</v>
@@ -19912,10 +19912,10 @@
         </is>
       </c>
       <c r="G475" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I475" t="n">
         <v>0</v>
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="G476" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H476" t="n">
         <v>2</v>
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="G477" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G479" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H479" t="n">
         <v>1</v>
@@ -20117,7 +20117,7 @@
         </is>
       </c>
       <c r="G480" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="G481" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H481" t="n">
         <v>2</v>
@@ -20199,7 +20199,7 @@
         </is>
       </c>
       <c r="G482" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H482" t="n">
         <v>7</v>
@@ -20240,7 +20240,7 @@
         </is>
       </c>
       <c r="G483" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -20281,7 +20281,7 @@
         </is>
       </c>
       <c r="G484" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="H484" t="n">
         <v>5</v>
@@ -20322,10 +20322,10 @@
         </is>
       </c>
       <c r="G485" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H485" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I485" t="n">
         <v>0</v>
@@ -20363,7 +20363,7 @@
         </is>
       </c>
       <c r="G486" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="H486" t="n">
         <v>2</v>
@@ -20404,7 +20404,7 @@
         </is>
       </c>
       <c r="G487" t="n">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="H487" t="n">
         <v>5</v>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="G488" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H488" t="n">
         <v>3</v>
@@ -20486,10 +20486,10 @@
         </is>
       </c>
       <c r="G489" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H489" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I489" t="n">
         <v>0</v>
@@ -20527,7 +20527,7 @@
         </is>
       </c>
       <c r="G490" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H490" t="n">
         <v>3</v>
@@ -20568,7 +20568,7 @@
         </is>
       </c>
       <c r="G491" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H491" t="n">
         <v>1</v>
@@ -20609,10 +20609,10 @@
         </is>
       </c>
       <c r="G492" t="n">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="H492" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I492" t="n">
         <v>0</v>
@@ -20650,10 +20650,10 @@
         </is>
       </c>
       <c r="G493" t="n">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="H493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I493" t="n">
         <v>0</v>
@@ -20691,10 +20691,10 @@
         </is>
       </c>
       <c r="G494" t="n">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="H494" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I494" t="n">
         <v>0</v>
@@ -20732,13 +20732,13 @@
         </is>
       </c>
       <c r="G495" t="n">
-        <v>205</v>
+        <v>364</v>
       </c>
       <c r="H495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I495" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -20773,10 +20773,10 @@
         </is>
       </c>
       <c r="G496" t="n">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="H496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I496" t="n">
         <v>0</v>
@@ -20814,13 +20814,13 @@
         </is>
       </c>
       <c r="G497" t="n">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="H497" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I497" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="498">
@@ -20855,10 +20855,10 @@
         </is>
       </c>
       <c r="G498" t="n">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="H498" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I498" t="n">
         <v>0</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G499" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H499" t="n">
         <v>3</v>
@@ -20937,7 +20937,7 @@
         </is>
       </c>
       <c r="G500" t="n">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="H500" t="n">
         <v>3</v>
@@ -20978,10 +20978,10 @@
         </is>
       </c>
       <c r="G501" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="H501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I501" t="n">
         <v>0</v>
@@ -21019,10 +21019,10 @@
         </is>
       </c>
       <c r="G502" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="H502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I502" t="n">
         <v>0</v>
@@ -21060,10 +21060,10 @@
         </is>
       </c>
       <c r="G503" t="n">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="H503" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I503" t="n">
         <v>0</v>
@@ -21101,10 +21101,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="H504" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I504" t="n">
         <v>0</v>
@@ -21142,10 +21142,10 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="H505" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I505" t="n">
         <v>0</v>
@@ -21183,12 +21183,545 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="H506" t="n">
         <v>3</v>
       </c>
       <c r="I506" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7667915128758717716</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ánh mắt em va vô em Quevo 2pro của nhà Roborock ❤️❤️#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G507" t="n">
+        <v>28</v>
+      </c>
+      <c r="H507" t="n">
+        <v>0</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7667596570539429140</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Em Quevo 2 pro khổ nhất vịnh bắc bộ🤣🤣🤣 Rớt cái che luôn con mắt của người ta😂😂😂Hết thấy đường chạy vòng vòng lun mà🤭🤭🤭#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G508" t="n">
+        <v>316</v>
+      </c>
+      <c r="H508" t="n">
+        <v>1</v>
+      </c>
+      <c r="I508" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7667819187095522567</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60 giây để khám phá lý do vì sao Roborock Qrevo 2 Pro trở thành sự lựa chọn hàng đầu trong phân khúc tầm trung ở thời điểm hiện tại. ✨Khả năng xử lý bụi bẩn vượt trội ✨Làm sạch mượt mà ở từng góc khuất  ✨Tối ưu thông minh cho không gian trải thảm Một sự đầu tư xứng đáng cho tổ ấm hiện đại 🏡 _________________ 🏡: Vua Robot 3T SMART - Số 272, phường Phan Đình Phùng, Thái Nguyên #Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G509" t="n">
+        <v>218</v>
+      </c>
+      <c r="H509" t="n">
+        <v>2</v>
+      </c>
+      <c r="I509" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7667614228424985876</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vệ sinh robot như thế nào là đúng cách?#suachuarobothutbui #mistorebienhoa #robothutbui #roborock #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G510" t="n">
+        <v>147</v>
+      </c>
+      <c r="H510" t="n">
+        <v>4</v>
+      </c>
+      <c r="I510" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>roborock.krng.n</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@roborock.krng.n/video/7667590422822259989</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>✨ Nhà có nhiều tóc, lông thú cưng mà cứ phải ngồi gỡ chổi sau mỗi lần dọn thì đúng là "mất vui". 😮‍💨 Với Qrevo 2 Pro, chuyện đó gần như là không còn nữa. Hệ thống chống rối được SGS chứng nhận 100% thu gom tóc, 0% quấn rối, giúp robot hút sạch tóc mà không làm bạn mất thêm thời gian và sức lực gỡ chổi. 💛 Một công nghệ từng chỉ có trên các dòng cao cấp, nay đã có mặt trên Qrevo 2 Pro để việc dọn nhà vừa sạch hơn, vừa nhàn hơn mỗi ngày. #Roborock #RoborockVietnam #Qrevo2Pro</t>
+        </is>
+      </c>
+      <c r="G511" t="n">
+        <v>106</v>
+      </c>
+      <c r="H511" t="n">
+        <v>1</v>
+      </c>
+      <c r="I511" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7667735804923481365</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 pro chống rối siêu đỉnh #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G512" t="n">
+        <v>82</v>
+      </c>
+      <c r="H512" t="n">
+        <v>1</v>
+      </c>
+      <c r="I512" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7667595025038970132</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mới mở bán mà cháy liên tục luôn ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G513" t="n">
+        <v>98</v>
+      </c>
+      <c r="H513" t="n">
+        <v>2</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>hatechz</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hatechz/video/7667584208121990418</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Qrevo 2 Pro tuyệt đỉnk kungfu #roborock #roborockvietnam #qrevo2pro #hatechz #quangtri</t>
+        </is>
+      </c>
+      <c r="G514" t="n">
+        <v>136</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I514" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7667921073660333332</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✨ Nhà có nhiều tóc, lông thú cưng mà cứ phải ngồi gỡ chổi sau mỗi lần dọn thì đúng là "mất vui". 😮‍💨 Với Qrevo 2 Pro, chuyện đó gần như là không còn nữa. Hệ thống chống rối được SGS chứng nhận 100% thu gom tóc, 0% quấn rối, giúp robot hút sạch tóc mà không làm bạn mất thêm thời gian và sức lực gỡ chổi. 💛 Một công nghệ từng chỉ có trên các dòng cao cấp, nay đã có mặt trên Qrevo 2 Pro để việc dọn nhà vừa sạch hơn, vừa nhàn hơn mỗi ngày. #Roborock #RoborockVietnam #Qrevo2Pro #robotductrong #Robotlaunha </t>
+        </is>
+      </c>
+      <c r="G515" t="n">
+        <v>9</v>
+      </c>
+      <c r="H515" t="n">
+        <v>0</v>
+      </c>
+      <c r="I515" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7667568436045696276</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📦 Đập hộp ngay em Roborock Qrevo 2 Pro thôi! ✨ Không chỉ gây ấn tượng với diện mạo mới, Qrevo 2 Pro còn mang theo hàng loạt nâng cấp đáng giá để việc dọn dẹp trở nên nhàn hơn mỗi ngày. Cùng đập hộp, khám phá từng chi tiết và xem vì sao Qrevo 2 Pro hiện đang là cái tên được nhiều người quan tâm trong phân khúc tầm trung nhé! 🚀 #Roborock #RoborockVietnam #Qrevo2Pro #robotductrong #RobotHutBui </t>
+        </is>
+      </c>
+      <c r="G516" t="n">
+        <v>102</v>
+      </c>
+      <c r="H516" t="n">
+        <v>3</v>
+      </c>
+      <c r="I516" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7667893611962354951</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phân khúc tầm trung cứ Qrevo 2 pro trải nghiệm yên tâm luôn ạ Cảm ơn chị Trang cho đánh giá công tâm ạ 🚘🏠 Số 05 Nguyễn Du, Nông Trang, Việt Trì nhận ưu đãi hoặc ☎ 0862505508 nha các bác  #qrevo2pro #roborock #Robothutbui #robotlaunha #xuhuong </t>
+        </is>
+      </c>
+      <c r="G517" t="n">
+        <v>67</v>
+      </c>
+      <c r="H517" t="n">
+        <v>3</v>
+      </c>
+      <c r="I517" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7667861932040408327</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qrevo 2 pro phân khúc giá 12tr là không thể chê ạ 🚘🏠 các bác qua 05 Nguyễn Du, Nông Trang, Việt Trì để nhận ưu đãi hoặc số 0862505508 ạ #qrevo2pro #roborock #Robothutbui #xuhuong #robotlaunha </t>
+        </is>
+      </c>
+      <c r="G518" t="n">
+        <v>87</v>
+      </c>
+      <c r="H518" t="n">
+        <v>2</v>
+      </c>
+      <c r="I518" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7667562244342959378</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t xml:space="preserve">còn mau chưa trải nghiệm qua ngày shop Xiaomi Phú Thọ để trải nghiệm sản phẩm nhé ạ  🚘🏠 Số 05 Nguyễn Du, Nông Trang, Việt Trì ☎ 0862505508 #qrevo2pro #roborock #robothutbui #robotlaunha #xuhuong </t>
+        </is>
+      </c>
+      <c r="G519" t="n">
+        <v>369</v>
+      </c>
+      <c r="H519" t="n">
+        <v>2</v>
+      </c>
+      <c r="I519" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I519"/>
+  <dimension ref="A1:I533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19338,7 +19338,7 @@
         </is>
       </c>
       <c r="G461" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H461" t="n">
         <v>3</v>
@@ -19461,7 +19461,7 @@
         </is>
       </c>
       <c r="G464" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H464" t="n">
         <v>5</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="G466" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H466" t="n">
         <v>4</v>
       </c>
       <c r="I466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="G468" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H468" t="n">
         <v>2</v>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="G469" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H469" t="n">
         <v>1</v>
@@ -19707,7 +19707,7 @@
         </is>
       </c>
       <c r="G470" t="n">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="H470" t="n">
         <v>2</v>
@@ -19748,7 +19748,7 @@
         </is>
       </c>
       <c r="G471" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H471" t="n">
         <v>3</v>
@@ -19789,7 +19789,7 @@
         </is>
       </c>
       <c r="G472" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -19830,7 +19830,7 @@
         </is>
       </c>
       <c r="G473" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H473" t="n">
         <v>7</v>
@@ -19871,7 +19871,7 @@
         </is>
       </c>
       <c r="G474" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H474" t="n">
         <v>4</v>
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="G476" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H476" t="n">
         <v>2</v>
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="G477" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -20076,13 +20076,13 @@
         </is>
       </c>
       <c r="G479" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H479" t="n">
+        <v>2</v>
+      </c>
+      <c r="I479" t="n">
         <v>1</v>
-      </c>
-      <c r="I479" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -20117,10 +20117,10 @@
         </is>
       </c>
       <c r="G480" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="H480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I480" t="n">
         <v>0</v>
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="G481" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H481" t="n">
         <v>2</v>
@@ -20199,7 +20199,7 @@
         </is>
       </c>
       <c r="G482" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H482" t="n">
         <v>7</v>
@@ -20240,7 +20240,7 @@
         </is>
       </c>
       <c r="G483" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -20281,7 +20281,7 @@
         </is>
       </c>
       <c r="G484" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H484" t="n">
         <v>5</v>
@@ -20322,7 +20322,7 @@
         </is>
       </c>
       <c r="G485" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H485" t="n">
         <v>3</v>
@@ -20404,7 +20404,7 @@
         </is>
       </c>
       <c r="G487" t="n">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="H487" t="n">
         <v>5</v>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="G488" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H488" t="n">
         <v>3</v>
@@ -20486,7 +20486,7 @@
         </is>
       </c>
       <c r="G489" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H489" t="n">
         <v>4</v>
@@ -20527,7 +20527,7 @@
         </is>
       </c>
       <c r="G490" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H490" t="n">
         <v>3</v>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="G492" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H492" t="n">
         <v>4</v>
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="G493" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H493" t="n">
         <v>2</v>
@@ -20691,7 +20691,7 @@
         </is>
       </c>
       <c r="G494" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H494" t="n">
         <v>2</v>
@@ -20732,7 +20732,7 @@
         </is>
       </c>
       <c r="G495" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="H495" t="n">
         <v>1</v>
@@ -20773,7 +20773,7 @@
         </is>
       </c>
       <c r="G496" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H496" t="n">
         <v>3</v>
@@ -20814,10 +20814,10 @@
         </is>
       </c>
       <c r="G497" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="H497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I497" t="n">
         <v>1</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G499" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H499" t="n">
         <v>3</v>
@@ -20937,7 +20937,7 @@
         </is>
       </c>
       <c r="G500" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H500" t="n">
         <v>3</v>
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="G501" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H501" t="n">
         <v>3</v>
@@ -21019,10 +21019,10 @@
         </is>
       </c>
       <c r="G502" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="H502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I502" t="n">
         <v>0</v>
@@ -21060,7 +21060,7 @@
         </is>
       </c>
       <c r="G503" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H503" t="n">
         <v>1</v>
@@ -21101,7 +21101,7 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H504" t="n">
         <v>3</v>
@@ -21142,7 +21142,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H505" t="n">
         <v>4</v>
@@ -21183,7 +21183,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="H506" t="n">
         <v>3</v>
@@ -21224,13 +21224,13 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>28</v>
+        <v>372</v>
       </c>
       <c r="H507" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I507" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -21265,7 +21265,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="H508" t="n">
         <v>1</v>
@@ -21306,10 +21306,10 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>218</v>
+        <v>389</v>
       </c>
       <c r="H509" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I509" t="n">
         <v>0</v>
@@ -21347,10 +21347,10 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>147</v>
+        <v>1727</v>
       </c>
       <c r="H510" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I510" t="n">
         <v>0</v>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H511" t="n">
         <v>1</v>
@@ -21429,7 +21429,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H512" t="n">
         <v>1</v>
@@ -21470,10 +21470,10 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H513" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I513" t="n">
         <v>0</v>
@@ -21511,7 +21511,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -21552,10 +21552,10 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="H515" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I515" t="n">
         <v>0</v>
@@ -21593,7 +21593,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H516" t="n">
         <v>3</v>
@@ -21634,10 +21634,10 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>67</v>
+        <v>244</v>
       </c>
       <c r="H517" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I517" t="n">
         <v>0</v>
@@ -21675,10 +21675,10 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>87</v>
+        <v>304</v>
       </c>
       <c r="H518" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I518" t="n">
         <v>0</v>
@@ -21716,12 +21716,586 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H519" t="n">
         <v>2</v>
       </c>
       <c r="I519" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>homesmediant99</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homesmediant99/video/7667936178208787719</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cách tôi tiết kiệm 30p lau nhà mỗi ngày🤩🤩#robothutbui #Roborock #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G520" t="n">
+        <v>103</v>
+      </c>
+      <c r="H520" t="n">
+        <v>1</v>
+      </c>
+      <c r="I520" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7667946278533369108</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#robothutbui#roborock#qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G521" t="n">
+        <v>146</v>
+      </c>
+      <c r="H521" t="n">
+        <v>4</v>
+      </c>
+      <c r="I521" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7667967162497207572</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t xml:space="preserve">🤭🤭🤭🤭🤭#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G522" t="n">
+        <v>377</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7668149768253738248</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G523" t="n">
+        <v>376</v>
+      </c>
+      <c r="H523" t="n">
+        <v>4</v>
+      </c>
+      <c r="I523" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7668148223516658962</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Quá đẹp, xuất sắc 🤭 #Qrevo2Pro #Roborock #robothutbui #3tsmart</t>
+        </is>
+      </c>
+      <c r="G524" t="n">
+        <v>236</v>
+      </c>
+      <c r="H524" t="n">
+        <v>1</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7668144581782850823</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Bạn có biết? #Qrevo2Pro #Roborock #robothutbui #3tsmart</t>
+        </is>
+      </c>
+      <c r="G525" t="n">
+        <v>430</v>
+      </c>
+      <c r="H525" t="n">
+        <v>4</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7667936601774869781</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#qrevo2pro #roborock #robothutbui </t>
+        </is>
+      </c>
+      <c r="G526" t="n">
+        <v>113</v>
+      </c>
+      <c r="H526" t="n">
+        <v>1</v>
+      </c>
+      <c r="I526" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7668236077618007317</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiêu chí nào em cũng cân hết ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G527" t="n">
+        <v>76</v>
+      </c>
+      <c r="H527" t="n">
+        <v>2</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7668178760918781205</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phải sắm ngay 1 em thôi ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G528" t="n">
+        <v>87</v>
+      </c>
+      <c r="H528" t="n">
+        <v>4</v>
+      </c>
+      <c r="I528" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7668154519401843989</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bất ngờ chửa tiểu mỹ? #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G529" t="n">
+        <v>368</v>
+      </c>
+      <c r="H529" t="n">
+        <v>6</v>
+      </c>
+      <c r="I529" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7668153018327649557</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xứng đang 10 điểm luôn ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong  </t>
+        </is>
+      </c>
+      <c r="G530" t="n">
+        <v>247</v>
+      </c>
+      <c r="H530" t="n">
+        <v>1</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>domotekvietnam</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@domotekvietnam/video/7668233575870762247</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⏰ CHỈ CÒN 1 NGÀY CUỐI! Đừng bỏ lỡ chương trình “Trải nghiệm trước – Mua sau” dành cho Roborock Qrevo 2 Pro và Roborock F25 Ultra. ✨ Đến trực tiếp showroom để trải nghiệm thực tế trước khi quyết định. 🎁 Ưu đãi hấp dẫn chỉ áp dụng đến hết 31/07. #roborock #Domotek #robothutbui #Qrevo2Pro #f25ultra </t>
+        </is>
+      </c>
+      <c r="G531" t="n">
+        <v>82</v>
+      </c>
+      <c r="H531" t="n">
+        <v>2</v>
+      </c>
+      <c r="I531" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7668233363035114759</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bụi mịn với Qrevo 2 pro cân được hết luôn ạ #qrevo2pro #roborock #Robothutbui #robotlaunha #xuhuong </t>
+        </is>
+      </c>
+      <c r="G532" t="n">
+        <v>94</v>
+      </c>
+      <c r="H532" t="n">
+        <v>2</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7668192349121416466</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trải nghiệm xong khách mê luôn 🤩 CTKM diễn ra hết 31/7 nha các bác 🚘🏠 Số 05 Nguyễn Du, Nông Trang, Việt Trì hoặc ☎ 0862505508 ạ #qrevo2pro #roborock #Robothutbui #robotlaunha #xuhuong </t>
+        </is>
+      </c>
+      <c r="G533" t="n">
+        <v>335</v>
+      </c>
+      <c r="H533" t="n">
+        <v>3</v>
+      </c>
+      <c r="I533" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I533"/>
+  <dimension ref="A1:I541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="G468" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H468" t="n">
         <v>2</v>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="G469" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H469" t="n">
         <v>1</v>
@@ -19707,7 +19707,7 @@
         </is>
       </c>
       <c r="G470" t="n">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="H470" t="n">
         <v>2</v>
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="G477" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -20076,13 +20076,13 @@
         </is>
       </c>
       <c r="G479" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H479" t="n">
+        <v>3</v>
+      </c>
+      <c r="I479" t="n">
         <v>2</v>
-      </c>
-      <c r="I479" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -20117,7 +20117,7 @@
         </is>
       </c>
       <c r="G480" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H480" t="n">
         <v>1</v>
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="G481" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H481" t="n">
         <v>2</v>
@@ -20199,10 +20199,10 @@
         </is>
       </c>
       <c r="G482" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H482" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I482" t="n">
         <v>0</v>
@@ -20240,7 +20240,7 @@
         </is>
       </c>
       <c r="G483" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -20281,7 +20281,7 @@
         </is>
       </c>
       <c r="G484" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="H484" t="n">
         <v>5</v>
@@ -20322,7 +20322,7 @@
         </is>
       </c>
       <c r="G485" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H485" t="n">
         <v>3</v>
@@ -20363,7 +20363,7 @@
         </is>
       </c>
       <c r="G486" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H486" t="n">
         <v>2</v>
@@ -20404,10 +20404,10 @@
         </is>
       </c>
       <c r="G487" t="n">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="H487" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I487" t="n">
         <v>0</v>
@@ -20445,10 +20445,10 @@
         </is>
       </c>
       <c r="G488" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H488" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I488" t="n">
         <v>2</v>
@@ -20486,7 +20486,7 @@
         </is>
       </c>
       <c r="G489" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H489" t="n">
         <v>4</v>
@@ -20527,7 +20527,7 @@
         </is>
       </c>
       <c r="G490" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H490" t="n">
         <v>3</v>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="G492" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H492" t="n">
         <v>4</v>
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="G493" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H493" t="n">
         <v>2</v>
@@ -20732,7 +20732,7 @@
         </is>
       </c>
       <c r="G495" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H495" t="n">
         <v>1</v>
@@ -20773,7 +20773,7 @@
         </is>
       </c>
       <c r="G496" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H496" t="n">
         <v>3</v>
@@ -20814,7 +20814,7 @@
         </is>
       </c>
       <c r="G497" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H497" t="n">
         <v>2</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G499" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H499" t="n">
         <v>3</v>
@@ -20937,7 +20937,7 @@
         </is>
       </c>
       <c r="G500" t="n">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H500" t="n">
         <v>3</v>
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="G501" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H501" t="n">
         <v>3</v>
@@ -21019,7 +21019,7 @@
         </is>
       </c>
       <c r="G502" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H502" t="n">
         <v>3</v>
@@ -21060,10 +21060,10 @@
         </is>
       </c>
       <c r="G503" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I503" t="n">
         <v>0</v>
@@ -21101,10 +21101,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H504" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I504" t="n">
         <v>0</v>
@@ -21142,7 +21142,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="H505" t="n">
         <v>4</v>
@@ -21183,7 +21183,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H506" t="n">
         <v>3</v>
@@ -21224,7 +21224,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H507" t="n">
         <v>3</v>
@@ -21265,7 +21265,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H508" t="n">
         <v>1</v>
@@ -21306,7 +21306,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="H509" t="n">
         <v>6</v>
@@ -21347,7 +21347,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>1727</v>
+        <v>1827</v>
       </c>
       <c r="H510" t="n">
         <v>13</v>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H511" t="n">
         <v>1</v>
@@ -21429,10 +21429,10 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H512" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I512" t="n">
         <v>0</v>
@@ -21470,10 +21470,10 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H513" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I513" t="n">
         <v>0</v>
@@ -21511,7 +21511,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H517" t="n">
         <v>4</v>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="H518" t="n">
         <v>4</v>
@@ -21716,7 +21716,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H519" t="n">
         <v>2</v>
@@ -21757,13 +21757,13 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H520" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I520" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="521">
@@ -21798,10 +21798,10 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="H521" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I521" t="n">
         <v>0</v>
@@ -21839,7 +21839,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -21880,7 +21880,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="H523" t="n">
         <v>4</v>
@@ -21921,7 +21921,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>236</v>
+        <v>338</v>
       </c>
       <c r="H524" t="n">
         <v>1</v>
@@ -21962,10 +21962,10 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="H525" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I525" t="n">
         <v>0</v>
@@ -22003,7 +22003,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H526" t="n">
         <v>1</v>
@@ -22044,10 +22044,10 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="H527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I527" t="n">
         <v>0</v>
@@ -22085,13 +22085,13 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="H528" t="n">
+        <v>5</v>
+      </c>
+      <c r="I528" t="n">
         <v>4</v>
-      </c>
-      <c r="I528" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="529">
@@ -22126,10 +22126,10 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="H529" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I529" t="n">
         <v>0</v>
@@ -22167,10 +22167,10 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>247</v>
+        <v>353</v>
       </c>
       <c r="H530" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I530" t="n">
         <v>0</v>
@@ -22208,10 +22208,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="H531" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I531" t="n">
         <v>0</v>
@@ -22249,7 +22249,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="H532" t="n">
         <v>2</v>
@@ -22290,12 +22290,340 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="H533" t="n">
         <v>3</v>
       </c>
       <c r="I533" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7668610517501611284</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>#roborock#robothutbui#qrevo2pro #vinhlong#dongthap</t>
+        </is>
+      </c>
+      <c r="G534" t="n">
+        <v>416</v>
+      </c>
+      <c r="H534" t="n">
+        <v>8</v>
+      </c>
+      <c r="I534" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7668540409756273940</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chủ nhà đi du lịch🤭🤭🤭 Còn con sen vẫn cần mẫn dọn nhà cho chủ yên tâm đi chơi🥰🥰🥰🥰🥰#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G535" t="n">
+        <v>358</v>
+      </c>
+      <c r="H535" t="n">
+        <v>5</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7668624665660771604</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cứ gọi là xuất sắc luôn ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G536" t="n">
+        <v>74</v>
+      </c>
+      <c r="H536" t="n">
+        <v>1</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7668488891900497172</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Các bác còn lăn tăn gì mà chưa sắm robot ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
+        </is>
+      </c>
+      <c r="G537" t="n">
+        <v>388</v>
+      </c>
+      <c r="H537" t="n">
+        <v>2</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7668269256617938196</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Em cũng muốn có con trai này ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G538" t="n">
+        <v>392</v>
+      </c>
+      <c r="H538" t="n">
+        <v>7</v>
+      </c>
+      <c r="I538" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>momimart.vn</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@momimart.vn/video/7668645193549204754</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📦 Đập hộp ngay em Roborock Qrevo 2 Pro thôi! ✨ Không chỉ gây ấn tượng với diện mạo mới, Qrevo 2 Pro còn mang theo hàng loạt nâng cấp đáng giá để việc dọn dẹp trở nên nhàn hơn mỗi ngày. Cùng đập hộp, khám phá từng chi tiết và xem vì sao Qrevo 2 Pro hiện đang là cái tên được nhiều người quan tâm trong phân khúc tầm trung nhé! 🚀 #Roborock #RoborockVietnam #Qrevo2Pro#robothutbuilaunha </t>
+        </is>
+      </c>
+      <c r="G539" t="n">
+        <v>46</v>
+      </c>
+      <c r="H539" t="n">
+        <v>0</v>
+      </c>
+      <c r="I539" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7668605819021413640</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giá hơn 12tr là không thể chê Qrevo 2 pro roborock dc nha các bác  🚘🏠 Hàng sẵn giao lắp toàn Phú Thọ ạ  ☎ 0862505508 #qrevo2pro #roborock #xuhuong #Robothutbui #robotlaunha </t>
+        </is>
+      </c>
+      <c r="G540" t="n">
+        <v>81</v>
+      </c>
+      <c r="H540" t="n">
+        <v>1</v>
+      </c>
+      <c r="I540" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7668552253464136967</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thử dùng robot rồi nghiện liền đó các bác 😂 #qrevo2pro #roborock #Robothutbui #xuhuong #robotlaunha </t>
+        </is>
+      </c>
+      <c r="G541" t="n">
+        <v>116</v>
+      </c>
+      <c r="H541" t="n">
+        <v>3</v>
+      </c>
+      <c r="I541" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I541"/>
+  <dimension ref="A1:I545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="G477" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -20076,13 +20076,13 @@
         </is>
       </c>
       <c r="G479" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H479" t="n">
         <v>3</v>
       </c>
       <c r="I479" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="480">
@@ -20117,7 +20117,7 @@
         </is>
       </c>
       <c r="G480" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H480" t="n">
         <v>1</v>
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="G481" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H481" t="n">
         <v>2</v>
@@ -20199,7 +20199,7 @@
         </is>
       </c>
       <c r="G482" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H482" t="n">
         <v>8</v>
@@ -20281,7 +20281,7 @@
         </is>
       </c>
       <c r="G484" t="n">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="H484" t="n">
         <v>5</v>
@@ -20404,7 +20404,7 @@
         </is>
       </c>
       <c r="G487" t="n">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="H487" t="n">
         <v>6</v>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="G488" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H488" t="n">
         <v>4</v>
@@ -20527,7 +20527,7 @@
         </is>
       </c>
       <c r="G490" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H490" t="n">
         <v>3</v>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="G492" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H492" t="n">
         <v>4</v>
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="G493" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H493" t="n">
         <v>2</v>
@@ -20732,7 +20732,7 @@
         </is>
       </c>
       <c r="G495" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H495" t="n">
         <v>1</v>
@@ -20773,7 +20773,7 @@
         </is>
       </c>
       <c r="G496" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H496" t="n">
         <v>3</v>
@@ -20814,7 +20814,7 @@
         </is>
       </c>
       <c r="G497" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H497" t="n">
         <v>2</v>
@@ -20855,10 +20855,10 @@
         </is>
       </c>
       <c r="G498" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H498" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I498" t="n">
         <v>0</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G499" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H499" t="n">
         <v>3</v>
@@ -21019,7 +21019,7 @@
         </is>
       </c>
       <c r="G502" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H502" t="n">
         <v>3</v>
@@ -21060,7 +21060,7 @@
         </is>
       </c>
       <c r="G503" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H503" t="n">
         <v>2</v>
@@ -21101,7 +21101,7 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H504" t="n">
         <v>4</v>
@@ -21224,7 +21224,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H507" t="n">
         <v>3</v>
@@ -21265,7 +21265,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H508" t="n">
         <v>1</v>
@@ -21306,7 +21306,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H509" t="n">
         <v>6</v>
@@ -21347,7 +21347,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>1827</v>
+        <v>1834</v>
       </c>
       <c r="H510" t="n">
         <v>13</v>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H511" t="n">
         <v>1</v>
@@ -21429,7 +21429,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H512" t="n">
         <v>2</v>
@@ -21470,7 +21470,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H513" t="n">
         <v>4</v>
@@ -21511,7 +21511,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -21757,7 +21757,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H520" t="n">
         <v>2</v>
@@ -21798,10 +21798,10 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H521" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I521" t="n">
         <v>0</v>
@@ -21839,7 +21839,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -21880,7 +21880,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="H523" t="n">
         <v>4</v>
@@ -21921,7 +21921,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H524" t="n">
         <v>1</v>
@@ -21962,13 +21962,13 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="H525" t="n">
         <v>5</v>
       </c>
       <c r="I525" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526">
@@ -22003,7 +22003,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H526" t="n">
         <v>1</v>
@@ -22044,7 +22044,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H527" t="n">
         <v>3</v>
@@ -22085,7 +22085,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H528" t="n">
         <v>5</v>
@@ -22126,7 +22126,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H529" t="n">
         <v>8</v>
@@ -22167,10 +22167,10 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="H530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I530" t="n">
         <v>0</v>
@@ -22208,7 +22208,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H531" t="n">
         <v>3</v>
@@ -22249,7 +22249,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H532" t="n">
         <v>2</v>
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H533" t="n">
         <v>3</v>
@@ -22331,10 +22331,10 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>416</v>
+        <v>467</v>
       </c>
       <c r="H534" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I534" t="n">
         <v>1</v>
@@ -22372,10 +22372,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="H535" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I535" t="n">
         <v>0</v>
@@ -22413,10 +22413,10 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>74</v>
+        <v>359</v>
       </c>
       <c r="H536" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I536" t="n">
         <v>0</v>
@@ -22454,10 +22454,10 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="H537" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I537" t="n">
         <v>0</v>
@@ -22495,13 +22495,13 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="H538" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I538" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -22536,13 +22536,13 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>46</v>
+        <v>351</v>
       </c>
       <c r="H539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540">
@@ -22577,10 +22577,10 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="H540" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I540" t="n">
         <v>0</v>
@@ -22618,12 +22618,176 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="H541" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I541" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7668958023699696917</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chọn robot hút bụi Roborock Qrevo 2 Pro có gì? #qrevo2pro #robothutbui #roborock #dongthap #vinhlong </t>
+        </is>
+      </c>
+      <c r="G542" t="n">
+        <v>51</v>
+      </c>
+      <c r="H542" t="n">
+        <v>2</v>
+      </c>
+      <c r="I542" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7668696925536849170</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
+        </is>
+      </c>
+      <c r="G543" t="n">
+        <v>353</v>
+      </c>
+      <c r="H543" t="n">
+        <v>2</v>
+      </c>
+      <c r="I543" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7668895582957718805</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#CapCut Chúc mừng Roborock Authorized Store Lâm Đồng Khai trương Hồng Phát. 350 Phan Đình Phùng - Đà Lạt#robothutbui #roborock #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G544" t="n">
+        <v>118</v>
+      </c>
+      <c r="H544" t="n">
+        <v>2</v>
+      </c>
+      <c r="I544" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>phanthulan715</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@phanthulan715/video/7668919716760587541</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mười điểm không có nhưng luôn ạ#roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
+        </is>
+      </c>
+      <c r="G545" t="n">
+        <v>87</v>
+      </c>
+      <c r="H545" t="n">
+        <v>1</v>
+      </c>
+      <c r="I545" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I545"/>
+  <dimension ref="A1:I546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="G479" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H479" t="n">
         <v>3</v>
@@ -20158,10 +20158,10 @@
         </is>
       </c>
       <c r="G481" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I481" t="n">
         <v>0</v>
@@ -20199,7 +20199,7 @@
         </is>
       </c>
       <c r="G482" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H482" t="n">
         <v>8</v>
@@ -20240,7 +20240,7 @@
         </is>
       </c>
       <c r="G483" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -20281,7 +20281,7 @@
         </is>
       </c>
       <c r="G484" t="n">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="H484" t="n">
         <v>5</v>
@@ -20363,7 +20363,7 @@
         </is>
       </c>
       <c r="G486" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H486" t="n">
         <v>2</v>
@@ -20404,7 +20404,7 @@
         </is>
       </c>
       <c r="G487" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H487" t="n">
         <v>6</v>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="G492" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H492" t="n">
         <v>4</v>
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="G493" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H493" t="n">
         <v>2</v>
@@ -20732,7 +20732,7 @@
         </is>
       </c>
       <c r="G495" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H495" t="n">
         <v>1</v>
@@ -20773,7 +20773,7 @@
         </is>
       </c>
       <c r="G496" t="n">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H496" t="n">
         <v>3</v>
@@ -20814,7 +20814,7 @@
         </is>
       </c>
       <c r="G497" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H497" t="n">
         <v>2</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G499" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H499" t="n">
         <v>3</v>
@@ -20937,7 +20937,7 @@
         </is>
       </c>
       <c r="G500" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H500" t="n">
         <v>3</v>
@@ -21019,7 +21019,7 @@
         </is>
       </c>
       <c r="G502" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H502" t="n">
         <v>3</v>
@@ -21101,7 +21101,7 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H504" t="n">
         <v>4</v>
@@ -21142,7 +21142,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H505" t="n">
         <v>4</v>
@@ -21183,7 +21183,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="H506" t="n">
         <v>3</v>
@@ -21224,7 +21224,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H507" t="n">
         <v>3</v>
@@ -21265,7 +21265,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H508" t="n">
         <v>1</v>
@@ -21306,10 +21306,10 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="H509" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I509" t="n">
         <v>0</v>
@@ -21347,7 +21347,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>1834</v>
+        <v>1838</v>
       </c>
       <c r="H510" t="n">
         <v>13</v>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="H511" t="n">
         <v>1</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H517" t="n">
         <v>4</v>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H518" t="n">
         <v>4</v>
@@ -21716,7 +21716,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="H519" t="n">
         <v>2</v>
@@ -21757,7 +21757,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H520" t="n">
         <v>2</v>
@@ -21839,7 +21839,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -21880,7 +21880,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="H523" t="n">
         <v>4</v>
@@ -21962,7 +21962,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H525" t="n">
         <v>5</v>
@@ -22126,7 +22126,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="H529" t="n">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H530" t="n">
         <v>3</v>
@@ -22208,7 +22208,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H531" t="n">
         <v>3</v>
@@ -22249,7 +22249,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H532" t="n">
         <v>2</v>
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="H533" t="n">
         <v>3</v>
@@ -22331,7 +22331,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="H534" t="n">
         <v>12</v>
@@ -22413,7 +22413,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="H536" t="n">
         <v>2</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="H537" t="n">
         <v>4</v>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="H538" t="n">
         <v>8</v>
@@ -22536,7 +22536,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="H539" t="n">
         <v>1</v>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H540" t="n">
         <v>2</v>
@@ -22618,7 +22618,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H541" t="n">
         <v>4</v>
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="H542" t="n">
         <v>2</v>
@@ -22700,7 +22700,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="H543" t="n">
         <v>2</v>
@@ -22741,10 +22741,10 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="H544" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I544" t="n">
         <v>0</v>
@@ -22782,12 +22782,53 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="H545" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I545" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7669046126682656020</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot hút bụi thời điểm nào là tốt nhất? #robotductrong #robotlaunha #robothutbui #Roborock #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G546" t="n">
+        <v>0</v>
+      </c>
+      <c r="H546" t="n">
+        <v>0</v>
+      </c>
+      <c r="I546" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I546"/>
+  <dimension ref="A1:I549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20199,7 +20199,7 @@
         </is>
       </c>
       <c r="G482" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H482" t="n">
         <v>8</v>
@@ -20240,7 +20240,7 @@
         </is>
       </c>
       <c r="G483" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -20281,7 +20281,7 @@
         </is>
       </c>
       <c r="G484" t="n">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="H484" t="n">
         <v>5</v>
@@ -20322,7 +20322,7 @@
         </is>
       </c>
       <c r="G485" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H485" t="n">
         <v>3</v>
@@ -20363,7 +20363,7 @@
         </is>
       </c>
       <c r="G486" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H486" t="n">
         <v>2</v>
@@ -20404,7 +20404,7 @@
         </is>
       </c>
       <c r="G487" t="n">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="H487" t="n">
         <v>6</v>
@@ -20445,7 +20445,7 @@
         </is>
       </c>
       <c r="G488" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H488" t="n">
         <v>4</v>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="G492" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H492" t="n">
         <v>4</v>
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="G493" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H493" t="n">
         <v>2</v>
@@ -20691,7 +20691,7 @@
         </is>
       </c>
       <c r="G494" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H494" t="n">
         <v>2</v>
@@ -20732,7 +20732,7 @@
         </is>
       </c>
       <c r="G495" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="H495" t="n">
         <v>1</v>
@@ -20773,7 +20773,7 @@
         </is>
       </c>
       <c r="G496" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H496" t="n">
         <v>3</v>
@@ -20814,7 +20814,7 @@
         </is>
       </c>
       <c r="G497" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H497" t="n">
         <v>2</v>
@@ -20937,7 +20937,7 @@
         </is>
       </c>
       <c r="G500" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H500" t="n">
         <v>3</v>
@@ -21019,7 +21019,7 @@
         </is>
       </c>
       <c r="G502" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H502" t="n">
         <v>3</v>
@@ -21101,7 +21101,7 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H504" t="n">
         <v>4</v>
@@ -21142,7 +21142,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H505" t="n">
         <v>4</v>
@@ -21183,7 +21183,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H506" t="n">
         <v>3</v>
@@ -21224,7 +21224,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="H507" t="n">
         <v>3</v>
@@ -21265,7 +21265,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H508" t="n">
         <v>1</v>
@@ -21306,7 +21306,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H509" t="n">
         <v>7</v>
@@ -21347,7 +21347,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>1838</v>
+        <v>1841</v>
       </c>
       <c r="H510" t="n">
         <v>13</v>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H511" t="n">
         <v>1</v>
@@ -21429,7 +21429,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H512" t="n">
         <v>2</v>
@@ -21470,7 +21470,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H513" t="n">
         <v>4</v>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H515" t="n">
         <v>1</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H517" t="n">
         <v>4</v>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H518" t="n">
         <v>4</v>
@@ -21716,7 +21716,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H519" t="n">
         <v>2</v>
@@ -21757,7 +21757,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H520" t="n">
         <v>2</v>
@@ -21798,7 +21798,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H521" t="n">
         <v>7</v>
@@ -21839,7 +21839,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -21880,7 +21880,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H523" t="n">
         <v>4</v>
@@ -21962,7 +21962,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="H525" t="n">
         <v>5</v>
@@ -22003,7 +22003,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H526" t="n">
         <v>1</v>
@@ -22044,7 +22044,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H527" t="n">
         <v>3</v>
@@ -22085,7 +22085,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H528" t="n">
         <v>5</v>
@@ -22126,7 +22126,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H529" t="n">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H530" t="n">
         <v>3</v>
@@ -22208,7 +22208,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H531" t="n">
         <v>3</v>
@@ -22249,7 +22249,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H532" t="n">
         <v>2</v>
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H533" t="n">
         <v>3</v>
@@ -22331,10 +22331,10 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="H534" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I534" t="n">
         <v>1</v>
@@ -22372,7 +22372,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H535" t="n">
         <v>6</v>
@@ -22413,10 +22413,10 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="H536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I536" t="n">
         <v>0</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="H537" t="n">
         <v>4</v>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="H538" t="n">
         <v>8</v>
@@ -22536,7 +22536,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="H539" t="n">
         <v>1</v>
@@ -22577,10 +22577,10 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H540" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I540" t="n">
         <v>0</v>
@@ -22618,7 +22618,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H541" t="n">
         <v>4</v>
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H542" t="n">
         <v>2</v>
@@ -22700,7 +22700,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H543" t="n">
         <v>2</v>
@@ -22741,10 +22741,10 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H544" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I544" t="n">
         <v>0</v>
@@ -22782,7 +22782,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H545" t="n">
         <v>2</v>
@@ -22823,12 +22823,135 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
       </c>
       <c r="I546" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7669421094713036040</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WHAT IS BEAUTIFUL? #Qrevo2Pro  #Roborock  #robothutbui  #3tsmart  #saros20 </t>
+        </is>
+      </c>
+      <c r="G547" t="n">
+        <v>363</v>
+      </c>
+      <c r="H547" t="n">
+        <v>1</v>
+      </c>
+      <c r="I547" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>tm.anh.kitchen.qu</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tm.anh.kitchen.qu/video/7669652416471780615</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Làm 5 điều này để Robot nhà bạn bền hơn 💯 #bepquangtri #roborock #roborockvietnam #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G548" t="n">
+        <v>127</v>
+      </c>
+      <c r="H548" t="n">
+        <v>1</v>
+      </c>
+      <c r="I548" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7669668002152975636</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✨ Sau trải nghiệm thực tế, Chú Tùng Ham Vui đánh giá Qrevo 2 Pro chính là robot hút bụi lau nhà đáng để cân nhắc trong phân khúc tầm trung. Các điểm nổi bật: ◾ Hút sạch bụi lớn ◾ Hạn chế tóc, lông quấn chổi ◾ Lau sát góc hiệu quả Không định vị mình bằng sự phô trương, Qrevo 2 Pro chinh phục người dùng bằng trải nghiệm làm sạch ổn định và sự tiện lợi trong sử dụng. #Roborock #RoborockVietnam #Qrevo2Pro #robotductrong #robotlaunha </t>
+        </is>
+      </c>
+      <c r="G549" t="n">
+        <v>3</v>
+      </c>
+      <c r="H549" t="n">
+        <v>0</v>
+      </c>
+      <c r="I549" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H538" t="n">
         <v>8</v>
@@ -22905,7 +22905,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H548" t="n">
         <v>1</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I549"/>
+  <dimension ref="A1:I550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20691,7 +20691,7 @@
         </is>
       </c>
       <c r="G494" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H494" t="n">
         <v>2</v>
@@ -20814,7 +20814,7 @@
         </is>
       </c>
       <c r="G497" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H497" t="n">
         <v>2</v>
@@ -20855,7 +20855,7 @@
         </is>
       </c>
       <c r="G498" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H498" t="n">
         <v>5</v>
@@ -21101,7 +21101,7 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H504" t="n">
         <v>4</v>
@@ -21142,7 +21142,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H505" t="n">
         <v>4</v>
@@ -21306,10 +21306,10 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H509" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I509" t="n">
         <v>0</v>
@@ -21347,7 +21347,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>1841</v>
+        <v>1851</v>
       </c>
       <c r="H510" t="n">
         <v>13</v>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H511" t="n">
         <v>1</v>
@@ -21552,7 +21552,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H515" t="n">
         <v>1</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H517" t="n">
         <v>4</v>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H518" t="n">
         <v>4</v>
@@ -21716,7 +21716,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H519" t="n">
         <v>2</v>
@@ -21757,7 +21757,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H520" t="n">
         <v>2</v>
@@ -21798,13 +21798,13 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H521" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I521" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
@@ -21880,7 +21880,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="H523" t="n">
         <v>4</v>
@@ -21921,7 +21921,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H524" t="n">
         <v>1</v>
@@ -21962,7 +21962,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H525" t="n">
         <v>5</v>
@@ -22003,7 +22003,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H526" t="n">
         <v>1</v>
@@ -22085,7 +22085,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H528" t="n">
         <v>5</v>
@@ -22126,7 +22126,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H529" t="n">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H530" t="n">
         <v>3</v>
@@ -22208,7 +22208,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H531" t="n">
         <v>3</v>
@@ -22249,7 +22249,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H532" t="n">
         <v>2</v>
@@ -22290,7 +22290,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="H533" t="n">
         <v>3</v>
@@ -22331,13 +22331,13 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H534" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I534" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -22413,7 +22413,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H536" t="n">
         <v>3</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H537" t="n">
         <v>4</v>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="H538" t="n">
         <v>8</v>
@@ -22536,7 +22536,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="H539" t="n">
         <v>1</v>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H540" t="n">
         <v>3</v>
@@ -22618,7 +22618,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H541" t="n">
         <v>4</v>
@@ -22659,13 +22659,13 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H542" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543">
@@ -22700,7 +22700,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H543" t="n">
         <v>2</v>
@@ -22741,7 +22741,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H544" t="n">
         <v>6</v>
@@ -22782,7 +22782,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H545" t="n">
         <v>2</v>
@@ -22823,7 +22823,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -22864,7 +22864,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H547" t="n">
         <v>1</v>
@@ -22905,7 +22905,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="H548" t="n">
         <v>1</v>
@@ -22952,6 +22952,47 @@
         <v>0</v>
       </c>
       <c r="I549" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7670053469948267797</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roborock đã lên xe, còn việc nhà thì sắp… xuống xe! 😄 Chúc khách sớm nhận được “trợ thủ” mới và tận hưởng cảm giác nhà sạch mà chẳng cần động tay.#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G550" t="n">
+        <v>235</v>
+      </c>
+      <c r="H550" t="n">
+        <v>1</v>
+      </c>
+      <c r="I550" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I550"/>
+  <dimension ref="A1:I552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21306,7 +21306,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="H509" t="n">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H512" t="n">
         <v>2</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H517" t="n">
         <v>4</v>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H518" t="n">
         <v>4</v>
@@ -21757,7 +21757,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H520" t="n">
         <v>2</v>
@@ -21798,7 +21798,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H521" t="n">
         <v>8</v>
@@ -21962,7 +21962,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H525" t="n">
         <v>5</v>
@@ -22003,10 +22003,10 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I526" t="n">
         <v>0</v>
@@ -22044,7 +22044,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H527" t="n">
         <v>3</v>
@@ -22085,7 +22085,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H528" t="n">
         <v>5</v>
@@ -22126,7 +22126,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="H529" t="n">
         <v>8</v>
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H530" t="n">
         <v>3</v>
@@ -22208,7 +22208,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H531" t="n">
         <v>3</v>
@@ -22249,7 +22249,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H532" t="n">
         <v>2</v>
@@ -22290,10 +22290,10 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="H533" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I533" t="n">
         <v>0</v>
@@ -22331,7 +22331,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="H534" t="n">
         <v>14</v>
@@ -22413,7 +22413,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="H536" t="n">
         <v>3</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="H537" t="n">
         <v>4</v>
@@ -22495,10 +22495,10 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="H538" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I538" t="n">
         <v>2</v>
@@ -22536,7 +22536,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H539" t="n">
         <v>1</v>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="H540" t="n">
         <v>3</v>
@@ -22618,7 +22618,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H541" t="n">
         <v>4</v>
@@ -22659,13 +22659,13 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H542" t="n">
         <v>3</v>
       </c>
       <c r="I542" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -22741,7 +22741,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H544" t="n">
         <v>6</v>
@@ -22782,7 +22782,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H545" t="n">
         <v>2</v>
@@ -22864,7 +22864,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H547" t="n">
         <v>1</v>
@@ -22905,7 +22905,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H548" t="n">
         <v>1</v>
@@ -22987,12 +22987,94 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>235</v>
+        <v>385</v>
       </c>
       <c r="H550" t="n">
+        <v>2</v>
+      </c>
+      <c r="I550" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>tigerbot.smarthome</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@tigerbot.smarthome/video/7670502767491829013</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#roborock#qrevo2pro #robothutbui#vinhlong#dongthap </t>
+        </is>
+      </c>
+      <c r="G551" t="n">
+        <v>37</v>
+      </c>
+      <c r="H551" t="n">
         <v>1</v>
       </c>
-      <c r="I550" t="n">
+      <c r="I551" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7670156715358276884</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Bộ trưởng bộ nội vụ ra chỉ thị #roborock #HTSmartHome #robotlaunha #Qrevo2Pro #RobotHutBui</t>
+        </is>
+      </c>
+      <c r="G552" t="n">
+        <v>0</v>
+      </c>
+      <c r="H552" t="n">
+        <v>0</v>
+      </c>
+      <c r="I552" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="videos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="videos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I555"/>
+  <dimension ref="A1:I556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24981,20 +24981,14 @@
           <t xml:space="preserve">#Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
         </is>
       </c>
-      <c r="G523" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="H523" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I523" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G523" t="n">
+        <v>416</v>
+      </c>
+      <c r="H523" t="n">
+        <v>4</v>
+      </c>
+      <c r="I523" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="524">
@@ -25028,20 +25022,14 @@
           <t>Quá đẹp, xuất sắc 🤭 #Qrevo2Pro #Roborock #robothutbui #3tsmart</t>
         </is>
       </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="H524" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I524" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G524" t="n">
+        <v>341</v>
+      </c>
+      <c r="H524" t="n">
+        <v>1</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="525">
@@ -25075,20 +25063,14 @@
           <t>Bạn có biết? #Qrevo2Pro #Roborock #robothutbui #3tsmart</t>
         </is>
       </c>
-      <c r="G525" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I525" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G525" t="n">
+        <v>454</v>
+      </c>
+      <c r="H525" t="n">
+        <v>5</v>
+      </c>
+      <c r="I525" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="526">
@@ -25169,20 +25151,14 @@
           <t xml:space="preserve">Tiêu chí nào em cũng cân hết ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
         </is>
       </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="H527" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I527" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G527" t="n">
+        <v>118</v>
+      </c>
+      <c r="H527" t="n">
+        <v>3</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="528">
@@ -25216,20 +25192,14 @@
           <t xml:space="preserve">Phải sắm ngay 1 em thôi ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
         </is>
       </c>
-      <c r="G528" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H528" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I528" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G528" t="n">
+        <v>110</v>
+      </c>
+      <c r="H528" t="n">
+        <v>5</v>
+      </c>
+      <c r="I528" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="529">
@@ -25263,20 +25233,14 @@
           <t xml:space="preserve">Bất ngờ chửa tiểu mỹ? #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
         </is>
       </c>
-      <c r="G529" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="H529" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I529" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G529" t="n">
+        <v>392</v>
+      </c>
+      <c r="H529" t="n">
+        <v>8</v>
+      </c>
+      <c r="I529" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="530">
@@ -25310,20 +25274,14 @@
           <t xml:space="preserve">Xứng đang 10 điểm luôn ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong  </t>
         </is>
       </c>
-      <c r="G530" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="H530" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I530" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G530" t="n">
+        <v>365</v>
+      </c>
+      <c r="H530" t="n">
+        <v>3</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -25357,20 +25315,14 @@
           <t xml:space="preserve">⏰ CHỈ CÒN 1 NGÀY CUỐI! Đừng bỏ lỡ chương trình “Trải nghiệm trước – Mua sau” dành cho Roborock Qrevo 2 Pro và Roborock F25 Ultra. ✨ Đến trực tiếp showroom để trải nghiệm thực tế trước khi quyết định. 🎁 Ưu đãi hấp dẫn chỉ áp dụng đến hết 31/07. #roborock #Domotek #robothutbui #Qrevo2Pro #f25ultra </t>
         </is>
       </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="H531" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I531" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G531" t="n">
+        <v>203</v>
+      </c>
+      <c r="H531" t="n">
+        <v>3</v>
+      </c>
+      <c r="I531" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="532">
@@ -25404,20 +25356,14 @@
           <t xml:space="preserve">bụi mịn với Qrevo 2 pro cân được hết luôn ạ #qrevo2pro #roborock #Robothutbui #robotlaunha #xuhuong </t>
         </is>
       </c>
-      <c r="G532" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="H532" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I532" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G532" t="n">
+        <v>183</v>
+      </c>
+      <c r="H532" t="n">
+        <v>2</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="533">
@@ -25451,20 +25397,14 @@
           <t xml:space="preserve">trải nghiệm xong khách mê luôn 🤩 CTKM diễn ra hết 31/7 nha các bác 🚘🏠 Số 05 Nguyễn Du, Nông Trang, Việt Trì hoặc ☎ 0862505508 ạ #qrevo2pro #roborock #Robothutbui #robotlaunha #xuhuong </t>
         </is>
       </c>
-      <c r="G533" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="H533" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I533" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G533" t="n">
+        <v>397</v>
+      </c>
+      <c r="H533" t="n">
+        <v>4</v>
+      </c>
+      <c r="I533" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="534">
@@ -25498,20 +25438,14 @@
           <t>#roborock#robothutbui#qrevo2pro #vinhlong#dongthap</t>
         </is>
       </c>
-      <c r="G534" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="H534" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I534" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G534" t="n">
+        <v>481</v>
+      </c>
+      <c r="H534" t="n">
+        <v>14</v>
+      </c>
+      <c r="I534" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -25545,20 +25479,14 @@
           <t xml:space="preserve">Chủ nhà đi du lịch🤭🤭🤭 Còn con sen vẫn cần mẫn dọn nhà cho chủ yên tâm đi chơi🥰🥰🥰🥰🥰#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
         </is>
       </c>
-      <c r="G535" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="H535" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I535" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G535" t="n">
+        <v>376</v>
+      </c>
+      <c r="H535" t="n">
+        <v>6</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="536">
@@ -25592,20 +25520,14 @@
           <t xml:space="preserve">Cứ gọi là xuất sắc luôn ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
         </is>
       </c>
-      <c r="G536" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="H536" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I536" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G536" t="n">
+        <v>378</v>
+      </c>
+      <c r="H536" t="n">
+        <v>3</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="537">
@@ -25639,20 +25561,14 @@
           <t xml:space="preserve">Các bác còn lăn tăn gì mà chưa sắm robot ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho #xuhuong </t>
         </is>
       </c>
-      <c r="G537" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="H537" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I537" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G537" t="n">
+        <v>421</v>
+      </c>
+      <c r="H537" t="n">
+        <v>4</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -25686,20 +25602,14 @@
           <t xml:space="preserve">Em cũng muốn có con trai này ạ #roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
         </is>
       </c>
-      <c r="G538" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="H538" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I538" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G538" t="n">
+        <v>469</v>
+      </c>
+      <c r="H538" t="n">
+        <v>9</v>
+      </c>
+      <c r="I538" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -25733,20 +25643,14 @@
           <t xml:space="preserve">📦 Đập hộp ngay em Roborock Qrevo 2 Pro thôi! ✨ Không chỉ gây ấn tượng với diện mạo mới, Qrevo 2 Pro còn mang theo hàng loạt nâng cấp đáng giá để việc dọn dẹp trở nên nhàn hơn mỗi ngày. Cùng đập hộp, khám phá từng chi tiết và xem vì sao Qrevo 2 Pro hiện đang là cái tên được nhiều người quan tâm trong phân khúc tầm trung nhé! 🚀 #Roborock #RoborockVietnam #Qrevo2Pro#robothutbuilaunha </t>
         </is>
       </c>
-      <c r="G539" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="H539" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I539" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G539" t="n">
+        <v>379</v>
+      </c>
+      <c r="H539" t="n">
+        <v>1</v>
+      </c>
+      <c r="I539" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="540">
@@ -25780,20 +25684,14 @@
           <t xml:space="preserve">Giá hơn 12tr là không thể chê Qrevo 2 pro roborock dc nha các bác  🚘🏠 Hàng sẵn giao lắp toàn Phú Thọ ạ  ☎ 0862505508 #qrevo2pro #roborock #xuhuong #Robothutbui #robotlaunha </t>
         </is>
       </c>
-      <c r="G540" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="H540" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I540" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G540" t="n">
+        <v>153</v>
+      </c>
+      <c r="H540" t="n">
+        <v>3</v>
+      </c>
+      <c r="I540" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="541">
@@ -25827,20 +25725,14 @@
           <t xml:space="preserve">Thử dùng robot rồi nghiện liền đó các bác 😂 #qrevo2pro #roborock #Robothutbui #xuhuong #robotlaunha </t>
         </is>
       </c>
-      <c r="G541" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="H541" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I541" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G541" t="n">
+        <v>160</v>
+      </c>
+      <c r="H541" t="n">
+        <v>4</v>
+      </c>
+      <c r="I541" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="542">
@@ -25874,20 +25766,14 @@
           <t xml:space="preserve">Chọn robot hút bụi Roborock Qrevo 2 Pro có gì? #qrevo2pro #robothutbui #roborock #dongthap #vinhlong </t>
         </is>
       </c>
-      <c r="G542" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="H542" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I542" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G542" t="n">
+        <v>85</v>
+      </c>
+      <c r="H542" t="n">
+        <v>3</v>
+      </c>
+      <c r="I542" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -25921,20 +25807,14 @@
           <t xml:space="preserve">#Qrevo2Pro #Roborock #robothutbui #3tsmart </t>
         </is>
       </c>
-      <c r="G543" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="H543" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I543" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G543" t="n">
+        <v>367</v>
+      </c>
+      <c r="H543" t="n">
+        <v>2</v>
+      </c>
+      <c r="I543" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="544">
@@ -25968,20 +25848,14 @@
           <t xml:space="preserve">#CapCut Chúc mừng Roborock Authorized Store Lâm Đồng Khai trương Hồng Phát. 350 Phan Đình Phùng - Đà Lạt#robothutbui #roborock #Qrevo2Pro </t>
         </is>
       </c>
-      <c r="G544" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="H544" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I544" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G544" t="n">
+        <v>153</v>
+      </c>
+      <c r="H544" t="n">
+        <v>7</v>
+      </c>
+      <c r="I544" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="545">
@@ -26015,20 +25889,14 @@
           <t xml:space="preserve">Mười điểm không có nhưng luôn ạ#roborock #Qrevo2Pro #robothutbui #smarthomephutho </t>
         </is>
       </c>
-      <c r="G545" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I545" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G545" t="n">
+        <v>116</v>
+      </c>
+      <c r="H545" t="n">
+        <v>2</v>
+      </c>
+      <c r="I545" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="546">
@@ -26062,20 +25930,14 @@
           <t xml:space="preserve">Robot hút bụi thời điểm nào là tốt nhất? #robotductrong #robotlaunha #robothutbui #Roborock #Qrevo2Pro </t>
         </is>
       </c>
-      <c r="G546" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H546" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I546" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G546" t="n">
+        <v>4</v>
+      </c>
+      <c r="H546" t="n">
+        <v>0</v>
+      </c>
+      <c r="I546" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="547">
@@ -26109,20 +25971,14 @@
           <t xml:space="preserve">WHAT IS BEAUTIFUL? #Qrevo2Pro  #Roborock  #robothutbui  #3tsmart  #saros20 </t>
         </is>
       </c>
-      <c r="G547" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="H547" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I547" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G547" t="n">
+        <v>370</v>
+      </c>
+      <c r="H547" t="n">
+        <v>1</v>
+      </c>
+      <c r="I547" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="548">
@@ -26156,20 +26012,14 @@
           <t xml:space="preserve">Làm 5 điều này để Robot nhà bạn bền hơn 💯 #bepquangtri #roborock #roborockvietnam #qrevo2pro </t>
         </is>
       </c>
-      <c r="G548" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="H548" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I548" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G548" t="n">
+        <v>164</v>
+      </c>
+      <c r="H548" t="n">
+        <v>1</v>
+      </c>
+      <c r="I548" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="549">
@@ -26203,20 +26053,14 @@
           <t xml:space="preserve">✨ Sau trải nghiệm thực tế, Chú Tùng Ham Vui đánh giá Qrevo 2 Pro chính là robot hút bụi lau nhà đáng để cân nhắc trong phân khúc tầm trung. Các điểm nổi bật: ◾ Hút sạch bụi lớn ◾ Hạn chế tóc, lông quấn chổi ◾ Lau sát góc hiệu quả Không định vị mình bằng sự phô trương, Qrevo 2 Pro chinh phục người dùng bằng trải nghiệm làm sạch ổn định và sự tiện lợi trong sử dụng. #Roborock #RoborockVietnam #Qrevo2Pro #robotductrong #robotlaunha </t>
         </is>
       </c>
-      <c r="G549" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H549" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I549" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G549" t="n">
+        <v>3</v>
+      </c>
+      <c r="H549" t="n">
+        <v>0</v>
+      </c>
+      <c r="I549" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="550">
@@ -26250,20 +26094,14 @@
           <t xml:space="preserve">Roborock đã lên xe, còn việc nhà thì sắp… xuống xe! 😄 Chúc khách sớm nhận được “trợ thủ” mới và tận hưởng cảm giác nhà sạch mà chẳng cần động tay.#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
         </is>
       </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="H550" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I550" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G550" t="n">
+        <v>385</v>
+      </c>
+      <c r="H550" t="n">
+        <v>2</v>
+      </c>
+      <c r="I550" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="551">
@@ -26297,20 +26135,14 @@
           <t xml:space="preserve">#roborock#qrevo2pro #robothutbui#vinhlong#dongthap </t>
         </is>
       </c>
-      <c r="G551" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="H551" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I551" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G551" t="n">
+        <v>372</v>
+      </c>
+      <c r="H551" t="n">
+        <v>3</v>
+      </c>
+      <c r="I551" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="552">
@@ -26344,20 +26176,14 @@
           <t>Bộ trưởng bộ nội vụ ra chỉ thị #roborock #HTSmartHome #robotlaunha #Qrevo2Pro #RobotHutBui</t>
         </is>
       </c>
-      <c r="G552" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H552" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I552" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G552" t="n">
+        <v>0</v>
+      </c>
+      <c r="H552" t="n">
+        <v>0</v>
+      </c>
+      <c r="I552" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="553">
@@ -26499,6 +26325,47 @@
         <is>
           <t>0</t>
         </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7670853748738084116</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#robothutbui #mistorebienhoa #robothutbuilaunha #roborock #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G556" t="n">
+        <v>63</v>
+      </c>
+      <c r="H556" t="n">
+        <v>0</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I556"/>
+  <dimension ref="A1:I557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25439,7 +25439,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H534" t="n">
         <v>14</v>
@@ -25480,7 +25480,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H535" t="n">
         <v>6</v>
@@ -25562,7 +25562,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H537" t="n">
         <v>4</v>
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H539" t="n">
         <v>1</v>
@@ -25685,7 +25685,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H540" t="n">
         <v>3</v>
@@ -25726,7 +25726,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H541" t="n">
         <v>4</v>
@@ -25849,7 +25849,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H544" t="n">
         <v>7</v>
@@ -25972,7 +25972,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H547" t="n">
         <v>1</v>
@@ -26013,10 +26013,10 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H548" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I548" t="n">
         <v>0</v>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H550" t="n">
         <v>2</v>
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H551" t="n">
         <v>3</v>
@@ -26177,7 +26177,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -26359,12 +26359,53 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
       </c>
       <c r="I556" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>homebotvietnam</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homebotvietnam/video/7670924472215833876</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Không phải làm gì mà nhà vẫn sạch mỗi ngày? 🤯🤖 Đây là lý do mình mê Qrevo 2 Pro! ✨🏡 #Qrevo2Pro #Roborock #robothutbui #ReviewCongNghe #SmartHome</t>
+        </is>
+      </c>
+      <c r="G557" t="n">
+        <v>375</v>
+      </c>
+      <c r="H557" t="n">
+        <v>3</v>
+      </c>
+      <c r="I557" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -25849,7 +25849,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H544" t="n">
         <v>7</v>
@@ -25890,7 +25890,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H545" t="n">
         <v>2</v>
@@ -26359,7 +26359,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -26400,7 +26400,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H557" t="n">
         <v>3</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I557"/>
+  <dimension ref="A1:I558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25972,7 +25972,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="H547" t="n">
         <v>1</v>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H550" t="n">
         <v>2</v>
@@ -26400,12 +26400,53 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="H557" t="n">
         <v>3</v>
       </c>
       <c r="I557" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7671839343798914325</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Em cứ thấy hàng lên xe là em zui lém rồi!!!! Ib cho em để em bận rộn tư vấn cho các nàng thơ của em nào❤️❤️❤️❤️#Roborock #Qrevo2Pro #robothutbui #thietbithongminh </t>
+        </is>
+      </c>
+      <c r="G558" t="n">
+        <v>380</v>
+      </c>
+      <c r="H558" t="n">
+        <v>3</v>
+      </c>
+      <c r="I558" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I558"/>
+  <dimension ref="A1:I559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H551" t="n">
         <v>3</v>
@@ -26359,7 +26359,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -26400,7 +26400,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H557" t="n">
         <v>3</v>
@@ -26441,13 +26441,54 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="H558" t="n">
         <v>3</v>
       </c>
       <c r="I558" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>roborock.krng.n</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@roborock.krng.n/video/7671995046618713364</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trực tiếp trải nghiệm tất cả các mã robot hút bụi lau nhà Roborock tại 30 Nguyễn Tất Thành - Krông Nô - Lâm Đồng Hotline: 0985.37.47.48 #RoborockVietnam  #krôngnô  #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G559" t="n">
+        <v>115</v>
+      </c>
+      <c r="H559" t="n">
+        <v>4</v>
+      </c>
+      <c r="I559" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H551" t="n">
         <v>3</v>
@@ -26482,7 +26482,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H559" t="n">
         <v>4</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I559"/>
+  <dimension ref="A1:I561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26359,7 +26359,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -26400,7 +26400,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H557" t="n">
         <v>3</v>
@@ -26482,13 +26482,95 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="H559" t="n">
         <v>4</v>
       </c>
       <c r="I559" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>mi360vn</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mi360vn/video/7672712167342263572</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Em robot Roborock Qrevo 2Pro này sáng bóng từ vỏ ngoài cho tới cách em ấy lau sàn 😍😍😍 #mi360 #roborock #qrevo2pro #robothutbui #xuhuong </t>
+        </is>
+      </c>
+      <c r="G560" t="n">
+        <v>45</v>
+      </c>
+      <c r="H560" t="n">
+        <v>1</v>
+      </c>
+      <c r="I560" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>roborock.krng.n</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@roborock.krng.n/video/7672649228119805204</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#robothutbuilaunha  #Roborock  #qrevo2pro  #krongno </t>
+        </is>
+      </c>
+      <c r="G561" t="n">
+        <v>107</v>
+      </c>
+      <c r="H561" t="n">
+        <v>2</v>
+      </c>
+      <c r="I561" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I561"/>
+  <dimension ref="A1:I564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H551" t="n">
         <v>3</v>
@@ -26359,7 +26359,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -26400,7 +26400,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H557" t="n">
         <v>3</v>
@@ -26482,10 +26482,10 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H559" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I559" t="n">
         <v>1</v>
@@ -26523,10 +26523,10 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>45</v>
+        <v>177</v>
       </c>
       <c r="H560" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I560" t="n">
         <v>0</v>
@@ -26564,12 +26564,135 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="H561" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I561" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>mistorebienhoa</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mistorebienhoa/video/7672980309671005460</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#mistorebienhoa #robothutbui #suachuarobothutbui #qrevo2pro #roborock </t>
+        </is>
+      </c>
+      <c r="G562" t="n">
+        <v>150</v>
+      </c>
+      <c r="H562" t="n">
+        <v>1</v>
+      </c>
+      <c r="I562" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>longrobot_284</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@longrobot_284/video/7672957453666979092</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Với cách di chuyển đi từ viền vào theo hình xoắn ốc, Robot hút bụi lau nhà sẽ không bỏ sót bụi bẩn đâu ạ. #roborock #qrevo2pro #robothutbuilaunha #longrobot #robottaidanang</t>
+        </is>
+      </c>
+      <c r="G563" t="n">
+        <v>172</v>
+      </c>
+      <c r="H563" t="n">
+        <v>12</v>
+      </c>
+      <c r="I563" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>quyrobot</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@quyrobot/video/7672810819553381639</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hdsd vệ sinh #qrevo2pro #roborock #robothutbui #quyrobot </t>
+        </is>
+      </c>
+      <c r="G564" t="n">
+        <v>455</v>
+      </c>
+      <c r="H564" t="n">
+        <v>3</v>
+      </c>
+      <c r="I564" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I564"/>
+  <dimension ref="A1:I565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26400,7 +26400,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H557" t="n">
         <v>3</v>
@@ -26523,7 +26523,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="H560" t="n">
         <v>5</v>
@@ -26564,7 +26564,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="H561" t="n">
         <v>8</v>
@@ -26605,7 +26605,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H562" t="n">
         <v>1</v>
@@ -26646,10 +26646,10 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="H563" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I563" t="n">
         <v>0</v>
@@ -26687,12 +26687,53 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>455</v>
+        <v>536</v>
       </c>
       <c r="H564" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I564" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>homebotvietnam</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homebotvietnam/video/7673147741786098965</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Một chiếc robot giúp mình tiết kiệm cả tiếng dọn nhà mỗi tuần. ⏳✨ Đáng để trải nghiệm! 🤖 #Qrevo2Pro #Roborock #robothutbui #SmartHome #Review</t>
+        </is>
+      </c>
+      <c r="G565" t="n">
+        <v>359</v>
+      </c>
+      <c r="H565" t="n">
+        <v>1</v>
+      </c>
+      <c r="I565" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I565"/>
+  <dimension ref="A1:I568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26441,7 +26441,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H558" t="n">
         <v>3</v>
@@ -26482,7 +26482,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H559" t="n">
         <v>6</v>
@@ -26523,7 +26523,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H560" t="n">
         <v>5</v>
@@ -26564,10 +26564,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="H561" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I561" t="n">
         <v>0</v>
@@ -26605,7 +26605,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="H562" t="n">
         <v>1</v>
@@ -26646,7 +26646,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="H563" t="n">
         <v>13</v>
@@ -26687,7 +26687,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="H564" t="n">
         <v>4</v>
@@ -26728,12 +26728,135 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="H565" t="n">
         <v>1</v>
       </c>
       <c r="I565" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>thuyduonggiadung</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuyduonggiadung/video/7673834724636347656</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#GiaDungThuyDuong #roborock #robothutbuilaunha #qrevo2pro #xuhuong </t>
+        </is>
+      </c>
+      <c r="G566" t="n">
+        <v>0</v>
+      </c>
+      <c r="H566" t="n">
+        <v>0</v>
+      </c>
+      <c r="I566" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7673781996711087378</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#f25ultra #qrevo2pro #3tsmart </t>
+        </is>
+      </c>
+      <c r="G567" t="n">
+        <v>134</v>
+      </c>
+      <c r="H567" t="n">
+        <v>1</v>
+      </c>
+      <c r="I567" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>hatechz</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@hatechz/video/7673516301070978312</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25,000Pa hút rẹc rẹc luôn he 😌 #roborock #roborockvietnam #qrevo2pro #hatechz #quangtri </t>
+        </is>
+      </c>
+      <c r="G568" t="n">
+        <v>161</v>
+      </c>
+      <c r="H568" t="n">
+        <v>2</v>
+      </c>
+      <c r="I568" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I568"/>
+  <dimension ref="A1:I574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26482,7 +26482,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H559" t="n">
         <v>6</v>
@@ -26523,7 +26523,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H560" t="n">
         <v>5</v>
@@ -26564,7 +26564,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="H561" t="n">
         <v>9</v>
@@ -26605,10 +26605,10 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H562" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I562" t="n">
         <v>0</v>
@@ -26646,7 +26646,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="H563" t="n">
         <v>13</v>
@@ -26687,7 +26687,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="H564" t="n">
         <v>4</v>
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H565" t="n">
         <v>1</v>
@@ -26769,13 +26769,13 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567">
@@ -26810,10 +26810,10 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>134</v>
+        <v>324</v>
       </c>
       <c r="H567" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I567" t="n">
         <v>0</v>
@@ -26851,12 +26851,258 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="H568" t="n">
         <v>2</v>
       </c>
       <c r="I568" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>thuyduonggiadung</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuyduonggiadung/video/7674153595033390354</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#robothutbuilaunha #qrevo2pro #roborock #GiaDungThuyDuong #xuhuong </t>
+        </is>
+      </c>
+      <c r="G569" t="n">
+        <v>120</v>
+      </c>
+      <c r="H569" t="n">
+        <v>1</v>
+      </c>
+      <c r="I569" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>thuyduonggiadung</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuyduonggiadung/video/7674153062411406610</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#robothutbuilaunha #qrevo2pro #roborock #GiaDungThuyDuong #xuhuong </t>
+        </is>
+      </c>
+      <c r="G570" t="n">
+        <v>114</v>
+      </c>
+      <c r="H570" t="n">
+        <v>1</v>
+      </c>
+      <c r="I570" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>thuyduonggiadung</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuyduonggiadung/video/7674152858878561544</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#robothutbuilaunha #qrevo2pro #roborock #xuhuong </t>
+        </is>
+      </c>
+      <c r="G571" t="n">
+        <v>98</v>
+      </c>
+      <c r="H571" t="n">
+        <v>2</v>
+      </c>
+      <c r="I571" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>thuyduonggiadung</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuyduonggiadung/video/7674151195795115272</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#robothutbuilaunha #qrevo2pro #roborock #xuhuong </t>
+        </is>
+      </c>
+      <c r="G572" t="n">
+        <v>98</v>
+      </c>
+      <c r="H572" t="n">
+        <v>0</v>
+      </c>
+      <c r="I572" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>thuyduonggiadung</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuyduonggiadung/video/7674149325483658504</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#GiaDungThuyDuong #robothutbuilaunha #qrevo2pro #roborock #xuhuong </t>
+        </is>
+      </c>
+      <c r="G573" t="n">
+        <v>102</v>
+      </c>
+      <c r="H573" t="n">
+        <v>2</v>
+      </c>
+      <c r="I573" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>3t.smart.robot.tn</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@3t.smart.robot.tn/video/7673874498411777298</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suy nghĩ của con trai và con gái #3tsmart  #qrevo2pro  #haihuoc #funny #boyorgirl </t>
+        </is>
+      </c>
+      <c r="G574" t="n">
+        <v>562</v>
+      </c>
+      <c r="H574" t="n">
+        <v>3</v>
+      </c>
+      <c r="I574" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -26482,7 +26482,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H559" t="n">
         <v>6</v>
@@ -26523,10 +26523,10 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="H560" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I560" t="n">
         <v>0</v>
@@ -26564,7 +26564,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="H561" t="n">
         <v>9</v>
@@ -26605,7 +26605,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="H562" t="n">
         <v>2</v>
@@ -26646,10 +26646,10 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="H563" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I563" t="n">
         <v>0</v>
@@ -26687,10 +26687,10 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="H564" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I564" t="n">
         <v>1</v>
@@ -26810,7 +26810,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H567" t="n">
         <v>2</v>
@@ -26851,7 +26851,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H568" t="n">
         <v>2</v>
@@ -26892,10 +26892,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>120</v>
+        <v>391</v>
       </c>
       <c r="H569" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I569" t="n">
         <v>0</v>
@@ -26933,13 +26933,13 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>114</v>
+        <v>342</v>
       </c>
       <c r="H570" t="n">
+        <v>3</v>
+      </c>
+      <c r="I570" t="n">
         <v>1</v>
-      </c>
-      <c r="I570" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="571">
@@ -26974,7 +26974,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>98</v>
+        <v>239</v>
       </c>
       <c r="H571" t="n">
         <v>2</v>
@@ -27015,10 +27015,10 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>98</v>
+        <v>226</v>
       </c>
       <c r="H572" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I572" t="n">
         <v>0</v>
@@ -27056,10 +27056,10 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>102</v>
+        <v>298</v>
       </c>
       <c r="H573" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I573" t="n">
         <v>0</v>
@@ -27097,10 +27097,10 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="H574" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I574" t="n">
         <v>0</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -26523,7 +26523,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="H560" t="n">
         <v>6</v>
@@ -26564,7 +26564,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="H561" t="n">
         <v>9</v>
@@ -26605,7 +26605,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H562" t="n">
         <v>2</v>
@@ -26646,7 +26646,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="H563" t="n">
         <v>15</v>
@@ -26687,7 +26687,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="H564" t="n">
         <v>5</v>
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H565" t="n">
         <v>1</v>
@@ -26851,7 +26851,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H568" t="n">
         <v>2</v>
@@ -26892,10 +26892,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="H569" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I569" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="H570" t="n">
         <v>3</v>
@@ -26974,7 +26974,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H571" t="n">
         <v>2</v>
@@ -27015,7 +27015,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H572" t="n">
         <v>1</v>
@@ -27056,10 +27056,10 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H573" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I573" t="n">
         <v>0</v>
@@ -27097,7 +27097,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="H574" t="n">
         <v>4</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I574"/>
+  <dimension ref="A1:I575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26564,7 +26564,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H561" t="n">
         <v>9</v>
@@ -26605,7 +26605,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H562" t="n">
         <v>2</v>
@@ -26646,7 +26646,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H563" t="n">
         <v>15</v>
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H570" t="n">
         <v>3</v>
@@ -27103,6 +27103,47 @@
         <v>4</v>
       </c>
       <c r="I574" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>robothutbuiductrong</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@robothutbuiductrong/video/7674961901599722773</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>🌌 QREVO 2 PRO 🌪️ Một - Lực hút 25.000Pa đánh thức sức mạnh làm sạch toàn diện, cuốn gọn bụi mịn, tóc rụng và mảnh vụn trong từng lần di chuyển. 🌪️ Hai - Giẻ lau FlexiArm cùng chổi cạnh đảo chiều mở rộng giới hạn làm sạch, len sát mép tường, chạm đến những góc nhỏ thường bị bỏ quên. 🌪️ Ba - Hệ thống chống rối 3 lớp giúp hành trình vận hành mượt mà hơn, để tóc và lông thú không còn là lý do khiến bạn phải cúi xuống gỡ thủ công. 🌪️ Bốn - Dock tự giặt giẻ, sấy nóng 45°C và làm sạch khay giặt, giữ chu trình sau mỗi lần lau luôn khô thoáng, gọn gàng và an tâm. 🌪️ Năm - Khi gặp thảm, robot tự để giẻ lại dock, chỉ tập trung hút sạch mà không kéo ẩm lên bề mặt vải. #Roborock #RoborockVietnam #OtechVietnam #Qrevo2Pro</t>
+        </is>
+      </c>
+      <c r="G575" t="n">
+        <v>11</v>
+      </c>
+      <c r="H575" t="n">
+        <v>0</v>
+      </c>
+      <c r="I575" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I575"/>
+  <dimension ref="A1:I576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26523,7 +26523,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="H560" t="n">
         <v>6</v>
@@ -26564,7 +26564,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="H561" t="n">
         <v>9</v>
@@ -26605,7 +26605,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="H562" t="n">
         <v>2</v>
@@ -26646,7 +26646,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="H563" t="n">
         <v>15</v>
@@ -26687,10 +26687,10 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="H564" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I564" t="n">
         <v>1</v>
@@ -26769,10 +26769,10 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H566" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I566" t="n">
         <v>1</v>
@@ -26851,7 +26851,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H568" t="n">
         <v>2</v>
@@ -26892,7 +26892,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="H569" t="n">
         <v>6</v>
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="H570" t="n">
         <v>3</v>
@@ -27056,7 +27056,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H573" t="n">
         <v>6</v>
@@ -27097,10 +27097,10 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="H574" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I574" t="n">
         <v>0</v>
@@ -27138,13 +27138,54 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>11</v>
+        <v>234</v>
       </c>
       <c r="H575" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I575" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>thuyduonggiadung</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thuyduonggiadung/video/7675246819080785160</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#GiaDungThuyDuong #robothutbuilaunha #qrevo2pro #xuhuong #xaykenh </t>
+        </is>
+      </c>
+      <c r="G576" t="n">
+        <v>157</v>
+      </c>
+      <c r="H576" t="n">
+        <v>2</v>
+      </c>
+      <c r="I576" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -26769,7 +26769,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H566" t="n">
         <v>2</v>
@@ -26851,10 +26851,10 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H568" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I568" t="n">
         <v>0</v>
@@ -26892,7 +26892,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H569" t="n">
         <v>6</v>
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H570" t="n">
         <v>3</v>
@@ -26974,7 +26974,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H571" t="n">
         <v>2</v>
@@ -27015,7 +27015,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H572" t="n">
         <v>1</v>
@@ -27056,7 +27056,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H573" t="n">
         <v>6</v>
@@ -27097,7 +27097,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="H574" t="n">
         <v>5</v>
@@ -27138,7 +27138,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="H575" t="n">
         <v>2</v>
@@ -27179,7 +27179,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>157</v>
+        <v>330</v>
       </c>
       <c r="H576" t="n">
         <v>2</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -26810,7 +26810,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H567" t="n">
         <v>2</v>
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="H570" t="n">
         <v>3</v>
@@ -27097,7 +27097,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="H574" t="n">
         <v>5</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H570" t="n">
         <v>3</v>
@@ -27138,7 +27138,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H575" t="n">
         <v>2</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I576"/>
+  <dimension ref="A1:I577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27138,10 +27138,10 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H575" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I575" t="n">
         <v>0</v>
@@ -27179,13 +27179,54 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H576" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I576" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>mivietnam_chuyengiarobot</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mivietnam_chuyengiarobot/video/7675683418939608340</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Roborock Qrevo 2 Pro #Mivietnam #Roborock #Qrevo2Pro #Robothutbui</t>
+        </is>
+      </c>
+      <c r="G577" t="n">
+        <v>390</v>
+      </c>
+      <c r="H577" t="n">
+        <v>7</v>
+      </c>
+      <c r="I577" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -27138,7 +27138,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H575" t="n">
         <v>3</v>
@@ -27179,10 +27179,10 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H576" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I576" t="n">
         <v>1</v>
@@ -27220,7 +27220,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="H577" t="n">
         <v>7</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I577"/>
+  <dimension ref="A1:I578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27220,13 +27220,54 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H577" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I577" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7676870322607623444</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hãy sử dụng nước lau sàn chuyên dụng để bảo vệ Robot cũng như đạt hiệu quả tốt nhất nhen khách iu của em❤️❤️❤️#Roborock #robothutbui #thietbithongminh #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G578" t="n">
+        <v>392</v>
+      </c>
+      <c r="H578" t="n">
+        <v>6</v>
+      </c>
+      <c r="I578" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -27179,7 +27179,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H576" t="n">
         <v>4</v>
@@ -27220,7 +27220,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="H577" t="n">
         <v>8</v>
@@ -27261,7 +27261,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H578" t="n">
         <v>6</v>

--- a/output/qrevo-videos.xlsx
+++ b/output/qrevo-videos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I578"/>
+  <dimension ref="A1:I588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27270,6 +27270,416 @@
         <v>0</v>
       </c>
     </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>homesmediant99</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homesmediant99/video/7678224674253212936</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Nên mua robot thời điểm nào để hời nhất🧐🧐#robothutbuilaunha #Roborock #qrevo2pro #mediahomesnhatrang</t>
+        </is>
+      </c>
+      <c r="G579" t="n">
+        <v>92</v>
+      </c>
+      <c r="H579" t="n">
+        <v>1</v>
+      </c>
+      <c r="I579" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>.hng0863</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@.hng0863/video/7682437981663333652</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chủ cứ phiêu còn sen thì vẫn cứ làm việc❤️❤️❤️❤️#Roborock #RoborockVietnam #Qrevo2Pro #thietbithongminh #robothutbui </t>
+        </is>
+      </c>
+      <c r="G580" t="n">
+        <v>151</v>
+      </c>
+      <c r="H580" t="n">
+        <v>3</v>
+      </c>
+      <c r="I580" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>mi360vn</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mi360vn/video/7679742938045222164</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t xml:space="preserve">“Osin” làm việc không biết mệt mỏi đích thị là em Roborock Qrevo 2 Pro rồi #mi360 #roborock #qrevo2pro #robothutbui #robotlaunha </t>
+        </is>
+      </c>
+      <c r="G581" t="n">
+        <v>131</v>
+      </c>
+      <c r="H581" t="n">
+        <v>3</v>
+      </c>
+      <c r="I581" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>roborock.krng.n</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@roborock.krng.n/video/7679304652327800085</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robot hút bụi lau nhà Qrevo 2 Pro Trắng Ngọc Trai siêu sang xịn. #roborock  #qrevo2pro  #robothutbuilaunha  #krongno </t>
+        </is>
+      </c>
+      <c r="G582" t="n">
+        <v>445</v>
+      </c>
+      <c r="H582" t="n">
+        <v>7</v>
+      </c>
+      <c r="I582" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>mivietnam_chuyengiarobot</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@mivietnam_chuyengiarobot/video/7677918054168169749</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Có ai để ý mấy Hoàng Thượng trong nhà cứ hay đi giám sát Robot làm việc không? #Mivietnam #Roborock #Qrevo2Pro #suarobothutbui #robothutbui</t>
+        </is>
+      </c>
+      <c r="G583" t="n">
+        <v>497</v>
+      </c>
+      <c r="H583" t="n">
+        <v>10</v>
+      </c>
+      <c r="I583" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>thurobot88</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@thurobot88/video/7676444262904466709</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#CapCut #robothutbui #daklak #roborock #Qrevo2Pro </t>
+        </is>
+      </c>
+      <c r="G584" t="n">
+        <v>221</v>
+      </c>
+      <c r="H584" t="n">
+        <v>4</v>
+      </c>
+      <c r="I584" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>quyrobot</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@quyrobot/video/7682800914779999496</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tay hàng xóm dùng trc tận mấy năm lận, mà cô giờ mới dùng, thế ko ổn rồi 🤭🤭🤭 #robothutbuivinhphuc #robothutbui #qrevo2pro </t>
+        </is>
+      </c>
+      <c r="G585" t="n">
+        <v>640</v>
+      </c>
+      <c r="H585" t="n">
+        <v>5</v>
+      </c>
+      <c r="I585" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>xiaomi.phu.tho</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@xiaomi.phu.tho/video/7675343178760850696</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hỗ trợ khách cài đặt robot Qrevo 2 pro tại nhà miễn phí 🤩 Dịch vụ 5 sao chưa các bác 😂 #qrevo2pro #robothutbui #robotlaunha #roborock #xiaomiphutho </t>
+        </is>
+      </c>
+      <c r="G586" t="n">
+        <v>449</v>
+      </c>
+      <c r="H586" t="n">
+        <v>5</v>
+      </c>
+      <c r="I586" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>homebotvietnam</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homebotvietnam/video/7681334761414987028</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Trước khi mua mình cũng phân vân... nhưng dùng rồi mới hiểu vì sao nhiều người thích Qrevo 2 Pro. 🤖❤️ #Qrevo2Pro #Roborock #robothutbui #ReviewCongNghe #NhaThongMinh</t>
+        </is>
+      </c>
+      <c r="G587" t="n">
+        <v>373</v>
+      </c>
+      <c r="H587" t="n">
+        <v>3</v>
+      </c>
+      <c r="I587" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>homebotvietnam</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>qrevo 2 pro</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@homebotvietnam/video/7678746963885427988</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Công nghệ ngày càng "gánh team" việc nhà! 🚀 🤖 Xem thử em Qrevo 2 Pro này có đáng nâng cấp không. 👀 #Qrevo2Pro #Roborock #robothutbui #CongNghe #SmartHome</t>
+        </is>
+      </c>
+      <c r="G588" t="n">
+        <v>308</v>
+      </c>
+      <c r="H588" t="n">
+        <v>1</v>
+      </c>
+      <c r="I588" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
